--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inhyu\OneDrive\바탕 화면\김인혁\김인혁_청년축구단\1. 출석부\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Han\codes\kcc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CEA67D-3D8D-4478-A927-DA4A524A108E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2B2B9F-0C5A-48DA-8C47-99FB3E118D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="370">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -1397,9 +1397,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="m&quot;/&quot;d;@"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="164" formatCode="m&quot;/&quot;d;@"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1900,13 +1900,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1921,7 +1921,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1936,16 +1936,16 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1960,10 +1960,10 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1972,7 +1972,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2062,25 +2062,25 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2104,7 +2104,7 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2804,23 +2804,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CT114"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.19921875" style="60" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.19921875" style="54" customWidth="1"/>
-    <col min="5" max="5" width="8.19921875" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.8984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="4.3984375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.8984375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.19921875" style="1" customWidth="1"/>
-    <col min="10" max="30" width="5.19921875" style="1" customWidth="1"/>
-    <col min="31" max="33" width="5.19921875" style="3" customWidth="1"/>
-    <col min="34" max="59" width="5.19921875" style="1" customWidth="1"/>
-    <col min="60" max="82" width="4.796875" style="1" customWidth="1"/>
-    <col min="83" max="90" width="8.8984375" style="1"/>
-    <col min="91" max="98" width="8.8984375" style="3"/>
+    <col min="1" max="1" width="4.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="60" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="54" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.9140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.4140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.1640625" style="1" customWidth="1"/>
+    <col min="10" max="30" width="5.1640625" style="1" customWidth="1"/>
+    <col min="31" max="33" width="5.1640625" style="3" customWidth="1"/>
+    <col min="34" max="59" width="5.1640625" style="1" customWidth="1"/>
+    <col min="60" max="82" width="4.83203125" style="1" customWidth="1"/>
+    <col min="83" max="90" width="8.9140625" style="1"/>
+    <col min="91" max="98" width="8.9140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:82" x14ac:dyDescent="0.25">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>3.0444444444444443</v>
+        <v>3.0666666666666669</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P2" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="0"/>
@@ -3334,11 +3334,11 @@
       </c>
       <c r="G4" s="2">
         <f>RANK(H4,$H$4:$H$122,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4" si="2">(COUNTIF(J4:CD4,"출전")*1)</f>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="G5" s="2">
         <f>RANK(H5,$H$4:$H$122,0)</f>
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="6">
         <f t="shared" ref="I5:I7" si="3">(COUNTIF(J5:CD5,"출전")*1)</f>
@@ -3552,11 +3552,11 @@
       </c>
       <c r="G6" s="2">
         <f>RANK(H6,$H$4:$H$122,0)</f>
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="6">
         <f t="shared" si="3"/>
@@ -3653,11 +3653,11 @@
       </c>
       <c r="G7" s="2">
         <f t="shared" ref="G7:G70" si="4">RANK(H7,$H$4:$H$122,0)</f>
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="6">
         <f t="shared" si="3"/>
@@ -3756,11 +3756,11 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C8</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I8" s="6">
         <f t="shared" ref="I8:I71" si="5">(COUNTIF(J8:CD8,"출전")*1)</f>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="I9" s="6">
         <f t="shared" si="5"/>
@@ -3966,11 +3966,11 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
-        <v>2.2999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="5"/>
@@ -4073,11 +4073,11 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="5"/>
@@ -4180,11 +4180,11 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C12</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I12" s="6">
         <f t="shared" si="5"/>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C13</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I13" s="6">
         <f t="shared" si="5"/>
@@ -4382,11 +4382,11 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C14</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="I14" s="6">
         <f t="shared" si="5"/>
@@ -4483,11 +4483,11 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="I15" s="6">
         <f t="shared" si="5"/>
@@ -4586,11 +4586,11 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="5"/>
@@ -4695,11 +4695,11 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="5"/>
@@ -4804,11 +4804,11 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C18</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="I18" s="6">
         <f t="shared" si="5"/>
@@ -4907,11 +4907,11 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
-        <v>4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I19" s="6">
         <f t="shared" si="5"/>
@@ -5018,11 +5018,11 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I20" s="6">
         <f t="shared" si="5"/>
@@ -5121,11 +5121,11 @@
       <c r="F21" s="61"/>
       <c r="G21" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C21</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="5"/>
@@ -5222,11 +5222,11 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H22" s="6">
         <f>I22+개인기록Sheet!C22</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I22" s="6">
         <f t="shared" si="5"/>
@@ -5325,11 +5325,11 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C23</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I23" s="6">
         <f t="shared" si="5"/>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="5"/>
@@ -5533,11 +5533,11 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="5"/>
@@ -5640,11 +5640,11 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="5"/>
@@ -5753,11 +5753,11 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
-        <v>2.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="5"/>
@@ -5858,11 +5858,11 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="5"/>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C29</f>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
@@ -6270,11 +6270,11 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="5"/>
@@ -6379,11 +6379,11 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="5"/>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
@@ -6605,11 +6605,11 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C35</f>
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="5"/>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C36</f>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="H39" s="6">
         <f>I39+개인기록Sheet!C39</f>
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I39" s="6">
         <f t="shared" si="5"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H40" s="6">
         <f>I40+개인기록Sheet!C40</f>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H41" s="6">
         <f>I41+개인기록Sheet!C41</f>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H42" s="6">
         <f>I42+개인기록Sheet!C42</f>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
@@ -7647,11 +7647,11 @@
       </c>
       <c r="G45" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H45" s="6">
         <f>I45+개인기록Sheet!C45</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I45" s="6">
         <f t="shared" si="5"/>
@@ -7754,7 +7754,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="G48" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H48" s="6">
         <f>I48+개인기록Sheet!C48</f>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="G49" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H49" s="6">
         <f>I49+개인기록Sheet!C49</f>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H50" s="6">
         <f>I50+개인기록Sheet!C50</f>
@@ -8269,11 +8269,11 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="I51" s="6">
         <f t="shared" si="5"/>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H52" s="6">
         <f>I52+개인기록Sheet!C52</f>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H53" s="6">
         <f>I53+개인기록Sheet!C53</f>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H54" s="6">
         <f>I54+개인기록Sheet!C54</f>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
@@ -8786,11 +8786,11 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="I56" s="6">
         <f t="shared" si="5"/>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H58" s="6">
         <f>I58+개인기록Sheet!C58</f>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
@@ -9315,11 +9315,11 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" s="6">
         <f t="shared" si="5"/>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="G62" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H62" s="6">
         <f>I62+개인기록Sheet!C62</f>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H63" s="6">
         <f>I63+개인기록Sheet!C63</f>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H64" s="6">
         <f>I64+개인기록Sheet!C64</f>
@@ -9723,11 +9723,11 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="I65" s="6">
         <f t="shared" si="5"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
@@ -9937,7 +9937,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H68" s="6">
         <f>I68+개인기록Sheet!C68</f>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
@@ -10355,11 +10355,11 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" ref="G71:G114" si="6">RANK(H71,$H$4:$H$122,0)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="I71" s="6">
         <f t="shared" si="5"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H72" s="6">
         <f>I72+개인기록Sheet!C72</f>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H73" s="6">
         <f>I73+개인기록Sheet!C73</f>
@@ -10662,11 +10662,11 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="I74" s="6">
         <f t="shared" si="7"/>
@@ -10769,11 +10769,11 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I75" s="6">
         <f t="shared" si="7"/>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="G89" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H89" s="6">
         <f>I89+개인기록Sheet!C89</f>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="G90" s="2">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
@@ -12637,11 +12637,11 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="I93" s="6">
         <f t="shared" si="7"/>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
@@ -12851,11 +12851,11 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I95" s="6">
         <f t="shared" si="7"/>
@@ -12964,11 +12964,11 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="7"/>
@@ -13081,7 +13081,7 @@
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="7"/>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H98" s="6">
         <f>I98+개인기록Sheet!C98</f>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H99" s="6">
         <f>I99+개인기록Sheet!C99</f>
@@ -13394,11 +13394,11 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="I100" s="6">
         <f t="shared" si="7"/>
@@ -13501,15 +13501,15 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I101" s="6">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>355</v>
@@ -13523,7 +13523,9 @@
       <c r="O101" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="P101" s="2"/>
+      <c r="P101" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="Q101" s="2"/>
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
@@ -13610,7 +13612,7 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
@@ -13717,11 +13719,11 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="I103" s="6">
         <f t="shared" si="7"/>
@@ -13824,7 +13826,7 @@
       </c>
       <c r="G104" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
@@ -13927,11 +13929,11 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="I105" s="6">
         <f t="shared" si="7"/>
@@ -14034,11 +14036,11 @@
       </c>
       <c r="G106" s="2">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I106" s="6">
         <f t="shared" si="7"/>
@@ -14141,7 +14143,7 @@
       </c>
       <c r="G107" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H107" s="6">
         <f>I107+개인기록Sheet!C107</f>
@@ -14242,7 +14244,7 @@
       </c>
       <c r="G108" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
@@ -14345,7 +14347,7 @@
       </c>
       <c r="G109" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
@@ -14446,7 +14448,7 @@
       </c>
       <c r="G110" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
@@ -14549,7 +14551,7 @@
       </c>
       <c r="G111" s="2">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
@@ -14652,7 +14654,7 @@
       </c>
       <c r="G112" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
@@ -14753,7 +14755,7 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
@@ -14854,7 +14856,7 @@
       </c>
       <c r="G114" s="2">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
@@ -14963,11 +14965,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:V22"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.8984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.9140625" style="1" customWidth="1"/>
     <col min="5" max="22" width="6.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15584,8 +15586,12 @@
       <c r="N20" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
+      <c r="O20" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="P20" s="20" t="s">
+        <v>230</v>
+      </c>
       <c r="Q20" s="9" t="s">
         <v>137</v>
       </c>
@@ -15674,15 +15680,15 @@
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -15696,35 +15702,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:CW114"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="10.796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.796875" style="17" customWidth="1"/>
-    <col min="10" max="10" width="4.796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.09765625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="4.69921875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.09765625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.69921875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.09765625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="4.69921875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8.09765625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.69921875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.09765625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="4.69921875" style="1" customWidth="1"/>
-    <col min="22" max="32" width="7.796875" style="1" customWidth="1"/>
-    <col min="33" max="33" width="4.796875" style="1" customWidth="1"/>
-    <col min="34" max="85" width="4.796875" style="3" customWidth="1"/>
-    <col min="86" max="101" width="8.8984375" style="3"/>
+    <col min="1" max="1" width="4.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="4.83203125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="4.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.08203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="4.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.08203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.08203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.08203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="4.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.08203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" style="1" customWidth="1"/>
+    <col min="22" max="32" width="7.83203125" style="1" customWidth="1"/>
+    <col min="33" max="33" width="4.83203125" style="1" customWidth="1"/>
+    <col min="34" max="85" width="4.83203125" style="3" customWidth="1"/>
+    <col min="86" max="101" width="8.9140625" style="3"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
@@ -15736,7 +15742,7 @@
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
@@ -15810,20 +15816,20 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <f>종합Sheet!A4</f>
-        <v>1</v>
+        <f>종합Sheet!A26</f>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="str">
-        <f>종합Sheet!B4</f>
-        <v>김인혁</v>
+        <f>종합Sheet!B26</f>
+        <v>김성준</v>
       </c>
       <c r="C4" s="2">
-        <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
-        <v>0.2</v>
+        <f t="shared" ref="C4:C35" si="0">((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
+        <v>1.4</v>
       </c>
       <c r="D4" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B4)</f>
@@ -15831,19 +15837,19 @@
       </c>
       <c r="F4" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B4)</f>
         <v>0</v>
       </c>
       <c r="I4" s="14">
-        <f>SUM(D4:H4)</f>
-        <v>1</v>
+        <f t="shared" ref="I4:I35" si="1">SUM(D4:H4)</f>
+        <v>6</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="2">
@@ -15853,50 +15859,50 @@
         <v>224</v>
       </c>
       <c r="M4" s="21">
-        <f t="shared" ref="M4:M13" si="0">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
+        <f t="shared" ref="M4:M13" si="2">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
         <v>2</v>
       </c>
       <c r="N4" s="34" t="s">
         <v>360</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O13" si="1">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
+        <f t="shared" ref="O4:O13" si="3">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
         <v>2</v>
       </c>
       <c r="P4" s="35" t="s">
         <v>224</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q13" si="2">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
+        <f t="shared" ref="Q4:Q13" si="4">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="R4" s="36" t="s">
         <v>326</v>
       </c>
       <c r="S4" s="56">
-        <f t="shared" ref="S4:S13" si="3">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
+        <f t="shared" ref="S4:S13" si="5">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
         <v>4</v>
       </c>
       <c r="T4" s="37" t="s">
         <v>229</v>
       </c>
       <c r="U4" s="57">
-        <f t="shared" ref="U4:U13" si="4">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
+        <f t="shared" ref="U4:U13" si="6">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <f>종합Sheet!A5</f>
-        <v>2</v>
+        <f>종합Sheet!A61</f>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="str">
-        <f>종합Sheet!B5</f>
-        <v>신재경</v>
+        <f>종합Sheet!B61</f>
+        <v>오우영</v>
       </c>
       <c r="C5" s="2">
-        <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="D5" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B5)</f>
@@ -15904,11 +15910,11 @@
       </c>
       <c r="E5" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B5)</f>
@@ -15919,8 +15925,8 @@
         <v>0</v>
       </c>
       <c r="I5" s="14">
-        <f>SUM(D5:H5)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="2">
@@ -15930,50 +15936,50 @@
         <v>229</v>
       </c>
       <c r="M5" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N5" s="34" t="s">
         <v>315</v>
       </c>
       <c r="O5" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P5" s="35" t="s">
         <v>222</v>
       </c>
       <c r="Q5" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R5" s="36" t="s">
         <v>231</v>
       </c>
       <c r="S5" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="T5" s="37" t="s">
         <v>361</v>
       </c>
       <c r="U5" s="57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <f>종합Sheet!A6</f>
-        <v>3</v>
+        <f>종합Sheet!A45</f>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="str">
-        <f>종합Sheet!B6</f>
-        <v>정효태</v>
+        <f>종합Sheet!B45</f>
+        <v>노민준</v>
       </c>
       <c r="C6" s="2">
-        <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="D6" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B6)</f>
@@ -15981,7 +15987,7 @@
       </c>
       <c r="E6" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B6)</f>
@@ -15989,15 +15995,15 @@
       </c>
       <c r="G6" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B6)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B6)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" s="14">
-        <f>SUM(D6:H6)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="2">
@@ -16007,54 +16013,54 @@
         <v>366</v>
       </c>
       <c r="M6" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N6" s="34" t="s">
         <v>50</v>
       </c>
       <c r="O6" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P6" s="35" t="s">
         <v>64</v>
       </c>
       <c r="Q6" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R6" s="36" t="s">
         <v>222</v>
       </c>
       <c r="S6" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T6" s="37" t="s">
         <v>64</v>
       </c>
       <c r="U6" s="57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>종합Sheet!A7</f>
-        <v>4</v>
+        <f>종합Sheet!A11</f>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="str">
-        <f>종합Sheet!B7</f>
-        <v>이승민</v>
+        <f>종합Sheet!B11</f>
+        <v>강기혁</v>
       </c>
       <c r="C7" s="2">
-        <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="D7" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B7)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B7)</f>
@@ -16062,7 +16068,7 @@
       </c>
       <c r="F7" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B7)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B7)</f>
@@ -16073,8 +16079,8 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f>SUM(D7:H7)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="2">
@@ -16084,50 +16090,50 @@
         <v>368</v>
       </c>
       <c r="M7" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N7" s="34" t="s">
         <v>222</v>
       </c>
       <c r="O7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P7" s="35" t="s">
         <v>53</v>
       </c>
       <c r="Q7" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R7" s="36" t="s">
         <v>361</v>
       </c>
       <c r="S7" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T7" s="37" t="s">
         <v>327</v>
       </c>
       <c r="U7" s="57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <f>종합Sheet!A8</f>
-        <v>5</v>
+        <f>종합Sheet!A32</f>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="str">
-        <f>종합Sheet!B8</f>
-        <v>이정석</v>
+        <f>종합Sheet!B32</f>
+        <v>김용현</v>
       </c>
       <c r="C8" s="2">
-        <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.8</v>
       </c>
       <c r="D8" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B8)</f>
@@ -16135,11 +16141,11 @@
       </c>
       <c r="E8" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B8)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B8)</f>
@@ -16150,8 +16156,8 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f>SUM(D8:H8)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="2">
@@ -16161,48 +16167,48 @@
         <v>222</v>
       </c>
       <c r="M8" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N8" s="34" t="s">
         <v>53</v>
       </c>
       <c r="O8" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P8" s="35" t="s">
         <v>369</v>
       </c>
       <c r="Q8" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R8" s="36" t="s">
         <v>242</v>
       </c>
       <c r="S8" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T8" s="37"/>
       <c r="U8" s="57" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <f>종합Sheet!A9</f>
-        <v>6</v>
+        <f>종합Sheet!A95</f>
+        <v>92</v>
       </c>
       <c r="B9" s="2" t="str">
-        <f>종합Sheet!B9</f>
-        <v>강종찬</v>
+        <f>종합Sheet!B95</f>
+        <v>조진한</v>
       </c>
       <c r="C9" s="2">
-        <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.8</v>
       </c>
       <c r="D9" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B9)</f>
@@ -16210,11 +16216,11 @@
       </c>
       <c r="E9" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B9)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B9)</f>
@@ -16225,8 +16231,8 @@
         <v>0</v>
       </c>
       <c r="I9" s="14">
-        <f>SUM(D9:H9)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="2">
@@ -16236,48 +16242,48 @@
         <v>360</v>
       </c>
       <c r="M9" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N9" s="34" t="s">
         <v>357</v>
       </c>
       <c r="O9" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P9" s="35" t="s">
         <v>315</v>
       </c>
       <c r="Q9" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R9" s="36" t="s">
         <v>327</v>
       </c>
       <c r="S9" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T9" s="37"/>
       <c r="U9" s="57" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <f>종합Sheet!A10</f>
-        <v>7</v>
+        <f>종합Sheet!A27</f>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="str">
-        <f>종합Sheet!B10</f>
-        <v>강관석</v>
+        <f>종합Sheet!B27</f>
+        <v>김송환</v>
       </c>
       <c r="C10" s="2">
-        <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
-        <v>0.3</v>
+        <f t="shared" si="0"/>
+        <v>0.8</v>
       </c>
       <c r="D10" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B10)</f>
@@ -16289,7 +16295,7 @@
       </c>
       <c r="F10" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B10)</f>
@@ -16297,11 +16303,11 @@
       </c>
       <c r="H10" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="14">
-        <f>SUM(D10:H10)</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="2">
@@ -16311,52 +16317,52 @@
         <v>357</v>
       </c>
       <c r="M10" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N10" s="34" t="s">
         <v>361</v>
       </c>
       <c r="O10" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P10" s="35" t="s">
         <v>306</v>
       </c>
       <c r="Q10" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R10" s="36" t="s">
         <v>62</v>
       </c>
       <c r="S10" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T10" s="37"/>
       <c r="U10" s="57" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <f>종합Sheet!A11</f>
-        <v>8</v>
+        <f>종합Sheet!A97</f>
+        <v>94</v>
       </c>
       <c r="B11" s="2" t="str">
-        <f>종합Sheet!B11</f>
-        <v>강기혁</v>
+        <f>종합Sheet!B97</f>
+        <v>차승원</v>
       </c>
       <c r="C11" s="2">
-        <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.8</v>
       </c>
       <c r="D11" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B11)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B11)</f>
@@ -16364,18 +16370,18 @@
       </c>
       <c r="F11" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B11)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B11)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B11)</f>
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f>SUM(D11:H11)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="J11" s="15"/>
@@ -16386,50 +16392,50 @@
         <v>242</v>
       </c>
       <c r="M11" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N11" s="34" t="s">
         <v>367</v>
       </c>
       <c r="O11" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P11" s="35"/>
       <c r="Q11" s="23" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="R11" s="36" t="s">
         <v>359</v>
       </c>
       <c r="S11" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T11" s="37"/>
       <c r="U11" s="57" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <f>종합Sheet!A12</f>
-        <v>9</v>
+        <f>종합Sheet!A33</f>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="str">
-        <f>종합Sheet!B12</f>
-        <v>강도일</v>
+        <f>종합Sheet!B33</f>
+        <v>김우인</v>
       </c>
       <c r="C12" s="2">
-        <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.8</v>
       </c>
       <c r="D12" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B12)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B12)</f>
@@ -16445,11 +16451,11 @@
       </c>
       <c r="H12" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B12)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" s="14">
-        <f>SUM(D12:H12)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="2">
@@ -16459,50 +16465,50 @@
         <v>362</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N12" s="34" t="s">
         <v>306</v>
       </c>
       <c r="O12" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P12" s="35"/>
       <c r="Q12" s="23" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="R12" s="36" t="s">
         <v>304</v>
       </c>
       <c r="S12" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T12" s="37"/>
       <c r="U12" s="57" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <f>종합Sheet!A13</f>
-        <v>10</v>
+        <f>종합Sheet!A71</f>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="str">
-        <f>종합Sheet!B13</f>
-        <v>강일수</v>
+        <f>종합Sheet!B71</f>
+        <v>윤현기</v>
       </c>
       <c r="C13" s="2">
-        <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.7</v>
       </c>
       <c r="D13" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B13)</f>
@@ -16510,7 +16516,7 @@
       </c>
       <c r="F13" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B13)</f>
@@ -16521,8 +16527,8 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f>SUM(D13:H13)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="2">
@@ -16532,52 +16538,52 @@
         <v>359</v>
       </c>
       <c r="M13" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N13" s="34"/>
       <c r="O13" s="22" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="P13" s="35"/>
       <c r="Q13" s="23" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="R13" s="36" t="s">
         <v>363</v>
       </c>
       <c r="S13" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="T13" s="37"/>
       <c r="U13" s="57" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <f>종합Sheet!A14</f>
-        <v>11</v>
+        <f>종합Sheet!A35</f>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="str">
-        <f>종합Sheet!B14</f>
-        <v>구교훈</v>
+        <f>종합Sheet!B35</f>
+        <v>김종혁</v>
       </c>
       <c r="C14" s="2">
-        <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D14" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B14)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B14)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B14)</f>
@@ -16592,8 +16598,8 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f>SUM(D14:H14)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J14" s="15"/>
       <c r="N14" s="33"/>
@@ -16602,16 +16608,16 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <f>종합Sheet!A15</f>
-        <v>12</v>
+        <f>종합Sheet!A65</f>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="str">
-        <f>종합Sheet!B15</f>
-        <v>권주용</v>
+        <f>종합Sheet!B65</f>
+        <v>유상근</v>
       </c>
       <c r="C15" s="2">
-        <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D15" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B15)</f>
@@ -16627,30 +16633,30 @@
       </c>
       <c r="G15" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B15)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="14">
-        <f>SUM(D15:H15)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <f>종합Sheet!A16</f>
-        <v>13</v>
+        <f>종합Sheet!A93</f>
+        <v>90</v>
       </c>
       <c r="B16" s="2" t="str">
-        <f>종합Sheet!B16</f>
-        <v>김기문</v>
+        <f>종합Sheet!B93</f>
+        <v>정민수</v>
       </c>
       <c r="C16" s="2">
-        <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D16" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B16)</f>
@@ -16666,30 +16672,30 @@
       </c>
       <c r="G16" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B16)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B16)</f>
         <v>0</v>
       </c>
       <c r="I16" s="14">
-        <f>SUM(D16:H16)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J16" s="15"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <f>종합Sheet!A17</f>
-        <v>14</v>
+        <f>종합Sheet!A51</f>
+        <v>48</v>
       </c>
       <c r="B17" s="2" t="str">
-        <f>종합Sheet!B17</f>
-        <v>김기태</v>
+        <f>종합Sheet!B51</f>
+        <v>박주연</v>
       </c>
       <c r="C17" s="2">
-        <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D17" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B17)</f>
@@ -16705,34 +16711,34 @@
       </c>
       <c r="G17" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B17)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B17)</f>
         <v>0</v>
       </c>
       <c r="I17" s="14">
-        <f>SUM(D17:H17)</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J17" s="15"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <f>종합Sheet!A18</f>
-        <v>15</v>
+        <f>종합Sheet!A100</f>
+        <v>97</v>
       </c>
       <c r="B18" s="2" t="str">
-        <f>종합Sheet!B18</f>
-        <v>김덕준</v>
+        <f>종합Sheet!B100</f>
+        <v>한상규</v>
       </c>
       <c r="C18" s="2">
-        <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D18" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B18)</f>
@@ -16744,30 +16750,30 @@
       </c>
       <c r="G18" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B18)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B18)</f>
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f>SUM(D18:H18)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <f>종합Sheet!A19</f>
-        <v>16</v>
+        <f>종합Sheet!A56</f>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="str">
-        <f>종합Sheet!B19</f>
-        <v>김동인</v>
+        <f>종합Sheet!B56</f>
+        <v>송윤상</v>
       </c>
       <c r="C19" s="2">
-        <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="D19" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B19)</f>
@@ -16779,7 +16785,7 @@
       </c>
       <c r="F19" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B19)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B19)</f>
@@ -16790,31 +16796,31 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f>SUM(D19:H19)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J19" s="15"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <f>종합Sheet!A20</f>
-        <v>17</v>
+        <f>종합Sheet!A39</f>
+        <v>36</v>
       </c>
       <c r="B20" s="2" t="str">
-        <f>종합Sheet!B20</f>
-        <v>김민섭</v>
+        <f>종합Sheet!B39</f>
+        <v>김진호</v>
       </c>
       <c r="C20" s="2">
-        <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.4</v>
       </c>
       <c r="D20" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B20)</f>
@@ -16829,23 +16835,23 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f>SUM(D20:H20)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <f>종합Sheet!A21</f>
-        <v>18</v>
+        <f>종합Sheet!A96</f>
+        <v>93</v>
       </c>
       <c r="B21" s="2" t="str">
-        <f>종합Sheet!B21</f>
-        <v>김민준</v>
+        <f>종합Sheet!B96</f>
+        <v>조현우</v>
       </c>
       <c r="C21" s="2">
-        <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.4</v>
       </c>
       <c r="D21" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B21)</f>
@@ -16861,30 +16867,30 @@
       </c>
       <c r="G21" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B21)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B21)</f>
         <v>0</v>
       </c>
       <c r="I21" s="14">
-        <f>SUM(D21:H21)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <f>종합Sheet!A22</f>
-        <v>19</v>
+        <f>종합Sheet!A106</f>
+        <v>103</v>
       </c>
       <c r="B22" s="2" t="str">
-        <f>종합Sheet!B22</f>
-        <v>김범기</v>
+        <f>종합Sheet!B106</f>
+        <v>황석원</v>
       </c>
       <c r="C22" s="2">
-        <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.4</v>
       </c>
       <c r="D22" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B22)</f>
@@ -16900,34 +16906,34 @@
       </c>
       <c r="G22" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B22)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B22)</f>
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f>SUM(D22:H22)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <f>종합Sheet!A23</f>
-        <v>20</v>
+        <f>종합Sheet!A75</f>
+        <v>72</v>
       </c>
       <c r="B23" s="2" t="str">
-        <f>종합Sheet!B23</f>
-        <v>김병준</v>
+        <f>종합Sheet!B75</f>
+        <v>이상민</v>
       </c>
       <c r="C23" s="2">
-        <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.4</v>
       </c>
       <c r="D23" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B23)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B23)</f>
@@ -16939,30 +16945,30 @@
       </c>
       <c r="G23" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B23)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B23)</f>
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f>SUM(D23:H23)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J23" s="15"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <f>종합Sheet!A24</f>
-        <v>21</v>
+        <f>종합Sheet!A10</f>
+        <v>7</v>
       </c>
       <c r="B24" s="2" t="str">
-        <f>종합Sheet!B24</f>
-        <v>김부건</v>
+        <f>종합Sheet!B10</f>
+        <v>강관석</v>
       </c>
       <c r="C24" s="2">
-        <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.3</v>
       </c>
       <c r="D24" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B24)</f>
@@ -16974,7 +16980,7 @@
       </c>
       <c r="F24" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B24)</f>
@@ -16985,23 +16991,23 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f>SUM(D24:H24)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J24" s="15"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <f>종합Sheet!A25</f>
-        <v>22</v>
+        <f>종합Sheet!A4</f>
+        <v>1</v>
       </c>
       <c r="B25" s="2" t="str">
-        <f>종합Sheet!B25</f>
-        <v>김성수</v>
+        <f>종합Sheet!B4</f>
+        <v>김인혁</v>
       </c>
       <c r="C25" s="2">
-        <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="D25" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B25)</f>
@@ -17009,7 +17015,7 @@
       </c>
       <c r="E25" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B25)</f>
@@ -17024,27 +17030,27 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f>SUM(D25:H25)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <f>종합Sheet!A26</f>
-        <v>23</v>
+        <f>종합Sheet!A74</f>
+        <v>71</v>
       </c>
       <c r="B26" s="2" t="str">
-        <f>종합Sheet!B26</f>
-        <v>김성준</v>
+        <f>종합Sheet!B74</f>
+        <v>이병현</v>
       </c>
       <c r="C26" s="2">
-        <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
-        <v>1.4</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="D26" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B26)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B26)</f>
@@ -17052,34 +17058,34 @@
       </c>
       <c r="F26" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B26)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B26)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B26)</f>
         <v>0</v>
       </c>
       <c r="I26" s="14">
-        <f>SUM(D26:H26)</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J26" s="15"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <f>종합Sheet!A27</f>
-        <v>24</v>
+        <f>종합Sheet!A105</f>
+        <v>102</v>
       </c>
       <c r="B27" s="2" t="str">
-        <f>종합Sheet!B27</f>
-        <v>김송환</v>
+        <f>종합Sheet!B105</f>
+        <v>홍현석</v>
       </c>
       <c r="C27" s="2">
-        <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="D27" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B27)</f>
@@ -17091,3075 +17097,3075 @@
       </c>
       <c r="F27" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B27)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B27)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="14">
+        <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="I27" s="14">
-        <f>SUM(D27:H27)</f>
-        <v>3</v>
       </c>
       <c r="J27" s="15"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
+        <f>종합Sheet!A17</f>
+        <v>14</v>
+      </c>
+      <c r="B28" s="2" t="str">
+        <f>종합Sheet!B17</f>
+        <v>김기태</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="D28" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B28)</f>
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B28)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B28)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B28)</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B28)</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J28" s="15"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <f>종합Sheet!A5</f>
+        <v>2</v>
+      </c>
+      <c r="B29" s="2" t="str">
+        <f>종합Sheet!B5</f>
+        <v>신재경</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B29)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B29)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B29)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B29)</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B29)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="15"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <f>종합Sheet!A6</f>
+        <v>3</v>
+      </c>
+      <c r="B30" s="2" t="str">
+        <f>종합Sheet!B6</f>
+        <v>정효태</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B30)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B30)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B30)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B30)</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B30)</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <f>종합Sheet!A7</f>
+        <v>4</v>
+      </c>
+      <c r="B31" s="2" t="str">
+        <f>종합Sheet!B7</f>
+        <v>이승민</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B31)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B31)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B31)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B31)</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B31)</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <f>종합Sheet!A8</f>
+        <v>5</v>
+      </c>
+      <c r="B32" s="2" t="str">
+        <f>종합Sheet!B8</f>
+        <v>이정석</v>
+      </c>
+      <c r="C32" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B32)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B32)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B32)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B32)</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B32)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <f>종합Sheet!A9</f>
+        <v>6</v>
+      </c>
+      <c r="B33" s="2" t="str">
+        <f>종합Sheet!B9</f>
+        <v>강종찬</v>
+      </c>
+      <c r="C33" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B33)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B33)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B33)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B33)</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B33)</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <f>종합Sheet!A12</f>
+        <v>9</v>
+      </c>
+      <c r="B34" s="2" t="str">
+        <f>종합Sheet!B12</f>
+        <v>강도일</v>
+      </c>
+      <c r="C34" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B34)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B34)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B34)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B34)</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B34)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <f>종합Sheet!A13</f>
+        <v>10</v>
+      </c>
+      <c r="B35" s="2" t="str">
+        <f>종합Sheet!B13</f>
+        <v>강일수</v>
+      </c>
+      <c r="C35" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B35)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B35)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B35)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B35)</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B35)</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <f>종합Sheet!A14</f>
+        <v>11</v>
+      </c>
+      <c r="B36" s="2" t="str">
+        <f>종합Sheet!B14</f>
+        <v>구교훈</v>
+      </c>
+      <c r="C36" s="2">
+        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B36)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B36)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B36)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B36)</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B36)</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="14">
+        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <f>종합Sheet!A15</f>
+        <v>12</v>
+      </c>
+      <c r="B37" s="2" t="str">
+        <f>종합Sheet!B15</f>
+        <v>권주용</v>
+      </c>
+      <c r="C37" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B37)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B37)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B37)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B37)</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B37)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="15"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <f>종합Sheet!A16</f>
+        <v>13</v>
+      </c>
+      <c r="B38" s="2" t="str">
+        <f>종합Sheet!B16</f>
+        <v>김기문</v>
+      </c>
+      <c r="C38" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B38)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B38)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B38)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B38)</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B38)</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="15"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <f>종합Sheet!A18</f>
+        <v>15</v>
+      </c>
+      <c r="B39" s="2" t="str">
+        <f>종합Sheet!B18</f>
+        <v>김덕준</v>
+      </c>
+      <c r="C39" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B39)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B39)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B39)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B39)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B39)</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="15"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <f>종합Sheet!A19</f>
+        <v>16</v>
+      </c>
+      <c r="B40" s="2" t="str">
+        <f>종합Sheet!B19</f>
+        <v>김동인</v>
+      </c>
+      <c r="C40" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B40)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B40)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B40)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B40)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B40)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="15"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <f>종합Sheet!A20</f>
+        <v>17</v>
+      </c>
+      <c r="B41" s="2" t="str">
+        <f>종합Sheet!B20</f>
+        <v>김민섭</v>
+      </c>
+      <c r="C41" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B41)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B41)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B41)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B41)</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B41)</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <f>종합Sheet!A21</f>
+        <v>18</v>
+      </c>
+      <c r="B42" s="2" t="str">
+        <f>종합Sheet!B21</f>
+        <v>김민준</v>
+      </c>
+      <c r="C42" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B42)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B42)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B42)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B42)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B42)</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <f>종합Sheet!A22</f>
+        <v>19</v>
+      </c>
+      <c r="B43" s="2" t="str">
+        <f>종합Sheet!B22</f>
+        <v>김범기</v>
+      </c>
+      <c r="C43" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <f>종합Sheet!A23</f>
+        <v>20</v>
+      </c>
+      <c r="B44" s="2" t="str">
+        <f>종합Sheet!B23</f>
+        <v>김병준</v>
+      </c>
+      <c r="C44" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B44)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B44)</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B44)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B44)</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B44)</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <f>종합Sheet!A24</f>
+        <v>21</v>
+      </c>
+      <c r="B45" s="2" t="str">
+        <f>종합Sheet!B24</f>
+        <v>김부건</v>
+      </c>
+      <c r="C45" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B45)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B45)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B45)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B45)</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B45)</f>
+        <v>0</v>
+      </c>
+      <c r="I45" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <f>종합Sheet!A25</f>
+        <v>22</v>
+      </c>
+      <c r="B46" s="2" t="str">
+        <f>종합Sheet!B25</f>
+        <v>김성수</v>
+      </c>
+      <c r="C46" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B46)</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B46)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B46)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B46)</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B46)</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="15"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
         <f>종합Sheet!A28</f>
         <v>25</v>
       </c>
-      <c r="B28" s="2" t="str">
+      <c r="B47" s="2" t="str">
         <f>종합Sheet!B28</f>
         <v>김승철</v>
       </c>
-      <c r="C28" s="2">
-        <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B28)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B28)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B28)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B28)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B28)</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="14">
-        <f>SUM(D28:H28)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="C47" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B47)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B47)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B47)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B47)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B47)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="15"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <f>종합Sheet!A29</f>
         <v>26</v>
       </c>
-      <c r="B29" s="2" t="str">
+      <c r="B48" s="2" t="str">
         <f>종합Sheet!B29</f>
         <v>김영태</v>
       </c>
-      <c r="C29" s="2">
-        <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B29)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B29)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B29)</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B29)</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B29)</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="14">
-        <f>SUM(D29:H29)</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="15"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="C48" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B48)</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B48)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B48)</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B48)</f>
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B48)</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="15"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
         <f>종합Sheet!A30</f>
         <v>27</v>
       </c>
-      <c r="B30" s="2" t="str">
+      <c r="B49" s="2" t="str">
         <f>종합Sheet!B30</f>
         <v>김용만</v>
       </c>
-      <c r="C30" s="2">
-        <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B30)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B30)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B30)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B30)</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B30)</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="14">
-        <f>SUM(D30:H30)</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="C49" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B49)</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B49)</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B49)</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B49)</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B49)</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="15"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
         <f>종합Sheet!A31</f>
         <v>28</v>
       </c>
-      <c r="B31" s="2" t="str">
+      <c r="B50" s="2" t="str">
         <f>종합Sheet!B31</f>
         <v>김용빈</v>
       </c>
-      <c r="C31" s="2">
-        <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B31)</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B31)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B31)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B31)</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B31)</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="14">
-        <f>SUM(D31:H31)</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <f>종합Sheet!A32</f>
-        <v>29</v>
-      </c>
-      <c r="B32" s="2" t="str">
-        <f>종합Sheet!B32</f>
-        <v>김용현</v>
-      </c>
-      <c r="C32" s="2">
-        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
-        <v>0.8</v>
-      </c>
-      <c r="D32" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B32)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B32)</f>
-        <v>1</v>
-      </c>
-      <c r="F32" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B32)</f>
-        <v>2</v>
-      </c>
-      <c r="G32" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B32)</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B32)</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="14">
-        <f>SUM(D32:H32)</f>
-        <v>3</v>
-      </c>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <f>종합Sheet!A33</f>
-        <v>30</v>
-      </c>
-      <c r="B33" s="2" t="str">
-        <f>종합Sheet!B33</f>
-        <v>김우인</v>
-      </c>
-      <c r="C33" s="2">
-        <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
-        <v>0.8</v>
-      </c>
-      <c r="D33" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B33)</f>
-        <v>2</v>
-      </c>
-      <c r="E33" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B33)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B33)</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B33)</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B33)</f>
-        <v>2</v>
-      </c>
-      <c r="I33" s="14">
-        <f>SUM(D33:H33)</f>
-        <v>4</v>
-      </c>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="C50" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B50)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B50)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B50)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B50)</f>
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B50)</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="15"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
         <f>종합Sheet!A34</f>
         <v>31</v>
       </c>
-      <c r="B34" s="2" t="str">
+      <c r="B51" s="2" t="str">
         <f>종합Sheet!B34</f>
         <v>김종준</v>
       </c>
-      <c r="C34" s="2">
-        <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B34)</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B34)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B34)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B34)</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B34)</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="14">
-        <f>SUM(D34:H34)</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <f>종합Sheet!A35</f>
-        <v>32</v>
-      </c>
-      <c r="B35" s="2" t="str">
-        <f>종합Sheet!B35</f>
-        <v>김종혁</v>
-      </c>
-      <c r="C35" s="2">
-        <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D35" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B35)</f>
-        <v>1</v>
-      </c>
-      <c r="E35" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B35)</f>
-        <v>2</v>
-      </c>
-      <c r="F35" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B35)</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B35)</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B35)</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="14">
-        <f>SUM(D35:H35)</f>
-        <v>3</v>
-      </c>
-      <c r="J35" s="15"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="C51" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D51" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B51)</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B51)</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B51)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B51)</f>
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B51)</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="15"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <f>종합Sheet!A36</f>
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="str">
+      <c r="B52" s="2" t="str">
         <f>종합Sheet!B36</f>
         <v>김주식</v>
       </c>
-      <c r="C36" s="2">
-        <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B36)</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B36)</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B36)</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B36)</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B36)</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="14">
-        <f>SUM(D36:H36)</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="15"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="C52" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D52" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B52)</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B52)</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B52)</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B52)</f>
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B52)</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="15"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
         <f>종합Sheet!A37</f>
         <v>34</v>
       </c>
-      <c r="B37" s="2" t="str">
+      <c r="B53" s="2" t="str">
         <f>종합Sheet!B37</f>
         <v>김준영</v>
       </c>
-      <c r="C37" s="2">
-        <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B37)</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B37)</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B37)</f>
-        <v>0</v>
-      </c>
-      <c r="G37" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B37)</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B37)</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="14">
-        <f>SUM(D37:H37)</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="15"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="C53" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B53)</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B53)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B53)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B53)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B53)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="15"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
         <f>종합Sheet!A38</f>
         <v>35</v>
       </c>
-      <c r="B38" s="2" t="str">
+      <c r="B54" s="2" t="str">
         <f>종합Sheet!B38</f>
         <v>김진형</v>
       </c>
-      <c r="C38" s="2">
-        <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B38)</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B38)</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B38)</f>
-        <v>0</v>
-      </c>
-      <c r="G38" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B38)</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B38)</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="14">
-        <f>SUM(D38:H38)</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="15"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <f>종합Sheet!A39</f>
-        <v>36</v>
-      </c>
-      <c r="B39" s="2" t="str">
-        <f>종합Sheet!B39</f>
-        <v>김진호</v>
-      </c>
-      <c r="C39" s="2">
-        <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
-        <v>0.4</v>
-      </c>
-      <c r="D39" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B39)</f>
-        <v>1</v>
-      </c>
-      <c r="E39" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B39)</f>
-        <v>1</v>
-      </c>
-      <c r="F39" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B39)</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B39)</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B39)</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="14">
-        <f>SUM(D39:H39)</f>
-        <v>2</v>
-      </c>
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="C54" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B54)</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B54)</f>
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B54)</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B54)</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B54)</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="15"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
         <f>종합Sheet!A40</f>
         <v>37</v>
       </c>
-      <c r="B40" s="2" t="str">
+      <c r="B55" s="2" t="str">
         <f>종합Sheet!B40</f>
         <v>김태성</v>
       </c>
-      <c r="C40" s="2">
-        <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B40)</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B40)</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B40)</f>
-        <v>0</v>
-      </c>
-      <c r="G40" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B40)</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B40)</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="14">
-        <f>SUM(D40:H40)</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="C55" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B55)</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B55)</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B55)</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B55)</f>
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B55)</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="15"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
         <f>종합Sheet!A41</f>
         <v>38</v>
       </c>
-      <c r="B41" s="2" t="str">
+      <c r="B56" s="2" t="str">
         <f>종합Sheet!B41</f>
         <v>김태양</v>
       </c>
-      <c r="C41" s="2">
-        <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D41" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B41)</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B41)</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B41)</f>
-        <v>0</v>
-      </c>
-      <c r="G41" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B41)</f>
-        <v>0</v>
-      </c>
-      <c r="H41" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B41)</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="14">
-        <f>SUM(D41:H41)</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="15"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="C56" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B56)</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B56)</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B56)</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B56)</f>
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B56)</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="15"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
         <f>종합Sheet!A42</f>
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="str">
+      <c r="B57" s="2" t="str">
         <f>종합Sheet!B42</f>
         <v>김태완</v>
       </c>
-      <c r="C42" s="2">
-        <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B42)</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B42)</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B42)</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B42)</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B42)</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="14">
-        <f>SUM(D42:H42)</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="C57" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B57)</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B57)</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B57)</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B57)</f>
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B57)</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="15"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
         <f>종합Sheet!A43</f>
         <v>40</v>
       </c>
-      <c r="B43" s="2" t="str">
+      <c r="B58" s="2" t="str">
         <f>종합Sheet!B43</f>
         <v>김태호</v>
       </c>
-      <c r="C43" s="2">
-        <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B43)</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B43)</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B43)</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B43)</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B43)</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="14">
-        <f>SUM(D43:H43)</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="C58" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D58" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B58)</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B58)</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B58)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B58)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B58)</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="15"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
         <f>종합Sheet!A44</f>
         <v>41</v>
       </c>
-      <c r="B44" s="2" t="str">
+      <c r="B59" s="2" t="str">
         <f>종합Sheet!B44</f>
         <v>김형원</v>
       </c>
-      <c r="C44" s="2">
-        <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B44)</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B44)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B44)</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B44)</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B44)</f>
-        <v>0</v>
-      </c>
-      <c r="I44" s="14">
-        <f>SUM(D44:H44)</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <f>종합Sheet!A45</f>
-        <v>42</v>
-      </c>
-      <c r="B45" s="2" t="str">
-        <f>종합Sheet!B45</f>
-        <v>노민준</v>
-      </c>
-      <c r="C45" s="2">
-        <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
-        <v>1</v>
-      </c>
-      <c r="D45" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B45)</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B45)</f>
-        <v>1</v>
-      </c>
-      <c r="F45" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B45)</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B45)</f>
-        <v>2</v>
-      </c>
-      <c r="H45" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B45)</f>
-        <v>2</v>
-      </c>
-      <c r="I45" s="14">
-        <f>SUM(D45:H45)</f>
-        <v>5</v>
-      </c>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="C59" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D59" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B59)</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B59)</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B59)</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B59)</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B59)</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="15"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
         <f>종합Sheet!A46</f>
         <v>43</v>
       </c>
-      <c r="B46" s="2" t="str">
+      <c r="B60" s="2" t="str">
         <f>종합Sheet!B46</f>
         <v>마창기</v>
       </c>
-      <c r="C46" s="2">
-        <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B46)</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B46)</f>
-        <v>0</v>
-      </c>
-      <c r="F46" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B46)</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B46)</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B46)</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="14">
-        <f>SUM(D46:H46)</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="C60" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D60" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B60)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B60)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B60)</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B60)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B60)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="15"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
         <f>종합Sheet!A47</f>
         <v>44</v>
       </c>
-      <c r="B47" s="2" t="str">
+      <c r="B61" s="2" t="str">
         <f>종합Sheet!B47</f>
         <v>문준수</v>
       </c>
-      <c r="C47" s="2">
-        <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B47)</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B47)</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B47)</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B47)</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B47)</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="14">
-        <f>SUM(D47:H47)</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="15"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="C61" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B61)</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B61)</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B61)</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B61)</f>
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B61)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="15"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
         <f>종합Sheet!A48</f>
         <v>45</v>
       </c>
-      <c r="B48" s="2" t="str">
+      <c r="B62" s="2" t="str">
         <f>종합Sheet!B48</f>
         <v>민건호</v>
       </c>
-      <c r="C48" s="2">
-        <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D48" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B48)</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B48)</f>
-        <v>0</v>
-      </c>
-      <c r="F48" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B48)</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B48)</f>
-        <v>0</v>
-      </c>
-      <c r="H48" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B48)</f>
-        <v>0</v>
-      </c>
-      <c r="I48" s="14">
-        <f>SUM(D48:H48)</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="15"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="C62" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D62" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B62)</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B62)</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B62)</f>
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B62)</f>
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B62)</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="15"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
         <f>종합Sheet!A49</f>
         <v>46</v>
       </c>
-      <c r="B49" s="2" t="str">
+      <c r="B63" s="2" t="str">
         <f>종합Sheet!B49</f>
         <v>박수천</v>
       </c>
-      <c r="C49" s="2">
-        <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D49" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B49)</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B49)</f>
-        <v>0</v>
-      </c>
-      <c r="F49" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B49)</f>
-        <v>0</v>
-      </c>
-      <c r="G49" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B49)</f>
-        <v>0</v>
-      </c>
-      <c r="H49" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B49)</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="14">
-        <f>SUM(D49:H49)</f>
-        <v>0</v>
-      </c>
-      <c r="J49" s="15"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="C63" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D63" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B63)</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B63)</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B63)</f>
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B63)</f>
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B63)</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="15"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
         <f>종합Sheet!A50</f>
         <v>47</v>
       </c>
-      <c r="B50" s="2" t="str">
+      <c r="B64" s="2" t="str">
         <f>종합Sheet!B50</f>
         <v>박정호</v>
       </c>
-      <c r="C50" s="2">
-        <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B50)</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B50)</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B50)</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B50)</f>
-        <v>0</v>
-      </c>
-      <c r="H50" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B50)</f>
-        <v>0</v>
-      </c>
-      <c r="I50" s="14">
-        <f>SUM(D50:H50)</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <f>종합Sheet!A51</f>
-        <v>48</v>
-      </c>
-      <c r="B51" s="2" t="str">
-        <f>종합Sheet!B51</f>
-        <v>박주연</v>
-      </c>
-      <c r="C51" s="2">
-        <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D51" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B51)</f>
-        <v>1</v>
-      </c>
-      <c r="E51" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B51)</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B51)</f>
-        <v>0</v>
-      </c>
-      <c r="G51" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B51)</f>
-        <v>2</v>
-      </c>
-      <c r="H51" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B51)</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="14">
-        <f>SUM(D51:H51)</f>
-        <v>3</v>
-      </c>
-      <c r="J51" s="15"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="C64" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D64" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B64)</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B64)</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B64)</f>
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B64)</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B64)</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="15"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
         <f>종합Sheet!A52</f>
         <v>49</v>
       </c>
-      <c r="B52" s="2" t="str">
+      <c r="B65" s="2" t="str">
         <f>종합Sheet!B52</f>
         <v>박주현</v>
       </c>
-      <c r="C52" s="2">
-        <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B52)</f>
-        <v>0</v>
-      </c>
-      <c r="E52" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B52)</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B52)</f>
-        <v>0</v>
-      </c>
-      <c r="G52" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B52)</f>
-        <v>0</v>
-      </c>
-      <c r="H52" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B52)</f>
-        <v>0</v>
-      </c>
-      <c r="I52" s="14">
-        <f>SUM(D52:H52)</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="15"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="C65" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D65" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B65)</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B65)</f>
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B65)</f>
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B65)</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B65)</f>
+        <v>0</v>
+      </c>
+      <c r="I65" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="15"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
         <f>종합Sheet!A53</f>
         <v>50</v>
       </c>
-      <c r="B53" s="2" t="str">
+      <c r="B66" s="2" t="str">
         <f>종합Sheet!B53</f>
         <v>박하빈</v>
       </c>
-      <c r="C53" s="2">
-        <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D53" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B53)</f>
-        <v>0</v>
-      </c>
-      <c r="E53" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B53)</f>
-        <v>0</v>
-      </c>
-      <c r="F53" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B53)</f>
-        <v>0</v>
-      </c>
-      <c r="G53" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B53)</f>
-        <v>0</v>
-      </c>
-      <c r="H53" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B53)</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="14">
-        <f>SUM(D53:H53)</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="15"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="C66" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D66" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B66)</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B66)</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B66)</f>
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B66)</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B66)</f>
+        <v>0</v>
+      </c>
+      <c r="I66" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="15"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
         <f>종합Sheet!A54</f>
         <v>51</v>
       </c>
-      <c r="B54" s="2" t="str">
+      <c r="B67" s="2" t="str">
         <f>종합Sheet!B54</f>
         <v>박형기</v>
       </c>
-      <c r="C54" s="2">
-        <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D54" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B54)</f>
-        <v>0</v>
-      </c>
-      <c r="E54" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B54)</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B54)</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B54)</f>
-        <v>0</v>
-      </c>
-      <c r="H54" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B54)</f>
-        <v>0</v>
-      </c>
-      <c r="I54" s="14">
-        <f>SUM(D54:H54)</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="15"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="C67" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D67" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B67)</f>
+        <v>0</v>
+      </c>
+      <c r="E67" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B67)</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B67)</f>
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B67)</f>
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B67)</f>
+        <v>0</v>
+      </c>
+      <c r="I67" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="15"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
         <f>종합Sheet!A55</f>
         <v>52</v>
       </c>
-      <c r="B55" s="2" t="str">
+      <c r="B68" s="2" t="str">
         <f>종합Sheet!B55</f>
         <v>손경호</v>
       </c>
-      <c r="C55" s="2">
-        <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B55)</f>
-        <v>0</v>
-      </c>
-      <c r="E55" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B55)</f>
-        <v>0</v>
-      </c>
-      <c r="F55" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B55)</f>
-        <v>0</v>
-      </c>
-      <c r="G55" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B55)</f>
-        <v>0</v>
-      </c>
-      <c r="H55" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B55)</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="14">
-        <f>SUM(D55:H55)</f>
-        <v>0</v>
-      </c>
-      <c r="J55" s="15"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <f>종합Sheet!A56</f>
-        <v>53</v>
-      </c>
-      <c r="B56" s="2" t="str">
-        <f>종합Sheet!B56</f>
-        <v>송윤상</v>
-      </c>
-      <c r="C56" s="2">
-        <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
-        <v>0.6</v>
-      </c>
-      <c r="D56" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B56)</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B56)</f>
-        <v>0</v>
-      </c>
-      <c r="F56" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B56)</f>
-        <v>2</v>
-      </c>
-      <c r="G56" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B56)</f>
-        <v>0</v>
-      </c>
-      <c r="H56" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B56)</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="14">
-        <f>SUM(D56:H56)</f>
-        <v>2</v>
-      </c>
-      <c r="J56" s="15"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="C68" s="2">
+        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B68)</f>
+        <v>0</v>
+      </c>
+      <c r="E68" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B68)</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B68)</f>
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B68)</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B68)</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="14">
+        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="15"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
         <f>종합Sheet!A57</f>
         <v>54</v>
       </c>
-      <c r="B57" s="2" t="str">
+      <c r="B69" s="2" t="str">
         <f>종합Sheet!B57</f>
         <v>신기웅</v>
       </c>
-      <c r="C57" s="2">
-        <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B57)</f>
-        <v>0</v>
-      </c>
-      <c r="E57" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B57)</f>
-        <v>0</v>
-      </c>
-      <c r="F57" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B57)</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B57)</f>
-        <v>0</v>
-      </c>
-      <c r="H57" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B57)</f>
-        <v>0</v>
-      </c>
-      <c r="I57" s="14">
-        <f>SUM(D57:H57)</f>
-        <v>0</v>
-      </c>
-      <c r="J57" s="15"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="C69" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D69" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B69)</f>
+        <v>0</v>
+      </c>
+      <c r="E69" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B69)</f>
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B69)</f>
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B69)</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B69)</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="15"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
         <f>종합Sheet!A58</f>
         <v>55</v>
       </c>
-      <c r="B58" s="2" t="str">
+      <c r="B70" s="2" t="str">
         <f>종합Sheet!B58</f>
         <v>신종훈</v>
       </c>
-      <c r="C58" s="2">
-        <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B58)</f>
-        <v>0</v>
-      </c>
-      <c r="E58" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B58)</f>
-        <v>0</v>
-      </c>
-      <c r="F58" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B58)</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B58)</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B58)</f>
-        <v>0</v>
-      </c>
-      <c r="I58" s="14">
-        <f>SUM(D58:H58)</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="15"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="C70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D70" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B70)</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B70)</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B70)</f>
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B70)</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B70)</f>
+        <v>0</v>
+      </c>
+      <c r="I70" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="15"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
         <f>종합Sheet!A59</f>
         <v>56</v>
       </c>
-      <c r="B59" s="2" t="str">
+      <c r="B71" s="2" t="str">
         <f>종합Sheet!B59</f>
         <v>안진혁</v>
       </c>
-      <c r="C59" s="2">
-        <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D59" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B59)</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B59)</f>
-        <v>0</v>
-      </c>
-      <c r="F59" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B59)</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B59)</f>
-        <v>0</v>
-      </c>
-      <c r="H59" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B59)</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="14">
-        <f>SUM(D59:H59)</f>
-        <v>0</v>
-      </c>
-      <c r="J59" s="15"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="C71" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D71" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B71)</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B71)</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B71)</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B71)</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B71)</f>
+        <v>0</v>
+      </c>
+      <c r="I71" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
         <f>종합Sheet!A60</f>
         <v>57</v>
       </c>
-      <c r="B60" s="2" t="str">
+      <c r="B72" s="2" t="str">
         <f>종합Sheet!B60</f>
         <v>양진웅</v>
       </c>
-      <c r="C60" s="2">
-        <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D60" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B60)</f>
-        <v>0</v>
-      </c>
-      <c r="E60" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B60)</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B60)</f>
-        <v>0</v>
-      </c>
-      <c r="G60" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B60)</f>
-        <v>0</v>
-      </c>
-      <c r="H60" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B60)</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="14">
-        <f>SUM(D60:H60)</f>
-        <v>0</v>
-      </c>
-      <c r="J60" s="15"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <f>종합Sheet!A61</f>
-        <v>58</v>
-      </c>
-      <c r="B61" s="2" t="str">
-        <f>종합Sheet!B61</f>
-        <v>오우영</v>
-      </c>
-      <c r="C61" s="2">
-        <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
-        <v>1</v>
-      </c>
-      <c r="D61" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B61)</f>
-        <v>0</v>
-      </c>
-      <c r="E61" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B61)</f>
-        <v>2</v>
-      </c>
-      <c r="F61" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B61)</f>
-        <v>2</v>
-      </c>
-      <c r="G61" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B61)</f>
-        <v>0</v>
-      </c>
-      <c r="H61" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B61)</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="14">
-        <f>SUM(D61:H61)</f>
-        <v>4</v>
-      </c>
-      <c r="J61" s="15"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="C72" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D72" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B72)</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B72)</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B72)</f>
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B72)</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B72)</f>
+        <v>0</v>
+      </c>
+      <c r="I72" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="15"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
         <f>종합Sheet!A62</f>
         <v>59</v>
       </c>
-      <c r="B62" s="2" t="str">
+      <c r="B73" s="2" t="str">
         <f>종합Sheet!B62</f>
         <v>오운용</v>
       </c>
-      <c r="C62" s="2">
-        <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B62)</f>
-        <v>0</v>
-      </c>
-      <c r="E62" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B62)</f>
-        <v>0</v>
-      </c>
-      <c r="F62" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B62)</f>
-        <v>0</v>
-      </c>
-      <c r="G62" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B62)</f>
-        <v>0</v>
-      </c>
-      <c r="H62" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B62)</f>
-        <v>0</v>
-      </c>
-      <c r="I62" s="14">
-        <f>SUM(D62:H62)</f>
-        <v>0</v>
-      </c>
-      <c r="J62" s="15"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="C73" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D73" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B73)</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B73)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B73)</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B73)</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B73)</f>
+        <v>0</v>
+      </c>
+      <c r="I73" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J73" s="15"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
         <f>종합Sheet!A63</f>
         <v>60</v>
       </c>
-      <c r="B63" s="2" t="str">
+      <c r="B74" s="2" t="str">
         <f>종합Sheet!B63</f>
         <v>오진환</v>
       </c>
-      <c r="C63" s="2">
-        <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D63" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B63)</f>
-        <v>0</v>
-      </c>
-      <c r="E63" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B63)</f>
-        <v>0</v>
-      </c>
-      <c r="F63" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B63)</f>
-        <v>0</v>
-      </c>
-      <c r="G63" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B63)</f>
-        <v>0</v>
-      </c>
-      <c r="H63" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B63)</f>
-        <v>0</v>
-      </c>
-      <c r="I63" s="14">
-        <f>SUM(D63:H63)</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="15"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="C74" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D74" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B74)</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B74)</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B74)</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B74)</f>
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B74)</f>
+        <v>0</v>
+      </c>
+      <c r="I74" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="15"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
         <f>종합Sheet!A64</f>
         <v>61</v>
       </c>
-      <c r="B64" s="2" t="str">
+      <c r="B75" s="2" t="str">
         <f>종합Sheet!B64</f>
         <v>우보광</v>
       </c>
-      <c r="C64" s="2">
-        <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D64" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B64)</f>
-        <v>0</v>
-      </c>
-      <c r="E64" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B64)</f>
-        <v>0</v>
-      </c>
-      <c r="F64" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B64)</f>
-        <v>0</v>
-      </c>
-      <c r="G64" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B64)</f>
-        <v>0</v>
-      </c>
-      <c r="H64" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B64)</f>
-        <v>0</v>
-      </c>
-      <c r="I64" s="14">
-        <f>SUM(D64:H64)</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="15"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <f>종합Sheet!A65</f>
-        <v>62</v>
-      </c>
-      <c r="B65" s="2" t="str">
-        <f>종합Sheet!B65</f>
-        <v>유상근</v>
-      </c>
-      <c r="C65" s="2">
-        <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D65" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B65)</f>
-        <v>0</v>
-      </c>
-      <c r="E65" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B65)</f>
-        <v>0</v>
-      </c>
-      <c r="F65" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B65)</f>
-        <v>0</v>
-      </c>
-      <c r="G65" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B65)</f>
-        <v>2</v>
-      </c>
-      <c r="H65" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B65)</f>
-        <v>1</v>
-      </c>
-      <c r="I65" s="14">
-        <f>SUM(D65:H65)</f>
-        <v>3</v>
-      </c>
-      <c r="J65" s="15"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="C75" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D75" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B75)</f>
+        <v>0</v>
+      </c>
+      <c r="E75" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B75)</f>
+        <v>0</v>
+      </c>
+      <c r="F75" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B75)</f>
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B75)</f>
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B75)</f>
+        <v>0</v>
+      </c>
+      <c r="I75" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J75" s="15"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
         <f>종합Sheet!A66</f>
         <v>63</v>
       </c>
-      <c r="B66" s="2" t="str">
+      <c r="B76" s="2" t="str">
         <f>종합Sheet!B66</f>
         <v>유인상</v>
       </c>
-      <c r="C66" s="2">
-        <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B66)</f>
-        <v>0</v>
-      </c>
-      <c r="E66" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B66)</f>
-        <v>0</v>
-      </c>
-      <c r="F66" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B66)</f>
-        <v>0</v>
-      </c>
-      <c r="G66" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B66)</f>
-        <v>0</v>
-      </c>
-      <c r="H66" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B66)</f>
-        <v>0</v>
-      </c>
-      <c r="I66" s="14">
-        <f>SUM(D66:H66)</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="15"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="C76" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D76" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B76)</f>
+        <v>0</v>
+      </c>
+      <c r="E76" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B76)</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B76)</f>
+        <v>0</v>
+      </c>
+      <c r="G76" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B76)</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B76)</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J76" s="15"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
         <f>종합Sheet!A67</f>
         <v>64</v>
       </c>
-      <c r="B67" s="2" t="str">
+      <c r="B77" s="2" t="str">
         <f>종합Sheet!B67</f>
         <v>유정훈</v>
       </c>
-      <c r="C67" s="2">
-        <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B67)</f>
-        <v>0</v>
-      </c>
-      <c r="E67" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B67)</f>
-        <v>0</v>
-      </c>
-      <c r="F67" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B67)</f>
-        <v>0</v>
-      </c>
-      <c r="G67" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B67)</f>
-        <v>0</v>
-      </c>
-      <c r="H67" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B67)</f>
-        <v>0</v>
-      </c>
-      <c r="I67" s="14">
-        <f>SUM(D67:H67)</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="15"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="C77" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D77" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B77)</f>
+        <v>0</v>
+      </c>
+      <c r="E77" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B77)</f>
+        <v>0</v>
+      </c>
+      <c r="F77" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B77)</f>
+        <v>0</v>
+      </c>
+      <c r="G77" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B77)</f>
+        <v>0</v>
+      </c>
+      <c r="H77" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B77)</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J77" s="15"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
         <f>종합Sheet!A68</f>
         <v>65</v>
       </c>
-      <c r="B68" s="2" t="str">
+      <c r="B78" s="2" t="str">
         <f>종합Sheet!B68</f>
         <v>유진효</v>
       </c>
-      <c r="C68" s="2">
-        <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B68)</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B68)</f>
-        <v>0</v>
-      </c>
-      <c r="F68" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B68)</f>
-        <v>0</v>
-      </c>
-      <c r="G68" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B68)</f>
-        <v>0</v>
-      </c>
-      <c r="H68" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B68)</f>
-        <v>0</v>
-      </c>
-      <c r="I68" s="14">
-        <f>SUM(D68:H68)</f>
-        <v>0</v>
-      </c>
-      <c r="J68" s="15"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="C78" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D78" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B78)</f>
+        <v>0</v>
+      </c>
+      <c r="E78" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B78)</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B78)</f>
+        <v>0</v>
+      </c>
+      <c r="G78" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B78)</f>
+        <v>0</v>
+      </c>
+      <c r="H78" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B78)</f>
+        <v>0</v>
+      </c>
+      <c r="I78" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J78" s="15"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
         <f>종합Sheet!A69</f>
         <v>66</v>
       </c>
-      <c r="B69" s="2" t="str">
+      <c r="B79" s="2" t="str">
         <f>종합Sheet!B69</f>
         <v>윤원택</v>
       </c>
-      <c r="C69" s="2">
-        <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B69)</f>
-        <v>0</v>
-      </c>
-      <c r="E69" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B69)</f>
-        <v>0</v>
-      </c>
-      <c r="F69" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B69)</f>
-        <v>0</v>
-      </c>
-      <c r="G69" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B69)</f>
-        <v>0</v>
-      </c>
-      <c r="H69" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B69)</f>
-        <v>0</v>
-      </c>
-      <c r="I69" s="14">
-        <f>SUM(D69:H69)</f>
-        <v>0</v>
-      </c>
-      <c r="J69" s="15"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="C79" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D79" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B79)</f>
+        <v>0</v>
+      </c>
+      <c r="E79" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B79)</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B79)</f>
+        <v>0</v>
+      </c>
+      <c r="G79" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B79)</f>
+        <v>0</v>
+      </c>
+      <c r="H79" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B79)</f>
+        <v>0</v>
+      </c>
+      <c r="I79" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J79" s="15"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
         <f>종합Sheet!A70</f>
         <v>67</v>
       </c>
-      <c r="B70" s="2" t="str">
+      <c r="B80" s="2" t="str">
         <f>종합Sheet!B70</f>
         <v>윤창현</v>
       </c>
-      <c r="C70" s="2">
-        <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D70" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B70)</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B70)</f>
-        <v>0</v>
-      </c>
-      <c r="F70" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B70)</f>
-        <v>0</v>
-      </c>
-      <c r="G70" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B70)</f>
-        <v>0</v>
-      </c>
-      <c r="H70" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B70)</f>
-        <v>0</v>
-      </c>
-      <c r="I70" s="14">
-        <f>SUM(D70:H70)</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="15"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <f>종합Sheet!A71</f>
-        <v>68</v>
-      </c>
-      <c r="B71" s="2" t="str">
-        <f>종합Sheet!B71</f>
-        <v>윤현기</v>
-      </c>
-      <c r="C71" s="2">
-        <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
-        <v>0.7</v>
-      </c>
-      <c r="D71" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B71)</f>
-        <v>2</v>
-      </c>
-      <c r="E71" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B71)</f>
-        <v>0</v>
-      </c>
-      <c r="F71" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B71)</f>
-        <v>1</v>
-      </c>
-      <c r="G71" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B71)</f>
-        <v>0</v>
-      </c>
-      <c r="H71" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B71)</f>
-        <v>0</v>
-      </c>
-      <c r="I71" s="14">
-        <f>SUM(D71:H71)</f>
-        <v>3</v>
-      </c>
-      <c r="J71" s="15"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="C80" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D80" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B80)</f>
+        <v>0</v>
+      </c>
+      <c r="E80" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B80)</f>
+        <v>0</v>
+      </c>
+      <c r="F80" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B80)</f>
+        <v>0</v>
+      </c>
+      <c r="G80" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B80)</f>
+        <v>0</v>
+      </c>
+      <c r="H80" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B80)</f>
+        <v>0</v>
+      </c>
+      <c r="I80" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J80" s="15"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
         <f>종합Sheet!A72</f>
         <v>69</v>
       </c>
-      <c r="B72" s="2" t="str">
+      <c r="B81" s="2" t="str">
         <f>종합Sheet!B72</f>
         <v>이경석</v>
       </c>
-      <c r="C72" s="2">
-        <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D72" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B72)</f>
-        <v>0</v>
-      </c>
-      <c r="E72" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B72)</f>
-        <v>0</v>
-      </c>
-      <c r="F72" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B72)</f>
-        <v>0</v>
-      </c>
-      <c r="G72" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B72)</f>
-        <v>0</v>
-      </c>
-      <c r="H72" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B72)</f>
-        <v>0</v>
-      </c>
-      <c r="I72" s="14">
-        <f>SUM(D72:H72)</f>
-        <v>0</v>
-      </c>
-      <c r="J72" s="15"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="C81" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D81" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B81)</f>
+        <v>0</v>
+      </c>
+      <c r="E81" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B81)</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B81)</f>
+        <v>0</v>
+      </c>
+      <c r="G81" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B81)</f>
+        <v>0</v>
+      </c>
+      <c r="H81" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B81)</f>
+        <v>0</v>
+      </c>
+      <c r="I81" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J81" s="15"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
         <f>종합Sheet!A73</f>
         <v>70</v>
       </c>
-      <c r="B73" s="2" t="str">
+      <c r="B82" s="2" t="str">
         <f>종합Sheet!B73</f>
         <v>이민재</v>
       </c>
-      <c r="C73" s="2">
-        <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B73)</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B73)</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B73)</f>
-        <v>0</v>
-      </c>
-      <c r="G73" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B73)</f>
-        <v>0</v>
-      </c>
-      <c r="H73" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B73)</f>
-        <v>0</v>
-      </c>
-      <c r="I73" s="14">
-        <f>SUM(D73:H73)</f>
-        <v>0</v>
-      </c>
-      <c r="J73" s="15"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <f>종합Sheet!A74</f>
-        <v>71</v>
-      </c>
-      <c r="B74" s="2" t="str">
-        <f>종합Sheet!B74</f>
-        <v>이병현</v>
-      </c>
-      <c r="C74" s="2">
-        <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
-        <v>0.2</v>
-      </c>
-      <c r="D74" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B74)</f>
-        <v>0</v>
-      </c>
-      <c r="E74" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B74)</f>
-        <v>1</v>
-      </c>
-      <c r="F74" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B74)</f>
-        <v>0</v>
-      </c>
-      <c r="G74" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B74)</f>
-        <v>0</v>
-      </c>
-      <c r="H74" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B74)</f>
-        <v>0</v>
-      </c>
-      <c r="I74" s="14">
-        <f>SUM(D74:H74)</f>
-        <v>1</v>
-      </c>
-      <c r="J74" s="15"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <f>종합Sheet!A75</f>
-        <v>72</v>
-      </c>
-      <c r="B75" s="2" t="str">
-        <f>종합Sheet!B75</f>
-        <v>이상민</v>
-      </c>
-      <c r="C75" s="2">
-        <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
-        <v>0.4</v>
-      </c>
-      <c r="D75" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B75)</f>
-        <v>1</v>
-      </c>
-      <c r="E75" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B75)</f>
-        <v>0</v>
-      </c>
-      <c r="F75" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B75)</f>
-        <v>0</v>
-      </c>
-      <c r="G75" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B75)</f>
-        <v>1</v>
-      </c>
-      <c r="H75" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B75)</f>
-        <v>0</v>
-      </c>
-      <c r="I75" s="14">
-        <f>SUM(D75:H75)</f>
-        <v>2</v>
-      </c>
-      <c r="J75" s="15"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="C82" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D82" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B82)</f>
+        <v>0</v>
+      </c>
+      <c r="E82" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B82)</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B82)</f>
+        <v>0</v>
+      </c>
+      <c r="G82" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B82)</f>
+        <v>0</v>
+      </c>
+      <c r="H82" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B82)</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J82" s="15"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
         <f>종합Sheet!A76</f>
         <v>73</v>
       </c>
-      <c r="B76" s="2" t="str">
+      <c r="B83" s="2" t="str">
         <f>종합Sheet!B76</f>
         <v>이상현</v>
       </c>
-      <c r="C76" s="2">
-        <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B76)</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B76)</f>
-        <v>0</v>
-      </c>
-      <c r="F76" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B76)</f>
-        <v>0</v>
-      </c>
-      <c r="G76" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B76)</f>
-        <v>0</v>
-      </c>
-      <c r="H76" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B76)</f>
-        <v>0</v>
-      </c>
-      <c r="I76" s="14">
-        <f>SUM(D76:H76)</f>
-        <v>0</v>
-      </c>
-      <c r="J76" s="15"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="C83" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D83" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B83)</f>
+        <v>0</v>
+      </c>
+      <c r="E83" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B83)</f>
+        <v>0</v>
+      </c>
+      <c r="F83" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B83)</f>
+        <v>0</v>
+      </c>
+      <c r="G83" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B83)</f>
+        <v>0</v>
+      </c>
+      <c r="H83" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B83)</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J83" s="15"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
         <f>종합Sheet!A77</f>
         <v>74</v>
       </c>
-      <c r="B77" s="2" t="str">
+      <c r="B84" s="2" t="str">
         <f>종합Sheet!B77</f>
         <v>이새샘</v>
       </c>
-      <c r="C77" s="2">
-        <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D77" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B77)</f>
-        <v>0</v>
-      </c>
-      <c r="E77" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B77)</f>
-        <v>0</v>
-      </c>
-      <c r="F77" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B77)</f>
-        <v>0</v>
-      </c>
-      <c r="G77" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B77)</f>
-        <v>0</v>
-      </c>
-      <c r="H77" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B77)</f>
-        <v>0</v>
-      </c>
-      <c r="I77" s="14">
-        <f>SUM(D77:H77)</f>
-        <v>0</v>
-      </c>
-      <c r="J77" s="15"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="C84" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D84" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B84)</f>
+        <v>0</v>
+      </c>
+      <c r="E84" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B84)</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B84)</f>
+        <v>0</v>
+      </c>
+      <c r="G84" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B84)</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B84)</f>
+        <v>0</v>
+      </c>
+      <c r="I84" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J84" s="15"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
         <f>종합Sheet!A78</f>
         <v>75</v>
       </c>
-      <c r="B78" s="2" t="str">
+      <c r="B85" s="2" t="str">
         <f>종합Sheet!B78</f>
         <v>이성관</v>
       </c>
-      <c r="C78" s="2">
-        <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D78" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B78)</f>
-        <v>0</v>
-      </c>
-      <c r="E78" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B78)</f>
-        <v>0</v>
-      </c>
-      <c r="F78" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B78)</f>
-        <v>0</v>
-      </c>
-      <c r="G78" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B78)</f>
-        <v>0</v>
-      </c>
-      <c r="H78" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B78)</f>
-        <v>0</v>
-      </c>
-      <c r="I78" s="14">
-        <f>SUM(D78:H78)</f>
-        <v>0</v>
-      </c>
-      <c r="J78" s="15"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="C85" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D85" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B85)</f>
+        <v>0</v>
+      </c>
+      <c r="E85" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B85)</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B85)</f>
+        <v>0</v>
+      </c>
+      <c r="G85" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B85)</f>
+        <v>0</v>
+      </c>
+      <c r="H85" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B85)</f>
+        <v>0</v>
+      </c>
+      <c r="I85" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J85" s="15"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
         <f>종합Sheet!A79</f>
         <v>76</v>
       </c>
-      <c r="B79" s="2" t="str">
+      <c r="B86" s="2" t="str">
         <f>종합Sheet!B79</f>
         <v>이승윤</v>
       </c>
-      <c r="C79" s="2">
-        <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D79" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B79)</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B79)</f>
-        <v>0</v>
-      </c>
-      <c r="F79" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B79)</f>
-        <v>0</v>
-      </c>
-      <c r="G79" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B79)</f>
-        <v>0</v>
-      </c>
-      <c r="H79" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B79)</f>
-        <v>0</v>
-      </c>
-      <c r="I79" s="14">
-        <f>SUM(D79:H79)</f>
-        <v>0</v>
-      </c>
-      <c r="J79" s="15"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="C86" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D86" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B86)</f>
+        <v>0</v>
+      </c>
+      <c r="E86" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B86)</f>
+        <v>0</v>
+      </c>
+      <c r="F86" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B86)</f>
+        <v>0</v>
+      </c>
+      <c r="G86" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B86)</f>
+        <v>0</v>
+      </c>
+      <c r="H86" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B86)</f>
+        <v>0</v>
+      </c>
+      <c r="I86" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J86" s="15"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
         <f>종합Sheet!A80</f>
         <v>77</v>
       </c>
-      <c r="B80" s="2" t="str">
+      <c r="B87" s="2" t="str">
         <f>종합Sheet!B80</f>
         <v>이연길</v>
       </c>
-      <c r="C80" s="2">
-        <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D80" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B80)</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B80)</f>
-        <v>0</v>
-      </c>
-      <c r="F80" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B80)</f>
-        <v>0</v>
-      </c>
-      <c r="G80" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B80)</f>
-        <v>0</v>
-      </c>
-      <c r="H80" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B80)</f>
-        <v>0</v>
-      </c>
-      <c r="I80" s="14">
-        <f>SUM(D80:H80)</f>
-        <v>0</v>
-      </c>
-      <c r="J80" s="15"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="C87" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D87" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B87)</f>
+        <v>0</v>
+      </c>
+      <c r="E87" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B87)</f>
+        <v>0</v>
+      </c>
+      <c r="F87" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B87)</f>
+        <v>0</v>
+      </c>
+      <c r="G87" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B87)</f>
+        <v>0</v>
+      </c>
+      <c r="H87" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B87)</f>
+        <v>0</v>
+      </c>
+      <c r="I87" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J87" s="15"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
         <f>종합Sheet!A81</f>
         <v>78</v>
       </c>
-      <c r="B81" s="2" t="str">
+      <c r="B88" s="2" t="str">
         <f>종합Sheet!B81</f>
         <v>이정범</v>
       </c>
-      <c r="C81" s="2">
-        <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D81" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B81)</f>
-        <v>0</v>
-      </c>
-      <c r="E81" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B81)</f>
-        <v>0</v>
-      </c>
-      <c r="F81" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B81)</f>
-        <v>0</v>
-      </c>
-      <c r="G81" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B81)</f>
-        <v>0</v>
-      </c>
-      <c r="H81" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B81)</f>
-        <v>0</v>
-      </c>
-      <c r="I81" s="14">
-        <f>SUM(D81:H81)</f>
-        <v>0</v>
-      </c>
-      <c r="J81" s="15"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="C88" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D88" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B88)</f>
+        <v>0</v>
+      </c>
+      <c r="E88" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B88)</f>
+        <v>0</v>
+      </c>
+      <c r="F88" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B88)</f>
+        <v>0</v>
+      </c>
+      <c r="G88" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B88)</f>
+        <v>0</v>
+      </c>
+      <c r="H88" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B88)</f>
+        <v>0</v>
+      </c>
+      <c r="I88" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J88" s="15"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
         <f>종합Sheet!A82</f>
         <v>79</v>
       </c>
-      <c r="B82" s="2" t="str">
+      <c r="B89" s="2" t="str">
         <f>종합Sheet!B82</f>
         <v>이종수</v>
       </c>
-      <c r="C82" s="2">
-        <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D82" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B82)</f>
-        <v>0</v>
-      </c>
-      <c r="E82" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B82)</f>
-        <v>0</v>
-      </c>
-      <c r="F82" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B82)</f>
-        <v>0</v>
-      </c>
-      <c r="G82" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B82)</f>
-        <v>0</v>
-      </c>
-      <c r="H82" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B82)</f>
-        <v>0</v>
-      </c>
-      <c r="I82" s="14">
-        <f>SUM(D82:H82)</f>
-        <v>0</v>
-      </c>
-      <c r="J82" s="15"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="C89" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D89" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B89)</f>
+        <v>0</v>
+      </c>
+      <c r="E89" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B89)</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B89)</f>
+        <v>0</v>
+      </c>
+      <c r="G89" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B89)</f>
+        <v>0</v>
+      </c>
+      <c r="H89" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B89)</f>
+        <v>0</v>
+      </c>
+      <c r="I89" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J89" s="15"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
         <f>종합Sheet!A83</f>
         <v>80</v>
       </c>
-      <c r="B83" s="2" t="str">
+      <c r="B90" s="2" t="str">
         <f>종합Sheet!B83</f>
         <v>이찬영</v>
       </c>
-      <c r="C83" s="2">
-        <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D83" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B83)</f>
-        <v>0</v>
-      </c>
-      <c r="E83" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B83)</f>
-        <v>0</v>
-      </c>
-      <c r="F83" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B83)</f>
-        <v>0</v>
-      </c>
-      <c r="G83" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B83)</f>
-        <v>0</v>
-      </c>
-      <c r="H83" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B83)</f>
-        <v>0</v>
-      </c>
-      <c r="I83" s="14">
-        <f>SUM(D83:H83)</f>
-        <v>0</v>
-      </c>
-      <c r="J83" s="15"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="C90" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D90" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B90)</f>
+        <v>0</v>
+      </c>
+      <c r="E90" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B90)</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B90)</f>
+        <v>0</v>
+      </c>
+      <c r="G90" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B90)</f>
+        <v>0</v>
+      </c>
+      <c r="H90" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B90)</f>
+        <v>0</v>
+      </c>
+      <c r="I90" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J90" s="15"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
         <f>종합Sheet!A84</f>
         <v>81</v>
       </c>
-      <c r="B84" s="2" t="str">
+      <c r="B91" s="2" t="str">
         <f>종합Sheet!B84</f>
         <v>이태한</v>
       </c>
-      <c r="C84" s="2">
-        <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D84" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B84)</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B84)</f>
-        <v>0</v>
-      </c>
-      <c r="F84" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B84)</f>
-        <v>0</v>
-      </c>
-      <c r="G84" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B84)</f>
-        <v>0</v>
-      </c>
-      <c r="H84" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B84)</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="14">
-        <f>SUM(D84:H84)</f>
-        <v>0</v>
-      </c>
-      <c r="J84" s="15"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="C91" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D91" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B91)</f>
+        <v>0</v>
+      </c>
+      <c r="E91" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B91)</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B91)</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B91)</f>
+        <v>0</v>
+      </c>
+      <c r="H91" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B91)</f>
+        <v>0</v>
+      </c>
+      <c r="I91" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J91" s="15"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
         <f>종합Sheet!A85</f>
         <v>82</v>
       </c>
-      <c r="B85" s="2" t="str">
+      <c r="B92" s="2" t="str">
         <f>종합Sheet!B85</f>
         <v>이호행</v>
       </c>
-      <c r="C85" s="2">
-        <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B85)</f>
-        <v>0</v>
-      </c>
-      <c r="E85" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B85)</f>
-        <v>0</v>
-      </c>
-      <c r="F85" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B85)</f>
-        <v>0</v>
-      </c>
-      <c r="G85" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B85)</f>
-        <v>0</v>
-      </c>
-      <c r="H85" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B85)</f>
-        <v>0</v>
-      </c>
-      <c r="I85" s="14">
-        <f>SUM(D85:H85)</f>
-        <v>0</v>
-      </c>
-      <c r="J85" s="15"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="C92" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D92" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B92)</f>
+        <v>0</v>
+      </c>
+      <c r="E92" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B92)</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B92)</f>
+        <v>0</v>
+      </c>
+      <c r="G92" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B92)</f>
+        <v>0</v>
+      </c>
+      <c r="H92" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B92)</f>
+        <v>0</v>
+      </c>
+      <c r="I92" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J92" s="15"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
         <f>종합Sheet!A86</f>
         <v>83</v>
       </c>
-      <c r="B86" s="2" t="str">
+      <c r="B93" s="2" t="str">
         <f>종합Sheet!B86</f>
         <v>임수철</v>
       </c>
-      <c r="C86" s="2">
-        <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D86" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B86)</f>
-        <v>0</v>
-      </c>
-      <c r="E86" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B86)</f>
-        <v>0</v>
-      </c>
-      <c r="F86" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B86)</f>
-        <v>0</v>
-      </c>
-      <c r="G86" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B86)</f>
-        <v>0</v>
-      </c>
-      <c r="H86" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B86)</f>
-        <v>0</v>
-      </c>
-      <c r="I86" s="14">
-        <f>SUM(D86:H86)</f>
-        <v>0</v>
-      </c>
-      <c r="J86" s="15"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="C93" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D93" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B93)</f>
+        <v>0</v>
+      </c>
+      <c r="E93" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B93)</f>
+        <v>0</v>
+      </c>
+      <c r="F93" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B93)</f>
+        <v>0</v>
+      </c>
+      <c r="G93" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B93)</f>
+        <v>0</v>
+      </c>
+      <c r="H93" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B93)</f>
+        <v>0</v>
+      </c>
+      <c r="I93" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J93" s="15"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
         <f>종합Sheet!A87</f>
         <v>84</v>
       </c>
-      <c r="B87" s="2" t="str">
+      <c r="B94" s="2" t="str">
         <f>종합Sheet!B87</f>
         <v>임태환</v>
       </c>
-      <c r="C87" s="2">
-        <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D87" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B87)</f>
-        <v>0</v>
-      </c>
-      <c r="E87" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B87)</f>
-        <v>0</v>
-      </c>
-      <c r="F87" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B87)</f>
-        <v>0</v>
-      </c>
-      <c r="G87" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B87)</f>
-        <v>0</v>
-      </c>
-      <c r="H87" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B87)</f>
-        <v>0</v>
-      </c>
-      <c r="I87" s="14">
-        <f>SUM(D87:H87)</f>
-        <v>0</v>
-      </c>
-      <c r="J87" s="15"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="C94" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D94" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B94)</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B94)</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B94)</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B94)</f>
+        <v>0</v>
+      </c>
+      <c r="H94" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B94)</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J94" s="15"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
         <f>종합Sheet!A88</f>
         <v>85</v>
       </c>
-      <c r="B88" s="2" t="str">
+      <c r="B95" s="2" t="str">
         <f>종합Sheet!B88</f>
         <v>장희도</v>
       </c>
-      <c r="C88" s="2">
-        <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D88" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B88)</f>
-        <v>0</v>
-      </c>
-      <c r="E88" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B88)</f>
-        <v>0</v>
-      </c>
-      <c r="F88" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B88)</f>
-        <v>0</v>
-      </c>
-      <c r="G88" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B88)</f>
-        <v>0</v>
-      </c>
-      <c r="H88" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B88)</f>
-        <v>0</v>
-      </c>
-      <c r="I88" s="14">
-        <f>SUM(D88:H88)</f>
-        <v>0</v>
-      </c>
-      <c r="J88" s="15"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="C95" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D95" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B95)</f>
+        <v>0</v>
+      </c>
+      <c r="E95" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B95)</f>
+        <v>0</v>
+      </c>
+      <c r="F95" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B95)</f>
+        <v>0</v>
+      </c>
+      <c r="G95" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B95)</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B95)</f>
+        <v>0</v>
+      </c>
+      <c r="I95" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J95" s="15"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
         <f>종합Sheet!A89</f>
         <v>86</v>
       </c>
-      <c r="B89" s="2" t="str">
+      <c r="B96" s="2" t="str">
         <f>종합Sheet!B89</f>
         <v>장희준</v>
       </c>
-      <c r="C89" s="2">
-        <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D89" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B89)</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B89)</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B89)</f>
-        <v>0</v>
-      </c>
-      <c r="G89" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B89)</f>
-        <v>0</v>
-      </c>
-      <c r="H89" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B89)</f>
-        <v>0</v>
-      </c>
-      <c r="I89" s="14">
-        <f>SUM(D89:H89)</f>
-        <v>0</v>
-      </c>
-      <c r="J89" s="15"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="C96" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D96" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B96)</f>
+        <v>0</v>
+      </c>
+      <c r="E96" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B96)</f>
+        <v>0</v>
+      </c>
+      <c r="F96" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B96)</f>
+        <v>0</v>
+      </c>
+      <c r="G96" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B96)</f>
+        <v>0</v>
+      </c>
+      <c r="H96" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B96)</f>
+        <v>0</v>
+      </c>
+      <c r="I96" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J96" s="15"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
         <f>종합Sheet!A90</f>
         <v>87</v>
       </c>
-      <c r="B90" s="2" t="str">
+      <c r="B97" s="2" t="str">
         <f>종합Sheet!B90</f>
         <v>전나현</v>
       </c>
-      <c r="C90" s="2">
-        <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D90" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B90)</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B90)</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B90)</f>
-        <v>0</v>
-      </c>
-      <c r="G90" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B90)</f>
-        <v>0</v>
-      </c>
-      <c r="H90" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B90)</f>
-        <v>0</v>
-      </c>
-      <c r="I90" s="14">
-        <f>SUM(D90:H90)</f>
-        <v>0</v>
-      </c>
-      <c r="J90" s="15"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="C97" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D97" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B97)</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B97)</f>
+        <v>0</v>
+      </c>
+      <c r="F97" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B97)</f>
+        <v>0</v>
+      </c>
+      <c r="G97" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B97)</f>
+        <v>0</v>
+      </c>
+      <c r="H97" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B97)</f>
+        <v>0</v>
+      </c>
+      <c r="I97" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J97" s="15"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
         <f>종합Sheet!A91</f>
         <v>88</v>
       </c>
-      <c r="B91" s="2" t="str">
+      <c r="B98" s="2" t="str">
         <f>종합Sheet!B91</f>
         <v>전성환</v>
       </c>
-      <c r="C91" s="2">
-        <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D91" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B91)</f>
-        <v>0</v>
-      </c>
-      <c r="E91" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B91)</f>
-        <v>0</v>
-      </c>
-      <c r="F91" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B91)</f>
-        <v>0</v>
-      </c>
-      <c r="G91" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B91)</f>
-        <v>0</v>
-      </c>
-      <c r="H91" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B91)</f>
-        <v>0</v>
-      </c>
-      <c r="I91" s="14">
-        <f>SUM(D91:H91)</f>
-        <v>0</v>
-      </c>
-      <c r="J91" s="15"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="C98" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D98" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B98)</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B98)</f>
+        <v>0</v>
+      </c>
+      <c r="F98" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B98)</f>
+        <v>0</v>
+      </c>
+      <c r="G98" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B98)</f>
+        <v>0</v>
+      </c>
+      <c r="H98" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B98)</f>
+        <v>0</v>
+      </c>
+      <c r="I98" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J98" s="15"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
         <f>종합Sheet!A92</f>
         <v>89</v>
       </c>
-      <c r="B92" s="2" t="str">
+      <c r="B99" s="2" t="str">
         <f>종합Sheet!B92</f>
         <v>전하늘</v>
       </c>
-      <c r="C92" s="2">
-        <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D92" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B92)</f>
-        <v>0</v>
-      </c>
-      <c r="E92" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B92)</f>
-        <v>0</v>
-      </c>
-      <c r="F92" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B92)</f>
-        <v>0</v>
-      </c>
-      <c r="G92" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B92)</f>
-        <v>0</v>
-      </c>
-      <c r="H92" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B92)</f>
-        <v>0</v>
-      </c>
-      <c r="I92" s="14">
-        <f>SUM(D92:H92)</f>
-        <v>0</v>
-      </c>
-      <c r="J92" s="15"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <f>종합Sheet!A93</f>
-        <v>90</v>
-      </c>
-      <c r="B93" s="2" t="str">
-        <f>종합Sheet!B93</f>
-        <v>정민수</v>
-      </c>
-      <c r="C93" s="2">
-        <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D93" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B93)</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B93)</f>
-        <v>0</v>
-      </c>
-      <c r="F93" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B93)</f>
-        <v>0</v>
-      </c>
-      <c r="G93" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B93)</f>
-        <v>3</v>
-      </c>
-      <c r="H93" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B93)</f>
-        <v>0</v>
-      </c>
-      <c r="I93" s="14">
-        <f>SUM(D93:H93)</f>
-        <v>3</v>
-      </c>
-      <c r="J93" s="15"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="C99" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D99" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B99)</f>
+        <v>0</v>
+      </c>
+      <c r="E99" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B99)</f>
+        <v>0</v>
+      </c>
+      <c r="F99" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B99)</f>
+        <v>0</v>
+      </c>
+      <c r="G99" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B99)</f>
+        <v>0</v>
+      </c>
+      <c r="H99" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B99)</f>
+        <v>0</v>
+      </c>
+      <c r="I99" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J99" s="15"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
         <f>종합Sheet!A94</f>
         <v>91</v>
       </c>
-      <c r="B94" s="2" t="str">
+      <c r="B100" s="2" t="str">
         <f>종합Sheet!B94</f>
         <v>정재명</v>
       </c>
-      <c r="C94" s="2">
-        <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D94" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B94)</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B94)</f>
-        <v>0</v>
-      </c>
-      <c r="F94" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B94)</f>
-        <v>0</v>
-      </c>
-      <c r="G94" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B94)</f>
-        <v>0</v>
-      </c>
-      <c r="H94" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B94)</f>
-        <v>0</v>
-      </c>
-      <c r="I94" s="14">
-        <f>SUM(D94:H94)</f>
-        <v>0</v>
-      </c>
-      <c r="J94" s="15"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <f>종합Sheet!A95</f>
-        <v>92</v>
-      </c>
-      <c r="B95" s="2" t="str">
-        <f>종합Sheet!B95</f>
-        <v>조진한</v>
-      </c>
-      <c r="C95" s="2">
-        <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
-        <v>0.8</v>
-      </c>
-      <c r="D95" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B95)</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B95)</f>
-        <v>1</v>
-      </c>
-      <c r="F95" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B95)</f>
-        <v>2</v>
-      </c>
-      <c r="G95" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B95)</f>
-        <v>0</v>
-      </c>
-      <c r="H95" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B95)</f>
-        <v>0</v>
-      </c>
-      <c r="I95" s="14">
-        <f>SUM(D95:H95)</f>
-        <v>3</v>
-      </c>
-      <c r="J95" s="15"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <f>종합Sheet!A96</f>
-        <v>93</v>
-      </c>
-      <c r="B96" s="2" t="str">
-        <f>종합Sheet!B96</f>
-        <v>조현우</v>
-      </c>
-      <c r="C96" s="2">
-        <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
-        <v>0.4</v>
-      </c>
-      <c r="D96" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B96)</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B96)</f>
-        <v>0</v>
-      </c>
-      <c r="F96" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B96)</f>
-        <v>0</v>
-      </c>
-      <c r="G96" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B96)</f>
-        <v>2</v>
-      </c>
-      <c r="H96" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B96)</f>
-        <v>0</v>
-      </c>
-      <c r="I96" s="14">
-        <f>SUM(D96:H96)</f>
-        <v>2</v>
-      </c>
-      <c r="J96" s="15"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <f>종합Sheet!A97</f>
-        <v>94</v>
-      </c>
-      <c r="B97" s="2" t="str">
-        <f>종합Sheet!B97</f>
-        <v>차승원</v>
-      </c>
-      <c r="C97" s="2">
-        <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
-        <v>0.8</v>
-      </c>
-      <c r="D97" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B97)</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B97)</f>
-        <v>0</v>
-      </c>
-      <c r="F97" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B97)</f>
-        <v>0</v>
-      </c>
-      <c r="G97" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B97)</f>
-        <v>4</v>
-      </c>
-      <c r="H97" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B97)</f>
-        <v>0</v>
-      </c>
-      <c r="I97" s="14">
-        <f>SUM(D97:H97)</f>
-        <v>4</v>
-      </c>
-      <c r="J97" s="15"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="C100" s="2">
+        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <v>0</v>
+      </c>
+      <c r="D100" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B100)</f>
+        <v>0</v>
+      </c>
+      <c r="E100" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B100)</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B100)</f>
+        <v>0</v>
+      </c>
+      <c r="G100" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B100)</f>
+        <v>0</v>
+      </c>
+      <c r="H100" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B100)</f>
+        <v>0</v>
+      </c>
+      <c r="I100" s="14">
+        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
+        <v>0</v>
+      </c>
+      <c r="J100" s="15"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
         <f>종합Sheet!A98</f>
         <v>95</v>
       </c>
-      <c r="B98" s="2" t="str">
+      <c r="B101" s="2" t="str">
         <f>종합Sheet!B98</f>
         <v>최령창</v>
       </c>
-      <c r="C98" s="2">
-        <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D98" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B98)</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B98)</f>
-        <v>0</v>
-      </c>
-      <c r="F98" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B98)</f>
-        <v>0</v>
-      </c>
-      <c r="G98" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B98)</f>
-        <v>0</v>
-      </c>
-      <c r="H98" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B98)</f>
-        <v>0</v>
-      </c>
-      <c r="I98" s="14">
-        <f>SUM(D98:H98)</f>
-        <v>0</v>
-      </c>
-      <c r="J98" s="15"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="C101" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="D101" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B101)</f>
+        <v>0</v>
+      </c>
+      <c r="E101" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B101)</f>
+        <v>0</v>
+      </c>
+      <c r="F101" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B101)</f>
+        <v>0</v>
+      </c>
+      <c r="G101" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B101)</f>
+        <v>0</v>
+      </c>
+      <c r="H101" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B101)</f>
+        <v>0</v>
+      </c>
+      <c r="I101" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J101" s="15"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
         <f>종합Sheet!A99</f>
         <v>96</v>
       </c>
-      <c r="B99" s="2" t="str">
+      <c r="B102" s="2" t="str">
         <f>종합Sheet!B99</f>
         <v>최승훈</v>
       </c>
-      <c r="C99" s="2">
-        <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D99" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B99)</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B99)</f>
-        <v>0</v>
-      </c>
-      <c r="F99" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B99)</f>
-        <v>0</v>
-      </c>
-      <c r="G99" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B99)</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B99)</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="14">
-        <f>SUM(D99:H99)</f>
-        <v>0</v>
-      </c>
-      <c r="J99" s="15"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
-        <f>종합Sheet!A100</f>
-        <v>97</v>
-      </c>
-      <c r="B100" s="2" t="str">
-        <f>종합Sheet!B100</f>
-        <v>한상규</v>
-      </c>
-      <c r="C100" s="2">
-        <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D100" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B100)</f>
-        <v>1</v>
-      </c>
-      <c r="E100" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B100)</f>
-        <v>0</v>
-      </c>
-      <c r="F100" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B100)</f>
-        <v>0</v>
-      </c>
-      <c r="G100" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B100)</f>
-        <v>2</v>
-      </c>
-      <c r="H100" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B100)</f>
-        <v>0</v>
-      </c>
-      <c r="I100" s="14">
-        <f>SUM(D100:H100)</f>
-        <v>3</v>
-      </c>
-      <c r="J100" s="15"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="C102" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="D102" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B102)</f>
+        <v>0</v>
+      </c>
+      <c r="E102" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B102)</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B102)</f>
+        <v>0</v>
+      </c>
+      <c r="G102" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B102)</f>
+        <v>0</v>
+      </c>
+      <c r="H102" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B102)</f>
+        <v>0</v>
+      </c>
+      <c r="I102" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J102" s="15"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
         <f>종합Sheet!A101</f>
         <v>98</v>
       </c>
-      <c r="B101" s="2" t="str">
+      <c r="B103" s="2" t="str">
         <f>종합Sheet!B101</f>
         <v>한의현</v>
       </c>
-      <c r="C101" s="2">
-        <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D101" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B101)</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B101)</f>
-        <v>0</v>
-      </c>
-      <c r="F101" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B101)</f>
-        <v>0</v>
-      </c>
-      <c r="G101" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B101)</f>
-        <v>0</v>
-      </c>
-      <c r="H101" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B101)</f>
-        <v>0</v>
-      </c>
-      <c r="I101" s="14">
-        <f>SUM(D101:H101)</f>
-        <v>0</v>
-      </c>
-      <c r="J101" s="15"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
+      <c r="C103" s="2">
+        <f t="shared" si="11"/>
+        <v>0.6</v>
+      </c>
+      <c r="D103" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
+        <v>0</v>
+      </c>
+      <c r="E103" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B103)</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B103)</f>
+        <v>2</v>
+      </c>
+      <c r="G103" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B103)</f>
+        <v>0</v>
+      </c>
+      <c r="H103" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B103)</f>
+        <v>0</v>
+      </c>
+      <c r="I103" s="14">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="J103" s="15"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
         <f>종합Sheet!A102</f>
         <v>99</v>
       </c>
-      <c r="B102" s="2" t="str">
+      <c r="B104" s="2" t="str">
         <f>종합Sheet!B102</f>
         <v>한중희</v>
       </c>
-      <c r="C102" s="2">
-        <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D102" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B102)</f>
-        <v>0</v>
-      </c>
-      <c r="E102" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B102)</f>
-        <v>0</v>
-      </c>
-      <c r="F102" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B102)</f>
-        <v>0</v>
-      </c>
-      <c r="G102" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B102)</f>
-        <v>0</v>
-      </c>
-      <c r="H102" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B102)</f>
-        <v>0</v>
-      </c>
-      <c r="I102" s="14">
-        <f>SUM(D102:H102)</f>
-        <v>0</v>
-      </c>
-      <c r="J102" s="15"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="C104" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="D104" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B104)</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B104)</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B104)</f>
+        <v>0</v>
+      </c>
+      <c r="G104" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B104)</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B104)</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J104" s="15"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
         <f>종합Sheet!A103</f>
         <v>100</v>
       </c>
-      <c r="B103" s="2" t="str">
+      <c r="B105" s="2" t="str">
         <f>종합Sheet!B103</f>
         <v>허동혁</v>
       </c>
-      <c r="C103" s="2">
-        <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D103" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
-        <v>0</v>
-      </c>
-      <c r="E103" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B103)</f>
-        <v>0</v>
-      </c>
-      <c r="F103" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B103)</f>
-        <v>0</v>
-      </c>
-      <c r="G103" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B103)</f>
-        <v>0</v>
-      </c>
-      <c r="H103" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B103)</f>
-        <v>0</v>
-      </c>
-      <c r="I103" s="14">
-        <f>SUM(D103:H103)</f>
-        <v>0</v>
-      </c>
-      <c r="J103" s="15"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="C105" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="D105" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B105)</f>
+        <v>0</v>
+      </c>
+      <c r="E105" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B105)</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B105)</f>
+        <v>0</v>
+      </c>
+      <c r="G105" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B105)</f>
+        <v>0</v>
+      </c>
+      <c r="H105" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B105)</f>
+        <v>0</v>
+      </c>
+      <c r="I105" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
         <f>종합Sheet!A104</f>
         <v>101</v>
       </c>
-      <c r="B104" s="2" t="str">
+      <c r="B106" s="2" t="str">
         <f>종합Sheet!B104</f>
         <v>홍석준</v>
       </c>
-      <c r="C104" s="2">
-        <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
-        <v>0</v>
-      </c>
-      <c r="D104" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B104)</f>
-        <v>0</v>
-      </c>
-      <c r="E104" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B104)</f>
-        <v>0</v>
-      </c>
-      <c r="F104" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B104)</f>
-        <v>0</v>
-      </c>
-      <c r="G104" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B104)</f>
-        <v>0</v>
-      </c>
-      <c r="H104" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B104)</f>
-        <v>0</v>
-      </c>
-      <c r="I104" s="14">
-        <f>SUM(D104:H104)</f>
-        <v>0</v>
-      </c>
-      <c r="J104" s="15"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <f>종합Sheet!A105</f>
-        <v>102</v>
-      </c>
-      <c r="B105" s="2" t="str">
-        <f>종합Sheet!B105</f>
-        <v>홍현석</v>
-      </c>
-      <c r="C105" s="2">
-        <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
-        <v>0.2</v>
-      </c>
-      <c r="D105" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B105)</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B105)</f>
-        <v>0</v>
-      </c>
-      <c r="F105" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B105)</f>
-        <v>0</v>
-      </c>
-      <c r="G105" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B105)</f>
-        <v>1</v>
-      </c>
-      <c r="H105" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B105)</f>
-        <v>0</v>
-      </c>
-      <c r="I105" s="14">
-        <f>SUM(D105:H105)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
-        <f>종합Sheet!A106</f>
-        <v>103</v>
-      </c>
-      <c r="B106" s="2" t="str">
-        <f>종합Sheet!B106</f>
-        <v>황석원</v>
-      </c>
       <c r="C106" s="2">
-        <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
-        <v>0.4</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="D106" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B106)</f>
@@ -20175,15 +20181,15 @@
       </c>
       <c r="G106" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B106)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H106" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B106)</f>
         <v>0</v>
       </c>
       <c r="I106" s="14">
-        <f>SUM(D106:H106)</f>
-        <v>2</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -20196,7 +20202,7 @@
         <v>황재순</v>
       </c>
       <c r="C107" s="2">
-        <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D107" s="14">
@@ -20220,7 +20226,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f>SUM(D107:H107)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -20234,7 +20240,7 @@
         <v>황철우</v>
       </c>
       <c r="C108" s="2">
-        <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D108" s="14">
@@ -20258,7 +20264,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f>SUM(D108:H108)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -20272,7 +20278,7 @@
         <v>김민성</v>
       </c>
       <c r="C109" s="2">
-        <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D109" s="14">
@@ -20296,7 +20302,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="14">
-        <f>SUM(D109:H109)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -20310,7 +20316,7 @@
         <v>송명섭</v>
       </c>
       <c r="C110" s="2">
-        <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D110" s="14">
@@ -20334,7 +20340,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="14">
-        <f>SUM(D110:H110)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -20348,7 +20354,7 @@
         <v>최경영</v>
       </c>
       <c r="C111" s="2">
-        <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D111" s="14">
@@ -20372,7 +20378,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f>SUM(D111:H111)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -20386,7 +20392,7 @@
         <v>김민찬</v>
       </c>
       <c r="C112" s="2">
-        <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D112" s="14">
@@ -20410,7 +20416,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f>SUM(D112:H112)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -20424,7 +20430,7 @@
         <v>김현우</v>
       </c>
       <c r="C113" s="2">
-        <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D113" s="14">
@@ -20448,7 +20454,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="14">
-        <f>SUM(D113:H113)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -20462,7 +20468,7 @@
         <v>류서진</v>
       </c>
       <c r="C114" s="2">
-        <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D114" s="14">
@@ -20486,14 +20492,14 @@
         <v>0</v>
       </c>
       <c r="I114" s="14">
-        <f>SUM(D114:H114)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I114">
-      <sortCondition ref="A3"/>
+      <sortCondition descending="1" ref="C3"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -20524,28 +20530,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:AA18"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.796875" style="1"/>
-    <col min="3" max="3" width="25.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.69921875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.69921875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.69921875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.69921875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.69921875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.69921875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.69921875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.69921875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.69921875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4.69921875" style="1" customWidth="1"/>
-    <col min="15" max="16" width="8.796875" style="1"/>
+    <col min="1" max="2" width="8.83203125" style="1"/>
+    <col min="3" max="3" width="25.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.6640625" style="1" customWidth="1"/>
+    <col min="15" max="16" width="8.83203125" style="1"/>
     <col min="17" max="17" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="27" width="8.796875" style="1"/>
+    <col min="18" max="18" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="27" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
@@ -21200,7 +21206,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="30" t="s">
         <v>195</v>
       </c>
@@ -21229,26 +21235,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F962A1E7-878E-4BD1-AA56-2AF3E69AA6A2}">
   <dimension ref="A2:V19"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.796875" style="1"/>
-    <col min="4" max="4" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.19921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.796875" style="1"/>
-    <col min="7" max="8" width="10.69921875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.796875" style="38"/>
-    <col min="10" max="10" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.19921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.796875" style="1"/>
-    <col min="13" max="13" width="8.796875" style="38"/>
-    <col min="14" max="15" width="8.796875" style="1"/>
-    <col min="16" max="16" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.19921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.796875" style="1"/>
-    <col min="19" max="19" width="8.796875" style="38"/>
-    <col min="20" max="20" width="8.796875" style="1"/>
-    <col min="21" max="22" width="8.796875" style="38"/>
+    <col min="2" max="3" width="8.83203125" style="1"/>
+    <col min="4" max="4" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="1"/>
+    <col min="7" max="8" width="10.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" style="38"/>
+    <col min="10" max="10" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" style="1"/>
+    <col min="13" max="13" width="8.83203125" style="38"/>
+    <col min="14" max="15" width="8.83203125" style="1"/>
+    <col min="16" max="16" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.83203125" style="1"/>
+    <col min="19" max="19" width="8.83203125" style="38"/>
+    <col min="20" max="20" width="8.83203125" style="1"/>
+    <col min="21" max="22" width="8.83203125" style="38"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -21327,7 +21333,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>152</v>
       </c>
@@ -22043,22 +22049,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94658DBD-49BC-431D-8A71-74E2FC7A3D82}">
   <dimension ref="A2:U30"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="1"/>
-    <col min="2" max="2" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.19921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" style="1"/>
-    <col min="5" max="7" width="10.69921875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" style="38"/>
-    <col min="9" max="9" width="10.09765625" style="54" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.19921875" style="68" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.796875" style="54"/>
-    <col min="12" max="12" width="10.69921875" style="54" customWidth="1"/>
-    <col min="14" max="14" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.19921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.796875" style="1"/>
-    <col min="17" max="19" width="10.69921875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="1"/>
+    <col min="5" max="7" width="10.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="38"/>
+    <col min="9" max="9" width="10.08203125" style="54" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.1640625" style="68" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" style="54"/>
+    <col min="12" max="12" width="10.6640625" style="54" customWidth="1"/>
+    <col min="14" max="14" width="10.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" style="1"/>
+    <col min="17" max="19" width="10.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.25">
@@ -22124,7 +22130,7 @@
       </c>
       <c r="G3" s="62">
         <f>VLOOKUP(F3,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>2.2999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="I3" s="95" t="s">
         <v>335</v>
@@ -22156,7 +22162,7 @@
       </c>
       <c r="S3" s="64">
         <f>VLOOKUP(R3,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>2.2999999999999998</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
@@ -22204,7 +22210,7 @@
       </c>
       <c r="S4" s="64">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -22224,7 +22230,7 @@
       </c>
       <c r="G5" s="62">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="I5" s="96"/>
       <c r="J5" s="67">
@@ -22252,7 +22258,7 @@
       </c>
       <c r="S5" s="64">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>5.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -22300,7 +22306,7 @@
       </c>
       <c r="S6" s="72">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -22320,7 +22326,7 @@
       </c>
       <c r="G7" s="62">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I7" s="97"/>
       <c r="J7" s="67">
@@ -22348,7 +22354,7 @@
       </c>
       <c r="S7" s="72">
         <f>VLOOKUP(R7,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
@@ -22368,7 +22374,7 @@
       </c>
       <c r="G8" s="64">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="N8" s="86"/>
       <c r="O8" s="49">
@@ -22454,7 +22460,7 @@
       </c>
       <c r="G10" s="62">
         <f>VLOOKUP(F10,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="I10" s="95" t="s">
         <v>336</v>
@@ -22504,7 +22510,7 @@
       </c>
       <c r="G11" s="62">
         <f>VLOOKUP(F11,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="I11" s="96"/>
       <c r="J11" s="67">
@@ -22532,7 +22538,7 @@
       </c>
       <c r="S11" s="72">
         <f>VLOOKUP(R11,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
@@ -22552,7 +22558,7 @@
       </c>
       <c r="G12" s="62">
         <f>VLOOKUP(F12,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I12" s="96"/>
       <c r="J12" s="67">
@@ -22600,7 +22606,7 @@
       </c>
       <c r="G13" s="62">
         <f>VLOOKUP(F13,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="67">
@@ -22636,7 +22642,7 @@
       </c>
       <c r="G14" s="62">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I14" s="97"/>
       <c r="J14" s="67">
@@ -22672,7 +22678,7 @@
       </c>
       <c r="G15" s="64">
         <f>VLOOKUP(F15,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N15"/>
       <c r="O15"/>
@@ -22698,7 +22704,7 @@
       </c>
       <c r="G16" s="64">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="H16" s="38"/>
       <c r="I16" s="99" t="s">
@@ -22715,7 +22721,7 @@
       <c r="N16"/>
       <c r="O16"/>
     </row>
-    <row r="17" spans="2:21" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="87"/>
       <c r="C17" s="49">
         <v>15</v>
@@ -22727,7 +22733,7 @@
       </c>
       <c r="G17" s="64">
         <f>VLOOKUP(F17,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="38"/>
       <c r="I17" s="95" t="s">
@@ -22784,7 +22790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="95" t="s">
         <v>341</v>
       </c>
@@ -22969,21 +22975,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CT37"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="6" width="5.8984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="4.3984375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.8984375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.19921875" style="1" customWidth="1"/>
-    <col min="10" max="30" width="5.19921875" style="1" customWidth="1"/>
-    <col min="31" max="33" width="5.19921875" style="3" customWidth="1"/>
-    <col min="34" max="56" width="5.19921875" style="1" customWidth="1"/>
-    <col min="57" max="82" width="4.796875" style="1" customWidth="1"/>
-    <col min="83" max="90" width="8.8984375" style="1"/>
-    <col min="91" max="98" width="8.8984375" style="3"/>
+    <col min="4" max="6" width="5.9140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.4140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.1640625" style="1" customWidth="1"/>
+    <col min="10" max="30" width="5.1640625" style="1" customWidth="1"/>
+    <col min="31" max="33" width="5.1640625" style="3" customWidth="1"/>
+    <col min="34" max="56" width="5.1640625" style="1" customWidth="1"/>
+    <col min="57" max="82" width="4.83203125" style="1" customWidth="1"/>
+    <col min="83" max="90" width="8.9140625" style="1"/>
+    <col min="91" max="98" width="8.9140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:82" x14ac:dyDescent="0.25">
@@ -23496,11 +23502,11 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ref="G4:G37" si="2">RANK(H4,$H$4:$H$37,0)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>3.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4:I28" si="3">(COUNTIF(J4:CD4,"출전")*1)</f>
@@ -23610,11 +23616,11 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6">
         <f t="shared" si="3"/>
@@ -23728,11 +23734,11 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="6">
         <f t="shared" si="3"/>
@@ -23844,7 +23850,7 @@
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C9</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I7" s="6">
         <f t="shared" si="3"/>
@@ -23952,7 +23958,7 @@
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C10</f>
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I8" s="6">
         <f t="shared" si="3"/>
@@ -24070,7 +24076,7 @@
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C15</f>
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I9" s="6">
         <f t="shared" si="3"/>
@@ -24184,7 +24190,7 @@
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C16</f>
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="3"/>
@@ -24298,7 +24304,7 @@
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C17</f>
-        <v>4.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="3"/>
@@ -24414,7 +24420,7 @@
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C18</f>
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I12" s="6">
         <f t="shared" si="3"/>
@@ -24528,7 +24534,7 @@
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C22</f>
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I13" s="6">
         <f t="shared" si="3"/>
@@ -24636,11 +24642,11 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C23</f>
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I14" s="6">
         <f t="shared" si="3"/>
@@ -24849,7 +24855,7 @@
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C25</f>
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="3"/>
@@ -24963,11 +24969,11 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C26</f>
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="3"/>
@@ -25073,7 +25079,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C29</f>
@@ -25191,7 +25197,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C34</f>
@@ -25309,7 +25315,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C40</f>
@@ -25421,7 +25427,7 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C44</f>
@@ -25632,7 +25638,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C49</f>
@@ -25748,7 +25754,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C57</f>
@@ -25860,7 +25866,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C59</f>
@@ -25974,7 +25980,7 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C60</f>
@@ -26090,7 +26096,7 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C62</f>
@@ -26204,7 +26210,7 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C63</f>
@@ -26318,7 +26324,7 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" ref="G29" si="4">RANK(H29,$H$4:$H$37,0)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C64</f>
@@ -26428,7 +26434,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C69</f>
@@ -26542,7 +26548,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C72</f>
@@ -26652,7 +26658,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C79</f>
@@ -26768,7 +26774,7 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C83</f>
@@ -26878,7 +26884,7 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C90</f>
@@ -26988,11 +26994,11 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C97</f>
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="6"/>
@@ -27106,7 +27112,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C102</f>
@@ -27220,7 +27226,7 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C104</f>
@@ -27343,12 +27349,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200146DD-3190-4B01-99D0-3AC5A9404CDF}">
   <dimension ref="A2:V26"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.8984375" style="1" customWidth="1"/>
-    <col min="5" max="22" width="5.796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.9140625" style="1" customWidth="1"/>
+    <col min="5" max="22" width="5.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -27356,7 +27362,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="11">
         <v>44985</v>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Han\codes\kcc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2B2B9F-0C5A-48DA-8C47-99FB3E118D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B99574-741D-41AE-9FEE-F076AF182266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="606" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="370">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -2167,10 +2167,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2179,20 +2179,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>3.0666666666666669</v>
+        <v>3.0444444444444443</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P2" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="0"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G5" s="2">
         <f>RANK(H5,$H$4:$H$122,0)</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H39" s="6">
         <f>I39+개인기록Sheet!C39</f>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H40" s="6">
         <f>I40+개인기록Sheet!C40</f>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
@@ -9937,7 +9937,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" ref="G71:G114" si="6">RANK(H71,$H$4:$H$122,0)</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="G90" s="2">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
@@ -13501,15 +13501,15 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I101" s="6">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>355</v>
@@ -13523,9 +13523,7 @@
       <c r="O101" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="P101" s="2" t="s">
-        <v>205</v>
-      </c>
+      <c r="P101" s="2"/>
       <c r="Q101" s="2"/>
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
@@ -13612,7 +13610,7 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
@@ -13719,11 +13717,11 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="I103" s="6">
         <f t="shared" si="7"/>
@@ -13929,7 +13927,7 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
@@ -14036,7 +14034,7 @@
       </c>
       <c r="G106" s="2">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
@@ -15586,12 +15584,8 @@
       <c r="N20" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="O20" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="P20" s="20" t="s">
-        <v>230</v>
-      </c>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
       <c r="Q20" s="9" t="s">
         <v>137</v>
       </c>
@@ -15657,6 +15651,29 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:V13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="D20:D21"/>
@@ -15666,29 +15683,6 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:V13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -19931,7 +19925,7 @@
         <v>정재명</v>
       </c>
       <c r="C100" s="2">
-        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f t="shared" ref="C100:C114" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
         <v>0</v>
       </c>
       <c r="D100" s="14">
@@ -19955,7 +19949,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
+        <f t="shared" ref="I100:I114" si="12">SUM(D100:H100)</f>
         <v>0</v>
       </c>
       <c r="J100" s="15"/>
@@ -20049,7 +20043,7 @@
       </c>
       <c r="C103" s="2">
         <f t="shared" si="11"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D103" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
@@ -20061,7 +20055,7 @@
       </c>
       <c r="F103" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B103)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G103" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B103)</f>
@@ -20073,7 +20067,7 @@
       </c>
       <c r="I103" s="14">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J103" s="15"/>
     </row>
@@ -22084,10 +22078,10 @@
       <c r="G2" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I2" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="99"/>
+      <c r="J2" s="94"/>
       <c r="K2" s="66" t="s">
         <v>277</v>
       </c>
@@ -22112,7 +22106,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="93" t="s">
         <v>340</v>
       </c>
       <c r="C3" s="73">
@@ -22328,7 +22322,7 @@
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$114,7,0)</f>
         <v>5</v>
       </c>
-      <c r="I7" s="97"/>
+      <c r="I7" s="98"/>
       <c r="J7" s="67">
         <v>5</v>
       </c>
@@ -22414,10 +22408,10 @@
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$114,7,0)</f>
         <v>1</v>
       </c>
-      <c r="I9" s="99" t="s">
+      <c r="I9" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="J9" s="99"/>
+      <c r="J9" s="94"/>
       <c r="K9" s="66" t="s">
         <v>277</v>
       </c>
@@ -22538,7 +22532,7 @@
       </c>
       <c r="S11" s="72">
         <f>VLOOKUP(R11,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
@@ -22570,7 +22564,7 @@
       <c r="L12" s="66">
         <v>8</v>
       </c>
-      <c r="N12" s="98"/>
+      <c r="N12" s="101"/>
       <c r="O12" s="49">
         <v>10</v>
       </c>
@@ -22644,7 +22638,7 @@
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$114,7,0)</f>
         <v>5</v>
       </c>
-      <c r="I14" s="97"/>
+      <c r="I14" s="98"/>
       <c r="J14" s="67">
         <v>5</v>
       </c>
@@ -22707,10 +22701,10 @@
         <v>3</v>
       </c>
       <c r="H16" s="38"/>
-      <c r="I16" s="99" t="s">
+      <c r="I16" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="J16" s="99"/>
+      <c r="J16" s="94"/>
       <c r="K16" s="66" t="s">
         <v>277</v>
       </c>
@@ -22733,7 +22727,7 @@
       </c>
       <c r="G17" s="64">
         <f>VLOOKUP(F17,종합Sheet!$B$3:$I$114,7,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" s="38"/>
       <c r="I17" s="95" t="s">
@@ -22771,10 +22765,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="C19" s="99"/>
+      <c r="C19" s="94"/>
       <c r="D19" s="66" t="s">
         <v>277</v>
       </c>
@@ -22825,7 +22819,7 @@
       <c r="E21" s="66" t="s">
         <v>343</v>
       </c>
-      <c r="I21" s="97"/>
+      <c r="I21" s="98"/>
       <c r="J21" s="67">
         <v>5</v>
       </c>
@@ -22837,7 +22831,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="101"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="67">
         <v>3</v>
       </c>
@@ -22849,10 +22843,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="93" t="s">
+      <c r="I23" s="99" t="s">
         <v>249</v>
       </c>
-      <c r="J23" s="94"/>
+      <c r="J23" s="100"/>
       <c r="K23" s="66" t="s">
         <v>277</v>
       </c>
@@ -22935,7 +22929,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="97"/>
+      <c r="I30" s="98"/>
       <c r="J30" s="67">
         <v>7</v>
       </c>
@@ -22948,12 +22942,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -22962,6 +22950,12 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inhyu\OneDrive\바탕 화면\김인혁\김인혁_청년축구단\1. 출석부\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECFB0F5-3BE5-4DC7-887A-6239B9DF82F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC05B59-DF77-4DED-AE4B-34DB9FEA98F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2266,10 +2266,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2278,20 +2278,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -18673,7 +18673,7 @@
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B77" s="11">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>383</v>
@@ -18999,15 +18999,94 @@
     </row>
   </sheetData>
   <mergeCells count="121">
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
     <mergeCell ref="Q77:V77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -19032,94 +19111,15 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="M77:P77"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -19255,7 +19255,7 @@
         <v>김인혁</v>
       </c>
       <c r="C4" s="2">
-        <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
+        <f t="shared" ref="C4:C35" si="0">((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="D4" s="14">
@@ -19279,7 +19279,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="14">
-        <f>SUM(D4:H4)</f>
+        <f t="shared" ref="I4:I35" si="1">SUM(D4:H4)</f>
         <v>6</v>
       </c>
       <c r="J4" s="15"/>
@@ -19290,35 +19290,35 @@
         <v>224</v>
       </c>
       <c r="M4" s="21">
-        <f t="shared" ref="M4:M15" si="0">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
+        <f t="shared" ref="M4:M15" si="2">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
         <v>10</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>53</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O13" si="1">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
+        <f t="shared" ref="O4:O13" si="3">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
         <v>6</v>
       </c>
       <c r="P4" s="34" t="s">
         <v>222</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q13" si="2">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
+        <f t="shared" ref="Q4:Q13" si="4">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
         <v>6</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>325</v>
       </c>
       <c r="S4" s="55">
-        <f t="shared" ref="S4:S15" si="3">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
+        <f t="shared" ref="S4:S15" si="5">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
         <v>9</v>
       </c>
       <c r="T4" s="36" t="s">
         <v>229</v>
       </c>
       <c r="U4" s="56">
-        <f t="shared" ref="U4:U15" si="4">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
+        <f t="shared" ref="U4:U15" si="6">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
         <v>6</v>
       </c>
     </row>
@@ -19332,7 +19332,7 @@
         <v>신재경</v>
       </c>
       <c r="C5" s="2">
-        <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D5" s="14">
@@ -19356,7 +19356,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="14">
-        <f>SUM(D5:H5)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J5" s="15"/>
@@ -19367,35 +19367,35 @@
         <v>222</v>
       </c>
       <c r="M5" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="N5" s="33" t="s">
         <v>50</v>
       </c>
       <c r="O5" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P5" s="34" t="s">
         <v>53</v>
       </c>
       <c r="Q5" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>231</v>
       </c>
       <c r="S5" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="T5" s="36" t="s">
         <v>42</v>
       </c>
       <c r="U5" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
         <v>정효태</v>
       </c>
       <c r="C6" s="2">
-        <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D6" s="14">
@@ -19433,7 +19433,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="14">
-        <f>SUM(D6:H6)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J6" s="15"/>
@@ -19444,35 +19444,35 @@
         <v>354</v>
       </c>
       <c r="M6" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="N6" s="33" t="s">
         <v>354</v>
       </c>
       <c r="O6" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P6" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Q6" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="R6" s="35" t="s">
         <v>365</v>
       </c>
       <c r="S6" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="T6" s="36" t="s">
         <v>357</v>
       </c>
       <c r="U6" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -19486,7 +19486,7 @@
         <v>이승민</v>
       </c>
       <c r="C7" s="2">
-        <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7" s="14">
@@ -19510,7 +19510,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f>SUM(D7:H7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J7" s="15"/>
@@ -19521,35 +19521,35 @@
         <v>361</v>
       </c>
       <c r="M7" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N7" s="33" t="s">
         <v>225</v>
       </c>
       <c r="O7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P7" s="34" t="s">
         <v>299</v>
       </c>
       <c r="Q7" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R7" s="35" t="s">
         <v>357</v>
       </c>
       <c r="S7" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T7" s="36" t="s">
         <v>222</v>
       </c>
       <c r="U7" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19563,7 +19563,7 @@
         <v>이정석</v>
       </c>
       <c r="C8" s="2">
-        <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D8" s="14">
@@ -19587,7 +19587,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f>SUM(D8:H8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="15"/>
@@ -19598,35 +19598,35 @@
         <v>305</v>
       </c>
       <c r="M8" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>361</v>
       </c>
       <c r="O8" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P8" s="34" t="s">
         <v>385</v>
       </c>
       <c r="Q8" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R8" s="35" t="s">
         <v>242</v>
       </c>
       <c r="S8" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T8" s="36" t="s">
         <v>64</v>
       </c>
       <c r="U8" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19640,7 +19640,7 @@
         <v>강종찬</v>
       </c>
       <c r="C9" s="2">
-        <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D9" s="14">
@@ -19664,7 +19664,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="14">
-        <f>SUM(D9:H9)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J9" s="15"/>
@@ -19675,35 +19675,35 @@
         <v>394</v>
       </c>
       <c r="M9" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>222</v>
       </c>
       <c r="O9" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P9" s="34" t="s">
         <v>314</v>
       </c>
       <c r="Q9" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R9" s="35" t="s">
         <v>222</v>
       </c>
       <c r="S9" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T9" s="36" t="s">
         <v>233</v>
       </c>
       <c r="U9" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19717,7 +19717,7 @@
         <v>강관석</v>
       </c>
       <c r="C10" s="2">
-        <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="D10" s="14">
@@ -19741,7 +19741,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="14">
-        <f>SUM(D10:H10)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J10" s="15"/>
@@ -19752,35 +19752,35 @@
         <v>395</v>
       </c>
       <c r="M10" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N10" s="33" t="s">
         <v>356</v>
       </c>
       <c r="O10" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P10" s="34" t="s">
         <v>305</v>
       </c>
       <c r="Q10" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R10" s="35" t="s">
         <v>303</v>
       </c>
       <c r="S10" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T10" s="36" t="s">
         <v>221</v>
       </c>
       <c r="U10" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19794,7 +19794,7 @@
         <v>강기혁</v>
       </c>
       <c r="C11" s="2">
-        <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="D11" s="14">
@@ -19818,7 +19818,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f>SUM(D11:H11)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="J11" s="15"/>
@@ -19829,35 +19829,35 @@
         <v>50</v>
       </c>
       <c r="M11" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N11" s="33" t="s">
         <v>314</v>
       </c>
       <c r="O11" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P11" s="34" t="s">
         <v>224</v>
       </c>
       <c r="Q11" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R11" s="35" t="s">
         <v>324</v>
       </c>
       <c r="S11" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="T11" s="36" t="s">
         <v>325</v>
       </c>
       <c r="U11" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19871,7 +19871,7 @@
         <v>강도일</v>
       </c>
       <c r="C12" s="2">
-        <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D12" s="14">
@@ -19895,7 +19895,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="14">
-        <f>SUM(D12:H12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J12" s="15"/>
@@ -19906,35 +19906,35 @@
         <v>229</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N12" s="33" t="s">
         <v>393</v>
       </c>
       <c r="O12" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P12" s="34" t="s">
         <v>362</v>
       </c>
       <c r="Q12" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R12" s="35" t="s">
         <v>366</v>
       </c>
       <c r="S12" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="T12" s="36" t="s">
         <v>366</v>
       </c>
       <c r="U12" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19948,7 +19948,7 @@
         <v>강일수</v>
       </c>
       <c r="C13" s="2">
-        <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D13" s="14">
@@ -19972,7 +19972,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f>SUM(D13:H13)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -19983,35 +19983,35 @@
         <v>360</v>
       </c>
       <c r="M13" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N13" s="33" t="s">
         <v>396</v>
       </c>
       <c r="O13" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P13" s="34" t="s">
         <v>225</v>
       </c>
       <c r="Q13" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R13" s="35" t="s">
         <v>34</v>
       </c>
       <c r="S13" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="T13" s="36" t="s">
         <v>365</v>
       </c>
       <c r="U13" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -20025,7 +20025,7 @@
         <v>구교훈</v>
       </c>
       <c r="C14" s="2">
-        <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D14" s="14">
@@ -20049,7 +20049,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f>SUM(D14:H14)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="15"/>
@@ -20060,7 +20060,7 @@
         <v>392</v>
       </c>
       <c r="M14" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N14" s="33"/>
@@ -20071,14 +20071,14 @@
         <v>386</v>
       </c>
       <c r="S14" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="T14" s="36" t="s">
         <v>303</v>
       </c>
       <c r="U14" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -20092,7 +20092,7 @@
         <v>권주용</v>
       </c>
       <c r="C15" s="2">
-        <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D15" s="14">
@@ -20116,7 +20116,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f>SUM(D15:H15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J15" s="15"/>
@@ -20127,7 +20127,7 @@
         <v>42</v>
       </c>
       <c r="M15" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N15" s="22"/>
@@ -20138,14 +20138,14 @@
         <v>62</v>
       </c>
       <c r="S15" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="T15" s="56" t="s">
         <v>377</v>
       </c>
       <c r="U15" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
         <v>김기문</v>
       </c>
       <c r="C16" s="2">
-        <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="14">
@@ -20183,7 +20183,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="14">
-        <f>SUM(D16:H16)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J16" s="15"/>
@@ -20211,7 +20211,7 @@
         <v>김기태</v>
       </c>
       <c r="C17" s="2">
-        <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D17" s="14">
@@ -20235,7 +20235,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="14">
-        <f>SUM(D17:H17)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J17" s="15"/>
@@ -20263,7 +20263,7 @@
         <v>김덕준</v>
       </c>
       <c r="C18" s="2">
-        <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D18" s="14">
@@ -20287,7 +20287,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f>SUM(D18:H18)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="15"/>
@@ -20315,7 +20315,7 @@
         <v>김동인</v>
       </c>
       <c r="C19" s="2">
-        <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D19" s="14">
@@ -20339,7 +20339,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f>SUM(D19:H19)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
@@ -20354,7 +20354,7 @@
         <v>김민섭</v>
       </c>
       <c r="C20" s="2">
-        <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="D20" s="14">
@@ -20378,7 +20378,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f>SUM(D20:H20)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J20" s="15"/>
@@ -20393,7 +20393,7 @@
         <v>김민준</v>
       </c>
       <c r="C21" s="2">
-        <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D21" s="14">
@@ -20417,7 +20417,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="14">
-        <f>SUM(D21:H21)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21" s="15"/>
@@ -20432,7 +20432,7 @@
         <v>김민찬</v>
       </c>
       <c r="C22" s="2">
-        <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D22" s="14">
@@ -20456,7 +20456,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f>SUM(D22:H22)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J22" s="15"/>
@@ -20471,7 +20471,7 @@
         <v>김범기</v>
       </c>
       <c r="C23" s="2">
-        <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D23" s="14">
@@ -20495,7 +20495,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f>SUM(D23:H23)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="15"/>
@@ -20510,7 +20510,7 @@
         <v>김병준</v>
       </c>
       <c r="C24" s="2">
-        <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D24" s="14">
@@ -20534,7 +20534,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f>SUM(D24:H24)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="15"/>
@@ -20549,7 +20549,7 @@
         <v>김부건</v>
       </c>
       <c r="C25" s="2">
-        <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D25" s="14">
@@ -20573,7 +20573,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f>SUM(D25:H25)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J25" s="15"/>
@@ -20588,7 +20588,7 @@
         <v>김성수</v>
       </c>
       <c r="C26" s="2">
-        <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="D26" s="14">
@@ -20612,7 +20612,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="14">
-        <f>SUM(D26:H26)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J26" s="15"/>
@@ -20627,7 +20627,7 @@
         <v>김성준</v>
       </c>
       <c r="C27" s="2">
-        <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="D27" s="14">
@@ -20651,7 +20651,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="14">
-        <f>SUM(D27:H27)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="J27" s="15"/>
@@ -20666,7 +20666,7 @@
         <v>김송환</v>
       </c>
       <c r="C28" s="2">
-        <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
       <c r="D28" s="14">
@@ -20690,7 +20690,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="14">
-        <f>SUM(D28:H28)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="J28" s="15"/>
@@ -20705,7 +20705,7 @@
         <v>김영태</v>
       </c>
       <c r="C29" s="2">
-        <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D29" s="14">
@@ -20729,7 +20729,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <f>SUM(D29:H29)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J29" s="15"/>
@@ -20744,7 +20744,7 @@
         <v>김용빈</v>
       </c>
       <c r="C30" s="2">
-        <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D30" s="14">
@@ -20768,7 +20768,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <f>SUM(D30:H30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J30" s="15"/>
@@ -20783,7 +20783,7 @@
         <v>김용현</v>
       </c>
       <c r="C31" s="2">
-        <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.9000000000000004</v>
       </c>
       <c r="D31" s="14">
@@ -20807,7 +20807,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <f>SUM(D31:H31)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="J31" s="15"/>
@@ -20822,7 +20822,7 @@
         <v>김우인</v>
       </c>
       <c r="C32" s="2">
-        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="D32" s="14">
@@ -20846,7 +20846,7 @@
         <v>6</v>
       </c>
       <c r="I32" s="14">
-        <f>SUM(D32:H32)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="J32" s="15"/>
@@ -20861,7 +20861,7 @@
         <v>김종준</v>
       </c>
       <c r="C33" s="2">
-        <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D33" s="14">
@@ -20885,7 +20885,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="14">
-        <f>SUM(D33:H33)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J33" s="15"/>
@@ -20900,7 +20900,7 @@
         <v>김종혁</v>
       </c>
       <c r="C34" s="2">
-        <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D34" s="14">
@@ -20924,7 +20924,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="14">
-        <f>SUM(D34:H34)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J34" s="15"/>
@@ -20939,7 +20939,7 @@
         <v>김준영</v>
       </c>
       <c r="C35" s="2">
-        <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D35" s="14">
@@ -20963,7 +20963,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="14">
-        <f>SUM(D35:H35)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J35" s="15"/>
@@ -20978,7 +20978,7 @@
         <v>김진형</v>
       </c>
       <c r="C36" s="2">
-        <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
         <v>0</v>
       </c>
       <c r="D36" s="14">
@@ -21002,7 +21002,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="14">
-        <f>SUM(D36:H36)</f>
+        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
         <v>0</v>
       </c>
       <c r="J36" s="15"/>
@@ -21017,7 +21017,7 @@
         <v>김진호</v>
       </c>
       <c r="C37" s="2">
-        <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.8</v>
       </c>
       <c r="D37" s="14">
@@ -21041,7 +21041,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="14">
-        <f>SUM(D37:H37)</f>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="J37" s="15"/>
@@ -21056,7 +21056,7 @@
         <v>김태성</v>
       </c>
       <c r="C38" s="2">
-        <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="D38" s="14">
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="14">
-        <f>SUM(D38:H38)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J38" s="15"/>
@@ -21095,7 +21095,7 @@
         <v>김태양</v>
       </c>
       <c r="C39" s="2">
-        <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D39" s="14">
@@ -21119,7 +21119,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="14">
-        <f>SUM(D39:H39)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J39" s="15"/>
@@ -21134,7 +21134,7 @@
         <v>김태완</v>
       </c>
       <c r="C40" s="2">
-        <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D40" s="14">
@@ -21158,7 +21158,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="14">
-        <f>SUM(D40:H40)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J40" s="15"/>
@@ -21173,7 +21173,7 @@
         <v>김태호</v>
       </c>
       <c r="C41" s="2">
-        <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D41" s="14">
@@ -21197,7 +21197,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="14">
-        <f>SUM(D41:H41)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J41" s="15"/>
@@ -21212,7 +21212,7 @@
         <v>김현우</v>
       </c>
       <c r="C42" s="2">
-        <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D42" s="14">
@@ -21236,7 +21236,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="14">
-        <f>SUM(D42:H42)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J42" s="15"/>
@@ -21251,7 +21251,7 @@
         <v>김형원</v>
       </c>
       <c r="C43" s="2">
-        <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D43" s="14">
@@ -21275,7 +21275,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="14">
-        <f>SUM(D43:H43)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J43" s="15"/>
@@ -21290,7 +21290,7 @@
         <v>노민준</v>
       </c>
       <c r="C44" s="2">
-        <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.8</v>
       </c>
       <c r="D44" s="14">
@@ -21314,7 +21314,7 @@
         <v>2</v>
       </c>
       <c r="I44" s="14">
-        <f>SUM(D44:H44)</f>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="J44" s="15"/>
@@ -21329,7 +21329,7 @@
         <v>류서진</v>
       </c>
       <c r="C45" s="2">
-        <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D45" s="14">
@@ -21353,7 +21353,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="14">
-        <f>SUM(D45:H45)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J45" s="15"/>
@@ -21368,7 +21368,7 @@
         <v>마창기</v>
       </c>
       <c r="C46" s="2">
-        <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D46" s="14">
@@ -21392,7 +21392,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="14">
-        <f>SUM(D46:H46)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J46" s="15"/>
@@ -21407,7 +21407,7 @@
         <v>문준수</v>
       </c>
       <c r="C47" s="2">
-        <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D47" s="14">
@@ -21431,7 +21431,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="14">
-        <f>SUM(D47:H47)</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="J47" s="15"/>
@@ -21446,7 +21446,7 @@
         <v>민건호</v>
       </c>
       <c r="C48" s="2">
-        <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D48" s="14">
@@ -21470,7 +21470,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="14">
-        <f>SUM(D48:H48)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J48" s="15"/>
@@ -21485,7 +21485,7 @@
         <v>박수천</v>
       </c>
       <c r="C49" s="2">
-        <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D49" s="14">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="14">
-        <f>SUM(D49:H49)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J49" s="15"/>
@@ -21524,7 +21524,7 @@
         <v>박정호</v>
       </c>
       <c r="C50" s="2">
-        <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D50" s="14">
@@ -21548,7 +21548,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="14">
-        <f>SUM(D50:H50)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J50" s="15"/>
@@ -21563,7 +21563,7 @@
         <v>박주연</v>
       </c>
       <c r="C51" s="2">
-        <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="D51" s="14">
@@ -21587,7 +21587,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="14">
-        <f>SUM(D51:H51)</f>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="J51" s="15"/>
@@ -21602,7 +21602,7 @@
         <v>박주현</v>
       </c>
       <c r="C52" s="2">
-        <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D52" s="14">
@@ -21626,7 +21626,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="14">
-        <f>SUM(D52:H52)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J52" s="15"/>
@@ -21641,7 +21641,7 @@
         <v>박하빈</v>
       </c>
       <c r="C53" s="2">
-        <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D53" s="14">
@@ -21665,7 +21665,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="14">
-        <f>SUM(D53:H53)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J53" s="15"/>
@@ -21680,7 +21680,7 @@
         <v>박형기</v>
       </c>
       <c r="C54" s="2">
-        <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D54" s="14">
@@ -21704,7 +21704,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="14">
-        <f>SUM(D54:H54)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J54" s="15"/>
@@ -21719,7 +21719,7 @@
         <v>손경호</v>
       </c>
       <c r="C55" s="2">
-        <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D55" s="14">
@@ -21743,7 +21743,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="14">
-        <f>SUM(D55:H55)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J55" s="15"/>
@@ -21758,7 +21758,7 @@
         <v>송윤상</v>
       </c>
       <c r="C56" s="2">
-        <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="D56" s="14">
@@ -21782,7 +21782,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="14">
-        <f>SUM(D56:H56)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J56" s="15"/>
@@ -21797,7 +21797,7 @@
         <v>신기웅</v>
       </c>
       <c r="C57" s="2">
-        <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D57" s="14">
@@ -21821,7 +21821,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="14">
-        <f>SUM(D57:H57)</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="J57" s="15"/>
@@ -21836,7 +21836,7 @@
         <v>신종훈</v>
       </c>
       <c r="C58" s="2">
-        <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D58" s="14">
@@ -21860,7 +21860,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="14">
-        <f>SUM(D58:H58)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J58" s="15"/>
@@ -21875,7 +21875,7 @@
         <v>안진혁</v>
       </c>
       <c r="C59" s="2">
-        <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D59" s="14">
@@ -21899,7 +21899,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="14">
-        <f>SUM(D59:H59)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J59" s="15"/>
@@ -21914,7 +21914,7 @@
         <v>양진웅</v>
       </c>
       <c r="C60" s="2">
-        <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="D60" s="14">
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="14">
-        <f>SUM(D60:H60)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J60" s="15"/>
@@ -21953,7 +21953,7 @@
         <v>오우영</v>
       </c>
       <c r="C61" s="2">
-        <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
       <c r="D61" s="14">
@@ -21977,7 +21977,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="14">
-        <f>SUM(D61:H61)</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="J61" s="15"/>
@@ -21992,7 +21992,7 @@
         <v>오운용</v>
       </c>
       <c r="C62" s="2">
-        <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D62" s="14">
@@ -22016,7 +22016,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="14">
-        <f>SUM(D62:H62)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J62" s="15"/>
@@ -22031,7 +22031,7 @@
         <v>오진환</v>
       </c>
       <c r="C63" s="2">
-        <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D63" s="14">
@@ -22055,7 +22055,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f>SUM(D63:H63)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J63" s="15"/>
@@ -22070,7 +22070,7 @@
         <v>우보광</v>
       </c>
       <c r="C64" s="2">
-        <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D64" s="14">
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="14">
-        <f>SUM(D64:H64)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J64" s="15"/>
@@ -22109,7 +22109,7 @@
         <v>유상근</v>
       </c>
       <c r="C65" s="2">
-        <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="D65" s="14">
@@ -22133,7 +22133,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="14">
-        <f>SUM(D65:H65)</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="J65" s="15"/>
@@ -22148,7 +22148,7 @@
         <v>유인상</v>
       </c>
       <c r="C66" s="2">
-        <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D66" s="14">
@@ -22172,7 +22172,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f>SUM(D66:H66)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J66" s="15"/>
@@ -22187,7 +22187,7 @@
         <v>유정훈</v>
       </c>
       <c r="C67" s="2">
-        <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D67" s="14">
@@ -22211,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f>SUM(D67:H67)</f>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="J67" s="15"/>
@@ -22226,7 +22226,7 @@
         <v>유진효</v>
       </c>
       <c r="C68" s="2">
-        <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
         <v>0</v>
       </c>
       <c r="D68" s="14">
@@ -22250,7 +22250,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="14">
-        <f>SUM(D68:H68)</f>
+        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
         <v>0</v>
       </c>
       <c r="J68" s="15"/>
@@ -22265,7 +22265,7 @@
         <v>윤원택</v>
       </c>
       <c r="C69" s="2">
-        <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D69" s="14">
@@ -22289,7 +22289,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f>SUM(D69:H69)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J69" s="15"/>
@@ -22304,7 +22304,7 @@
         <v>윤창현</v>
       </c>
       <c r="C70" s="2">
-        <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D70" s="14">
@@ -22328,7 +22328,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="14">
-        <f>SUM(D70:H70)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J70" s="15"/>
@@ -22343,7 +22343,7 @@
         <v>윤현기</v>
       </c>
       <c r="C71" s="2">
-        <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
       <c r="D71" s="14">
@@ -22367,7 +22367,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <f>SUM(D71:H71)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J71" s="15"/>
@@ -22382,7 +22382,7 @@
         <v>이경석</v>
       </c>
       <c r="C72" s="2">
-        <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D72" s="14">
@@ -22406,7 +22406,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f>SUM(D72:H72)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J72" s="15"/>
@@ -22421,7 +22421,7 @@
         <v>이민재</v>
       </c>
       <c r="C73" s="2">
-        <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D73" s="14">
@@ -22445,7 +22445,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f>SUM(D73:H73)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J73" s="15"/>
@@ -22460,7 +22460,7 @@
         <v>이병현</v>
       </c>
       <c r="C74" s="2">
-        <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D74" s="14">
@@ -22484,7 +22484,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="14">
-        <f>SUM(D74:H74)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J74" s="15"/>
@@ -22499,7 +22499,7 @@
         <v>이상민</v>
       </c>
       <c r="C75" s="2">
-        <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D75" s="14">
@@ -22523,7 +22523,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="14">
-        <f>SUM(D75:H75)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J75" s="15"/>
@@ -22538,7 +22538,7 @@
         <v>이상현</v>
       </c>
       <c r="C76" s="2">
-        <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D76" s="14">
@@ -22562,7 +22562,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="14">
-        <f>SUM(D76:H76)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J76" s="15"/>
@@ -22577,7 +22577,7 @@
         <v>이새샘</v>
       </c>
       <c r="C77" s="2">
-        <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.8</v>
       </c>
       <c r="D77" s="14">
@@ -22601,7 +22601,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="14">
-        <f>SUM(D77:H77)</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="J77" s="15"/>
@@ -22616,7 +22616,7 @@
         <v>이성관</v>
       </c>
       <c r="C78" s="2">
-        <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D78" s="14">
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="14">
-        <f>SUM(D78:H78)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J78" s="15"/>
@@ -22655,7 +22655,7 @@
         <v>이승윤</v>
       </c>
       <c r="C79" s="2">
-        <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D79" s="14">
@@ -22679,7 +22679,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="14">
-        <f>SUM(D79:H79)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J79" s="15"/>
@@ -22694,7 +22694,7 @@
         <v>이연길</v>
       </c>
       <c r="C80" s="2">
-        <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D80" s="14">
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="14">
-        <f>SUM(D80:H80)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J80" s="15"/>
@@ -22733,7 +22733,7 @@
         <v>이정범</v>
       </c>
       <c r="C81" s="2">
-        <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D81" s="14">
@@ -22757,7 +22757,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="14">
-        <f>SUM(D81:H81)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J81" s="15"/>
@@ -22772,7 +22772,7 @@
         <v>이종수</v>
       </c>
       <c r="C82" s="2">
-        <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D82" s="14">
@@ -22796,7 +22796,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="14">
-        <f>SUM(D82:H82)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J82" s="15"/>
@@ -22811,7 +22811,7 @@
         <v>이찬영</v>
       </c>
       <c r="C83" s="2">
-        <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D83" s="14">
@@ -22835,7 +22835,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="14">
-        <f>SUM(D83:H83)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J83" s="15"/>
@@ -22850,7 +22850,7 @@
         <v>이태한</v>
       </c>
       <c r="C84" s="2">
-        <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D84" s="14">
@@ -22874,7 +22874,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="14">
-        <f>SUM(D84:H84)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J84" s="15"/>
@@ -22889,7 +22889,7 @@
         <v>이호행</v>
       </c>
       <c r="C85" s="2">
-        <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D85" s="14">
@@ -22913,7 +22913,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="14">
-        <f>SUM(D85:H85)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J85" s="15"/>
@@ -22928,7 +22928,7 @@
         <v>임수철</v>
       </c>
       <c r="C86" s="2">
-        <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D86" s="14">
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="14">
-        <f>SUM(D86:H86)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J86" s="15"/>
@@ -22967,7 +22967,7 @@
         <v>임태환</v>
       </c>
       <c r="C87" s="2">
-        <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D87" s="14">
@@ -22991,7 +22991,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="14">
-        <f>SUM(D87:H87)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J87" s="15"/>
@@ -23006,7 +23006,7 @@
         <v>장희도</v>
       </c>
       <c r="C88" s="2">
-        <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D88" s="14">
@@ -23030,7 +23030,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="14">
-        <f>SUM(D88:H88)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J88" s="15"/>
@@ -23045,7 +23045,7 @@
         <v>장희준</v>
       </c>
       <c r="C89" s="2">
-        <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D89" s="14">
@@ -23069,7 +23069,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="14">
-        <f>SUM(D89:H89)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J89" s="15"/>
@@ -23084,7 +23084,7 @@
         <v>전나현</v>
       </c>
       <c r="C90" s="2">
-        <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
       <c r="D90" s="14">
@@ -23108,7 +23108,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="14">
-        <f>SUM(D90:H90)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J90" s="15"/>
@@ -23123,7 +23123,7 @@
         <v>전성환</v>
       </c>
       <c r="C91" s="2">
-        <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D91" s="14">
@@ -23147,7 +23147,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="14">
-        <f>SUM(D91:H91)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J91" s="15"/>
@@ -23162,7 +23162,7 @@
         <v>전하늘</v>
       </c>
       <c r="C92" s="2">
-        <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D92" s="14">
@@ -23186,7 +23186,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="14">
-        <f>SUM(D92:H92)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J92" s="15"/>
@@ -23201,7 +23201,7 @@
         <v>정민수</v>
       </c>
       <c r="C93" s="2">
-        <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.6</v>
       </c>
       <c r="D93" s="14">
@@ -23225,7 +23225,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="14">
-        <f>SUM(D93:H93)</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="J93" s="15"/>
@@ -23240,7 +23240,7 @@
         <v>정재명</v>
       </c>
       <c r="C94" s="2">
-        <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D94" s="14">
@@ -23264,7 +23264,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="14">
-        <f>SUM(D94:H94)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J94" s="15"/>
@@ -23279,7 +23279,7 @@
         <v>조진한</v>
       </c>
       <c r="C95" s="2">
-        <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.9</v>
       </c>
       <c r="D95" s="14">
@@ -23303,7 +23303,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="14">
-        <f>SUM(D95:H95)</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="J95" s="15"/>
@@ -23318,7 +23318,7 @@
         <v>조현우</v>
       </c>
       <c r="C96" s="2">
-        <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D96" s="14">
@@ -23342,7 +23342,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="14">
-        <f>SUM(D96:H96)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J96" s="15"/>
@@ -23357,7 +23357,7 @@
         <v>차승원</v>
       </c>
       <c r="C97" s="2">
-        <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D97" s="14">
@@ -23381,7 +23381,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="14">
-        <f>SUM(D97:H97)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J97" s="15"/>
@@ -23396,7 +23396,7 @@
         <v>최령창</v>
       </c>
       <c r="C98" s="2">
-        <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="D98" s="14">
@@ -23420,7 +23420,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="14">
-        <f>SUM(D98:H98)</f>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="J98" s="15"/>
@@ -23435,7 +23435,7 @@
         <v>최승훈</v>
       </c>
       <c r="C99" s="2">
-        <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D99" s="14">
@@ -23459,7 +23459,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="14">
-        <f>SUM(D99:H99)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J99" s="15"/>
@@ -23474,7 +23474,7 @@
         <v>한상규</v>
       </c>
       <c r="C100" s="2">
-        <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D100" s="14">
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f>SUM(D100:H100)</f>
+        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
         <v>3</v>
       </c>
       <c r="J100" s="15"/>
@@ -23513,7 +23513,7 @@
         <v>한의현</v>
       </c>
       <c r="C101" s="2">
-        <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D101" s="14">
@@ -23537,7 +23537,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f>SUM(D101:H101)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J101" s="15"/>
@@ -23552,7 +23552,7 @@
         <v>한중희</v>
       </c>
       <c r="C102" s="2">
-        <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D102" s="14">
@@ -23576,7 +23576,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="14">
-        <f>SUM(D102:H102)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J102" s="15"/>
@@ -23591,7 +23591,7 @@
         <v>허동혁</v>
       </c>
       <c r="C103" s="2">
-        <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D103" s="14">
@@ -23615,7 +23615,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f>SUM(D103:H103)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J103" s="15"/>
@@ -23630,7 +23630,7 @@
         <v>홍석준</v>
       </c>
       <c r="C104" s="2">
-        <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D104" s="14">
@@ -23654,7 +23654,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f>SUM(D104:H104)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J104" s="15"/>
@@ -23669,7 +23669,7 @@
         <v>홍현석</v>
       </c>
       <c r="C105" s="2">
-        <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D105" s="14">
@@ -23693,7 +23693,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="14">
-        <f>SUM(D105:H105)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -23707,7 +23707,7 @@
         <v>황석원</v>
       </c>
       <c r="C106" s="2">
-        <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D106" s="14">
@@ -23731,7 +23731,7 @@
         <v>1</v>
       </c>
       <c r="I106" s="14">
-        <f>SUM(D106:H106)</f>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
     </row>
@@ -23745,7 +23745,7 @@
         <v>황재순</v>
       </c>
       <c r="C107" s="2">
-        <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D107" s="14">
@@ -23769,7 +23769,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f>SUM(D107:H107)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -23783,7 +23783,7 @@
         <v>황철우</v>
       </c>
       <c r="C108" s="2">
-        <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D108" s="14">
@@ -23807,7 +23807,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f>SUM(D108:H108)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -23821,7 +23821,7 @@
         <v>김진우</v>
       </c>
       <c r="C109" s="2">
-        <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D109" s="14">
@@ -23845,7 +23845,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="14">
-        <f>SUM(D109:H109)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -23859,7 +23859,7 @@
         <v>노성호</v>
       </c>
       <c r="C110" s="2">
-        <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D110" s="14">
@@ -23883,7 +23883,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="14">
-        <f>SUM(D110:H110)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -23897,7 +23897,7 @@
         <v>박준영</v>
       </c>
       <c r="C111" s="2">
-        <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D111" s="14">
@@ -23921,7 +23921,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f>SUM(D111:H111)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -23935,7 +23935,7 @@
         <v>박태현</v>
       </c>
       <c r="C112" s="2">
-        <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D112" s="14">
@@ -23959,7 +23959,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f>SUM(D112:H112)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
         <v>서영진</v>
       </c>
       <c r="C113" s="2">
-        <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D113" s="14">
@@ -23997,7 +23997,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="14">
-        <f>SUM(D113:H113)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -24011,7 +24011,7 @@
         <v>오상준</v>
       </c>
       <c r="C114" s="2">
-        <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.7</v>
       </c>
       <c r="D114" s="14">
@@ -24035,7 +24035,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="14">
-        <f>SUM(D114:H114)</f>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
     </row>
@@ -24049,7 +24049,7 @@
         <v>오성찬</v>
       </c>
       <c r="C115" s="2">
-        <f>((D115+E115+G115+H115)*0.2)+(F115*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.3</v>
       </c>
       <c r="D115" s="14">
@@ -24073,7 +24073,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="14">
-        <f>SUM(D115:H115)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -24087,7 +24087,7 @@
         <v>유우진</v>
       </c>
       <c r="C116" s="2">
-        <f>((D116+E116+G116+H116)*0.2)+(F116*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D116" s="14">
@@ -24111,7 +24111,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="14">
-        <f>SUM(D116:H116)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -24125,7 +24125,7 @@
         <v>이영준</v>
       </c>
       <c r="C117" s="2">
-        <f>((D117+E117+G117+H117)*0.2)+(F117*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.3</v>
       </c>
       <c r="D117" s="14">
@@ -24149,7 +24149,7 @@
         <v>0</v>
       </c>
       <c r="I117" s="14">
-        <f>SUM(D117:H117)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -24163,7 +24163,7 @@
         <v>이찬솔</v>
       </c>
       <c r="C118" s="2">
-        <f>((D118+E118+G118+H118)*0.2)+(F118*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D118" s="14">
@@ -24187,7 +24187,7 @@
         <v>0</v>
       </c>
       <c r="I118" s="14">
-        <f>SUM(D118:H118)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
         <v>정현서</v>
       </c>
       <c r="C119" s="2">
-        <f>((D119+E119+G119+H119)*0.2)+(F119*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D119" s="14">
@@ -24225,7 +24225,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f>SUM(D119:H119)</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
     </row>
@@ -24239,7 +24239,7 @@
         <v>황건호</v>
       </c>
       <c r="C120" s="2">
-        <f>((D120+E120+G120+H120)*0.2)+(F120*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="D120" s="14">
@@ -24263,7 +24263,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="14">
-        <f>SUM(D120:H120)</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
     </row>
@@ -24277,7 +24277,7 @@
         <v>김민성</v>
       </c>
       <c r="C121" s="2">
-        <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D121" s="14">
@@ -24301,7 +24301,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="14">
-        <f>SUM(D121:H121)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -24315,7 +24315,7 @@
         <v>송명섭</v>
       </c>
       <c r="C122" s="2">
-        <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D122" s="14">
@@ -24339,7 +24339,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f>SUM(D122:H122)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
         <v>최경영</v>
       </c>
       <c r="C123" s="2">
-        <f>((D123+E123+G123+H123)*0.2)+(F123*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.6</v>
       </c>
       <c r="D123" s="14">
@@ -24377,7 +24377,7 @@
         <v>3</v>
       </c>
       <c r="I123" s="14">
-        <f>SUM(D123:H123)</f>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
     </row>
@@ -25969,10 +25969,10 @@
       <c r="G2" s="47" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="98" t="s">
+      <c r="I2" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="98"/>
+      <c r="J2" s="93"/>
       <c r="K2" s="65" t="s">
         <v>277</v>
       </c>
@@ -25997,7 +25997,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="92" t="s">
         <v>338</v>
       </c>
       <c r="C3" s="72">
@@ -26213,7 +26213,7 @@
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
         <v>10.9</v>
       </c>
-      <c r="I7" s="96"/>
+      <c r="I7" s="97"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -26299,10 +26299,10 @@
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
         <v>2</v>
       </c>
-      <c r="I9" s="98" t="s">
+      <c r="I9" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="J9" s="98"/>
+      <c r="J9" s="93"/>
       <c r="K9" s="65" t="s">
         <v>277</v>
       </c>
@@ -26455,7 +26455,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="97"/>
+      <c r="N12" s="100"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -26529,7 +26529,7 @@
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
         <v>9.6</v>
       </c>
-      <c r="I14" s="96"/>
+      <c r="I14" s="97"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -26592,10 +26592,10 @@
         <v>6.6</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="98" t="s">
+      <c r="I16" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="J16" s="98"/>
+      <c r="J16" s="93"/>
       <c r="K16" s="65" t="s">
         <v>277</v>
       </c>
@@ -26656,10 +26656,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="C19" s="98"/>
+      <c r="C19" s="93"/>
       <c r="D19" s="65" t="s">
         <v>277</v>
       </c>
@@ -26710,7 +26710,7 @@
       <c r="E21" s="65" t="s">
         <v>341</v>
       </c>
-      <c r="I21" s="96"/>
+      <c r="I21" s="97"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -26722,7 +26722,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="100"/>
+      <c r="B22" s="96"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -26734,10 +26734,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="92" t="s">
+      <c r="I23" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="J23" s="93"/>
+      <c r="J23" s="99"/>
       <c r="K23" s="65" t="s">
         <v>277</v>
       </c>
@@ -26820,7 +26820,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="96"/>
+      <c r="I30" s="97"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -26833,12 +26833,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -26847,6 +26841,12 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inhyu\OneDrive\바탕 화면\김인혁\김인혁_청년축구단\1. 출석부\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC05B59-DF77-4DED-AE4B-34DB9FEA98F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B419E5-8C65-48B6-84BD-19C1D9562032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="399">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -1449,10 +1449,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Orange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>김성수</t>
   </si>
   <si>
@@ -1492,6 +1488,17 @@
   </si>
   <si>
     <t>정현서</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Red</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2266,10 +2273,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2278,20 +2285,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3092,7 +3099,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>6.1111111111111107</v>
+        <v>6.6222222222222218</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3151,7 +3158,7 @@
       </c>
       <c r="W2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X2" s="1">
         <f t="shared" si="0"/>
@@ -3365,7 +3372,9 @@
       <c r="V3" s="4">
         <v>46133</v>
       </c>
-      <c r="W3" s="4"/>
+      <c r="W3" s="4">
+        <v>46149</v>
+      </c>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
@@ -3449,11 +3458,11 @@
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4" si="2">(COUNTIF(J4:CD4,"출전")*1)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>352</v>
@@ -3490,7 +3499,9 @@
       <c r="V4" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="W4" s="2"/>
+      <c r="W4" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
@@ -3570,7 +3581,7 @@
       </c>
       <c r="G5" s="2">
         <f>RANK(H5,$H$4:$H$123,0)</f>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -3987,7 +3998,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
@@ -4098,15 +4109,15 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
-        <v>5.9</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>352</v>
@@ -4131,7 +4142,9 @@
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
+      <c r="W10" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
@@ -4211,7 +4224,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
@@ -4327,7 +4340,7 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C12</f>
@@ -4744,15 +4757,15 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="4"/>
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -4773,7 +4786,9 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
+      <c r="W16" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
@@ -4853,15 +4868,15 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
-        <v>8.1999999999999993</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
@@ -4890,7 +4905,9 @@
         <v>352</v>
       </c>
       <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
+      <c r="W17" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
@@ -5073,7 +5090,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
@@ -5184,7 +5201,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="4"/>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -5603,7 +5620,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
@@ -5708,7 +5725,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
@@ -5813,7 +5830,7 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
@@ -5928,11 +5945,11 @@
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
@@ -5967,7 +5984,9 @@
       <c r="V27" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="W27" s="2"/>
+      <c r="W27" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
@@ -6047,15 +6066,15 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
-        <v>4.4000000000000004</v>
+        <v>6.3000000000000007</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -6076,7 +6095,9 @@
         <v>352</v>
       </c>
       <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
+      <c r="W28" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
@@ -6260,7 +6281,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="4"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6369,7 +6390,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
@@ -6484,15 +6505,15 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>352</v>
@@ -6523,7 +6544,9 @@
         <v>352</v>
       </c>
       <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
+      <c r="W32" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
@@ -6603,7 +6626,7 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
@@ -6716,7 +6739,7 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
@@ -7039,15 +7062,15 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
-        <v>7.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -7074,7 +7097,9 @@
         <v>352</v>
       </c>
       <c r="V37" s="2"/>
-      <c r="W37" s="2"/>
+      <c r="W37" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X37" s="2"/>
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
@@ -7154,7 +7179,7 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="4"/>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
@@ -7367,7 +7392,7 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H40" s="6">
         <f>I40+개인기록Sheet!C40</f>
@@ -7680,7 +7705,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
@@ -7785,7 +7810,7 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
@@ -8110,7 +8135,7 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
@@ -8537,7 +8562,7 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
@@ -8964,7 +8989,7 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
@@ -9077,7 +9102,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="4"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
@@ -9177,7 +9202,7 @@
       </c>
       <c r="D57" s="54">
         <f t="shared" ref="D57:D58" si="13">COUNTA(J57:W57)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" s="54"/>
       <c r="F57" s="2" t="s">
@@ -9185,15 +9210,15 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
-        <v>4.5999999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="I57" s="6">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -9216,7 +9241,9 @@
       <c r="V57" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="W57" s="2"/>
+      <c r="W57" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
@@ -9400,7 +9427,7 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
@@ -9505,7 +9532,7 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
@@ -9620,7 +9647,7 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
@@ -10045,11 +10072,11 @@
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
-        <v>8.1999999999999993</v>
+        <v>9.4</v>
       </c>
       <c r="I65" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -10076,7 +10103,9 @@
         <v>352</v>
       </c>
       <c r="V65" s="2"/>
-      <c r="W65" s="2"/>
+      <c r="W65" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X65" s="2"/>
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
@@ -10156,7 +10185,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="4"/>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
@@ -10263,7 +10292,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
@@ -10478,7 +10507,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" si="4"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
@@ -10587,15 +10616,15 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="I70" s="6">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -10612,7 +10641,9 @@
       <c r="T70" s="2"/>
       <c r="U70" s="2"/>
       <c r="V70" s="2"/>
-      <c r="W70" s="2"/>
+      <c r="W70" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X70" s="2"/>
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
@@ -10693,7 +10724,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="4"/>
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -11003,7 +11034,7 @@
       </c>
       <c r="D74" s="54">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74" s="54"/>
       <c r="F74" s="2" t="s">
@@ -11011,15 +11042,15 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="16"/>
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="I74" s="6">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
@@ -11040,7 +11071,9 @@
       </c>
       <c r="U74" s="2"/>
       <c r="V74" s="2"/>
-      <c r="W74" s="2"/>
+      <c r="W74" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X74" s="2"/>
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
@@ -11120,7 +11153,7 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="16"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
@@ -11231,7 +11264,7 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="16"/>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
@@ -11338,15 +11371,15 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="16"/>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="I77" s="6">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
@@ -11367,7 +11400,9 @@
       <c r="T77" s="2"/>
       <c r="U77" s="2"/>
       <c r="V77" s="2"/>
-      <c r="W77" s="2"/>
+      <c r="W77" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X77" s="2"/>
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
@@ -11447,15 +11482,15 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="16"/>
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
-        <v>3.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
@@ -11476,7 +11511,9 @@
         <v>352</v>
       </c>
       <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
+      <c r="W78" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X78" s="2"/>
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
@@ -11556,7 +11593,7 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" si="16"/>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
@@ -11663,7 +11700,7 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="16"/>
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
@@ -11976,7 +12013,7 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="16"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
@@ -12085,7 +12122,7 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="16"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
@@ -12190,7 +12227,7 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="16"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
@@ -12400,15 +12437,15 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="16"/>
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="I87" s="6">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
@@ -12425,7 +12462,9 @@
       <c r="T87" s="2"/>
       <c r="U87" s="2"/>
       <c r="V87" s="2"/>
-      <c r="W87" s="2"/>
+      <c r="W87" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X87" s="2"/>
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
@@ -12712,7 +12751,7 @@
       </c>
       <c r="G90" s="2">
         <f t="shared" si="16"/>
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
@@ -12822,7 +12861,7 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" si="16"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
@@ -12927,7 +12966,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="16"/>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
@@ -13036,15 +13075,15 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" si="16"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="I93" s="6">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
@@ -13069,7 +13108,9 @@
         <v>352</v>
       </c>
       <c r="V93" s="2"/>
-      <c r="W93" s="2"/>
+      <c r="W93" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X93" s="2"/>
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
@@ -13149,7 +13190,7 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="16"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
@@ -13262,11 +13303,11 @@
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="I95" s="6">
         <f t="shared" si="17"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>352</v>
@@ -13299,7 +13340,9 @@
       <c r="V95" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="W95" s="2"/>
+      <c r="W95" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X95" s="2"/>
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
@@ -13379,7 +13422,7 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" si="16"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
@@ -13496,7 +13539,7 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
@@ -13609,7 +13652,7 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" si="16"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H98" s="6">
         <f>I98+개인기록Sheet!C98</f>
@@ -13824,7 +13867,7 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
@@ -13935,7 +13978,7 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="16"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
@@ -14046,7 +14089,7 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="16"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
@@ -14159,7 +14202,7 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="16"/>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
@@ -14266,7 +14309,7 @@
       </c>
       <c r="G104" s="2">
         <f t="shared" si="16"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
@@ -14371,7 +14414,7 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="16"/>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
@@ -14478,7 +14521,7 @@
       </c>
       <c r="G106" s="2">
         <f t="shared" si="16"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
@@ -14691,7 +14734,7 @@
       </c>
       <c r="G108" s="2">
         <f t="shared" si="16"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
@@ -14797,7 +14840,7 @@
       </c>
       <c r="G109" s="2">
         <f t="shared" si="16"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
@@ -14895,7 +14938,7 @@
       </c>
       <c r="D110" s="54">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="54"/>
       <c r="F110" s="2" t="s">
@@ -14903,15 +14946,15 @@
       </c>
       <c r="G110" s="2">
         <f t="shared" si="16"/>
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110" s="6">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
@@ -14928,7 +14971,9 @@
       </c>
       <c r="U110" s="2"/>
       <c r="V110" s="2"/>
-      <c r="W110" s="2"/>
+      <c r="W110" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X110" s="2"/>
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
@@ -15009,7 +15054,7 @@
       </c>
       <c r="G111" s="2">
         <f t="shared" si="16"/>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
@@ -15117,7 +15162,7 @@
       </c>
       <c r="G112" s="2">
         <f t="shared" si="16"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
@@ -15219,7 +15264,7 @@
       </c>
       <c r="D113" s="54">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" s="54"/>
       <c r="F113" s="2" t="s">
@@ -15227,15 +15272,15 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="16"/>
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="I113" s="6">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J113" s="2"/>
       <c r="K113" s="2"/>
@@ -15252,7 +15297,9 @@
         <v>352</v>
       </c>
       <c r="V113" s="2"/>
-      <c r="W113" s="2"/>
+      <c r="W113" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X113" s="2"/>
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
@@ -15333,7 +15380,7 @@
       </c>
       <c r="G114" s="2">
         <f t="shared" si="16"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
@@ -15441,7 +15488,7 @@
       </c>
       <c r="G115" s="2">
         <f t="shared" si="16"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
@@ -15543,7 +15590,7 @@
       </c>
       <c r="D116" s="54">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="54"/>
       <c r="F116" s="2" t="s">
@@ -15551,15 +15598,15 @@
       </c>
       <c r="G116" s="2">
         <f t="shared" si="16"/>
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H116" s="6">
         <f>I116+개인기록Sheet!C116</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I116" s="6">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
@@ -15576,7 +15623,9 @@
         <v>352</v>
       </c>
       <c r="V116" s="2"/>
-      <c r="W116" s="2"/>
+      <c r="W116" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X116" s="2"/>
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
@@ -15649,7 +15698,7 @@
       </c>
       <c r="D117" s="54">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="54"/>
       <c r="F117" s="2" t="s">
@@ -15657,15 +15706,15 @@
       </c>
       <c r="G117" s="2">
         <f t="shared" si="16"/>
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H117" s="6">
         <f>I117+개인기록Sheet!C117</f>
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="I117" s="6">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
@@ -15682,7 +15731,9 @@
         <v>352</v>
       </c>
       <c r="V117" s="2"/>
-      <c r="W117" s="2"/>
+      <c r="W117" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X117" s="2"/>
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
@@ -15763,7 +15814,7 @@
       </c>
       <c r="G118" s="2">
         <f t="shared" si="16"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
@@ -15861,7 +15912,7 @@
       </c>
       <c r="D119" s="54">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" s="54"/>
       <c r="F119" s="2" t="s">
@@ -15869,15 +15920,15 @@
       </c>
       <c r="G119" s="2">
         <f t="shared" si="16"/>
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H119" s="6">
         <f>I119+개인기록Sheet!C119</f>
-        <v>2.9000000000000004</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="I119" s="6">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
@@ -15896,7 +15947,9 @@
       <c r="V119" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="W119" s="2"/>
+      <c r="W119" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X119" s="2"/>
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
@@ -15969,7 +16022,7 @@
       </c>
       <c r="D120" s="54">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E120" s="54"/>
       <c r="F120" s="2" t="s">
@@ -15977,15 +16030,15 @@
       </c>
       <c r="G120" s="2">
         <f t="shared" si="16"/>
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H120" s="6">
         <f>I120+개인기록Sheet!C120</f>
-        <v>3.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I120" s="6">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
@@ -16004,7 +16057,9 @@
       <c r="V120" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="W120" s="2"/>
+      <c r="W120" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X120" s="2"/>
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
@@ -16291,7 +16346,7 @@
       </c>
       <c r="G123" s="2">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H123" s="6">
         <f>I123+개인기록Sheet!C123</f>
@@ -16382,7 +16437,6 @@
       <c r="CD123" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:CT123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:E123">
     <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="지급">
@@ -16406,7 +16460,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:V86"/>
+  <dimension ref="A2:V98"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -18253,7 +18307,7 @@
         <v>383</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="E63" s="77" t="s">
         <v>82</v>
@@ -18351,7 +18405,7 @@
       </c>
       <c r="U65" s="9"/>
       <c r="V65" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
@@ -18386,7 +18440,7 @@
         <v>202</v>
       </c>
       <c r="T66" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="U66" s="9"/>
       <c r="V66" s="13" t="s">
@@ -18579,7 +18633,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
@@ -18591,17 +18645,17 @@
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
       <c r="M72" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="N72" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="N72" s="20" t="s">
+      <c r="O72" s="20" t="s">
         <v>388</v>
-      </c>
-      <c r="O72" s="20" t="s">
-        <v>389</v>
       </c>
       <c r="P72" s="20"/>
       <c r="Q72" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R72" s="9" t="s">
         <v>104</v>
@@ -18679,7 +18733,7 @@
         <v>383</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="E77" s="77" t="s">
         <v>82</v>
@@ -18997,96 +19051,395 @@
       <c r="U86" s="2"/>
       <c r="V86" s="2"/>
     </row>
+    <row r="89" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B89" s="11">
+        <v>46149</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="E89" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="F89" s="77"/>
+      <c r="G89" s="77"/>
+      <c r="H89" s="77"/>
+      <c r="I89" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="J89" s="78"/>
+      <c r="K89" s="78"/>
+      <c r="L89" s="78"/>
+      <c r="M89" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="N89" s="79"/>
+      <c r="O89" s="79"/>
+      <c r="P89" s="79"/>
+      <c r="Q89" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="R89" s="80"/>
+      <c r="S89" s="80"/>
+      <c r="T89" s="80"/>
+      <c r="U89" s="80"/>
+      <c r="V89" s="80"/>
+    </row>
+    <row r="90" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B90" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C90" s="75">
+        <v>3</v>
+      </c>
+      <c r="D90" s="75">
+        <v>0</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H90" s="7"/>
+      <c r="I90" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="K90" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="L90" s="8"/>
+      <c r="M90" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="N90" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="O90" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="P90" s="20"/>
+      <c r="Q90" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="R90" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="S90" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="T90" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="U90" s="9"/>
+      <c r="V90" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="91" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B91" s="74"/>
+      <c r="C91" s="76"/>
+      <c r="D91" s="76"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="20"/>
+      <c r="N91" s="20"/>
+      <c r="O91" s="20"/>
+      <c r="P91" s="20"/>
+      <c r="Q91" s="9"/>
+      <c r="R91" s="9"/>
+      <c r="S91" s="9"/>
+      <c r="T91" s="9"/>
+      <c r="U91" s="9"/>
+      <c r="V91" s="13"/>
+    </row>
+    <row r="92" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B92" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C92" s="75">
+        <v>2</v>
+      </c>
+      <c r="D92" s="75">
+        <v>2</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+      <c r="M92" s="20"/>
+      <c r="N92" s="20"/>
+      <c r="O92" s="20"/>
+      <c r="P92" s="20"/>
+      <c r="Q92" s="9"/>
+      <c r="R92" s="9"/>
+      <c r="S92" s="9"/>
+      <c r="T92" s="9"/>
+      <c r="U92" s="9"/>
+      <c r="V92" s="13"/>
+    </row>
+    <row r="93" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B93" s="74"/>
+      <c r="C93" s="76"/>
+      <c r="D93" s="76"/>
+      <c r="E93" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="20"/>
+      <c r="N93" s="20"/>
+      <c r="O93" s="20"/>
+      <c r="P93" s="20"/>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
+      <c r="S93" s="9"/>
+      <c r="T93" s="9"/>
+      <c r="U93" s="9"/>
+      <c r="V93" s="13"/>
+    </row>
+    <row r="94" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B94" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" s="75">
+        <v>1</v>
+      </c>
+      <c r="D94" s="75">
+        <v>0</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="N94" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="O94" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="P94" s="20"/>
+      <c r="Q94" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="R94" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="S94" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="T94" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="U94" s="9"/>
+      <c r="V94" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="95" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B95" s="74"/>
+      <c r="C95" s="76"/>
+      <c r="D95" s="76"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="20"/>
+      <c r="N95" s="20"/>
+      <c r="O95" s="20"/>
+      <c r="P95" s="20"/>
+      <c r="Q95" s="9"/>
+      <c r="R95" s="9"/>
+      <c r="S95" s="9"/>
+      <c r="T95" s="9"/>
+      <c r="U95" s="9"/>
+      <c r="V95" s="13"/>
+    </row>
+    <row r="96" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B96" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C96" s="75">
+        <v>4</v>
+      </c>
+      <c r="D96" s="75">
+        <v>0</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="K96" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="M96" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="N96" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="O96" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="P96" s="20"/>
+      <c r="Q96" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="R96" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="S96" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="T96" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="U96" s="9"/>
+      <c r="V96" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="97" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B97" s="74"/>
+      <c r="C97" s="76"/>
+      <c r="D97" s="76"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="20"/>
+      <c r="N97" s="20"/>
+      <c r="O97" s="20"/>
+      <c r="P97" s="20"/>
+      <c r="Q97" s="9"/>
+      <c r="R97" s="9"/>
+      <c r="S97" s="9"/>
+      <c r="T97" s="9"/>
+      <c r="U97" s="9"/>
+      <c r="V97" s="13"/>
+    </row>
+    <row r="98" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B98" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C98" s="2">
+        <f>SUM(C90:C97)</f>
+        <v>10</v>
+      </c>
+      <c r="D98" s="2">
+        <f>SUM(D90:D97)</f>
+        <v>2</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" s="2"/>
+      <c r="Q98" s="2"/>
+      <c r="R98" s="2"/>
+      <c r="S98" s="2"/>
+      <c r="T98" s="2"/>
+      <c r="U98" s="2"/>
+      <c r="V98" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="121">
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
+  <mergeCells count="137">
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="M77:P77"/>
     <mergeCell ref="Q77:V77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -19111,15 +19464,94 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="I2:L2"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -19161,23 +19593,23 @@
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -19255,12 +19687,12 @@
         <v>김인혁</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" ref="C4:C35" si="0">((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
-        <v>1.2000000000000002</v>
+        <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D4" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B4)</f>
@@ -19279,8 +19711,8 @@
         <v>0</v>
       </c>
       <c r="I4" s="14">
-        <f t="shared" ref="I4:I35" si="1">SUM(D4:H4)</f>
-        <v>6</v>
+        <f>SUM(D4:H4)</f>
+        <v>7</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="2">
@@ -19290,35 +19722,35 @@
         <v>224</v>
       </c>
       <c r="M4" s="21">
-        <f t="shared" ref="M4:M15" si="2">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
+        <f t="shared" ref="M4:M17" si="0">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
         <v>10</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>53</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O13" si="3">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
+        <f t="shared" ref="O4:O13" si="1">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
         <v>6</v>
       </c>
       <c r="P4" s="34" t="s">
         <v>222</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q13" si="4">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
-        <v>6</v>
+        <f t="shared" ref="Q4:Q13" si="2">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
+        <v>8</v>
       </c>
       <c r="R4" s="35" t="s">
-        <v>325</v>
+        <v>231</v>
       </c>
       <c r="S4" s="55">
-        <f t="shared" ref="S4:S15" si="5">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
-        <v>9</v>
+        <f t="shared" ref="S4:S17" si="3">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
+        <v>11</v>
       </c>
       <c r="T4" s="36" t="s">
         <v>229</v>
       </c>
       <c r="U4" s="56">
-        <f t="shared" ref="U4:U15" si="6">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
+        <f t="shared" ref="U4:U18" si="4">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
         <v>6</v>
       </c>
     </row>
@@ -19332,7 +19764,7 @@
         <v>신재경</v>
       </c>
       <c r="C5" s="2">
-        <f t="shared" si="0"/>
+        <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
         <v>0</v>
       </c>
       <c r="D5" s="14">
@@ -19356,7 +19788,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D5:H5)</f>
         <v>0</v>
       </c>
       <c r="J5" s="15"/>
@@ -19367,35 +19799,35 @@
         <v>222</v>
       </c>
       <c r="M5" s="21">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N5" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="O5" s="22">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="P5" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q5" s="23">
         <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="N5" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" s="22">
+        <v>7</v>
+      </c>
+      <c r="R5" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="S5" s="55">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P5" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="23">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="R5" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="S5" s="55">
-        <f t="shared" si="5"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" s="36" t="s">
         <v>42</v>
       </c>
       <c r="U5" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
@@ -19409,7 +19841,7 @@
         <v>정효태</v>
       </c>
       <c r="C6" s="2">
-        <f t="shared" si="0"/>
+        <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
         <v>0</v>
       </c>
       <c r="D6" s="14">
@@ -19433,7 +19865,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D6:H6)</f>
         <v>0</v>
       </c>
       <c r="J6" s="15"/>
@@ -19444,35 +19876,35 @@
         <v>354</v>
       </c>
       <c r="M6" s="21">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N6" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" s="22">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q6" s="23">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N6" s="33" t="s">
-        <v>354</v>
-      </c>
-      <c r="O6" s="22">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P6" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="23">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
       <c r="R6" s="35" t="s">
         <v>365</v>
       </c>
       <c r="S6" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="T6" s="36" t="s">
         <v>357</v>
       </c>
       <c r="U6" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
@@ -19486,7 +19918,7 @@
         <v>이승민</v>
       </c>
       <c r="C7" s="2">
-        <f t="shared" si="0"/>
+        <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
         <v>0</v>
       </c>
       <c r="D7" s="14">
@@ -19510,7 +19942,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D7:H7)</f>
         <v>0</v>
       </c>
       <c r="J7" s="15"/>
@@ -19521,35 +19953,35 @@
         <v>361</v>
       </c>
       <c r="M7" s="21">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N7" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="O7" s="22">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="P7" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q7" s="23">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N7" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="O7" s="22">
+        <v>5</v>
+      </c>
+      <c r="R7" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="S7" s="55">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="P7" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="U7" s="56">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="R7" s="35" t="s">
-        <v>357</v>
-      </c>
-      <c r="S7" s="55">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="T7" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="U7" s="56">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19563,7 +19995,7 @@
         <v>이정석</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" si="0"/>
+        <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
         <v>0</v>
       </c>
       <c r="D8" s="14">
@@ -19587,7 +20019,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D8:H8)</f>
         <v>0</v>
       </c>
       <c r="J8" s="15"/>
@@ -19598,35 +20030,35 @@
         <v>305</v>
       </c>
       <c r="M8" s="21">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N8" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="O8" s="22">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q8" s="23">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N8" s="33" t="s">
-        <v>361</v>
-      </c>
-      <c r="O8" s="22">
+        <v>3</v>
+      </c>
+      <c r="R8" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="S8" s="55">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P8" s="34" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q8" s="23">
+        <v>6</v>
+      </c>
+      <c r="T8" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="U8" s="56">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="S8" s="55">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="T8" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="U8" s="56">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19640,7 +20072,7 @@
         <v>강종찬</v>
       </c>
       <c r="C9" s="2">
-        <f t="shared" si="0"/>
+        <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D9" s="14">
@@ -19664,7 +20096,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D9:H9)</f>
         <v>2</v>
       </c>
       <c r="J9" s="15"/>
@@ -19672,38 +20104,38 @@
         <v>6</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>394</v>
+        <v>50</v>
       </c>
       <c r="M9" s="21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="O9" s="22">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="P9" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q9" s="23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="R9" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="S9" s="55">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="T9" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="O9" s="22">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P9" s="34" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q9" s="23">
+      <c r="U9" s="56">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="S9" s="55">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="T9" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="U9" s="56">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19717,20 +20149,20 @@
         <v>강관석</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D10" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B10)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B10)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B10)</f>
@@ -19738,49 +20170,49 @@
       </c>
       <c r="H10" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="14">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>SUM(D10:H10)</f>
+        <v>9</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="2">
         <v>7</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M10" s="21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="O10" s="22">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q10" s="23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="N10" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="O10" s="22">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P10" s="34" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q10" s="23">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
       <c r="R10" s="35" t="s">
         <v>303</v>
       </c>
       <c r="S10" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="T10" s="36" t="s">
-        <v>221</v>
+        <v>64</v>
       </c>
       <c r="U10" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -19794,7 +20226,7 @@
         <v>강기혁</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="0"/>
+        <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
         <v>2.8000000000000003</v>
       </c>
       <c r="D11" s="14">
@@ -19818,7 +20250,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D11:H11)</f>
         <v>13</v>
       </c>
       <c r="J11" s="15"/>
@@ -19826,38 +20258,38 @@
         <v>8</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>50</v>
+        <v>232</v>
       </c>
       <c r="M11" s="21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N11" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="O11" s="22">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q11" s="23">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N11" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="O11" s="22">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P11" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q11" s="23">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
       <c r="R11" s="35" t="s">
         <v>324</v>
       </c>
       <c r="S11" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="T11" s="36" t="s">
-        <v>325</v>
+        <v>233</v>
       </c>
       <c r="U11" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -19871,7 +20303,7 @@
         <v>강도일</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="0"/>
+        <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
         <v>0</v>
       </c>
       <c r="D12" s="14">
@@ -19895,7 +20327,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D12:H12)</f>
         <v>0</v>
       </c>
       <c r="J12" s="15"/>
@@ -19903,38 +20335,38 @@
         <v>9</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>229</v>
+        <v>394</v>
       </c>
       <c r="M12" s="21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="O12" s="22">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P12" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q12" s="23">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N12" s="33" t="s">
+      <c r="R12" s="35" t="s">
         <v>393</v>
       </c>
-      <c r="O12" s="22">
+      <c r="S12" s="55">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P12" s="34" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q12" s="23">
+        <v>3</v>
+      </c>
+      <c r="T12" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="U12" s="56">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="S12" s="55">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="T12" s="36" t="s">
-        <v>366</v>
-      </c>
-      <c r="U12" s="56">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -19948,7 +20380,7 @@
         <v>강일수</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" si="0"/>
+        <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
         <v>0</v>
       </c>
       <c r="D13" s="14">
@@ -19972,7 +20404,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D13:H13)</f>
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -19980,38 +20412,38 @@
         <v>10</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>360</v>
+        <v>299</v>
       </c>
       <c r="M13" s="21">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="O13" s="22">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P13" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q13" s="23">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N13" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="O13" s="22">
+      <c r="R13" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="S13" s="55">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P13" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q13" s="23">
+        <v>3</v>
+      </c>
+      <c r="T13" s="36" t="s">
+        <v>325</v>
+      </c>
+      <c r="U13" s="56">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="S13" s="55">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="T13" s="36" t="s">
-        <v>365</v>
-      </c>
-      <c r="U13" s="56">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -20025,7 +20457,7 @@
         <v>구교훈</v>
       </c>
       <c r="C14" s="2">
-        <f t="shared" si="0"/>
+        <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
@@ -20049,7 +20481,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D14:H14)</f>
         <v>0</v>
       </c>
       <c r="J14" s="15"/>
@@ -20057,10 +20489,10 @@
         <v>11</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>392</v>
+        <v>229</v>
       </c>
       <c r="M14" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N14" s="33"/>
@@ -20068,17 +20500,17 @@
       <c r="P14" s="34"/>
       <c r="Q14" s="23"/>
       <c r="R14" s="55" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="S14" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="T14" s="36" t="s">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="U14" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -20092,7 +20524,7 @@
         <v>권주용</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" si="0"/>
+        <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
         <v>0</v>
       </c>
       <c r="D15" s="14">
@@ -20116,7 +20548,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D15:H15)</f>
         <v>0</v>
       </c>
       <c r="J15" s="15"/>
@@ -20124,10 +20556,10 @@
         <v>12</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>42</v>
+        <v>360</v>
       </c>
       <c r="M15" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N15" s="22"/>
@@ -20135,17 +20567,17 @@
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="55" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="S15" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="T15" s="56" t="s">
-        <v>377</v>
+        <v>232</v>
       </c>
       <c r="U15" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -20159,8 +20591,8 @@
         <v>김기문</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
+        <v>0.7</v>
       </c>
       <c r="D16" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B16)</f>
@@ -20172,34 +20604,49 @@
       </c>
       <c r="F16" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(D16:H16)</f>
+        <v>3</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="2">
         <v>13</v>
       </c>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
+      <c r="L16" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="M16" s="21">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="23"/>
       <c r="Q16" s="23"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="56"/>
-      <c r="U16" s="56"/>
+      <c r="R16" s="55" t="s">
+        <v>385</v>
+      </c>
+      <c r="S16" s="55">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T16" s="56" t="s">
+        <v>365</v>
+      </c>
+      <c r="U16" s="56">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -20211,16 +20658,16 @@
         <v>김기태</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
+        <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D17" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B17)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B17)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B17)</f>
@@ -20235,23 +20682,38 @@
         <v>0</v>
       </c>
       <c r="I17" s="14">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f>SUM(D17:H17)</f>
+        <v>11</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="2">
         <v>14</v>
       </c>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
+      <c r="L17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="M17" s="21">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
       <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="56"/>
-      <c r="U17" s="56"/>
+      <c r="R17" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="S17" s="55">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T17" s="56" t="s">
+        <v>303</v>
+      </c>
+      <c r="U17" s="56">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -20263,7 +20725,7 @@
         <v>김덕준</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" si="0"/>
+        <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
         <v>0</v>
       </c>
       <c r="D18" s="14">
@@ -20287,7 +20749,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D18:H18)</f>
         <v>0</v>
       </c>
       <c r="J18" s="15"/>
@@ -20302,8 +20764,13 @@
       <c r="Q18" s="23"/>
       <c r="R18" s="55"/>
       <c r="S18" s="55"/>
-      <c r="T18" s="56"/>
-      <c r="U18" s="56"/>
+      <c r="T18" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="U18" s="56">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -20315,7 +20782,7 @@
         <v>김동인</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" si="0"/>
+        <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
         <v>0</v>
       </c>
       <c r="D19" s="14">
@@ -20339,7 +20806,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D19:H19)</f>
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
@@ -20354,7 +20821,7 @@
         <v>김민섭</v>
       </c>
       <c r="C20" s="2">
-        <f t="shared" si="0"/>
+        <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D20" s="14">
@@ -20378,7 +20845,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D20:H20)</f>
         <v>1</v>
       </c>
       <c r="J20" s="15"/>
@@ -20393,7 +20860,7 @@
         <v>김민준</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" si="0"/>
+        <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
         <v>0</v>
       </c>
       <c r="D21" s="14">
@@ -20417,7 +20884,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D21:H21)</f>
         <v>0</v>
       </c>
       <c r="J21" s="15"/>
@@ -20432,7 +20899,7 @@
         <v>김민찬</v>
       </c>
       <c r="C22" s="2">
-        <f t="shared" si="0"/>
+        <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
         <v>0</v>
       </c>
       <c r="D22" s="14">
@@ -20456,7 +20923,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D22:H22)</f>
         <v>0</v>
       </c>
       <c r="J22" s="15"/>
@@ -20471,7 +20938,7 @@
         <v>김범기</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" si="0"/>
+        <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
         <v>0</v>
       </c>
       <c r="D23" s="14">
@@ -20495,7 +20962,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D23:H23)</f>
         <v>0</v>
       </c>
       <c r="J23" s="15"/>
@@ -20510,7 +20977,7 @@
         <v>김병준</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" si="0"/>
+        <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
         <v>0</v>
       </c>
       <c r="D24" s="14">
@@ -20534,7 +21001,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D24:H24)</f>
         <v>0</v>
       </c>
       <c r="J24" s="15"/>
@@ -20549,7 +21016,7 @@
         <v>김부건</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" si="0"/>
+        <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
         <v>0</v>
       </c>
       <c r="D25" s="14">
@@ -20573,7 +21040,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D25:H25)</f>
         <v>0</v>
       </c>
       <c r="J25" s="15"/>
@@ -20588,7 +21055,7 @@
         <v>김성수</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" si="0"/>
+        <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
         <v>0.89999999999999991</v>
       </c>
       <c r="D26" s="14">
@@ -20612,7 +21079,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D26:H26)</f>
         <v>3</v>
       </c>
       <c r="J26" s="15"/>
@@ -20627,8 +21094,8 @@
         <v>김성준</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
+        <v>6</v>
       </c>
       <c r="D27" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B27)</f>
@@ -20636,23 +21103,23 @@
       </c>
       <c r="E27" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B27)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B27)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B27)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B27)</f>
         <v>1</v>
       </c>
       <c r="I27" s="14">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <f>SUM(D27:H27)</f>
+        <v>26</v>
       </c>
       <c r="J27" s="15"/>
     </row>
@@ -20666,8 +21133,8 @@
         <v>김송환</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" si="0"/>
-        <v>1.4</v>
+        <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
+        <v>2.3000000000000003</v>
       </c>
       <c r="D28" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B28)</f>
@@ -20679,7 +21146,7 @@
       </c>
       <c r="F28" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B28)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B28)</f>
@@ -20690,8 +21157,8 @@
         <v>1</v>
       </c>
       <c r="I28" s="14">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f>SUM(D28:H28)</f>
+        <v>8</v>
       </c>
       <c r="J28" s="15"/>
     </row>
@@ -20705,7 +21172,7 @@
         <v>김영태</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" si="0"/>
+        <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
         <v>0</v>
       </c>
       <c r="D29" s="14">
@@ -20729,7 +21196,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D29:H29)</f>
         <v>0</v>
       </c>
       <c r="J29" s="15"/>
@@ -20744,7 +21211,7 @@
         <v>김용빈</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" si="0"/>
+        <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
         <v>0</v>
       </c>
       <c r="D30" s="14">
@@ -20768,7 +21235,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D30:H30)</f>
         <v>0</v>
       </c>
       <c r="J30" s="15"/>
@@ -20783,7 +21250,7 @@
         <v>김용현</v>
       </c>
       <c r="C31" s="2">
-        <f t="shared" si="0"/>
+        <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
         <v>2.9000000000000004</v>
       </c>
       <c r="D31" s="14">
@@ -20807,7 +21274,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D31:H31)</f>
         <v>12</v>
       </c>
       <c r="J31" s="15"/>
@@ -20822,7 +21289,7 @@
         <v>김우인</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" si="0"/>
+        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
         <v>1.6</v>
       </c>
       <c r="D32" s="14">
@@ -20846,7 +21313,7 @@
         <v>6</v>
       </c>
       <c r="I32" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D32:H32)</f>
         <v>8</v>
       </c>
       <c r="J32" s="15"/>
@@ -20861,7 +21328,7 @@
         <v>김종준</v>
       </c>
       <c r="C33" s="2">
-        <f t="shared" si="0"/>
+        <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
         <v>0</v>
       </c>
       <c r="D33" s="14">
@@ -20885,7 +21352,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D33:H33)</f>
         <v>0</v>
       </c>
       <c r="J33" s="15"/>
@@ -20900,7 +21367,7 @@
         <v>김종혁</v>
       </c>
       <c r="C34" s="2">
-        <f t="shared" si="0"/>
+        <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D34" s="14">
@@ -20924,7 +21391,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D34:H34)</f>
         <v>3</v>
       </c>
       <c r="J34" s="15"/>
@@ -20939,7 +21406,7 @@
         <v>김준영</v>
       </c>
       <c r="C35" s="2">
-        <f t="shared" si="0"/>
+        <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
         <v>0</v>
       </c>
       <c r="D35" s="14">
@@ -20963,7 +21430,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D35:H35)</f>
         <v>0</v>
       </c>
       <c r="J35" s="15"/>
@@ -20978,7 +21445,7 @@
         <v>김진형</v>
       </c>
       <c r="C36" s="2">
-        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
         <v>0</v>
       </c>
       <c r="D36" s="14">
@@ -21002,7 +21469,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="14">
-        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
+        <f>SUM(D36:H36)</f>
         <v>0</v>
       </c>
       <c r="J36" s="15"/>
@@ -21017,16 +21484,16 @@
         <v>김진호</v>
       </c>
       <c r="C37" s="2">
-        <f t="shared" si="7"/>
-        <v>1.8</v>
+        <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D37" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B37)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E37" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B37)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F37" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B37)</f>
@@ -21041,8 +21508,8 @@
         <v>0</v>
       </c>
       <c r="I37" s="14">
-        <f t="shared" si="8"/>
-        <v>9</v>
+        <f>SUM(D37:H37)</f>
+        <v>14</v>
       </c>
       <c r="J37" s="15"/>
     </row>
@@ -21056,7 +21523,7 @@
         <v>김태성</v>
       </c>
       <c r="C38" s="2">
-        <f t="shared" si="7"/>
+        <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D38" s="14">
@@ -21080,7 +21547,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D38:H38)</f>
         <v>1</v>
       </c>
       <c r="J38" s="15"/>
@@ -21095,7 +21562,7 @@
         <v>김태양</v>
       </c>
       <c r="C39" s="2">
-        <f t="shared" si="7"/>
+        <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
         <v>0</v>
       </c>
       <c r="D39" s="14">
@@ -21119,7 +21586,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D39:H39)</f>
         <v>0</v>
       </c>
       <c r="J39" s="15"/>
@@ -21134,7 +21601,7 @@
         <v>김태완</v>
       </c>
       <c r="C40" s="2">
-        <f t="shared" si="7"/>
+        <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
         <v>0</v>
       </c>
       <c r="D40" s="14">
@@ -21158,7 +21625,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D40:H40)</f>
         <v>0</v>
       </c>
       <c r="J40" s="15"/>
@@ -21173,7 +21640,7 @@
         <v>김태호</v>
       </c>
       <c r="C41" s="2">
-        <f t="shared" si="7"/>
+        <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
         <v>0</v>
       </c>
       <c r="D41" s="14">
@@ -21197,7 +21664,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D41:H41)</f>
         <v>0</v>
       </c>
       <c r="J41" s="15"/>
@@ -21212,7 +21679,7 @@
         <v>김현우</v>
       </c>
       <c r="C42" s="2">
-        <f t="shared" si="7"/>
+        <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
         <v>0</v>
       </c>
       <c r="D42" s="14">
@@ -21236,7 +21703,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D42:H42)</f>
         <v>0</v>
       </c>
       <c r="J42" s="15"/>
@@ -21251,7 +21718,7 @@
         <v>김형원</v>
       </c>
       <c r="C43" s="2">
-        <f t="shared" si="7"/>
+        <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
         <v>0</v>
       </c>
       <c r="D43" s="14">
@@ -21275,7 +21742,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D43:H43)</f>
         <v>0</v>
       </c>
       <c r="J43" s="15"/>
@@ -21290,7 +21757,7 @@
         <v>노민준</v>
       </c>
       <c r="C44" s="2">
-        <f t="shared" si="7"/>
+        <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
         <v>1.8</v>
       </c>
       <c r="D44" s="14">
@@ -21314,7 +21781,7 @@
         <v>2</v>
       </c>
       <c r="I44" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D44:H44)</f>
         <v>9</v>
       </c>
       <c r="J44" s="15"/>
@@ -21329,7 +21796,7 @@
         <v>류서진</v>
       </c>
       <c r="C45" s="2">
-        <f t="shared" si="7"/>
+        <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
         <v>0</v>
       </c>
       <c r="D45" s="14">
@@ -21353,7 +21820,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D45:H45)</f>
         <v>0</v>
       </c>
       <c r="J45" s="15"/>
@@ -21368,7 +21835,7 @@
         <v>마창기</v>
       </c>
       <c r="C46" s="2">
-        <f t="shared" si="7"/>
+        <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
         <v>0</v>
       </c>
       <c r="D46" s="14">
@@ -21392,7 +21859,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D46:H46)</f>
         <v>0</v>
       </c>
       <c r="J46" s="15"/>
@@ -21407,7 +21874,7 @@
         <v>문준수</v>
       </c>
       <c r="C47" s="2">
-        <f t="shared" si="7"/>
+        <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D47" s="14">
@@ -21431,7 +21898,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D47:H47)</f>
         <v>3</v>
       </c>
       <c r="J47" s="15"/>
@@ -21446,7 +21913,7 @@
         <v>민건호</v>
       </c>
       <c r="C48" s="2">
-        <f t="shared" si="7"/>
+        <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
         <v>0</v>
       </c>
       <c r="D48" s="14">
@@ -21470,7 +21937,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D48:H48)</f>
         <v>0</v>
       </c>
       <c r="J48" s="15"/>
@@ -21485,7 +21952,7 @@
         <v>박수천</v>
       </c>
       <c r="C49" s="2">
-        <f t="shared" si="7"/>
+        <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
         <v>0</v>
       </c>
       <c r="D49" s="14">
@@ -21509,7 +21976,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D49:H49)</f>
         <v>0</v>
       </c>
       <c r="J49" s="15"/>
@@ -21524,7 +21991,7 @@
         <v>박정호</v>
       </c>
       <c r="C50" s="2">
-        <f t="shared" si="7"/>
+        <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
         <v>0</v>
       </c>
       <c r="D50" s="14">
@@ -21548,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D50:H50)</f>
         <v>0</v>
       </c>
       <c r="J50" s="15"/>
@@ -21563,7 +22030,7 @@
         <v>박주연</v>
       </c>
       <c r="C51" s="2">
-        <f t="shared" si="7"/>
+        <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="D51" s="14">
@@ -21587,7 +22054,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D51:H51)</f>
         <v>7</v>
       </c>
       <c r="J51" s="15"/>
@@ -21602,7 +22069,7 @@
         <v>박주현</v>
       </c>
       <c r="C52" s="2">
-        <f t="shared" si="7"/>
+        <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
         <v>0</v>
       </c>
       <c r="D52" s="14">
@@ -21626,7 +22093,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D52:H52)</f>
         <v>0</v>
       </c>
       <c r="J52" s="15"/>
@@ -21641,7 +22108,7 @@
         <v>박하빈</v>
       </c>
       <c r="C53" s="2">
-        <f t="shared" si="7"/>
+        <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
         <v>0</v>
       </c>
       <c r="D53" s="14">
@@ -21665,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D53:H53)</f>
         <v>0</v>
       </c>
       <c r="J53" s="15"/>
@@ -21680,7 +22147,7 @@
         <v>박형기</v>
       </c>
       <c r="C54" s="2">
-        <f t="shared" si="7"/>
+        <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
         <v>0</v>
       </c>
       <c r="D54" s="14">
@@ -21704,7 +22171,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D54:H54)</f>
         <v>0</v>
       </c>
       <c r="J54" s="15"/>
@@ -21719,7 +22186,7 @@
         <v>손경호</v>
       </c>
       <c r="C55" s="2">
-        <f t="shared" si="7"/>
+        <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D55" s="14">
@@ -21743,7 +22210,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D55:H55)</f>
         <v>2</v>
       </c>
       <c r="J55" s="15"/>
@@ -21758,7 +22225,7 @@
         <v>송윤상</v>
       </c>
       <c r="C56" s="2">
-        <f t="shared" si="7"/>
+        <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
         <v>0.6</v>
       </c>
       <c r="D56" s="14">
@@ -21782,7 +22249,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D56:H56)</f>
         <v>2</v>
       </c>
       <c r="J56" s="15"/>
@@ -21797,8 +22264,8 @@
         <v>신기웅</v>
       </c>
       <c r="C57" s="2">
-        <f t="shared" si="7"/>
-        <v>0.60000000000000009</v>
+        <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D57" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B57)</f>
@@ -21814,15 +22281,15 @@
       </c>
       <c r="G57" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B57)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B57)</f>
         <v>0</v>
       </c>
       <c r="I57" s="14">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f>SUM(D57:H57)</f>
+        <v>6</v>
       </c>
       <c r="J57" s="15"/>
     </row>
@@ -21836,7 +22303,7 @@
         <v>신종훈</v>
       </c>
       <c r="C58" s="2">
-        <f t="shared" si="7"/>
+        <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
         <v>0</v>
       </c>
       <c r="D58" s="14">
@@ -21860,7 +22327,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D58:H58)</f>
         <v>0</v>
       </c>
       <c r="J58" s="15"/>
@@ -21875,7 +22342,7 @@
         <v>안진혁</v>
       </c>
       <c r="C59" s="2">
-        <f t="shared" si="7"/>
+        <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
         <v>0</v>
       </c>
       <c r="D59" s="14">
@@ -21899,7 +22366,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D59:H59)</f>
         <v>0</v>
       </c>
       <c r="J59" s="15"/>
@@ -21914,7 +22381,7 @@
         <v>양진웅</v>
       </c>
       <c r="C60" s="2">
-        <f t="shared" si="7"/>
+        <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
         <v>0.5</v>
       </c>
       <c r="D60" s="14">
@@ -21938,7 +22405,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D60:H60)</f>
         <v>2</v>
       </c>
       <c r="J60" s="15"/>
@@ -21953,7 +22420,7 @@
         <v>오우영</v>
       </c>
       <c r="C61" s="2">
-        <f t="shared" si="7"/>
+        <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
         <v>1.5</v>
       </c>
       <c r="D61" s="14">
@@ -21977,7 +22444,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D61:H61)</f>
         <v>6</v>
       </c>
       <c r="J61" s="15"/>
@@ -21992,7 +22459,7 @@
         <v>오운용</v>
       </c>
       <c r="C62" s="2">
-        <f t="shared" si="7"/>
+        <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
         <v>0</v>
       </c>
       <c r="D62" s="14">
@@ -22016,7 +22483,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D62:H62)</f>
         <v>0</v>
       </c>
       <c r="J62" s="15"/>
@@ -22031,7 +22498,7 @@
         <v>오진환</v>
       </c>
       <c r="C63" s="2">
-        <f t="shared" si="7"/>
+        <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
         <v>0</v>
       </c>
       <c r="D63" s="14">
@@ -22055,7 +22522,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D63:H63)</f>
         <v>0</v>
       </c>
       <c r="J63" s="15"/>
@@ -22070,7 +22537,7 @@
         <v>우보광</v>
       </c>
       <c r="C64" s="2">
-        <f t="shared" si="7"/>
+        <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
         <v>0</v>
       </c>
       <c r="D64" s="14">
@@ -22094,7 +22561,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D64:H64)</f>
         <v>0</v>
       </c>
       <c r="J64" s="15"/>
@@ -22109,8 +22576,8 @@
         <v>유상근</v>
       </c>
       <c r="C65" s="2">
-        <f t="shared" si="7"/>
-        <v>2.2000000000000002</v>
+        <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D65" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B65)</f>
@@ -22126,15 +22593,15 @@
       </c>
       <c r="G65" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B65)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H65" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B65)</f>
         <v>1</v>
       </c>
       <c r="I65" s="14">
-        <f t="shared" si="8"/>
-        <v>11</v>
+        <f>SUM(D65:H65)</f>
+        <v>12</v>
       </c>
       <c r="J65" s="15"/>
     </row>
@@ -22148,7 +22615,7 @@
         <v>유인상</v>
       </c>
       <c r="C66" s="2">
-        <f t="shared" si="7"/>
+        <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
         <v>0</v>
       </c>
       <c r="D66" s="14">
@@ -22172,7 +22639,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D66:H66)</f>
         <v>0</v>
       </c>
       <c r="J66" s="15"/>
@@ -22187,7 +22654,7 @@
         <v>유정훈</v>
       </c>
       <c r="C67" s="2">
-        <f t="shared" si="7"/>
+        <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="D67" s="14">
@@ -22211,7 +22678,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D67:H67)</f>
         <v>5</v>
       </c>
       <c r="J67" s="15"/>
@@ -22226,7 +22693,7 @@
         <v>유진효</v>
       </c>
       <c r="C68" s="2">
-        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
         <v>0</v>
       </c>
       <c r="D68" s="14">
@@ -22250,7 +22717,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="14">
-        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
+        <f>SUM(D68:H68)</f>
         <v>0</v>
       </c>
       <c r="J68" s="15"/>
@@ -22265,7 +22732,7 @@
         <v>윤원택</v>
       </c>
       <c r="C69" s="2">
-        <f t="shared" si="9"/>
+        <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
         <v>0</v>
       </c>
       <c r="D69" s="14">
@@ -22289,7 +22756,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D69:H69)</f>
         <v>0</v>
       </c>
       <c r="J69" s="15"/>
@@ -22304,8 +22771,8 @@
         <v>윤창현</v>
       </c>
       <c r="C70" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D70" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B70)</f>
@@ -22321,15 +22788,15 @@
       </c>
       <c r="G70" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B70)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H70" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B70)</f>
         <v>0</v>
       </c>
       <c r="I70" s="14">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>SUM(D70:H70)</f>
+        <v>3</v>
       </c>
       <c r="J70" s="15"/>
     </row>
@@ -22343,7 +22810,7 @@
         <v>윤현기</v>
       </c>
       <c r="C71" s="2">
-        <f t="shared" si="9"/>
+        <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
         <v>0.7</v>
       </c>
       <c r="D71" s="14">
@@ -22367,7 +22834,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D71:H71)</f>
         <v>3</v>
       </c>
       <c r="J71" s="15"/>
@@ -22382,7 +22849,7 @@
         <v>이경석</v>
       </c>
       <c r="C72" s="2">
-        <f t="shared" si="9"/>
+        <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
         <v>0</v>
       </c>
       <c r="D72" s="14">
@@ -22406,7 +22873,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D72:H72)</f>
         <v>0</v>
       </c>
       <c r="J72" s="15"/>
@@ -22421,7 +22888,7 @@
         <v>이민재</v>
       </c>
       <c r="C73" s="2">
-        <f t="shared" si="9"/>
+        <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
         <v>0</v>
       </c>
       <c r="D73" s="14">
@@ -22445,7 +22912,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D73:H73)</f>
         <v>0</v>
       </c>
       <c r="J73" s="15"/>
@@ -22460,7 +22927,7 @@
         <v>이병현</v>
       </c>
       <c r="C74" s="2">
-        <f t="shared" si="9"/>
+        <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D74" s="14">
@@ -22484,7 +22951,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D74:H74)</f>
         <v>1</v>
       </c>
       <c r="J74" s="15"/>
@@ -22499,7 +22966,7 @@
         <v>이상민</v>
       </c>
       <c r="C75" s="2">
-        <f t="shared" si="9"/>
+        <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D75" s="14">
@@ -22523,7 +22990,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D75:H75)</f>
         <v>2</v>
       </c>
       <c r="J75" s="15"/>
@@ -22538,7 +23005,7 @@
         <v>이상현</v>
       </c>
       <c r="C76" s="2">
-        <f t="shared" si="9"/>
+        <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
         <v>0</v>
       </c>
       <c r="D76" s="14">
@@ -22562,7 +23029,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D76:H76)</f>
         <v>0</v>
       </c>
       <c r="J76" s="15"/>
@@ -22577,7 +23044,7 @@
         <v>이새샘</v>
       </c>
       <c r="C77" s="2">
-        <f t="shared" si="9"/>
+        <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
         <v>0.8</v>
       </c>
       <c r="D77" s="14">
@@ -22601,7 +23068,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D77:H77)</f>
         <v>4</v>
       </c>
       <c r="J77" s="15"/>
@@ -22616,7 +23083,7 @@
         <v>이성관</v>
       </c>
       <c r="C78" s="2">
-        <f t="shared" si="9"/>
+        <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D78" s="14">
@@ -22640,7 +23107,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D78:H78)</f>
         <v>3</v>
       </c>
       <c r="J78" s="15"/>
@@ -22655,7 +23122,7 @@
         <v>이승윤</v>
       </c>
       <c r="C79" s="2">
-        <f t="shared" si="9"/>
+        <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D79" s="14">
@@ -22679,7 +23146,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D79:H79)</f>
         <v>1</v>
       </c>
       <c r="J79" s="15"/>
@@ -22694,7 +23161,7 @@
         <v>이연길</v>
       </c>
       <c r="C80" s="2">
-        <f t="shared" si="9"/>
+        <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D80" s="14">
@@ -22718,7 +23185,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D80:H80)</f>
         <v>2</v>
       </c>
       <c r="J80" s="15"/>
@@ -22733,7 +23200,7 @@
         <v>이정범</v>
       </c>
       <c r="C81" s="2">
-        <f t="shared" si="9"/>
+        <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
         <v>0</v>
       </c>
       <c r="D81" s="14">
@@ -22757,7 +23224,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D81:H81)</f>
         <v>0</v>
       </c>
       <c r="J81" s="15"/>
@@ -22772,7 +23239,7 @@
         <v>이종수</v>
       </c>
       <c r="C82" s="2">
-        <f t="shared" si="9"/>
+        <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
         <v>0</v>
       </c>
       <c r="D82" s="14">
@@ -22796,7 +23263,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D82:H82)</f>
         <v>0</v>
       </c>
       <c r="J82" s="15"/>
@@ -22811,7 +23278,7 @@
         <v>이찬영</v>
       </c>
       <c r="C83" s="2">
-        <f t="shared" si="9"/>
+        <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D83" s="14">
@@ -22835,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D83:H83)</f>
         <v>2</v>
       </c>
       <c r="J83" s="15"/>
@@ -22850,7 +23317,7 @@
         <v>이태한</v>
       </c>
       <c r="C84" s="2">
-        <f t="shared" si="9"/>
+        <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
         <v>0</v>
       </c>
       <c r="D84" s="14">
@@ -22874,7 +23341,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D84:H84)</f>
         <v>0</v>
       </c>
       <c r="J84" s="15"/>
@@ -22889,7 +23356,7 @@
         <v>이호행</v>
       </c>
       <c r="C85" s="2">
-        <f t="shared" si="9"/>
+        <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D85" s="14">
@@ -22913,7 +23380,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D85:H85)</f>
         <v>3</v>
       </c>
       <c r="J85" s="15"/>
@@ -22928,7 +23395,7 @@
         <v>임수철</v>
       </c>
       <c r="C86" s="2">
-        <f t="shared" si="9"/>
+        <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
         <v>0</v>
       </c>
       <c r="D86" s="14">
@@ -22952,7 +23419,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D86:H86)</f>
         <v>0</v>
       </c>
       <c r="J86" s="15"/>
@@ -22967,12 +23434,12 @@
         <v>임태환</v>
       </c>
       <c r="C87" s="2">
-        <f t="shared" si="9"/>
-        <v>0.4</v>
+        <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
+        <v>1.3</v>
       </c>
       <c r="D87" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B87)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B87)</f>
@@ -22980,7 +23447,7 @@
       </c>
       <c r="F87" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B87)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B87)</f>
@@ -22988,11 +23455,11 @@
       </c>
       <c r="H87" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B87)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="14">
-        <f t="shared" si="10"/>
-        <v>2</v>
+        <f>SUM(D87:H87)</f>
+        <v>6</v>
       </c>
       <c r="J87" s="15"/>
     </row>
@@ -23006,7 +23473,7 @@
         <v>장희도</v>
       </c>
       <c r="C88" s="2">
-        <f t="shared" si="9"/>
+        <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
         <v>0</v>
       </c>
       <c r="D88" s="14">
@@ -23030,7 +23497,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D88:H88)</f>
         <v>0</v>
       </c>
       <c r="J88" s="15"/>
@@ -23045,7 +23512,7 @@
         <v>장희준</v>
       </c>
       <c r="C89" s="2">
-        <f t="shared" si="9"/>
+        <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
         <v>0</v>
       </c>
       <c r="D89" s="14">
@@ -23069,7 +23536,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D89:H89)</f>
         <v>0</v>
       </c>
       <c r="J89" s="15"/>
@@ -23084,7 +23551,7 @@
         <v>전나현</v>
       </c>
       <c r="C90" s="2">
-        <f t="shared" si="9"/>
+        <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
         <v>0.7</v>
       </c>
       <c r="D90" s="14">
@@ -23108,7 +23575,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D90:H90)</f>
         <v>3</v>
       </c>
       <c r="J90" s="15"/>
@@ -23123,7 +23590,7 @@
         <v>전성환</v>
       </c>
       <c r="C91" s="2">
-        <f t="shared" si="9"/>
+        <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D91" s="14">
@@ -23147,7 +23614,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D91:H91)</f>
         <v>1</v>
       </c>
       <c r="J91" s="15"/>
@@ -23162,7 +23629,7 @@
         <v>전하늘</v>
       </c>
       <c r="C92" s="2">
-        <f t="shared" si="9"/>
+        <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D92" s="14">
@@ -23186,7 +23653,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D92:H92)</f>
         <v>1</v>
       </c>
       <c r="J92" s="15"/>
@@ -23201,8 +23668,8 @@
         <v>정민수</v>
       </c>
       <c r="C93" s="2">
-        <f t="shared" si="9"/>
-        <v>1.6</v>
+        <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D93" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B93)</f>
@@ -23210,7 +23677,7 @@
       </c>
       <c r="E93" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B93)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B93)</f>
@@ -23218,15 +23685,15 @@
       </c>
       <c r="G93" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B93)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H93" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B93)</f>
         <v>0</v>
       </c>
       <c r="I93" s="14">
-        <f t="shared" si="10"/>
-        <v>8</v>
+        <f>SUM(D93:H93)</f>
+        <v>12</v>
       </c>
       <c r="J93" s="15"/>
     </row>
@@ -23240,7 +23707,7 @@
         <v>정재명</v>
       </c>
       <c r="C94" s="2">
-        <f t="shared" si="9"/>
+        <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
         <v>0</v>
       </c>
       <c r="D94" s="14">
@@ -23264,7 +23731,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D94:H94)</f>
         <v>0</v>
       </c>
       <c r="J94" s="15"/>
@@ -23279,7 +23746,7 @@
         <v>조진한</v>
       </c>
       <c r="C95" s="2">
-        <f t="shared" si="9"/>
+        <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
         <v>1.9</v>
       </c>
       <c r="D95" s="14">
@@ -23303,7 +23770,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D95:H95)</f>
         <v>8</v>
       </c>
       <c r="J95" s="15"/>
@@ -23318,7 +23785,7 @@
         <v>조현우</v>
       </c>
       <c r="C96" s="2">
-        <f t="shared" si="9"/>
+        <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D96" s="14">
@@ -23342,7 +23809,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D96:H96)</f>
         <v>3</v>
       </c>
       <c r="J96" s="15"/>
@@ -23357,7 +23824,7 @@
         <v>차승원</v>
       </c>
       <c r="C97" s="2">
-        <f t="shared" si="9"/>
+        <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
         <v>1</v>
       </c>
       <c r="D97" s="14">
@@ -23381,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D97:H97)</f>
         <v>5</v>
       </c>
       <c r="J97" s="15"/>
@@ -23396,7 +23863,7 @@
         <v>최령창</v>
       </c>
       <c r="C98" s="2">
-        <f t="shared" si="9"/>
+        <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
         <v>1.8</v>
       </c>
       <c r="D98" s="14">
@@ -23420,7 +23887,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D98:H98)</f>
         <v>9</v>
       </c>
       <c r="J98" s="15"/>
@@ -23435,7 +23902,7 @@
         <v>최승훈</v>
       </c>
       <c r="C99" s="2">
-        <f t="shared" si="9"/>
+        <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
         <v>0</v>
       </c>
       <c r="D99" s="14">
@@ -23459,7 +23926,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D99:H99)</f>
         <v>0</v>
       </c>
       <c r="J99" s="15"/>
@@ -23474,7 +23941,7 @@
         <v>한상규</v>
       </c>
       <c r="C100" s="2">
-        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D100" s="14">
@@ -23498,7 +23965,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
+        <f>SUM(D100:H100)</f>
         <v>3</v>
       </c>
       <c r="J100" s="15"/>
@@ -23513,7 +23980,7 @@
         <v>한의현</v>
       </c>
       <c r="C101" s="2">
-        <f t="shared" si="11"/>
+        <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D101" s="14">
@@ -23537,7 +24004,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D101:H101)</f>
         <v>1</v>
       </c>
       <c r="J101" s="15"/>
@@ -23552,7 +24019,7 @@
         <v>한중희</v>
       </c>
       <c r="C102" s="2">
-        <f t="shared" si="11"/>
+        <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D102" s="14">
@@ -23576,7 +24043,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D102:H102)</f>
         <v>1</v>
       </c>
       <c r="J102" s="15"/>
@@ -23591,7 +24058,7 @@
         <v>허동혁</v>
       </c>
       <c r="C103" s="2">
-        <f t="shared" si="11"/>
+        <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
         <v>0</v>
       </c>
       <c r="D103" s="14">
@@ -23615,7 +24082,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D103:H103)</f>
         <v>0</v>
       </c>
       <c r="J103" s="15"/>
@@ -23630,7 +24097,7 @@
         <v>홍석준</v>
       </c>
       <c r="C104" s="2">
-        <f t="shared" si="11"/>
+        <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D104" s="14">
@@ -23654,7 +24121,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D104:H104)</f>
         <v>1</v>
       </c>
       <c r="J104" s="15"/>
@@ -23669,7 +24136,7 @@
         <v>홍현석</v>
       </c>
       <c r="C105" s="2">
-        <f t="shared" si="11"/>
+        <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D105" s="14">
@@ -23693,7 +24160,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D105:H105)</f>
         <v>1</v>
       </c>
     </row>
@@ -23707,7 +24174,7 @@
         <v>황석원</v>
       </c>
       <c r="C106" s="2">
-        <f t="shared" si="11"/>
+        <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="D106" s="14">
@@ -23731,7 +24198,7 @@
         <v>1</v>
       </c>
       <c r="I106" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D106:H106)</f>
         <v>6</v>
       </c>
     </row>
@@ -23745,7 +24212,7 @@
         <v>황재순</v>
       </c>
       <c r="C107" s="2">
-        <f t="shared" si="11"/>
+        <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
         <v>0</v>
       </c>
       <c r="D107" s="14">
@@ -23769,7 +24236,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D107:H107)</f>
         <v>0</v>
       </c>
     </row>
@@ -23783,7 +24250,7 @@
         <v>황철우</v>
       </c>
       <c r="C108" s="2">
-        <f t="shared" si="11"/>
+        <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D108" s="14">
@@ -23807,7 +24274,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D108:H108)</f>
         <v>1</v>
       </c>
     </row>
@@ -23821,7 +24288,7 @@
         <v>김진우</v>
       </c>
       <c r="C109" s="2">
-        <f t="shared" si="11"/>
+        <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
         <v>0</v>
       </c>
       <c r="D109" s="14">
@@ -23845,7 +24312,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D109:H109)</f>
         <v>0</v>
       </c>
     </row>
@@ -23859,7 +24326,7 @@
         <v>노성호</v>
       </c>
       <c r="C110" s="2">
-        <f t="shared" si="11"/>
+        <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
         <v>0</v>
       </c>
       <c r="D110" s="14">
@@ -23883,7 +24350,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D110:H110)</f>
         <v>0</v>
       </c>
     </row>
@@ -23897,7 +24364,7 @@
         <v>박준영</v>
       </c>
       <c r="C111" s="2">
-        <f t="shared" si="11"/>
+        <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D111" s="14">
@@ -23921,7 +24388,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D111:H111)</f>
         <v>1</v>
       </c>
     </row>
@@ -23935,7 +24402,7 @@
         <v>박태현</v>
       </c>
       <c r="C112" s="2">
-        <f t="shared" si="11"/>
+        <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
         <v>0</v>
       </c>
       <c r="D112" s="14">
@@ -23959,7 +24426,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D112:H112)</f>
         <v>0</v>
       </c>
     </row>
@@ -23973,7 +24440,7 @@
         <v>서영진</v>
       </c>
       <c r="C113" s="2">
-        <f t="shared" si="11"/>
+        <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D113" s="14">
@@ -23997,7 +24464,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D113:H113)</f>
         <v>2</v>
       </c>
     </row>
@@ -24011,7 +24478,7 @@
         <v>오상준</v>
       </c>
       <c r="C114" s="2">
-        <f t="shared" si="11"/>
+        <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
         <v>0.7</v>
       </c>
       <c r="D114" s="14">
@@ -24035,7 +24502,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D114:H114)</f>
         <v>3</v>
       </c>
     </row>
@@ -24049,7 +24516,7 @@
         <v>오성찬</v>
       </c>
       <c r="C115" s="2">
-        <f t="shared" si="11"/>
+        <f>((D115+E115+G115+H115)*0.2)+(F115*0.3)</f>
         <v>0.3</v>
       </c>
       <c r="D115" s="14">
@@ -24073,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D115:H115)</f>
         <v>1</v>
       </c>
     </row>
@@ -24087,7 +24554,7 @@
         <v>유우진</v>
       </c>
       <c r="C116" s="2">
-        <f t="shared" si="11"/>
+        <f>((D116+E116+G116+H116)*0.2)+(F116*0.3)</f>
         <v>0</v>
       </c>
       <c r="D116" s="14">
@@ -24111,7 +24578,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D116:H116)</f>
         <v>0</v>
       </c>
     </row>
@@ -24125,12 +24592,12 @@
         <v>이영준</v>
       </c>
       <c r="C117" s="2">
-        <f t="shared" si="11"/>
-        <v>0.3</v>
+        <f>((D117+E117+G117+H117)*0.2)+(F117*0.3)</f>
+        <v>0.5</v>
       </c>
       <c r="D117" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B117)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B117)</f>
@@ -24149,8 +24616,8 @@
         <v>0</v>
       </c>
       <c r="I117" s="14">
-        <f t="shared" si="12"/>
-        <v>1</v>
+        <f>SUM(D117:H117)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -24163,7 +24630,7 @@
         <v>이찬솔</v>
       </c>
       <c r="C118" s="2">
-        <f t="shared" si="11"/>
+        <f>((D118+E118+G118+H118)*0.2)+(F118*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D118" s="14">
@@ -24187,7 +24654,7 @@
         <v>0</v>
       </c>
       <c r="I118" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D118:H118)</f>
         <v>1</v>
       </c>
     </row>
@@ -24201,7 +24668,7 @@
         <v>정현서</v>
       </c>
       <c r="C119" s="2">
-        <f t="shared" si="11"/>
+        <f>((D119+E119+G119+H119)*0.2)+(F119*0.3)</f>
         <v>0.90000000000000013</v>
       </c>
       <c r="D119" s="14">
@@ -24225,7 +24692,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D119:H119)</f>
         <v>4</v>
       </c>
     </row>
@@ -24239,7 +24706,7 @@
         <v>황건호</v>
       </c>
       <c r="C120" s="2">
-        <f t="shared" si="11"/>
+        <f>((D120+E120+G120+H120)*0.2)+(F120*0.3)</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="D120" s="14">
@@ -24263,7 +24730,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D120:H120)</f>
         <v>5</v>
       </c>
     </row>
@@ -24277,7 +24744,7 @@
         <v>김민성</v>
       </c>
       <c r="C121" s="2">
-        <f t="shared" si="11"/>
+        <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
         <v>0</v>
       </c>
       <c r="D121" s="14">
@@ -24301,7 +24768,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D121:H121)</f>
         <v>0</v>
       </c>
     </row>
@@ -24315,7 +24782,7 @@
         <v>송명섭</v>
       </c>
       <c r="C122" s="2">
-        <f t="shared" si="11"/>
+        <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
         <v>0</v>
       </c>
       <c r="D122" s="14">
@@ -24339,7 +24806,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D122:H122)</f>
         <v>0</v>
       </c>
     </row>
@@ -24353,7 +24820,7 @@
         <v>최경영</v>
       </c>
       <c r="C123" s="2">
-        <f t="shared" si="11"/>
+        <f>((D123+E123+G123+H123)*0.2)+(F123*0.3)</f>
         <v>1.6</v>
       </c>
       <c r="D123" s="14">
@@ -24377,16 +24844,11 @@
         <v>3</v>
       </c>
       <c r="I123" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D123:H123)</f>
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I123">
-      <sortCondition ref="A3"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:D123">
     <cfRule type="top10" dxfId="9" priority="862" rank="7"/>
@@ -25969,10 +26431,10 @@
       <c r="G2" s="47" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="93" t="s">
+      <c r="I2" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="93"/>
+      <c r="J2" s="98"/>
       <c r="K2" s="65" t="s">
         <v>277</v>
       </c>
@@ -25997,7 +26459,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="99" t="s">
         <v>338</v>
       </c>
       <c r="C3" s="72">
@@ -26008,14 +26470,14 @@
       </c>
       <c r="E3" s="70">
         <f>VLOOKUP(D3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="70" t="s">
         <v>299</v>
       </c>
       <c r="G3" s="61">
         <f>VLOOKUP(F3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>5.9</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I3" s="94" t="s">
         <v>333</v>
@@ -26040,14 +26502,14 @@
       </c>
       <c r="Q3" s="62">
         <f>VLOOKUP(P3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>299</v>
       </c>
       <c r="S3" s="63">
         <f>VLOOKUP(R3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>5.9</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
@@ -26060,7 +26522,7 @@
       </c>
       <c r="E4" s="62">
         <f>VLOOKUP(D4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="70" t="s">
         <v>225</v>
@@ -26088,14 +26550,14 @@
       </c>
       <c r="Q4" s="62">
         <f>VLOOKUP(P4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>222</v>
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -26108,14 +26570,14 @@
       </c>
       <c r="E5" s="47">
         <f>VLOOKUP(D5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>222</v>
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I5" s="95"/>
       <c r="J5" s="66">
@@ -26136,14 +26598,14 @@
       </c>
       <c r="Q5" s="62">
         <f>VLOOKUP(P5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>305</v>
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -26156,7 +26618,7 @@
       </c>
       <c r="E6" s="47">
         <f>VLOOKUP(D6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>233</v>
@@ -26184,14 +26646,14 @@
       </c>
       <c r="Q6" s="69">
         <f>VLOOKUP(P6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>231</v>
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -26211,9 +26673,9 @@
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.9</v>
-      </c>
-      <c r="I7" s="97"/>
+        <v>11.9</v>
+      </c>
+      <c r="I7" s="96"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -26232,14 +26694,14 @@
       </c>
       <c r="Q7" s="69">
         <f>VLOOKUP(P7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R7" s="65" t="s">
         <v>325</v>
       </c>
       <c r="S7" s="71">
         <f>VLOOKUP(R7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.1999999999999993</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
@@ -26259,7 +26721,7 @@
       </c>
       <c r="G8" s="63">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="N8" s="85"/>
       <c r="O8" s="48">
@@ -26299,10 +26761,10 @@
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
         <v>2</v>
       </c>
-      <c r="I9" s="93" t="s">
+      <c r="I9" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="J9" s="93"/>
+      <c r="J9" s="98"/>
       <c r="K9" s="65" t="s">
         <v>277</v>
       </c>
@@ -26455,7 +26917,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="100"/>
+      <c r="N12" s="97"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -26520,16 +26982,16 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>229</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.6</v>
-      </c>
-      <c r="I14" s="97"/>
+        <v>10.6</v>
+      </c>
+      <c r="I14" s="96"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -26563,7 +27025,7 @@
       </c>
       <c r="G15" s="63">
         <f>VLOOKUP(F15,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="N15"/>
       <c r="O15"/>
@@ -26582,20 +27044,20 @@
       </c>
       <c r="E16" s="65">
         <f>VLOOKUP(D16,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>231</v>
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="93" t="s">
+      <c r="I16" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="J16" s="93"/>
+      <c r="J16" s="98"/>
       <c r="K16" s="65" t="s">
         <v>277</v>
       </c>
@@ -26656,10 +27118,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="93" t="s">
+      <c r="B19" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="C19" s="93"/>
+      <c r="C19" s="98"/>
       <c r="D19" s="65" t="s">
         <v>277</v>
       </c>
@@ -26710,7 +27172,7 @@
       <c r="E21" s="65" t="s">
         <v>341</v>
       </c>
-      <c r="I21" s="97"/>
+      <c r="I21" s="96"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -26722,7 +27184,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="96"/>
+      <c r="B22" s="100"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -26734,10 +27196,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="98" t="s">
+      <c r="I23" s="92" t="s">
         <v>249</v>
       </c>
-      <c r="J23" s="99"/>
+      <c r="J23" s="93"/>
       <c r="K23" s="65" t="s">
         <v>277</v>
       </c>
@@ -26820,7 +27282,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="97"/>
+      <c r="I30" s="96"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -26833,6 +27295,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -26841,12 +27309,6 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27391,7 +27853,7 @@
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4:I28" si="3">(COUNTIF(J4:CD4,"출전")*1)</f>
@@ -27839,11 +28301,11 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C10</f>
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="I8" s="6">
         <f t="shared" si="3"/>
@@ -27957,7 +28419,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C15</f>
@@ -28071,11 +28533,11 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C16</f>
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="3"/>
@@ -28185,11 +28647,11 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C17</f>
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="3"/>
@@ -28301,7 +28763,7 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C18</f>
@@ -29082,7 +29544,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C34</f>
@@ -29639,11 +30101,11 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C57</f>
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="3"/>
@@ -29751,7 +30213,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C59</f>
@@ -29981,7 +30443,7 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C62</f>
@@ -30095,7 +30557,7 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C63</f>
@@ -30319,7 +30781,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C69</f>
@@ -30543,7 +31005,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C79</f>
@@ -30879,7 +31341,7 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C97</f>
@@ -30997,7 +31459,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C102</f>
@@ -31111,7 +31573,7 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C104</f>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inhyu\OneDrive\바탕 화면\김인혁\김인혁_청년축구단\1. 출석부\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B419E5-8C65-48B6-84BD-19C1D9562032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219FD164-3D60-4F5B-9642-3CD2DEA807DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="401">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -1359,9 +1359,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>윤현기</t>
-  </si>
-  <si>
     <t>김기태</t>
   </si>
   <si>
@@ -1423,58 +1420,52 @@
   </si>
   <si>
     <t>서영진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>황건호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박준영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정현서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김성수</t>
+  </si>
+  <si>
+    <t>황건호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정현서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박준영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>서영진</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>황건호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이영준</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박준영</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정현서</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Black</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김성수</t>
-  </si>
-  <si>
-    <t>이호행</t>
-  </si>
-  <si>
-    <t>황건호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정현서</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이영준</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박준영</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>서영진</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>오상준</t>
   </si>
   <si>
@@ -1498,6 +1489,25 @@
   </si>
   <si>
     <t>Blue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시너지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이찬솔</t>
+  </si>
+  <si>
+    <t>노민진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김민재</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍서준</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2228,6 +2238,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2235,9 +2248,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2932,7 +2942,7 @@
     <row r="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D1" s="53">
         <f>COUNTIF(D4:D159,"발주")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I1" s="18" t="s">
         <v>87</v>
@@ -3099,7 +3109,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>6.6222222222222218</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3162,11 +3172,11 @@
       </c>
       <c r="X2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z2" s="1">
         <f t="shared" si="0"/>
@@ -3375,8 +3385,12 @@
       <c r="W3" s="4">
         <v>46149</v>
       </c>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="X3" s="4">
+        <v>46153</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>46156</v>
+      </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
@@ -3454,15 +3468,15 @@
       </c>
       <c r="G4" s="2">
         <f>RANK(H4,$H$4:$H$123,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4" si="2">(COUNTIF(J4:CD4,"출전")*1)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>352</v>
@@ -3503,7 +3517,9 @@
         <v>352</v>
       </c>
       <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
+      <c r="Y4" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
@@ -3581,7 +3597,7 @@
       </c>
       <c r="G5" s="2">
         <f>RANK(H5,$H$4:$H$123,0)</f>
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -3688,7 +3704,7 @@
       </c>
       <c r="G6" s="2">
         <f>RANK(H6,$H$4:$H$123,0)</f>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
@@ -3783,7 +3799,7 @@
         <v>322</v>
       </c>
       <c r="D7" s="54">
-        <f>COUNTA(J7:W7)</f>
+        <f>COUNTA(L7:AB7)</f>
         <v>0</v>
       </c>
       <c r="E7" s="54"/>
@@ -3792,7 +3808,7 @@
       </c>
       <c r="G7" s="2">
         <f>RANK(H7,$H$4:$H$123,0)</f>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C7</f>
@@ -3887,7 +3903,7 @@
         <v>322</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>227</v>
+        <v>353</v>
       </c>
       <c r="E8" s="54"/>
       <c r="F8" s="2" t="s">
@@ -3895,7 +3911,7 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" ref="G8:G71" si="4">RANK(H8,$H$4:$H$123,0)</f>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C8</f>
@@ -3998,7 +4014,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="4"/>
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
@@ -4109,15 +4125,15 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
-        <v>8.3000000000000007</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>352</v>
@@ -4146,7 +4162,9 @@
         <v>352</v>
       </c>
       <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
+      <c r="Y10" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
@@ -4224,15 +4242,15 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
-        <v>8.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>352</v>
@@ -4261,7 +4279,9 @@
       </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
+      <c r="Y11" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
@@ -4331,7 +4351,7 @@
         <v>2025</v>
       </c>
       <c r="D12" s="54">
-        <f t="shared" ref="D12:D15" si="6">COUNTA(J12:W12)</f>
+        <f t="shared" ref="D12:D15" si="6">COUNTA(L12:AB12)</f>
         <v>1</v>
       </c>
       <c r="E12" s="54"/>
@@ -4340,7 +4360,7 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="4"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C12</f>
@@ -4446,7 +4466,7 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C13</f>
@@ -4550,7 +4570,7 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C14</f>
@@ -4654,7 +4674,7 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
@@ -4757,15 +4777,15 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -4789,7 +4809,9 @@
       <c r="W16" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X16" s="2"/>
+      <c r="X16" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
@@ -4868,15 +4890,15 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
-        <v>10.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
@@ -4908,7 +4930,9 @@
       <c r="W17" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X17" s="2"/>
+      <c r="X17" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
@@ -4987,7 +5011,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C18</f>
@@ -5090,7 +5114,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="4"/>
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
@@ -5201,7 +5225,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="4"/>
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -5302,14 +5326,14 @@
         <v>2023</v>
       </c>
       <c r="D21" s="54">
-        <f t="shared" ref="D21:D23" si="7">COUNTA(J21:W21)</f>
+        <f t="shared" ref="D21:D23" si="7">COUNTA(L21:AB21)</f>
         <v>0</v>
       </c>
       <c r="E21" s="54"/>
       <c r="F21" s="60"/>
       <c r="G21" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C21</f>
@@ -5413,7 +5437,7 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H22" s="6">
         <f>I22+개인기록Sheet!C22</f>
@@ -5517,7 +5541,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C23</f>
@@ -5620,7 +5644,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="4"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
@@ -5725,15 +5749,15 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="4"/>
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -5752,7 +5776,9 @@
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
+      <c r="Y25" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
@@ -5830,15 +5856,15 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
-        <v>4.9000000000000004</v>
+        <v>6.5</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
@@ -5862,7 +5888,9 @@
       </c>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
+      <c r="X26" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
@@ -5945,11 +5973,11 @@
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
-        <v>17</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
@@ -5987,7 +6015,9 @@
       <c r="W27" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X27" s="2"/>
+      <c r="X27" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
@@ -6066,7 +6096,7 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
@@ -6169,7 +6199,7 @@
         <v>2023</v>
       </c>
       <c r="D29" s="54">
-        <f>COUNTA(J29:W29)</f>
+        <f>COUNTA(L29:AB29)</f>
         <v>0</v>
       </c>
       <c r="E29" s="54"/>
@@ -6178,7 +6208,7 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C29</f>
@@ -6281,7 +6311,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="4"/>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6390,15 +6420,15 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="I31" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
@@ -6427,7 +6457,9 @@
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
-      <c r="Y31" s="2"/>
+      <c r="Y31" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
       <c r="AB31" s="2"/>
@@ -6505,15 +6537,15 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>352</v>
@@ -6548,7 +6580,9 @@
         <v>352</v>
       </c>
       <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
+      <c r="Y32" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
@@ -6626,15 +6660,15 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
@@ -6661,7 +6695,9 @@
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
-      <c r="Y33" s="2"/>
+      <c r="Y33" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
       <c r="AB33" s="2"/>
@@ -6739,7 +6775,7 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
@@ -6846,7 +6882,7 @@
         <v>2025</v>
       </c>
       <c r="D35" s="54">
-        <f t="shared" ref="D35:D36" si="8">COUNTA(J35:W35)</f>
+        <f t="shared" ref="D35:D36" si="8">COUNTA(L35:AB35)</f>
         <v>0</v>
       </c>
       <c r="E35" s="54"/>
@@ -6855,7 +6891,7 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C35</f>
@@ -6959,7 +6995,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C36</f>
@@ -7062,15 +7098,15 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
-        <v>9.8000000000000007</v>
+        <v>11.8</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -7100,7 +7136,9 @@
       <c r="W37" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X37" s="2"/>
+      <c r="X37" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
@@ -7179,7 +7217,7 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="4"/>
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
@@ -7280,7 +7318,7 @@
         <v>2025</v>
       </c>
       <c r="D39" s="54">
-        <f>COUNTA(J39:W39)</f>
+        <f>COUNTA(L39:AB39)</f>
         <v>0</v>
       </c>
       <c r="E39" s="54"/>
@@ -7289,7 +7327,7 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H39" s="6">
         <f>I39+개인기록Sheet!C39</f>
@@ -7392,7 +7430,7 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="4"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H40" s="6">
         <f>I40+개인기록Sheet!C40</f>
@@ -7489,7 +7527,7 @@
         <v>322</v>
       </c>
       <c r="D41" s="54">
-        <f t="shared" ref="D41:D42" si="9">COUNTA(J41:W41)</f>
+        <f t="shared" ref="D41:D42" si="9">COUNTA(L41:AB41)</f>
         <v>0</v>
       </c>
       <c r="E41" s="54"/>
@@ -7498,7 +7536,7 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H41" s="6">
         <f>I41+개인기록Sheet!C41</f>
@@ -7602,7 +7640,7 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H42" s="6">
         <f>I42+개인기록Sheet!C42</f>
@@ -7705,7 +7743,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="4"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
@@ -7814,11 +7852,11 @@
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
-        <v>9.8000000000000007</v>
+        <v>11.2</v>
       </c>
       <c r="I44" s="6">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -7850,7 +7888,9 @@
         <v>352</v>
       </c>
       <c r="W44" s="2"/>
-      <c r="X44" s="2"/>
+      <c r="X44" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
@@ -7921,7 +7961,7 @@
         <v>2024</v>
       </c>
       <c r="D45" s="54">
-        <f t="shared" ref="D45:D46" si="10">COUNTA(J45:W45)</f>
+        <f t="shared" ref="D45:D46" si="10">COUNTA(L45:AB45)</f>
         <v>0</v>
       </c>
       <c r="E45" s="54"/>
@@ -7930,7 +7970,7 @@
       </c>
       <c r="G45" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H45" s="6">
         <f>I45+개인기록Sheet!C45</f>
@@ -8032,7 +8072,7 @@
       <c r="F46" s="60"/>
       <c r="G46" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
@@ -8135,15 +8175,15 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="I47" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
@@ -8172,7 +8212,9 @@
       </c>
       <c r="W47" s="2"/>
       <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
+      <c r="Y47" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
       <c r="AB47" s="2"/>
@@ -8242,7 +8284,7 @@
         <v>2022</v>
       </c>
       <c r="D48" s="54">
-        <f t="shared" ref="D48:D50" si="11">COUNTA(J48:W48)</f>
+        <f t="shared" ref="D48:D50" si="11">COUNTA(L48:AB48)</f>
         <v>0</v>
       </c>
       <c r="E48" s="54"/>
@@ -8251,7 +8293,7 @@
       </c>
       <c r="G48" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H48" s="6">
         <f>I48+개인기록Sheet!C48</f>
@@ -8355,7 +8397,7 @@
       </c>
       <c r="G49" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H49" s="6">
         <f>I49+개인기록Sheet!C49</f>
@@ -8459,7 +8501,7 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H50" s="6">
         <f>I50+개인기록Sheet!C50</f>
@@ -8562,15 +8604,15 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I51" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
@@ -8599,7 +8641,9 @@
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
+      <c r="Y51" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
       <c r="AB51" s="2"/>
@@ -8669,7 +8713,7 @@
         <v>2023</v>
       </c>
       <c r="D52" s="54">
-        <f t="shared" ref="D52:D54" si="12">COUNTA(J52:W52)</f>
+        <f t="shared" ref="D52:D54" si="12">COUNTA(L52:AB52)</f>
         <v>0</v>
       </c>
       <c r="E52" s="54"/>
@@ -8678,7 +8722,7 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H52" s="6">
         <f>I52+개인기록Sheet!C52</f>
@@ -8782,7 +8826,7 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H53" s="6">
         <f>I53+개인기록Sheet!C53</f>
@@ -8886,7 +8930,7 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H54" s="6">
         <f>I54+개인기록Sheet!C54</f>
@@ -8981,7 +9025,7 @@
         <v>2023</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>227</v>
+        <v>353</v>
       </c>
       <c r="E55" s="54"/>
       <c r="F55" s="2" t="s">
@@ -8989,15 +9033,15 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
-        <v>5.4</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I55" s="6">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -9023,8 +9067,12 @@
         <v>352</v>
       </c>
       <c r="W55" s="2"/>
-      <c r="X55" s="2"/>
-      <c r="Y55" s="2"/>
+      <c r="X55" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
       <c r="AB55" s="2"/>
@@ -9102,7 +9150,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
@@ -9200,9 +9248,8 @@
       <c r="C57" s="58">
         <v>2025</v>
       </c>
-      <c r="D57" s="54">
-        <f t="shared" ref="D57:D58" si="13">COUNTA(J57:W57)</f>
-        <v>5</v>
+      <c r="D57" s="54" t="s">
+        <v>227</v>
       </c>
       <c r="E57" s="54"/>
       <c r="F57" s="2" t="s">
@@ -9210,15 +9257,15 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="4"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
-        <v>6.2</v>
+        <v>7.9</v>
       </c>
       <c r="I57" s="6">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -9244,7 +9291,9 @@
       <c r="W57" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X57" s="2"/>
+      <c r="X57" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
@@ -9315,7 +9364,7 @@
         <v>2024</v>
       </c>
       <c r="D58" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="D58" si="13">COUNTA(L58:AB58)</f>
         <v>0</v>
       </c>
       <c r="E58" s="54"/>
@@ -9324,7 +9373,7 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H58" s="6">
         <f>I58+개인기록Sheet!C58</f>
@@ -9427,7 +9476,7 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="4"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
@@ -9532,7 +9581,7 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
@@ -9647,7 +9696,7 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
@@ -9748,7 +9797,7 @@
         <v>322</v>
       </c>
       <c r="D62" s="54">
-        <f t="shared" ref="D62:D64" si="14">COUNTA(J62:W62)</f>
+        <f t="shared" ref="D62:D64" si="14">COUNTA(L62:AB62)</f>
         <v>0</v>
       </c>
       <c r="E62" s="54"/>
@@ -9757,7 +9806,7 @@
       </c>
       <c r="G62" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H62" s="6">
         <f>I62+개인기록Sheet!C62</f>
@@ -9861,7 +9910,7 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H63" s="6">
         <f>I63+개인기록Sheet!C63</f>
@@ -9965,7 +10014,7 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H64" s="6">
         <f>I64+개인기록Sheet!C64</f>
@@ -10068,7 +10117,7 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
@@ -10185,15 +10234,15 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="4"/>
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I66" s="6">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -10214,7 +10263,9 @@
       <c r="V66" s="2"/>
       <c r="W66" s="2"/>
       <c r="X66" s="2"/>
-      <c r="Y66" s="2"/>
+      <c r="Y66" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z66" s="2"/>
       <c r="AA66" s="2"/>
       <c r="AB66" s="2"/>
@@ -10292,7 +10343,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
@@ -10395,7 +10446,7 @@
         <v>322</v>
       </c>
       <c r="D68" s="54">
-        <f>COUNTA(J68:W68)</f>
+        <f t="shared" ref="D68" si="15">COUNTA(L68:AB68)</f>
         <v>0</v>
       </c>
       <c r="E68" s="54"/>
@@ -10404,7 +10455,7 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H68" s="6">
         <f>I68+개인기록Sheet!C68</f>
@@ -10507,7 +10558,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" si="4"/>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
@@ -10616,7 +10667,7 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
@@ -10715,7 +10766,7 @@
         <v>2026</v>
       </c>
       <c r="D71" s="54">
-        <f t="shared" ref="D71:D74" si="15">COUNTA(J71:W71)</f>
+        <f t="shared" ref="D71:D74" si="16">COUNTA(L71:AB71)</f>
         <v>3</v>
       </c>
       <c r="E71" s="54"/>
@@ -10724,7 +10775,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="4"/>
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -10825,7 +10876,7 @@
         <v>2025</v>
       </c>
       <c r="D72" s="54">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E72" s="54"/>
@@ -10833,8 +10884,8 @@
         <v>37</v>
       </c>
       <c r="G72" s="2">
-        <f t="shared" ref="G72:G123" si="16">RANK(H72,$H$4:$H$123,0)</f>
-        <v>81</v>
+        <f t="shared" ref="G72:G123" si="17">RANK(H72,$H$4:$H$123,0)</f>
+        <v>83</v>
       </c>
       <c r="H72" s="6">
         <f>I72+개인기록Sheet!C72</f>
@@ -10929,24 +10980,24 @@
         <v>2023</v>
       </c>
       <c r="D73" s="54">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E73" s="54"/>
       <c r="F73" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G73" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>74</v>
       </c>
       <c r="H73" s="6">
         <f>I73+개인기록Sheet!C73</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" ref="I73:I123" si="17">(COUNTIF(J73:CD73,"출전")*1)</f>
-        <v>0</v>
+        <f t="shared" ref="I73:I123" si="18">(COUNTIF(J73:CD73,"출전")*1)</f>
+        <v>1</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -10963,7 +11014,9 @@
       <c r="V73" s="2"/>
       <c r="W73" s="2"/>
       <c r="X73" s="2"/>
-      <c r="Y73" s="2"/>
+      <c r="Y73" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
       <c r="AB73" s="2"/>
@@ -11033,24 +11086,24 @@
         <v>2025</v>
       </c>
       <c r="D74" s="54">
-        <f t="shared" si="15"/>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="E74" s="54"/>
       <c r="F74" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G74" s="2">
-        <f t="shared" si="16"/>
-        <v>35</v>
+        <f t="shared" si="17"/>
+        <v>30</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="I74" s="6">
-        <f t="shared" si="17"/>
-        <v>4</v>
+        <f t="shared" si="18"/>
+        <v>5</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
@@ -11074,7 +11127,9 @@
       <c r="W74" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X74" s="2"/>
+      <c r="X74" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
@@ -11152,15 +11207,15 @@
         <v>37</v>
       </c>
       <c r="G75" s="2">
-        <f t="shared" si="16"/>
-        <v>33</v>
+        <f t="shared" si="17"/>
+        <v>38</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="J75" s="2"/>
@@ -11263,16 +11318,16 @@
         <v>37</v>
       </c>
       <c r="G76" s="2">
-        <f t="shared" si="16"/>
-        <v>63</v>
+        <f t="shared" si="17"/>
+        <v>54</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76" s="6">
-        <f t="shared" si="17"/>
-        <v>2</v>
+        <f t="shared" si="18"/>
+        <v>3</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
@@ -11293,7 +11348,9 @@
       <c r="V76" s="2"/>
       <c r="W76" s="2"/>
       <c r="X76" s="2"/>
-      <c r="Y76" s="2"/>
+      <c r="Y76" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z76" s="2"/>
       <c r="AA76" s="2"/>
       <c r="AB76" s="2"/>
@@ -11370,16 +11427,16 @@
         <v>37</v>
       </c>
       <c r="G77" s="2">
-        <f t="shared" si="16"/>
-        <v>27</v>
+        <f t="shared" si="17"/>
+        <v>26</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" si="17"/>
-        <v>4</v>
+        <f t="shared" si="18"/>
+        <v>5</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
@@ -11404,7 +11461,9 @@
         <v>352</v>
       </c>
       <c r="X77" s="2"/>
-      <c r="Y77" s="2"/>
+      <c r="Y77" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
       <c r="AB77" s="2"/>
@@ -11481,15 +11540,15 @@
         <v>37</v>
       </c>
       <c r="G78" s="2">
-        <f t="shared" si="16"/>
-        <v>29</v>
+        <f t="shared" si="17"/>
+        <v>34</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="I78" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="J78" s="2"/>
@@ -11592,15 +11651,15 @@
         <v>37</v>
       </c>
       <c r="G79" s="2">
-        <f t="shared" si="16"/>
-        <v>60</v>
+        <f t="shared" si="17"/>
+        <v>66</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="I79" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="J79" s="2"/>
@@ -11699,16 +11758,16 @@
         <v>37</v>
       </c>
       <c r="G80" s="2">
-        <f t="shared" si="16"/>
-        <v>58</v>
+        <f t="shared" si="17"/>
+        <v>49</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="I80" s="6">
-        <f t="shared" si="17"/>
-        <v>2</v>
+        <f t="shared" si="18"/>
+        <v>3</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
@@ -11728,7 +11787,9 @@
         <v>352</v>
       </c>
       <c r="W80" s="2"/>
-      <c r="X80" s="2"/>
+      <c r="X80" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
@@ -11806,15 +11867,15 @@
         <v>37</v>
       </c>
       <c r="G81" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>83</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
         <v>0</v>
       </c>
       <c r="I81" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J81" s="2"/>
@@ -11902,22 +11963,22 @@
         <v>322</v>
       </c>
       <c r="D82" s="54" t="s">
-        <v>227</v>
+        <v>353</v>
       </c>
       <c r="E82" s="54"/>
       <c r="F82" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G82" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>83</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
         <v>0</v>
       </c>
       <c r="I82" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J82" s="2"/>
@@ -12012,15 +12073,15 @@
         <v>37</v>
       </c>
       <c r="G83" s="2">
-        <f t="shared" si="16"/>
-        <v>43</v>
+        <f t="shared" si="17"/>
+        <v>49</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
         <v>3.4</v>
       </c>
       <c r="I83" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="J83" s="2"/>
@@ -12121,15 +12182,15 @@
         <v>37</v>
       </c>
       <c r="G84" s="2">
-        <f t="shared" si="16"/>
-        <v>73</v>
+        <f t="shared" si="17"/>
+        <v>74</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
         <v>1</v>
       </c>
       <c r="I84" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J84" s="2"/>
@@ -12226,15 +12287,15 @@
         <v>37</v>
       </c>
       <c r="G85" s="2">
-        <f t="shared" si="16"/>
-        <v>54</v>
+        <f t="shared" si="17"/>
+        <v>60</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
         <v>2.6</v>
       </c>
       <c r="I85" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="J85" s="2"/>
@@ -12333,15 +12394,15 @@
         <v>37</v>
       </c>
       <c r="G86" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>83</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
         <v>0</v>
       </c>
       <c r="I86" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J86" s="2"/>
@@ -12436,16 +12497,16 @@
         <v>37</v>
       </c>
       <c r="G87" s="2">
-        <f t="shared" si="16"/>
-        <v>44</v>
+        <f t="shared" si="17"/>
+        <v>41</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I87" s="6">
-        <f t="shared" si="17"/>
-        <v>2</v>
+        <f t="shared" si="18"/>
+        <v>3</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
@@ -12466,7 +12527,9 @@
         <v>352</v>
       </c>
       <c r="X87" s="2"/>
-      <c r="Y87" s="2"/>
+      <c r="Y87" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z87" s="2"/>
       <c r="AA87" s="2"/>
       <c r="AB87" s="2"/>
@@ -12543,16 +12606,16 @@
         <v>37</v>
       </c>
       <c r="G88" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>74</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
@@ -12569,7 +12632,9 @@
       <c r="V88" s="2"/>
       <c r="W88" s="2"/>
       <c r="X88" s="2"/>
-      <c r="Y88" s="2"/>
+      <c r="Y88" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z88" s="2"/>
       <c r="AA88" s="2"/>
       <c r="AB88" s="2"/>
@@ -12639,7 +12704,7 @@
         <v>2022</v>
       </c>
       <c r="D89" s="54">
-        <f>COUNTA(J89:W89)</f>
+        <f t="shared" ref="D89" si="19">COUNTA(L89:AB89)</f>
         <v>0</v>
       </c>
       <c r="E89" s="54"/>
@@ -12647,15 +12712,15 @@
         <v>37</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>83</v>
       </c>
       <c r="H89" s="6">
         <f>I89+개인기록Sheet!C89</f>
         <v>0</v>
       </c>
       <c r="I89" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J89" s="2"/>
@@ -12750,15 +12815,15 @@
         <v>37</v>
       </c>
       <c r="G90" s="2">
-        <f t="shared" si="16"/>
-        <v>41</v>
+        <f t="shared" si="17"/>
+        <v>47</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
         <v>3.7</v>
       </c>
       <c r="I90" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="J90" s="2"/>
@@ -12852,7 +12917,7 @@
         <v>2022</v>
       </c>
       <c r="D91" s="54">
-        <f>COUNTA(J91:W91)</f>
+        <f t="shared" ref="D91" si="20">COUNTA(L91:AB91)</f>
         <v>1</v>
       </c>
       <c r="E91" s="54"/>
@@ -12860,15 +12925,15 @@
         <v>37</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="16"/>
-        <v>69</v>
+        <f t="shared" si="17"/>
+        <v>72</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
         <v>1.2</v>
       </c>
       <c r="I91" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J91" s="2"/>
@@ -12965,15 +13030,15 @@
         <v>37</v>
       </c>
       <c r="G92" s="2">
-        <f t="shared" si="16"/>
-        <v>46</v>
+        <f t="shared" si="17"/>
+        <v>51</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
         <v>3.2</v>
       </c>
       <c r="I92" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="J92" s="2"/>
@@ -13074,16 +13139,16 @@
         <v>37</v>
       </c>
       <c r="G93" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
-        <v>8.4</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I93" s="6">
-        <f t="shared" si="17"/>
-        <v>6</v>
+        <f t="shared" si="18"/>
+        <v>7</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
@@ -13111,7 +13176,9 @@
       <c r="W93" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X93" s="2"/>
+      <c r="X93" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
       <c r="AA93" s="2"/>
@@ -13189,15 +13256,15 @@
         <v>37</v>
       </c>
       <c r="G94" s="2">
-        <f t="shared" si="16"/>
-        <v>49</v>
+        <f t="shared" si="17"/>
+        <v>54</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
         <v>3</v>
       </c>
       <c r="I94" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="J94" s="2"/>
@@ -13298,16 +13365,16 @@
         <v>37</v>
       </c>
       <c r="G95" s="2">
-        <f t="shared" si="16"/>
-        <v>3</v>
+        <f t="shared" si="17"/>
+        <v>2</v>
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
-        <v>11.9</v>
+        <v>15</v>
       </c>
       <c r="I95" s="6">
-        <f t="shared" si="17"/>
-        <v>10</v>
+        <f t="shared" si="18"/>
+        <v>12</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>352</v>
@@ -13343,8 +13410,12 @@
       <c r="W95" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X95" s="2"/>
-      <c r="Y95" s="2"/>
+      <c r="X95" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y95" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
       <c r="AB95" s="2"/>
@@ -13421,16 +13492,16 @@
         <v>37</v>
       </c>
       <c r="G96" s="2">
-        <f t="shared" si="16"/>
-        <v>13</v>
+        <f t="shared" si="17"/>
+        <v>8</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
-        <v>7.6</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I96" s="6">
-        <f t="shared" si="17"/>
-        <v>7</v>
+        <f t="shared" si="18"/>
+        <v>9</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>352</v>
@@ -13460,8 +13531,12 @@
       </c>
       <c r="V96" s="2"/>
       <c r="W96" s="2"/>
-      <c r="X96" s="2"/>
-      <c r="Y96" s="2"/>
+      <c r="X96" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y96" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z96" s="2"/>
       <c r="AA96" s="2"/>
       <c r="AB96" s="2"/>
@@ -13538,15 +13613,15 @@
         <v>37</v>
       </c>
       <c r="G97" s="2">
-        <f t="shared" si="16"/>
-        <v>20</v>
+        <f t="shared" si="17"/>
+        <v>28</v>
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
         <v>6</v>
       </c>
       <c r="I97" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
       <c r="J97" s="2" t="s">
@@ -13651,16 +13726,16 @@
         <v>37</v>
       </c>
       <c r="G98" s="2">
-        <f t="shared" si="16"/>
-        <v>21</v>
+        <f t="shared" si="17"/>
+        <v>20</v>
       </c>
       <c r="H98" s="6">
         <f>I98+개인기록Sheet!C98</f>
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="I98" s="6">
-        <f t="shared" si="17"/>
-        <v>4</v>
+        <f t="shared" si="18"/>
+        <v>5</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>352</v>
@@ -13685,7 +13760,9 @@
       <c r="V98" s="2"/>
       <c r="W98" s="2"/>
       <c r="X98" s="2"/>
-      <c r="Y98" s="2"/>
+      <c r="Y98" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z98" s="2"/>
       <c r="AA98" s="2"/>
       <c r="AB98" s="2"/>
@@ -13755,7 +13832,7 @@
         <v>2021</v>
       </c>
       <c r="D99" s="54">
-        <f>COUNTA(J99:W99)</f>
+        <f t="shared" ref="D99" si="21">COUNTA(L99:AB99)</f>
         <v>0</v>
       </c>
       <c r="E99" s="54"/>
@@ -13763,15 +13840,15 @@
         <v>37</v>
       </c>
       <c r="G99" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>83</v>
       </c>
       <c r="H99" s="6">
         <f>I99+개인기록Sheet!C99</f>
         <v>0</v>
       </c>
       <c r="I99" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J99" s="2"/>
@@ -13866,15 +13943,15 @@
         <v>37</v>
       </c>
       <c r="G100" s="2">
-        <f t="shared" si="16"/>
-        <v>29</v>
+        <f t="shared" si="17"/>
+        <v>34</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="I100" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="J100" s="2" t="s">
@@ -13977,15 +14054,15 @@
         <v>37</v>
       </c>
       <c r="G101" s="2">
-        <f t="shared" si="16"/>
-        <v>35</v>
+        <f t="shared" si="17"/>
+        <v>43</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
         <v>4.2</v>
       </c>
       <c r="I101" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="J101" s="2" t="s">
@@ -14088,16 +14165,16 @@
         <v>37</v>
       </c>
       <c r="G102" s="2">
-        <f t="shared" si="16"/>
-        <v>23</v>
+        <f t="shared" si="17"/>
+        <v>16</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="I102" s="6">
-        <f t="shared" si="17"/>
-        <v>5</v>
+        <f t="shared" si="18"/>
+        <v>7</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>352</v>
@@ -14123,8 +14200,12 @@
       <c r="U102" s="2"/>
       <c r="V102" s="2"/>
       <c r="W102" s="2"/>
-      <c r="X102" s="2"/>
-      <c r="Y102" s="2"/>
+      <c r="X102" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y102" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z102" s="2"/>
       <c r="AA102" s="2"/>
       <c r="AB102" s="2"/>
@@ -14201,15 +14282,15 @@
         <v>37</v>
       </c>
       <c r="G103" s="2">
-        <f t="shared" si="16"/>
-        <v>63</v>
+        <f t="shared" si="17"/>
+        <v>69</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
         <v>2</v>
       </c>
       <c r="I103" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="J103" s="2" t="s">
@@ -14308,16 +14389,16 @@
         <v>37</v>
       </c>
       <c r="G104" s="2">
-        <f t="shared" si="16"/>
-        <v>69</v>
+        <f t="shared" si="17"/>
+        <v>60</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="I104" s="6">
-        <f t="shared" si="17"/>
-        <v>1</v>
+        <f t="shared" si="18"/>
+        <v>2</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
@@ -14336,7 +14417,9 @@
       <c r="V104" s="2"/>
       <c r="W104" s="2"/>
       <c r="X104" s="2"/>
-      <c r="Y104" s="2"/>
+      <c r="Y104" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z104" s="2"/>
       <c r="AA104" s="2"/>
       <c r="AB104" s="2"/>
@@ -14413,15 +14496,15 @@
         <v>37</v>
       </c>
       <c r="G105" s="2">
-        <f t="shared" si="16"/>
-        <v>60</v>
+        <f t="shared" si="17"/>
+        <v>66</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="I105" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="J105" s="2"/>
@@ -14520,15 +14603,15 @@
         <v>37</v>
       </c>
       <c r="G106" s="2">
-        <f t="shared" si="16"/>
-        <v>35</v>
+        <f t="shared" si="17"/>
+        <v>43</v>
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
         <v>4.2</v>
       </c>
       <c r="I106" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="J106" s="2"/>
@@ -14629,15 +14712,15 @@
         <v>37</v>
       </c>
       <c r="G107" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>83</v>
       </c>
       <c r="H107" s="6">
         <f>I107+개인기록Sheet!C107</f>
         <v>0</v>
       </c>
       <c r="I107" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J107" s="2"/>
@@ -14725,7 +14808,7 @@
         <v>2025</v>
       </c>
       <c r="D108" s="54">
-        <f t="shared" ref="D108:D120" si="18">COUNTA(J108:W108)</f>
+        <f t="shared" ref="D108:D120" si="22">COUNTA(L108:AB108)</f>
         <v>1</v>
       </c>
       <c r="E108" s="54"/>
@@ -14733,15 +14816,15 @@
         <v>37</v>
       </c>
       <c r="G108" s="2">
-        <f t="shared" si="16"/>
-        <v>69</v>
+        <f t="shared" si="17"/>
+        <v>72</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
         <v>1.2</v>
       </c>
       <c r="I108" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J108" s="2"/>
@@ -14825,13 +14908,13 @@
         <v>106</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C109" s="58">
         <v>2026</v>
       </c>
       <c r="D109" s="54">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="E109" s="54"/>
@@ -14839,15 +14922,15 @@
         <v>37</v>
       </c>
       <c r="G109" s="2">
-        <f t="shared" si="16"/>
-        <v>73</v>
+        <f t="shared" si="17"/>
+        <v>74</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
         <v>1</v>
       </c>
       <c r="I109" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J109" s="2"/>
@@ -14931,13 +15014,13 @@
         <v>107</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C110" s="58">
         <v>2026</v>
       </c>
       <c r="D110" s="54">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="E110" s="54"/>
@@ -14945,15 +15028,15 @@
         <v>37</v>
       </c>
       <c r="G110" s="2">
-        <f t="shared" si="16"/>
-        <v>63</v>
+        <f t="shared" si="17"/>
+        <v>69</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
         <v>2</v>
       </c>
       <c r="I110" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="J110" s="2"/>
@@ -15039,13 +15122,13 @@
         <v>108</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C111" s="58">
         <v>2026</v>
       </c>
       <c r="D111" s="54">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="E111" s="54"/>
@@ -15053,15 +15136,15 @@
         <v>37</v>
       </c>
       <c r="G111" s="2">
-        <f t="shared" si="16"/>
-        <v>60</v>
+        <f t="shared" si="17"/>
+        <v>66</v>
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="I111" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="J111" s="2"/>
@@ -15147,30 +15230,30 @@
         <v>109</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C112" s="58">
         <v>2026</v>
       </c>
       <c r="D112" s="54">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="E112" s="54"/>
       <c r="F112" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G112" s="2">
-        <f t="shared" si="16"/>
-        <v>49</v>
+        <f t="shared" si="17"/>
+        <v>43</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="I112" s="6">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" si="18"/>
+        <v>4</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2"/>
@@ -15193,7 +15276,9 @@
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
       <c r="X112" s="2"/>
-      <c r="Y112" s="2"/>
+      <c r="Y112" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z112" s="2"/>
       <c r="AA112" s="2"/>
       <c r="AB112" s="2"/>
@@ -15257,13 +15342,13 @@
         <v>110</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C113" s="58">
         <v>2026</v>
       </c>
       <c r="D113" s="54">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="E113" s="54"/>
@@ -15271,15 +15356,15 @@
         <v>37</v>
       </c>
       <c r="G113" s="2">
-        <f t="shared" si="16"/>
-        <v>58</v>
+        <f t="shared" si="17"/>
+        <v>65</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
         <v>2.4</v>
       </c>
       <c r="I113" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="J113" s="2"/>
@@ -15365,30 +15450,30 @@
         <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C114" s="58">
         <v>2026</v>
       </c>
       <c r="D114" s="54">
-        <f t="shared" si="18"/>
-        <v>2</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="E114" s="54"/>
       <c r="F114" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G114" s="2">
-        <f t="shared" si="16"/>
-        <v>53</v>
+        <f t="shared" si="17"/>
+        <v>27</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
       <c r="I114" s="6">
-        <f t="shared" si="17"/>
-        <v>2</v>
+        <f t="shared" si="18"/>
+        <v>4</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
@@ -15408,8 +15493,12 @@
       <c r="U114" s="2"/>
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
-      <c r="X114" s="2"/>
-      <c r="Y114" s="2"/>
+      <c r="X114" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y114" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
       <c r="AB114" s="2"/>
@@ -15473,30 +15562,30 @@
         <v>112</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C115" s="58">
         <v>2026</v>
       </c>
       <c r="D115" s="54">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="E115" s="54"/>
       <c r="F115" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G115" s="2">
-        <f t="shared" si="16"/>
-        <v>44</v>
+        <f t="shared" si="17"/>
+        <v>41</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I115" s="6">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" si="18"/>
+        <v>4</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
@@ -15519,7 +15608,9 @@
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
       <c r="X115" s="2"/>
-      <c r="Y115" s="2"/>
+      <c r="Y115" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z115" s="2"/>
       <c r="AA115" s="2"/>
       <c r="AB115" s="2"/>
@@ -15583,30 +15674,30 @@
         <v>113</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C116" s="58">
         <v>2026</v>
       </c>
       <c r="D116" s="54">
-        <f t="shared" si="18"/>
-        <v>2</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="E116" s="54"/>
       <c r="F116" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G116" s="2">
-        <f t="shared" si="16"/>
-        <v>63</v>
+        <f t="shared" si="17"/>
+        <v>38</v>
       </c>
       <c r="H116" s="6">
         <f>I116+개인기록Sheet!C116</f>
-        <v>2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I116" s="6">
-        <f t="shared" si="17"/>
-        <v>2</v>
+        <f t="shared" si="18"/>
+        <v>4</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
@@ -15626,8 +15717,12 @@
       <c r="W116" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X116" s="2"/>
-      <c r="Y116" s="2"/>
+      <c r="X116" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y116" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z116" s="2"/>
       <c r="AA116" s="2"/>
       <c r="AB116" s="2"/>
@@ -15691,30 +15786,30 @@
         <v>114</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C117" s="58">
         <v>2026</v>
       </c>
       <c r="D117" s="54">
-        <f t="shared" si="18"/>
-        <v>2</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="E117" s="54"/>
       <c r="F117" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G117" s="2">
-        <f t="shared" si="16"/>
-        <v>57</v>
+        <f t="shared" si="17"/>
+        <v>33</v>
       </c>
       <c r="H117" s="6">
         <f>I117+개인기록Sheet!C117</f>
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="I117" s="6">
-        <f t="shared" si="17"/>
-        <v>2</v>
+        <f t="shared" si="18"/>
+        <v>4</v>
       </c>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
@@ -15734,8 +15829,12 @@
       <c r="W117" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X117" s="2"/>
-      <c r="Y117" s="2"/>
+      <c r="X117" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y117" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
       <c r="AB117" s="2"/>
@@ -15799,30 +15898,30 @@
         <v>115</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C118" s="58">
         <v>2026</v>
       </c>
       <c r="D118" s="54">
-        <f t="shared" si="18"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>2</v>
       </c>
       <c r="E118" s="54"/>
       <c r="F118" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G118" s="2">
-        <f t="shared" si="16"/>
-        <v>69</v>
+        <f t="shared" si="17"/>
+        <v>59</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="I118" s="6">
-        <f t="shared" si="17"/>
-        <v>1</v>
+        <f t="shared" si="18"/>
+        <v>2</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
@@ -15840,7 +15939,9 @@
       </c>
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
-      <c r="X118" s="2"/>
+      <c r="X118" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
@@ -15905,30 +16006,30 @@
         <v>116</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C119" s="58">
         <v>2026</v>
       </c>
       <c r="D119" s="54">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="E119" s="54"/>
       <c r="F119" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G119" s="2">
-        <f t="shared" si="16"/>
-        <v>40</v>
+        <f t="shared" si="17"/>
+        <v>32</v>
       </c>
       <c r="H119" s="6">
         <f>I119+개인기록Sheet!C119</f>
-        <v>3.9000000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I119" s="6">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" si="18"/>
+        <v>4</v>
       </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
@@ -15951,7 +16052,9 @@
         <v>352</v>
       </c>
       <c r="X119" s="2"/>
-      <c r="Y119" s="2"/>
+      <c r="Y119" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z119" s="2"/>
       <c r="AA119" s="2"/>
       <c r="AB119" s="2"/>
@@ -16015,30 +16118,30 @@
         <v>117</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C120" s="58">
         <v>2026</v>
       </c>
       <c r="D120" s="54">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" si="22"/>
+        <v>5</v>
       </c>
       <c r="E120" s="54"/>
       <c r="F120" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G120" s="2">
-        <f t="shared" si="16"/>
-        <v>38</v>
+        <f t="shared" si="17"/>
+        <v>19</v>
       </c>
       <c r="H120" s="6">
         <f>I120+개인기록Sheet!C120</f>
-        <v>4.0999999999999996</v>
+        <v>7.5</v>
       </c>
       <c r="I120" s="6">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" si="18"/>
+        <v>5</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
@@ -16060,8 +16163,12 @@
       <c r="W120" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="X120" s="2"/>
-      <c r="Y120" s="2"/>
+      <c r="X120" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y120" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Z120" s="2"/>
       <c r="AA120" s="2"/>
       <c r="AB120" s="2"/>
@@ -16138,15 +16245,15 @@
         <v>37</v>
       </c>
       <c r="G121" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>83</v>
       </c>
       <c r="H121" s="6">
         <f>I121+개인기록Sheet!C121</f>
         <v>0</v>
       </c>
       <c r="I121" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J121" s="2"/>
@@ -16234,7 +16341,7 @@
         <v>2024</v>
       </c>
       <c r="D122" s="54">
-        <f>COUNTA(J122:W122)</f>
+        <f t="shared" ref="D122" si="23">COUNTA(L122:AB122)</f>
         <v>0</v>
       </c>
       <c r="E122" s="54"/>
@@ -16242,15 +16349,15 @@
         <v>37</v>
       </c>
       <c r="G122" s="2">
-        <f t="shared" si="16"/>
-        <v>81</v>
+        <f t="shared" si="17"/>
+        <v>83</v>
       </c>
       <c r="H122" s="6">
         <f>I122+개인기록Sheet!C122</f>
         <v>0</v>
       </c>
       <c r="I122" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J122" s="2"/>
@@ -16345,15 +16452,15 @@
         <v>37</v>
       </c>
       <c r="G123" s="2">
-        <f t="shared" si="16"/>
-        <v>29</v>
+        <f t="shared" si="17"/>
+        <v>34</v>
       </c>
       <c r="H123" s="6">
         <f>I123+개인기록Sheet!C123</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="I123" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="J123" s="2"/>
@@ -16460,7 +16567,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:V98"/>
+  <dimension ref="A2:V122"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -16479,32 +16586,32 @@
       <c r="D2" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="78" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="79" t="s">
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="80" t="s">
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
@@ -16851,32 +16958,32 @@
       <c r="D13" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="E13" s="77" t="s">
+      <c r="E13" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="78" t="s">
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="79" t="s">
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N13" s="79"/>
-      <c r="O13" s="79"/>
-      <c r="P13" s="79"/>
-      <c r="Q13" s="80" t="s">
+      <c r="N13" s="80"/>
+      <c r="O13" s="80"/>
+      <c r="P13" s="80"/>
+      <c r="Q13" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R13" s="80"/>
-      <c r="S13" s="80"/>
-      <c r="T13" s="80"/>
-      <c r="U13" s="80"/>
-      <c r="V13" s="80"/>
+      <c r="R13" s="77"/>
+      <c r="S13" s="77"/>
+      <c r="T13" s="77"/>
+      <c r="U13" s="77"/>
+      <c r="V13" s="77"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
@@ -17169,32 +17276,32 @@
       <c r="D24" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="E24" s="77" t="s">
+      <c r="E24" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="78" t="s">
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="79" t="s">
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N24" s="79"/>
-      <c r="O24" s="79"/>
-      <c r="P24" s="79"/>
-      <c r="Q24" s="80" t="s">
+      <c r="N24" s="80"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R24" s="80"/>
-      <c r="S24" s="80"/>
-      <c r="T24" s="80"/>
-      <c r="U24" s="80"/>
-      <c r="V24" s="80"/>
+      <c r="R24" s="77"/>
+      <c r="S24" s="77"/>
+      <c r="T24" s="77"/>
+      <c r="U24" s="77"/>
+      <c r="V24" s="77"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
@@ -17244,7 +17351,7 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -17500,7 +17607,7 @@
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B33" s="73" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C33" s="75">
         <v>2</v>
@@ -17603,34 +17710,34 @@
         <v>358</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="E37" s="77" t="s">
+        <v>369</v>
+      </c>
+      <c r="E37" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="78" t="s">
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="78"/>
+      <c r="I37" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="79" t="s">
+      <c r="J37" s="79"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="79"/>
+      <c r="M37" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N37" s="79"/>
-      <c r="O37" s="79"/>
-      <c r="P37" s="79"/>
-      <c r="Q37" s="80" t="s">
+      <c r="N37" s="80"/>
+      <c r="O37" s="80"/>
+      <c r="P37" s="80"/>
+      <c r="Q37" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R37" s="80"/>
-      <c r="S37" s="80"/>
-      <c r="T37" s="80"/>
-      <c r="U37" s="80"/>
-      <c r="V37" s="80"/>
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
+      <c r="T37" s="77"/>
+      <c r="U37" s="77"/>
+      <c r="V37" s="77"/>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B38" s="73" t="s">
@@ -17891,32 +17998,32 @@
       <c r="D49" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="E49" s="77" t="s">
+      <c r="E49" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="77"/>
-      <c r="I49" s="78" t="s">
+      <c r="F49" s="78"/>
+      <c r="G49" s="78"/>
+      <c r="H49" s="78"/>
+      <c r="I49" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J49" s="78"/>
-      <c r="K49" s="78"/>
-      <c r="L49" s="78"/>
-      <c r="M49" s="79" t="s">
+      <c r="J49" s="79"/>
+      <c r="K49" s="79"/>
+      <c r="L49" s="79"/>
+      <c r="M49" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N49" s="79"/>
-      <c r="O49" s="79"/>
-      <c r="P49" s="79"/>
-      <c r="Q49" s="80" t="s">
+      <c r="N49" s="80"/>
+      <c r="O49" s="80"/>
+      <c r="P49" s="80"/>
+      <c r="Q49" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R49" s="80"/>
-      <c r="S49" s="80"/>
-      <c r="T49" s="80"/>
-      <c r="U49" s="80"/>
-      <c r="V49" s="80"/>
+      <c r="R49" s="77"/>
+      <c r="S49" s="77"/>
+      <c r="T49" s="77"/>
+      <c r="U49" s="77"/>
+      <c r="V49" s="77"/>
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="73" t="s">
@@ -17951,7 +18058,7 @@
       </c>
       <c r="P50" s="20"/>
       <c r="Q50" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R50" s="9" t="s">
         <v>234</v>
@@ -18022,7 +18129,7 @@
         <v>203</v>
       </c>
       <c r="T52" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U52" s="9"/>
       <c r="V52" s="13" t="s">
@@ -18079,7 +18186,7 @@
         <v>311</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="8" t="s">
@@ -18092,7 +18199,7 @@
         <v>237</v>
       </c>
       <c r="N54" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O54" s="20" t="s">
         <v>135</v>
@@ -18198,7 +18305,7 @@
     </row>
     <row r="58" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B58" s="73" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C58" s="75">
         <v>2</v>
@@ -18210,7 +18317,7 @@
         <v>109</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -18240,7 +18347,7 @@
         <v>298</v>
       </c>
       <c r="T58" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U58" s="9"/>
       <c r="V58" s="13"/>
@@ -18304,37 +18411,37 @@
         <v>46128</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="E63" s="77" t="s">
+        <v>393</v>
+      </c>
+      <c r="E63" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F63" s="77"/>
-      <c r="G63" s="77"/>
-      <c r="H63" s="77"/>
-      <c r="I63" s="78" t="s">
+      <c r="F63" s="78"/>
+      <c r="G63" s="78"/>
+      <c r="H63" s="78"/>
+      <c r="I63" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J63" s="78"/>
-      <c r="K63" s="78"/>
-      <c r="L63" s="78"/>
-      <c r="M63" s="79" t="s">
+      <c r="J63" s="79"/>
+      <c r="K63" s="79"/>
+      <c r="L63" s="79"/>
+      <c r="M63" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N63" s="79"/>
-      <c r="O63" s="79"/>
-      <c r="P63" s="79"/>
-      <c r="Q63" s="80" t="s">
+      <c r="N63" s="80"/>
+      <c r="O63" s="80"/>
+      <c r="P63" s="80"/>
+      <c r="Q63" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R63" s="80"/>
-      <c r="S63" s="80"/>
-      <c r="T63" s="80"/>
-      <c r="U63" s="80"/>
-      <c r="V63" s="80"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="77"/>
+      <c r="T63" s="77"/>
+      <c r="U63" s="77"/>
+      <c r="V63" s="77"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="73" t="s">
@@ -18388,7 +18495,7 @@
         <v>135</v>
       </c>
       <c r="O65" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P65" s="20"/>
       <c r="Q65" s="9" t="s">
@@ -18405,7 +18512,7 @@
       </c>
       <c r="U65" s="9"/>
       <c r="V65" s="13" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
@@ -18440,7 +18547,7 @@
         <v>202</v>
       </c>
       <c r="T66" s="9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="U66" s="9"/>
       <c r="V66" s="13" t="s">
@@ -18624,7 +18731,7 @@
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B72" s="73" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C72" s="75">
         <v>1</v>
@@ -18633,29 +18740,29 @@
         <v>0</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
       <c r="I72" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
       <c r="M72" s="20" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N72" s="20" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O72" s="20" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="P72" s="20"/>
       <c r="Q72" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="R72" s="9" t="s">
         <v>104</v>
@@ -18730,37 +18837,37 @@
         <v>46133</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="E77" s="77" t="s">
+        <v>393</v>
+      </c>
+      <c r="E77" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F77" s="77"/>
-      <c r="G77" s="77"/>
-      <c r="H77" s="77"/>
-      <c r="I77" s="78" t="s">
+      <c r="F77" s="78"/>
+      <c r="G77" s="78"/>
+      <c r="H77" s="78"/>
+      <c r="I77" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J77" s="78"/>
-      <c r="K77" s="78"/>
-      <c r="L77" s="78"/>
-      <c r="M77" s="79" t="s">
+      <c r="J77" s="79"/>
+      <c r="K77" s="79"/>
+      <c r="L77" s="79"/>
+      <c r="M77" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N77" s="79"/>
-      <c r="O77" s="79"/>
-      <c r="P77" s="79"/>
-      <c r="Q77" s="80" t="s">
+      <c r="N77" s="80"/>
+      <c r="O77" s="80"/>
+      <c r="P77" s="80"/>
+      <c r="Q77" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R77" s="80"/>
-      <c r="S77" s="80"/>
-      <c r="T77" s="80"/>
-      <c r="U77" s="80"/>
-      <c r="V77" s="80"/>
+      <c r="R77" s="77"/>
+      <c r="S77" s="77"/>
+      <c r="T77" s="77"/>
+      <c r="U77" s="77"/>
+      <c r="V77" s="77"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="73" t="s">
@@ -18900,7 +19007,7 @@
         <v>348</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>202</v>
@@ -18934,7 +19041,7 @@
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="8"/>
@@ -18994,19 +19101,19 @@
       <c r="C85" s="76"/>
       <c r="D85" s="76"/>
       <c r="E85" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L85" s="8"/>
       <c r="M85" s="20"/>
@@ -19056,37 +19163,37 @@
         <v>46149</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="E89" s="77" t="s">
+        <v>395</v>
+      </c>
+      <c r="E89" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F89" s="77"/>
-      <c r="G89" s="77"/>
-      <c r="H89" s="77"/>
-      <c r="I89" s="78" t="s">
+      <c r="F89" s="78"/>
+      <c r="G89" s="78"/>
+      <c r="H89" s="78"/>
+      <c r="I89" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J89" s="78"/>
-      <c r="K89" s="78"/>
-      <c r="L89" s="78"/>
-      <c r="M89" s="79" t="s">
+      <c r="J89" s="79"/>
+      <c r="K89" s="79"/>
+      <c r="L89" s="79"/>
+      <c r="M89" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N89" s="79"/>
-      <c r="O89" s="79"/>
-      <c r="P89" s="79"/>
-      <c r="Q89" s="80" t="s">
+      <c r="N89" s="80"/>
+      <c r="O89" s="80"/>
+      <c r="P89" s="80"/>
+      <c r="Q89" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R89" s="80"/>
-      <c r="S89" s="80"/>
-      <c r="T89" s="80"/>
-      <c r="U89" s="80"/>
-      <c r="V89" s="80"/>
+      <c r="R89" s="77"/>
+      <c r="S89" s="77"/>
+      <c r="T89" s="77"/>
+      <c r="U89" s="77"/>
+      <c r="V89" s="77"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B90" s="73" t="s">
@@ -19209,7 +19316,7 @@
         <v>105</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
@@ -19413,17 +19520,706 @@
       <c r="U98" s="2"/>
       <c r="V98" s="2"/>
     </row>
+    <row r="101" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B101" s="11">
+        <v>46153</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="E101" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="F101" s="78"/>
+      <c r="G101" s="78"/>
+      <c r="H101" s="78"/>
+      <c r="I101" s="79" t="s">
+        <v>85</v>
+      </c>
+      <c r="J101" s="79"/>
+      <c r="K101" s="79"/>
+      <c r="L101" s="79"/>
+      <c r="M101" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="N101" s="80"/>
+      <c r="O101" s="80"/>
+      <c r="P101" s="80"/>
+      <c r="Q101" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="R101" s="77"/>
+      <c r="S101" s="77"/>
+      <c r="T101" s="77"/>
+      <c r="U101" s="77"/>
+      <c r="V101" s="77"/>
+    </row>
+    <row r="102" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B102" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C102" s="75">
+        <v>2</v>
+      </c>
+      <c r="D102" s="75">
+        <v>0</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="J102" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="N102" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="O102" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="P102" s="20"/>
+      <c r="Q102" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="R102" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="S102" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="T102" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="U102" s="9"/>
+      <c r="V102" s="13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="103" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B103" s="74"/>
+      <c r="C103" s="76"/>
+      <c r="D103" s="76"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+      <c r="M103" s="20"/>
+      <c r="N103" s="20"/>
+      <c r="O103" s="20"/>
+      <c r="P103" s="20"/>
+      <c r="Q103" s="9"/>
+      <c r="R103" s="9"/>
+      <c r="S103" s="9"/>
+      <c r="T103" s="9"/>
+      <c r="U103" s="9"/>
+      <c r="V103" s="13"/>
+    </row>
+    <row r="104" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B104" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" s="75">
+        <v>1</v>
+      </c>
+      <c r="D104" s="75">
+        <v>0</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+      <c r="M104" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="N104" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="O104" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="P104" s="20"/>
+      <c r="Q104" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="R104" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="S104" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="T104" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="U104" s="9"/>
+      <c r="V104" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B105" s="74"/>
+      <c r="C105" s="76"/>
+      <c r="D105" s="76"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+      <c r="M105" s="20"/>
+      <c r="N105" s="20"/>
+      <c r="O105" s="20"/>
+      <c r="P105" s="20"/>
+      <c r="Q105" s="9"/>
+      <c r="R105" s="9"/>
+      <c r="S105" s="9"/>
+      <c r="T105" s="9"/>
+      <c r="U105" s="9"/>
+      <c r="V105" s="13"/>
+    </row>
+    <row r="106" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B106" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C106" s="75">
+        <v>2</v>
+      </c>
+      <c r="D106" s="75">
+        <v>0</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+      <c r="M106" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="N106" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="O106" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="P106" s="20"/>
+      <c r="Q106" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="R106" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="S106" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="T106" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="U106" s="9"/>
+      <c r="V106" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="107" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B107" s="74"/>
+      <c r="C107" s="76"/>
+      <c r="D107" s="76"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="8"/>
+      <c r="J107" s="8"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+      <c r="M107" s="20"/>
+      <c r="N107" s="20"/>
+      <c r="O107" s="20"/>
+      <c r="P107" s="20"/>
+      <c r="Q107" s="9"/>
+      <c r="R107" s="9"/>
+      <c r="S107" s="9"/>
+      <c r="T107" s="9"/>
+      <c r="U107" s="9"/>
+      <c r="V107" s="13"/>
+    </row>
+    <row r="108" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B108" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C108" s="75">
+        <v>1</v>
+      </c>
+      <c r="D108" s="75">
+        <v>0</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="8"/>
+      <c r="M108" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="N108" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="O108" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="P108" s="20"/>
+      <c r="Q108" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="R108" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="S108" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="T108" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="U108" s="9"/>
+      <c r="V108" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="109" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B109" s="74"/>
+      <c r="C109" s="76"/>
+      <c r="D109" s="76"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="8"/>
+      <c r="J109" s="8"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
+      <c r="M109" s="20"/>
+      <c r="N109" s="20"/>
+      <c r="O109" s="20"/>
+      <c r="P109" s="20"/>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+      <c r="S109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
+      <c r="V109" s="13"/>
+    </row>
+    <row r="110" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B110" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C110" s="2">
+        <f>SUM(C102:C109)</f>
+        <v>6</v>
+      </c>
+      <c r="D110" s="2">
+        <f>SUM(D102:D109)</f>
+        <v>0</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+      <c r="P110" s="2"/>
+      <c r="Q110" s="2"/>
+      <c r="R110" s="2"/>
+      <c r="S110" s="2"/>
+      <c r="T110" s="2"/>
+      <c r="U110" s="2"/>
+      <c r="V110" s="2"/>
+    </row>
+    <row r="113" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B113" s="11">
+        <v>46156</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D113" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="E113" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="F113" s="78"/>
+      <c r="G113" s="78"/>
+      <c r="H113" s="78"/>
+      <c r="I113" s="79" t="s">
+        <v>85</v>
+      </c>
+      <c r="J113" s="79"/>
+      <c r="K113" s="79"/>
+      <c r="L113" s="79"/>
+      <c r="M113" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="N113" s="80"/>
+      <c r="O113" s="80"/>
+      <c r="P113" s="80"/>
+      <c r="Q113" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="R113" s="77"/>
+      <c r="S113" s="77"/>
+      <c r="T113" s="77"/>
+      <c r="U113" s="77"/>
+      <c r="V113" s="77"/>
+    </row>
+    <row r="114" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B114" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C114" s="75">
+        <v>1</v>
+      </c>
+      <c r="D114" s="75">
+        <v>0</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="8"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="8"/>
+      <c r="L114" s="8"/>
+      <c r="M114" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="N114" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="O114" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="P114" s="20"/>
+      <c r="Q114" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="R114" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="S114" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="T114" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="U114" s="9"/>
+      <c r="V114" s="13" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="115" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B115" s="74"/>
+      <c r="C115" s="76"/>
+      <c r="D115" s="76"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="8"/>
+      <c r="L115" s="8"/>
+      <c r="M115" s="20"/>
+      <c r="N115" s="20"/>
+      <c r="O115" s="20"/>
+      <c r="P115" s="20"/>
+      <c r="Q115" s="9"/>
+      <c r="R115" s="9"/>
+      <c r="S115" s="9"/>
+      <c r="T115" s="9"/>
+      <c r="U115" s="9"/>
+      <c r="V115" s="13"/>
+    </row>
+    <row r="116" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B116" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C116" s="75">
+        <v>1</v>
+      </c>
+      <c r="D116" s="75">
+        <v>0</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="F116" s="7"/>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="8"/>
+      <c r="K116" s="8"/>
+      <c r="L116" s="8"/>
+      <c r="M116" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="N116" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="O116" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="P116" s="20"/>
+      <c r="Q116" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="R116" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="S116" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="T116" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="U116" s="9"/>
+      <c r="V116" s="13" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="117" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B117" s="74"/>
+      <c r="C117" s="76"/>
+      <c r="D117" s="76"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="8"/>
+      <c r="J117" s="8"/>
+      <c r="K117" s="8"/>
+      <c r="L117" s="8"/>
+      <c r="M117" s="20"/>
+      <c r="N117" s="20"/>
+      <c r="O117" s="20"/>
+      <c r="P117" s="20"/>
+      <c r="Q117" s="9"/>
+      <c r="R117" s="9"/>
+      <c r="S117" s="9"/>
+      <c r="T117" s="9"/>
+      <c r="U117" s="9"/>
+      <c r="V117" s="13"/>
+    </row>
+    <row r="118" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B118" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" s="75">
+        <v>2</v>
+      </c>
+      <c r="D118" s="75">
+        <v>2</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="J118" s="8"/>
+      <c r="K118" s="8"/>
+      <c r="L118" s="8"/>
+      <c r="M118" s="20"/>
+      <c r="N118" s="20"/>
+      <c r="O118" s="20"/>
+      <c r="P118" s="20"/>
+      <c r="Q118" s="9"/>
+      <c r="R118" s="9"/>
+      <c r="S118" s="9"/>
+      <c r="T118" s="9"/>
+      <c r="U118" s="9"/>
+      <c r="V118" s="13"/>
+    </row>
+    <row r="119" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B119" s="74"/>
+      <c r="C119" s="76"/>
+      <c r="D119" s="76"/>
+      <c r="E119" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J119" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="K119" s="8"/>
+      <c r="L119" s="8"/>
+      <c r="M119" s="20"/>
+      <c r="N119" s="20"/>
+      <c r="O119" s="20"/>
+      <c r="P119" s="20"/>
+      <c r="Q119" s="9"/>
+      <c r="R119" s="9"/>
+      <c r="S119" s="9"/>
+      <c r="T119" s="9"/>
+      <c r="U119" s="9"/>
+      <c r="V119" s="13"/>
+    </row>
+    <row r="120" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B120" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C120" s="75">
+        <v>2</v>
+      </c>
+      <c r="D120" s="75">
+        <v>1</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="J120" s="8"/>
+      <c r="K120" s="8"/>
+      <c r="L120" s="8"/>
+      <c r="M120" s="20"/>
+      <c r="N120" s="20"/>
+      <c r="O120" s="20"/>
+      <c r="P120" s="20"/>
+      <c r="Q120" s="9"/>
+      <c r="R120" s="9"/>
+      <c r="S120" s="9"/>
+      <c r="T120" s="9"/>
+      <c r="U120" s="9"/>
+      <c r="V120" s="13"/>
+    </row>
+    <row r="121" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B121" s="74"/>
+      <c r="C121" s="76"/>
+      <c r="D121" s="76"/>
+      <c r="E121" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J121" s="8"/>
+      <c r="K121" s="8"/>
+      <c r="L121" s="8"/>
+      <c r="M121" s="20"/>
+      <c r="N121" s="20"/>
+      <c r="O121" s="20"/>
+      <c r="P121" s="20"/>
+      <c r="Q121" s="9"/>
+      <c r="R121" s="9"/>
+      <c r="S121" s="9"/>
+      <c r="T121" s="9"/>
+      <c r="U121" s="9"/>
+      <c r="V121" s="13"/>
+    </row>
+    <row r="122" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B122" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C122" s="2">
+        <f>SUM(C114:C121)</f>
+        <v>6</v>
+      </c>
+      <c r="D122" s="2">
+        <f>SUM(D114:D121)</f>
+        <v>3</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" s="2"/>
+      <c r="R122" s="2"/>
+      <c r="S122" s="2"/>
+      <c r="T122" s="2"/>
+      <c r="U122" s="2"/>
+      <c r="V122" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="137">
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="M89:P89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
+  <mergeCells count="169">
     <mergeCell ref="B94:B95"/>
     <mergeCell ref="C94:C95"/>
     <mergeCell ref="D94:D95"/>
@@ -19437,6 +20233,15 @@
     <mergeCell ref="B84:B85"/>
     <mergeCell ref="C84:C85"/>
     <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
     <mergeCell ref="E77:H77"/>
     <mergeCell ref="I77:L77"/>
     <mergeCell ref="M77:P77"/>
@@ -19468,8 +20273,6 @@
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
     <mergeCell ref="E13:H13"/>
     <mergeCell ref="I13:L13"/>
     <mergeCell ref="B20:B21"/>
@@ -19492,6 +20295,8 @@
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
     <mergeCell ref="Q37:V37"/>
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="C38:C39"/>
@@ -19552,6 +20357,38 @@
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="M101:P101"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="Q113:V113"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -19593,23 +20430,23 @@
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -19687,7 +20524,7 @@
         <v>김인혁</v>
       </c>
       <c r="C4" s="2">
-        <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
+        <f t="shared" ref="C4:C35" si="0">((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="D4" s="14">
@@ -19711,7 +20548,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="14">
-        <f>SUM(D4:H4)</f>
+        <f t="shared" ref="I4:I35" si="1">SUM(D4:H4)</f>
         <v>7</v>
       </c>
       <c r="J4" s="15"/>
@@ -19719,38 +20556,38 @@
         <v>1</v>
       </c>
       <c r="L4" s="32" t="s">
-        <v>224</v>
+        <v>354</v>
       </c>
       <c r="M4" s="21">
-        <f t="shared" ref="M4:M17" si="0">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
-        <v>10</v>
+        <f t="shared" ref="M4:M13" si="2">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
+        <v>12</v>
       </c>
       <c r="N4" s="33" t="s">
-        <v>53</v>
+        <v>354</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O13" si="1">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
-        <v>6</v>
+        <f t="shared" ref="O4:O16" si="3">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
+        <v>7</v>
       </c>
       <c r="P4" s="34" t="s">
         <v>222</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q13" si="2">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
-        <v>8</v>
+        <f t="shared" ref="Q4:Q16" si="4">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
+        <v>11</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>231</v>
       </c>
       <c r="S4" s="55">
-        <f t="shared" ref="S4:S17" si="3">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
-        <v>11</v>
+        <f t="shared" ref="S4:S16" si="5">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
+        <v>13</v>
       </c>
       <c r="T4" s="36" t="s">
         <v>229</v>
       </c>
       <c r="U4" s="56">
-        <f t="shared" ref="U4:U18" si="4">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
+        <f t="shared" ref="U4:U7" si="6">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
         <v>6</v>
       </c>
     </row>
@@ -19764,7 +20601,7 @@
         <v>신재경</v>
       </c>
       <c r="C5" s="2">
-        <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D5" s="14">
@@ -19788,7 +20625,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="14">
-        <f>SUM(D5:H5)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J5" s="15"/>
@@ -19796,38 +20633,38 @@
         <v>2</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M5" s="21">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>354</v>
+        <v>53</v>
       </c>
       <c r="O5" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="P5" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Q5" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>325</v>
       </c>
       <c r="S5" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="T5" s="36" t="s">
-        <v>42</v>
+        <v>221</v>
       </c>
       <c r="U5" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -19841,7 +20678,7 @@
         <v>정효태</v>
       </c>
       <c r="C6" s="2">
-        <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D6" s="14">
@@ -19865,7 +20702,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="14">
-        <f>SUM(D6:H6)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J6" s="15"/>
@@ -19873,39 +20710,39 @@
         <v>3</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>354</v>
+        <v>222</v>
       </c>
       <c r="M6" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="N6" s="33" t="s">
         <v>50</v>
       </c>
       <c r="O6" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="Q6" s="23">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>6</v>
       </c>
       <c r="R6" s="35" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="S6" s="55">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>8</v>
       </c>
       <c r="T6" s="36" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
       <c r="U6" s="56">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -19918,7 +20755,7 @@
         <v>이승민</v>
       </c>
       <c r="C7" s="2">
-        <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7" s="14">
@@ -19942,7 +20779,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f>SUM(D7:H7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J7" s="15"/>
@@ -19950,39 +20787,39 @@
         <v>4</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M7" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P7" s="34" t="s">
-        <v>53</v>
+        <v>299</v>
       </c>
       <c r="Q7" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R7" s="35" t="s">
-        <v>222</v>
+        <v>364</v>
       </c>
       <c r="S7" s="55">
-        <f t="shared" si="3"/>
-        <v>6</v>
+        <f t="shared" si="5"/>
+        <v>7</v>
       </c>
       <c r="T7" s="36" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="U7" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -19995,7 +20832,7 @@
         <v>이정석</v>
       </c>
       <c r="C8" s="2">
-        <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D8" s="14">
@@ -20019,7 +20856,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f>SUM(D8:H8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="15"/>
@@ -20030,37 +20867,32 @@
         <v>305</v>
       </c>
       <c r="M8" s="21">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>222</v>
       </c>
       <c r="O8" s="22">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Q8" s="23">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="R8" s="35" t="s">
-        <v>357</v>
+        <v>222</v>
       </c>
       <c r="S8" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="T8" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="U8" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+      <c r="T8" s="36"/>
+      <c r="U8" s="56"/>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -20072,7 +20904,7 @@
         <v>강종찬</v>
       </c>
       <c r="C9" s="2">
-        <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D9" s="14">
@@ -20096,7 +20928,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="14">
-        <f>SUM(D9:H9)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J9" s="15"/>
@@ -20104,40 +20936,35 @@
         <v>6</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>50</v>
+        <v>391</v>
       </c>
       <c r="M9" s="21">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>225</v>
       </c>
       <c r="O9" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="Q9" s="23">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="R9" s="35" t="s">
         <v>242</v>
       </c>
       <c r="S9" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="T9" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="U9" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+      <c r="T9" s="36"/>
+      <c r="U9" s="56"/>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -20149,7 +20976,7 @@
         <v>강관석</v>
       </c>
       <c r="C10" s="2">
-        <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="D10" s="14">
@@ -20173,7 +21000,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="14">
-        <f>SUM(D10:H10)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="J10" s="15"/>
@@ -20181,40 +21008,35 @@
         <v>7</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>393</v>
+        <v>50</v>
       </c>
       <c r="M10" s="21">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N10" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="O10" s="22">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="P10" s="34" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q10" s="23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
+      <c r="N10" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="O10" s="22">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q10" s="23">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
       <c r="R10" s="35" t="s">
-        <v>303</v>
+        <v>62</v>
       </c>
       <c r="S10" s="55">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="T10" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="U10" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="T10" s="36"/>
+      <c r="U10" s="56"/>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -20226,12 +21048,12 @@
         <v>강기혁</v>
       </c>
       <c r="C11" s="2">
-        <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
-        <v>2.8000000000000003</v>
+        <f t="shared" si="0"/>
+        <v>3.0000000000000004</v>
       </c>
       <c r="D11" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B11)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B11)</f>
@@ -20250,48 +21072,43 @@
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f>SUM(D11:H11)</f>
-        <v>13</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="2">
         <v>8</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="M11" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>314</v>
+        <v>356</v>
       </c>
       <c r="O11" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>224</v>
+        <v>391</v>
       </c>
       <c r="Q11" s="23">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="R11" s="35" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="S11" s="55">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="T11" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="U11" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="T11" s="36"/>
+      <c r="U11" s="56"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -20303,7 +21120,7 @@
         <v>강도일</v>
       </c>
       <c r="C12" s="2">
-        <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D12" s="14">
@@ -20327,7 +21144,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="14">
-        <f>SUM(D12:H12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J12" s="15"/>
@@ -20335,40 +21152,35 @@
         <v>9</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>392</v>
+        <v>221</v>
       </c>
       <c r="O12" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P12" s="34" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="Q12" s="23">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="R12" s="35" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="S12" s="55">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="T12" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="U12" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="T12" s="36"/>
+      <c r="U12" s="56"/>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -20380,7 +21192,7 @@
         <v>강일수</v>
       </c>
       <c r="C13" s="2">
-        <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D13" s="14">
@@ -20404,7 +21216,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f>SUM(D13:H13)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -20412,40 +21224,35 @@
         <v>10</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="M13" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="O13" s="22">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="N13" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="O13" s="22">
-        <f t="shared" si="1"/>
+      <c r="P13" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q13" s="23">
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="P13" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q13" s="23">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
       <c r="R13" s="35" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="S13" s="55">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="T13" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="U13" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="T13" s="36"/>
+      <c r="U13" s="56"/>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -20457,7 +21264,7 @@
         <v>구교훈</v>
       </c>
       <c r="C14" s="2">
-        <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D14" s="14">
@@ -20481,38 +21288,38 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f>SUM(D14:H14)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="2">
         <v>11</v>
       </c>
-      <c r="L14" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="M14" s="21">
-        <f t="shared" si="0"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="33" t="s">
+        <v>389</v>
+      </c>
+      <c r="O14" s="22">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="N14" s="33"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="23"/>
+      <c r="P14" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q14" s="23">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
       <c r="R14" s="55" t="s">
-        <v>366</v>
+        <v>303</v>
       </c>
       <c r="S14" s="55">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="T14" s="36" t="s">
-        <v>366</v>
-      </c>
-      <c r="U14" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="T14" s="36"/>
+      <c r="U14" s="56"/>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -20524,7 +21331,7 @@
         <v>권주용</v>
       </c>
       <c r="C15" s="2">
-        <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D15" s="14">
@@ -20548,38 +21355,38 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f>SUM(D15:H15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="2">
         <v>12</v>
       </c>
-      <c r="L15" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="M15" s="21">
-        <f t="shared" si="0"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="O15" s="22">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
+      <c r="P15" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q15" s="23">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
       <c r="R15" s="55" t="s">
-        <v>34</v>
+        <v>233</v>
       </c>
       <c r="S15" s="55">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="T15" s="56" t="s">
-        <v>232</v>
-      </c>
-      <c r="U15" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="T15" s="56"/>
+      <c r="U15" s="56"/>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -20591,12 +21398,12 @@
         <v>김기문</v>
       </c>
       <c r="C16" s="2">
-        <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
-        <v>0.7</v>
+        <f t="shared" si="0"/>
+        <v>1.4</v>
       </c>
       <c r="D16" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B16)</f>
@@ -20604,49 +21411,49 @@
       </c>
       <c r="F16" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B16)</f>
         <v>1</v>
       </c>
       <c r="I16" s="14">
-        <f>SUM(D16:H16)</f>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="2">
         <v>13</v>
       </c>
-      <c r="L16" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="M16" s="21">
-        <f t="shared" si="0"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="O16" s="22">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
+      <c r="P16" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q16" s="23">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
       <c r="R16" s="55" t="s">
-        <v>385</v>
+        <v>324</v>
       </c>
       <c r="S16" s="55">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="T16" s="56" t="s">
-        <v>365</v>
-      </c>
-      <c r="U16" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="T16" s="56"/>
+      <c r="U16" s="56"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -20658,7 +21465,7 @@
         <v>김기태</v>
       </c>
       <c r="C17" s="2">
-        <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="D17" s="14">
@@ -20682,38 +21489,23 @@
         <v>0</v>
       </c>
       <c r="I17" s="14">
-        <f>SUM(D17:H17)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="2">
         <v>14</v>
       </c>
-      <c r="L17" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="M17" s="21">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
       <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
-      <c r="R17" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="S17" s="55">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="T17" s="56" t="s">
-        <v>303</v>
-      </c>
-      <c r="U17" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+      <c r="R17" s="55"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="56"/>
+      <c r="U17" s="56"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -20725,7 +21517,7 @@
         <v>김덕준</v>
       </c>
       <c r="C18" s="2">
-        <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D18" s="14">
@@ -20749,7 +21541,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f>SUM(D18:H18)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="15"/>
@@ -20764,13 +21556,8 @@
       <c r="Q18" s="23"/>
       <c r="R18" s="55"/>
       <c r="S18" s="55"/>
-      <c r="T18" s="56" t="s">
-        <v>377</v>
-      </c>
-      <c r="U18" s="56">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+      <c r="T18" s="56"/>
+      <c r="U18" s="56"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -20782,7 +21569,7 @@
         <v>김동인</v>
       </c>
       <c r="C19" s="2">
-        <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D19" s="14">
@@ -20806,7 +21593,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f>SUM(D19:H19)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
@@ -20821,7 +21608,7 @@
         <v>김민섭</v>
       </c>
       <c r="C20" s="2">
-        <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="D20" s="14">
@@ -20845,7 +21632,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f>SUM(D20:H20)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J20" s="15"/>
@@ -20860,7 +21647,7 @@
         <v>김민준</v>
       </c>
       <c r="C21" s="2">
-        <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D21" s="14">
@@ -20884,7 +21671,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="14">
-        <f>SUM(D21:H21)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21" s="15"/>
@@ -20899,7 +21686,7 @@
         <v>김민찬</v>
       </c>
       <c r="C22" s="2">
-        <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D22" s="14">
@@ -20923,7 +21710,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f>SUM(D22:H22)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J22" s="15"/>
@@ -20938,7 +21725,7 @@
         <v>김범기</v>
       </c>
       <c r="C23" s="2">
-        <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D23" s="14">
@@ -20962,7 +21749,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f>SUM(D23:H23)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="15"/>
@@ -20977,7 +21764,7 @@
         <v>김병준</v>
       </c>
       <c r="C24" s="2">
-        <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D24" s="14">
@@ -21001,7 +21788,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f>SUM(D24:H24)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="15"/>
@@ -21016,16 +21803,16 @@
         <v>김부건</v>
       </c>
       <c r="C25" s="2">
-        <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D25" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B25)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B25)</f>
@@ -21040,8 +21827,8 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f>SUM(D25:H25)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J25" s="15"/>
     </row>
@@ -21055,8 +21842,8 @@
         <v>김성수</v>
       </c>
       <c r="C26" s="2">
-        <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
-        <v>0.89999999999999991</v>
+        <f t="shared" si="0"/>
+        <v>1.5</v>
       </c>
       <c r="D26" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B26)</f>
@@ -21068,7 +21855,7 @@
       </c>
       <c r="F26" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B26)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G26" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B26)</f>
@@ -21079,8 +21866,8 @@
         <v>0</v>
       </c>
       <c r="I26" s="14">
-        <f>SUM(D26:H26)</f>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="J26" s="15"/>
     </row>
@@ -21094,8 +21881,8 @@
         <v>김성준</v>
       </c>
       <c r="C27" s="2">
-        <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>7.1</v>
       </c>
       <c r="D27" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B27)</f>
@@ -21103,11 +21890,11 @@
       </c>
       <c r="E27" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B27)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B27)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G27" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B27)</f>
@@ -21118,8 +21905,8 @@
         <v>1</v>
       </c>
       <c r="I27" s="14">
-        <f>SUM(D27:H27)</f>
-        <v>26</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J27" s="15"/>
     </row>
@@ -21133,7 +21920,7 @@
         <v>김송환</v>
       </c>
       <c r="C28" s="2">
-        <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.3000000000000003</v>
       </c>
       <c r="D28" s="14">
@@ -21157,7 +21944,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="14">
-        <f>SUM(D28:H28)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="J28" s="15"/>
@@ -21172,7 +21959,7 @@
         <v>김영태</v>
       </c>
       <c r="C29" s="2">
-        <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D29" s="14">
@@ -21196,7 +21983,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <f>SUM(D29:H29)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J29" s="15"/>
@@ -21211,7 +21998,7 @@
         <v>김용빈</v>
       </c>
       <c r="C30" s="2">
-        <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D30" s="14">
@@ -21235,7 +22022,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <f>SUM(D30:H30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J30" s="15"/>
@@ -21250,7 +22037,7 @@
         <v>김용현</v>
       </c>
       <c r="C31" s="2">
-        <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.9000000000000004</v>
       </c>
       <c r="D31" s="14">
@@ -21274,7 +22061,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <f>SUM(D31:H31)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="J31" s="15"/>
@@ -21289,7 +22076,7 @@
         <v>김우인</v>
       </c>
       <c r="C32" s="2">
-        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="D32" s="14">
@@ -21313,7 +22100,7 @@
         <v>6</v>
       </c>
       <c r="I32" s="14">
-        <f>SUM(D32:H32)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="J32" s="15"/>
@@ -21328,7 +22115,7 @@
         <v>김종준</v>
       </c>
       <c r="C33" s="2">
-        <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D33" s="14">
@@ -21352,7 +22139,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="14">
-        <f>SUM(D33:H33)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J33" s="15"/>
@@ -21367,7 +22154,7 @@
         <v>김종혁</v>
       </c>
       <c r="C34" s="2">
-        <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D34" s="14">
@@ -21391,7 +22178,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="14">
-        <f>SUM(D34:H34)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J34" s="15"/>
@@ -21406,7 +22193,7 @@
         <v>김준영</v>
       </c>
       <c r="C35" s="2">
-        <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D35" s="14">
@@ -21430,7 +22217,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="14">
-        <f>SUM(D35:H35)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J35" s="15"/>
@@ -21445,7 +22232,7 @@
         <v>김진형</v>
       </c>
       <c r="C36" s="2">
-        <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
         <v>0</v>
       </c>
       <c r="D36" s="14">
@@ -21469,7 +22256,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="14">
-        <f>SUM(D36:H36)</f>
+        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
         <v>0</v>
       </c>
       <c r="J36" s="15"/>
@@ -21484,16 +22271,16 @@
         <v>김진호</v>
       </c>
       <c r="C37" s="2">
-        <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
-        <v>2.8000000000000003</v>
+        <f t="shared" si="7"/>
+        <v>3.8000000000000003</v>
       </c>
       <c r="D37" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B37)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E37" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B37)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B37)</f>
@@ -21508,8 +22295,8 @@
         <v>0</v>
       </c>
       <c r="I37" s="14">
-        <f>SUM(D37:H37)</f>
-        <v>14</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
       <c r="J37" s="15"/>
     </row>
@@ -21523,7 +22310,7 @@
         <v>김태성</v>
       </c>
       <c r="C38" s="2">
-        <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="D38" s="14">
@@ -21547,7 +22334,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="14">
-        <f>SUM(D38:H38)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J38" s="15"/>
@@ -21562,7 +22349,7 @@
         <v>김태양</v>
       </c>
       <c r="C39" s="2">
-        <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D39" s="14">
@@ -21586,7 +22373,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="14">
-        <f>SUM(D39:H39)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J39" s="15"/>
@@ -21601,7 +22388,7 @@
         <v>김태완</v>
       </c>
       <c r="C40" s="2">
-        <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D40" s="14">
@@ -21625,7 +22412,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="14">
-        <f>SUM(D40:H40)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J40" s="15"/>
@@ -21640,7 +22427,7 @@
         <v>김태호</v>
       </c>
       <c r="C41" s="2">
-        <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D41" s="14">
@@ -21664,7 +22451,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="14">
-        <f>SUM(D41:H41)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J41" s="15"/>
@@ -21679,7 +22466,7 @@
         <v>김현우</v>
       </c>
       <c r="C42" s="2">
-        <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D42" s="14">
@@ -21703,7 +22490,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="14">
-        <f>SUM(D42:H42)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J42" s="15"/>
@@ -21718,7 +22505,7 @@
         <v>김형원</v>
       </c>
       <c r="C43" s="2">
-        <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D43" s="14">
@@ -21742,7 +22529,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="14">
-        <f>SUM(D43:H43)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J43" s="15"/>
@@ -21757,8 +22544,8 @@
         <v>노민준</v>
       </c>
       <c r="C44" s="2">
-        <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
-        <v>1.8</v>
+        <f t="shared" si="7"/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D44" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B44)</f>
@@ -21774,15 +22561,15 @@
       </c>
       <c r="G44" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B44)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H44" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B44)</f>
         <v>2</v>
       </c>
       <c r="I44" s="14">
-        <f>SUM(D44:H44)</f>
-        <v>9</v>
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="J44" s="15"/>
     </row>
@@ -21796,7 +22583,7 @@
         <v>류서진</v>
       </c>
       <c r="C45" s="2">
-        <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D45" s="14">
@@ -21820,7 +22607,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="14">
-        <f>SUM(D45:H45)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J45" s="15"/>
@@ -21835,7 +22622,7 @@
         <v>마창기</v>
       </c>
       <c r="C46" s="2">
-        <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D46" s="14">
@@ -21859,7 +22646,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="14">
-        <f>SUM(D46:H46)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J46" s="15"/>
@@ -21874,8 +22661,8 @@
         <v>문준수</v>
       </c>
       <c r="C47" s="2">
-        <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
-        <v>0.60000000000000009</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="D47" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B47)</f>
@@ -21891,15 +22678,15 @@
       </c>
       <c r="G47" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B47)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B47)</f>
         <v>1</v>
       </c>
       <c r="I47" s="14">
-        <f>SUM(D47:H47)</f>
-        <v>3</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="J47" s="15"/>
     </row>
@@ -21913,7 +22700,7 @@
         <v>민건호</v>
       </c>
       <c r="C48" s="2">
-        <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D48" s="14">
@@ -21937,7 +22724,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="14">
-        <f>SUM(D48:H48)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J48" s="15"/>
@@ -21952,7 +22739,7 @@
         <v>박수천</v>
       </c>
       <c r="C49" s="2">
-        <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D49" s="14">
@@ -21976,7 +22763,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="14">
-        <f>SUM(D49:H49)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J49" s="15"/>
@@ -21991,7 +22778,7 @@
         <v>박정호</v>
       </c>
       <c r="C50" s="2">
-        <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D50" s="14">
@@ -22015,7 +22802,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="14">
-        <f>SUM(D50:H50)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J50" s="15"/>
@@ -22030,7 +22817,7 @@
         <v>박주연</v>
       </c>
       <c r="C51" s="2">
-        <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="D51" s="14">
@@ -22054,7 +22841,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="14">
-        <f>SUM(D51:H51)</f>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="J51" s="15"/>
@@ -22069,7 +22856,7 @@
         <v>박주현</v>
       </c>
       <c r="C52" s="2">
-        <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D52" s="14">
@@ -22093,7 +22880,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="14">
-        <f>SUM(D52:H52)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J52" s="15"/>
@@ -22108,7 +22895,7 @@
         <v>박하빈</v>
       </c>
       <c r="C53" s="2">
-        <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D53" s="14">
@@ -22132,7 +22919,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="14">
-        <f>SUM(D53:H53)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J53" s="15"/>
@@ -22147,7 +22934,7 @@
         <v>박형기</v>
       </c>
       <c r="C54" s="2">
-        <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D54" s="14">
@@ -22171,7 +22958,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="14">
-        <f>SUM(D54:H54)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J54" s="15"/>
@@ -22186,16 +22973,16 @@
         <v>손경호</v>
       </c>
       <c r="C55" s="2">
-        <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
-        <v>0.4</v>
+        <f t="shared" si="7"/>
+        <v>1.8</v>
       </c>
       <c r="D55" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B55)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E55" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B55)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F55" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B55)</f>
@@ -22207,11 +22994,11 @@
       </c>
       <c r="H55" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B55)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" s="14">
-        <f>SUM(D55:H55)</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="J55" s="15"/>
     </row>
@@ -22225,7 +23012,7 @@
         <v>송윤상</v>
       </c>
       <c r="C56" s="2">
-        <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="D56" s="14">
@@ -22249,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="14">
-        <f>SUM(D56:H56)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J56" s="15"/>
@@ -22264,8 +23051,8 @@
         <v>신기웅</v>
       </c>
       <c r="C57" s="2">
-        <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
-        <v>1.2000000000000002</v>
+        <f t="shared" si="7"/>
+        <v>1.9000000000000001</v>
       </c>
       <c r="D57" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B57)</f>
@@ -22277,19 +23064,19 @@
       </c>
       <c r="F57" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B57)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B57)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H57" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B57)</f>
         <v>0</v>
       </c>
       <c r="I57" s="14">
-        <f>SUM(D57:H57)</f>
-        <v>6</v>
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="J57" s="15"/>
     </row>
@@ -22303,7 +23090,7 @@
         <v>신종훈</v>
       </c>
       <c r="C58" s="2">
-        <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D58" s="14">
@@ -22327,7 +23114,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="14">
-        <f>SUM(D58:H58)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J58" s="15"/>
@@ -22342,7 +23129,7 @@
         <v>안진혁</v>
       </c>
       <c r="C59" s="2">
-        <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D59" s="14">
@@ -22366,7 +23153,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="14">
-        <f>SUM(D59:H59)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J59" s="15"/>
@@ -22381,7 +23168,7 @@
         <v>양진웅</v>
       </c>
       <c r="C60" s="2">
-        <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="D60" s="14">
@@ -22405,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="14">
-        <f>SUM(D60:H60)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J60" s="15"/>
@@ -22420,7 +23207,7 @@
         <v>오우영</v>
       </c>
       <c r="C61" s="2">
-        <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
       <c r="D61" s="14">
@@ -22444,7 +23231,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="14">
-        <f>SUM(D61:H61)</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="J61" s="15"/>
@@ -22459,7 +23246,7 @@
         <v>오운용</v>
       </c>
       <c r="C62" s="2">
-        <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D62" s="14">
@@ -22483,7 +23270,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="14">
-        <f>SUM(D62:H62)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J62" s="15"/>
@@ -22498,7 +23285,7 @@
         <v>오진환</v>
       </c>
       <c r="C63" s="2">
-        <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D63" s="14">
@@ -22522,7 +23309,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f>SUM(D63:H63)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J63" s="15"/>
@@ -22537,7 +23324,7 @@
         <v>우보광</v>
       </c>
       <c r="C64" s="2">
-        <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D64" s="14">
@@ -22561,7 +23348,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="14">
-        <f>SUM(D64:H64)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J64" s="15"/>
@@ -22576,7 +23363,7 @@
         <v>유상근</v>
       </c>
       <c r="C65" s="2">
-        <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="D65" s="14">
@@ -22600,7 +23387,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="14">
-        <f>SUM(D65:H65)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="J65" s="15"/>
@@ -22615,7 +23402,7 @@
         <v>유인상</v>
       </c>
       <c r="C66" s="2">
-        <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D66" s="14">
@@ -22639,7 +23426,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f>SUM(D66:H66)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J66" s="15"/>
@@ -22654,7 +23441,7 @@
         <v>유정훈</v>
       </c>
       <c r="C67" s="2">
-        <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D67" s="14">
@@ -22678,7 +23465,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f>SUM(D67:H67)</f>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="J67" s="15"/>
@@ -22693,7 +23480,7 @@
         <v>유진효</v>
       </c>
       <c r="C68" s="2">
-        <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
         <v>0</v>
       </c>
       <c r="D68" s="14">
@@ -22717,7 +23504,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="14">
-        <f>SUM(D68:H68)</f>
+        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
         <v>0</v>
       </c>
       <c r="J68" s="15"/>
@@ -22732,7 +23519,7 @@
         <v>윤원택</v>
       </c>
       <c r="C69" s="2">
-        <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D69" s="14">
@@ -22756,7 +23543,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f>SUM(D69:H69)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J69" s="15"/>
@@ -22771,7 +23558,7 @@
         <v>윤창현</v>
       </c>
       <c r="C70" s="2">
-        <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D70" s="14">
@@ -22795,7 +23582,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="14">
-        <f>SUM(D70:H70)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J70" s="15"/>
@@ -22810,7 +23597,7 @@
         <v>윤현기</v>
       </c>
       <c r="C71" s="2">
-        <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
       <c r="D71" s="14">
@@ -22834,7 +23621,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <f>SUM(D71:H71)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J71" s="15"/>
@@ -22849,7 +23636,7 @@
         <v>이경석</v>
       </c>
       <c r="C72" s="2">
-        <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D72" s="14">
@@ -22873,7 +23660,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f>SUM(D72:H72)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J72" s="15"/>
@@ -22888,7 +23675,7 @@
         <v>이민재</v>
       </c>
       <c r="C73" s="2">
-        <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D73" s="14">
@@ -22912,7 +23699,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f>SUM(D73:H73)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J73" s="15"/>
@@ -22927,8 +23714,8 @@
         <v>이병현</v>
       </c>
       <c r="C74" s="2">
-        <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
-        <v>0.2</v>
+        <f t="shared" si="9"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D74" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B74)</f>
@@ -22944,15 +23731,15 @@
       </c>
       <c r="G74" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H74" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B74)</f>
         <v>0</v>
       </c>
       <c r="I74" s="14">
-        <f>SUM(D74:H74)</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="J74" s="15"/>
     </row>
@@ -22966,7 +23753,7 @@
         <v>이상민</v>
       </c>
       <c r="C75" s="2">
-        <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D75" s="14">
@@ -22990,7 +23777,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="14">
-        <f>SUM(D75:H75)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J75" s="15"/>
@@ -23005,7 +23792,7 @@
         <v>이상현</v>
       </c>
       <c r="C76" s="2">
-        <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D76" s="14">
@@ -23029,7 +23816,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="14">
-        <f>SUM(D76:H76)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J76" s="15"/>
@@ -23044,8 +23831,8 @@
         <v>이새샘</v>
       </c>
       <c r="C77" s="2">
-        <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
-        <v>0.8</v>
+        <f t="shared" si="9"/>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D77" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B77)</f>
@@ -23061,15 +23848,15 @@
       </c>
       <c r="G77" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B77)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H77" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B77)</f>
         <v>1</v>
       </c>
       <c r="I77" s="14">
-        <f>SUM(D77:H77)</f>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>6</v>
       </c>
       <c r="J77" s="15"/>
     </row>
@@ -23083,7 +23870,7 @@
         <v>이성관</v>
       </c>
       <c r="C78" s="2">
-        <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D78" s="14">
@@ -23107,7 +23894,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="14">
-        <f>SUM(D78:H78)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J78" s="15"/>
@@ -23122,7 +23909,7 @@
         <v>이승윤</v>
       </c>
       <c r="C79" s="2">
-        <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D79" s="14">
@@ -23146,7 +23933,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="14">
-        <f>SUM(D79:H79)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J79" s="15"/>
@@ -23161,7 +23948,7 @@
         <v>이연길</v>
       </c>
       <c r="C80" s="2">
-        <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D80" s="14">
@@ -23185,7 +23972,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="14">
-        <f>SUM(D80:H80)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J80" s="15"/>
@@ -23200,7 +23987,7 @@
         <v>이정범</v>
       </c>
       <c r="C81" s="2">
-        <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D81" s="14">
@@ -23224,7 +24011,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="14">
-        <f>SUM(D81:H81)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J81" s="15"/>
@@ -23239,7 +24026,7 @@
         <v>이종수</v>
       </c>
       <c r="C82" s="2">
-        <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D82" s="14">
@@ -23263,7 +24050,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="14">
-        <f>SUM(D82:H82)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J82" s="15"/>
@@ -23278,7 +24065,7 @@
         <v>이찬영</v>
       </c>
       <c r="C83" s="2">
-        <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D83" s="14">
@@ -23302,7 +24089,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="14">
-        <f>SUM(D83:H83)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J83" s="15"/>
@@ -23317,7 +24104,7 @@
         <v>이태한</v>
       </c>
       <c r="C84" s="2">
-        <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D84" s="14">
@@ -23341,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="14">
-        <f>SUM(D84:H84)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J84" s="15"/>
@@ -23356,7 +24143,7 @@
         <v>이호행</v>
       </c>
       <c r="C85" s="2">
-        <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D85" s="14">
@@ -23380,7 +24167,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="14">
-        <f>SUM(D85:H85)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J85" s="15"/>
@@ -23395,7 +24182,7 @@
         <v>임수철</v>
       </c>
       <c r="C86" s="2">
-        <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D86" s="14">
@@ -23419,7 +24206,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="14">
-        <f>SUM(D86:H86)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J86" s="15"/>
@@ -23434,7 +24221,7 @@
         <v>임태환</v>
       </c>
       <c r="C87" s="2">
-        <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.3</v>
       </c>
       <c r="D87" s="14">
@@ -23458,7 +24245,7 @@
         <v>1</v>
       </c>
       <c r="I87" s="14">
-        <f>SUM(D87:H87)</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="J87" s="15"/>
@@ -23473,7 +24260,7 @@
         <v>장희도</v>
       </c>
       <c r="C88" s="2">
-        <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D88" s="14">
@@ -23497,7 +24284,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="14">
-        <f>SUM(D88:H88)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J88" s="15"/>
@@ -23512,7 +24299,7 @@
         <v>장희준</v>
       </c>
       <c r="C89" s="2">
-        <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D89" s="14">
@@ -23536,7 +24323,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="14">
-        <f>SUM(D89:H89)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J89" s="15"/>
@@ -23551,7 +24338,7 @@
         <v>전나현</v>
       </c>
       <c r="C90" s="2">
-        <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
       <c r="D90" s="14">
@@ -23575,7 +24362,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="14">
-        <f>SUM(D90:H90)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J90" s="15"/>
@@ -23590,7 +24377,7 @@
         <v>전성환</v>
       </c>
       <c r="C91" s="2">
-        <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D91" s="14">
@@ -23614,7 +24401,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="14">
-        <f>SUM(D91:H91)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J91" s="15"/>
@@ -23629,7 +24416,7 @@
         <v>전하늘</v>
       </c>
       <c r="C92" s="2">
-        <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D92" s="14">
@@ -23653,7 +24440,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="14">
-        <f>SUM(D92:H92)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J92" s="15"/>
@@ -23668,8 +24455,8 @@
         <v>정민수</v>
       </c>
       <c r="C93" s="2">
-        <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
-        <v>2.4000000000000004</v>
+        <f t="shared" si="9"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D93" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B93)</f>
@@ -23685,15 +24472,15 @@
       </c>
       <c r="G93" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B93)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H93" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B93)</f>
         <v>0</v>
       </c>
       <c r="I93" s="14">
-        <f>SUM(D93:H93)</f>
-        <v>12</v>
+        <f t="shared" si="10"/>
+        <v>14</v>
       </c>
       <c r="J93" s="15"/>
     </row>
@@ -23707,7 +24494,7 @@
         <v>정재명</v>
       </c>
       <c r="C94" s="2">
-        <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D94" s="14">
@@ -23731,7 +24518,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="14">
-        <f>SUM(D94:H94)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J94" s="15"/>
@@ -23746,12 +24533,12 @@
         <v>조진한</v>
       </c>
       <c r="C95" s="2">
-        <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
-        <v>1.9</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="D95" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B95)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E95" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B95)</f>
@@ -23759,7 +24546,7 @@
       </c>
       <c r="F95" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B95)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G95" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B95)</f>
@@ -23770,8 +24557,8 @@
         <v>0</v>
       </c>
       <c r="I95" s="14">
-        <f>SUM(D95:H95)</f>
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>12</v>
       </c>
       <c r="J95" s="15"/>
     </row>
@@ -23785,8 +24572,8 @@
         <v>조현우</v>
       </c>
       <c r="C96" s="2">
-        <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
-        <v>0.60000000000000009</v>
+        <f t="shared" si="9"/>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D96" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B96)</f>
@@ -23802,15 +24589,15 @@
       </c>
       <c r="G96" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B96)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H96" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B96)</f>
         <v>0</v>
       </c>
       <c r="I96" s="14">
-        <f>SUM(D96:H96)</f>
-        <v>3</v>
+        <f t="shared" si="10"/>
+        <v>6</v>
       </c>
       <c r="J96" s="15"/>
     </row>
@@ -23824,7 +24611,7 @@
         <v>차승원</v>
       </c>
       <c r="C97" s="2">
-        <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D97" s="14">
@@ -23848,7 +24635,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="14">
-        <f>SUM(D97:H97)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J97" s="15"/>
@@ -23863,12 +24650,12 @@
         <v>최령창</v>
       </c>
       <c r="C98" s="2">
-        <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
-        <v>1.8</v>
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="D98" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B98)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B98)</f>
@@ -23887,8 +24674,8 @@
         <v>1</v>
       </c>
       <c r="I98" s="14">
-        <f>SUM(D98:H98)</f>
-        <v>9</v>
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="J98" s="15"/>
     </row>
@@ -23902,7 +24689,7 @@
         <v>최승훈</v>
       </c>
       <c r="C99" s="2">
-        <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D99" s="14">
@@ -23926,7 +24713,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="14">
-        <f>SUM(D99:H99)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J99" s="15"/>
@@ -23941,7 +24728,7 @@
         <v>한상규</v>
       </c>
       <c r="C100" s="2">
-        <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D100" s="14">
@@ -23965,7 +24752,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f>SUM(D100:H100)</f>
+        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
         <v>3</v>
       </c>
       <c r="J100" s="15"/>
@@ -23980,7 +24767,7 @@
         <v>한의현</v>
       </c>
       <c r="C101" s="2">
-        <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D101" s="14">
@@ -24004,7 +24791,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f>SUM(D101:H101)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J101" s="15"/>
@@ -24019,8 +24806,8 @@
         <v>한중희</v>
       </c>
       <c r="C102" s="2">
-        <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
-        <v>0.2</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="D102" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B102)</f>
@@ -24036,15 +24823,15 @@
       </c>
       <c r="G102" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B102)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H102" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B102)</f>
         <v>0</v>
       </c>
       <c r="I102" s="14">
-        <f>SUM(D102:H102)</f>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
       <c r="J102" s="15"/>
     </row>
@@ -24058,7 +24845,7 @@
         <v>허동혁</v>
       </c>
       <c r="C103" s="2">
-        <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D103" s="14">
@@ -24082,7 +24869,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f>SUM(D103:H103)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J103" s="15"/>
@@ -24097,16 +24884,16 @@
         <v>홍석준</v>
       </c>
       <c r="C104" s="2">
-        <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
-        <v>0.2</v>
+        <f t="shared" si="11"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D104" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B104)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B104)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B104)</f>
@@ -24121,8 +24908,8 @@
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f>SUM(D104:H104)</f>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
       <c r="J104" s="15"/>
     </row>
@@ -24136,7 +24923,7 @@
         <v>홍현석</v>
       </c>
       <c r="C105" s="2">
-        <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D105" s="14">
@@ -24160,7 +24947,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="14">
-        <f>SUM(D105:H105)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -24174,7 +24961,7 @@
         <v>황석원</v>
       </c>
       <c r="C106" s="2">
-        <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D106" s="14">
@@ -24198,7 +24985,7 @@
         <v>1</v>
       </c>
       <c r="I106" s="14">
-        <f>SUM(D106:H106)</f>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
     </row>
@@ -24212,7 +24999,7 @@
         <v>황재순</v>
       </c>
       <c r="C107" s="2">
-        <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D107" s="14">
@@ -24236,7 +25023,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f>SUM(D107:H107)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -24250,7 +25037,7 @@
         <v>황철우</v>
       </c>
       <c r="C108" s="2">
-        <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D108" s="14">
@@ -24274,7 +25061,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f>SUM(D108:H108)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -24288,7 +25075,7 @@
         <v>김진우</v>
       </c>
       <c r="C109" s="2">
-        <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D109" s="14">
@@ -24312,7 +25099,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="14">
-        <f>SUM(D109:H109)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -24326,7 +25113,7 @@
         <v>노성호</v>
       </c>
       <c r="C110" s="2">
-        <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D110" s="14">
@@ -24350,7 +25137,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="14">
-        <f>SUM(D110:H110)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -24364,7 +25151,7 @@
         <v>박준영</v>
       </c>
       <c r="C111" s="2">
-        <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D111" s="14">
@@ -24388,7 +25175,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f>SUM(D111:H111)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -24402,8 +25189,8 @@
         <v>박태현</v>
       </c>
       <c r="C112" s="2">
-        <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0.2</v>
       </c>
       <c r="D112" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B112)</f>
@@ -24411,7 +25198,7 @@
       </c>
       <c r="E112" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B112)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B112)</f>
@@ -24426,8 +25213,8 @@
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f>SUM(D112:H112)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -24440,7 +25227,7 @@
         <v>서영진</v>
       </c>
       <c r="C113" s="2">
-        <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D113" s="14">
@@ -24464,7 +25251,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="14">
-        <f>SUM(D113:H113)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -24478,8 +25265,8 @@
         <v>오상준</v>
       </c>
       <c r="C114" s="2">
-        <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>2.1</v>
       </c>
       <c r="D114" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B114)</f>
@@ -24487,11 +25274,11 @@
       </c>
       <c r="E114" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B114)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B114)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G114" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B114)</f>
@@ -24502,8 +25289,8 @@
         <v>0</v>
       </c>
       <c r="I114" s="14">
-        <f>SUM(D114:H114)</f>
-        <v>3</v>
+        <f t="shared" si="12"/>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -24516,7 +25303,7 @@
         <v>오성찬</v>
       </c>
       <c r="C115" s="2">
-        <f>((D115+E115+G115+H115)*0.2)+(F115*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.3</v>
       </c>
       <c r="D115" s="14">
@@ -24540,7 +25327,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="14">
-        <f>SUM(D115:H115)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -24554,8 +25341,8 @@
         <v>유우진</v>
       </c>
       <c r="C116" s="2">
-        <f>((D116+E116+G116+H116)*0.2)+(F116*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0.4</v>
       </c>
       <c r="D116" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B116)</f>
@@ -24571,15 +25358,15 @@
       </c>
       <c r="G116" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B116)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H116" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B116)</f>
         <v>0</v>
       </c>
       <c r="I116" s="14">
-        <f>SUM(D116:H116)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -24592,8 +25379,8 @@
         <v>이영준</v>
       </c>
       <c r="C117" s="2">
-        <f>((D117+E117+G117+H117)*0.2)+(F117*0.3)</f>
-        <v>0.5</v>
+        <f t="shared" si="11"/>
+        <v>0.7</v>
       </c>
       <c r="D117" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B117)</f>
@@ -24609,15 +25396,15 @@
       </c>
       <c r="G117" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B117)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B117)</f>
         <v>0</v>
       </c>
       <c r="I117" s="14">
-        <f>SUM(D117:H117)</f>
-        <v>2</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -24630,8 +25417,8 @@
         <v>이찬솔</v>
       </c>
       <c r="C118" s="2">
-        <f>((D118+E118+G118+H118)*0.2)+(F118*0.3)</f>
-        <v>0.2</v>
+        <f t="shared" si="11"/>
+        <v>0.8</v>
       </c>
       <c r="D118" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B118)</f>
@@ -24639,7 +25426,7 @@
       </c>
       <c r="E118" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B118)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B118)</f>
@@ -24647,15 +25434,15 @@
       </c>
       <c r="G118" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B118)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B118)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="14">
-        <f>SUM(D118:H118)</f>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -24668,7 +25455,7 @@
         <v>정현서</v>
       </c>
       <c r="C119" s="2">
-        <f>((D119+E119+G119+H119)*0.2)+(F119*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D119" s="14">
@@ -24692,7 +25479,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f>SUM(D119:H119)</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
     </row>
@@ -24706,12 +25493,12 @@
         <v>황건호</v>
       </c>
       <c r="C120" s="2">
-        <f>((D120+E120+G120+H120)*0.2)+(F120*0.3)</f>
-        <v>1.1000000000000001</v>
+        <f t="shared" si="11"/>
+        <v>2.5</v>
       </c>
       <c r="D120" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B120)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E120" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B120)</f>
@@ -24719,7 +25506,7 @@
       </c>
       <c r="F120" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B120)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G120" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B120)</f>
@@ -24730,8 +25517,8 @@
         <v>0</v>
       </c>
       <c r="I120" s="14">
-        <f>SUM(D120:H120)</f>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -24744,7 +25531,7 @@
         <v>김민성</v>
       </c>
       <c r="C121" s="2">
-        <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D121" s="14">
@@ -24768,7 +25555,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="14">
-        <f>SUM(D121:H121)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -24782,7 +25569,7 @@
         <v>송명섭</v>
       </c>
       <c r="C122" s="2">
-        <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D122" s="14">
@@ -24806,7 +25593,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f>SUM(D122:H122)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -24820,7 +25607,7 @@
         <v>최경영</v>
       </c>
       <c r="C123" s="2">
-        <f>((D123+E123+G123+H123)*0.2)+(F123*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.6</v>
       </c>
       <c r="D123" s="14">
@@ -24844,11 +25631,16 @@
         <v>3</v>
       </c>
       <c r="I123" s="14">
-        <f>SUM(D123:H123)</f>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I123">
+      <sortCondition ref="A3"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:D123">
     <cfRule type="top10" dxfId="9" priority="862" rank="7"/>
@@ -26470,14 +27262,14 @@
       </c>
       <c r="E3" s="70">
         <f>VLOOKUP(D3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="70" t="s">
         <v>299</v>
       </c>
       <c r="G3" s="61">
         <f>VLOOKUP(F3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.3000000000000007</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I3" s="94" t="s">
         <v>333</v>
@@ -26502,14 +27294,14 @@
       </c>
       <c r="Q3" s="62">
         <f>VLOOKUP(P3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>299</v>
       </c>
       <c r="S3" s="63">
         <f>VLOOKUP(R3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.3000000000000007</v>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
@@ -26522,7 +27314,7 @@
       </c>
       <c r="E4" s="62">
         <f>VLOOKUP(D4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="70" t="s">
         <v>225</v>
@@ -26550,14 +27342,14 @@
       </c>
       <c r="Q4" s="62">
         <f>VLOOKUP(P4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>222</v>
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>17</v>
+        <v>19.100000000000001</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -26570,14 +27362,14 @@
       </c>
       <c r="E5" s="47">
         <f>VLOOKUP(D5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>222</v>
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>17</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="I5" s="95"/>
       <c r="J5" s="66">
@@ -26598,14 +27390,14 @@
       </c>
       <c r="Q5" s="62">
         <f>VLOOKUP(P5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>305</v>
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11.9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -26618,14 +27410,14 @@
       </c>
       <c r="E6" s="47">
         <f>VLOOKUP(D6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>233</v>
       </c>
       <c r="G6" s="61">
         <f>VLOOKUP(F6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="I6" s="95"/>
       <c r="J6" s="66">
@@ -26646,14 +27438,14 @@
       </c>
       <c r="Q6" s="69">
         <f>VLOOKUP(P6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>231</v>
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.4</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -26666,14 +27458,14 @@
       </c>
       <c r="E7" s="47">
         <f>VLOOKUP(D7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="70" t="s">
         <v>305</v>
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11.9</v>
+        <v>15</v>
       </c>
       <c r="I7" s="96"/>
       <c r="J7" s="66">
@@ -26721,7 +27513,7 @@
       </c>
       <c r="G8" s="63">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="N8" s="85"/>
       <c r="O8" s="48">
@@ -26759,7 +27551,7 @@
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="98" t="s">
         <v>249</v>
@@ -26800,14 +27592,14 @@
       </c>
       <c r="E10" s="64">
         <f>VLOOKUP(D10,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="70" t="s">
         <v>53</v>
       </c>
       <c r="G10" s="61">
         <f>VLOOKUP(F10,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="I10" s="94" t="s">
         <v>334</v>
@@ -26850,7 +27642,7 @@
       </c>
       <c r="E11" s="65">
         <f>VLOOKUP(D11,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="70" t="s">
         <v>48</v>
@@ -26898,14 +27690,14 @@
       </c>
       <c r="E12" s="65">
         <f>VLOOKUP(D12,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="70" t="s">
         <v>224</v>
       </c>
       <c r="G12" s="61">
         <f>VLOOKUP(F12,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="I12" s="95"/>
       <c r="J12" s="66">
@@ -26946,14 +27738,14 @@
       </c>
       <c r="E13" s="65">
         <f>VLOOKUP(D13,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="70" t="s">
         <v>242</v>
       </c>
       <c r="G13" s="61">
         <f>VLOOKUP(F13,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I13" s="95"/>
       <c r="J13" s="66">
@@ -26982,14 +27774,14 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>229</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="I14" s="96"/>
       <c r="J14" s="66">
@@ -27018,14 +27810,14 @@
       </c>
       <c r="E15" s="65">
         <f>VLOOKUP(D15,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" s="62" t="s">
         <v>300</v>
       </c>
       <c r="G15" s="63">
         <f>VLOOKUP(F15,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="N15"/>
       <c r="O15"/>
@@ -27044,14 +27836,14 @@
       </c>
       <c r="E16" s="65">
         <f>VLOOKUP(D16,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>231</v>
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.4</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H16" s="37"/>
       <c r="I16" s="98" t="s">
@@ -27963,7 +28755,7 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -28081,7 +28873,7 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
@@ -28533,11 +29325,11 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C16</f>
-        <v>3.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="3"/>
@@ -28877,7 +29669,7 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C22</f>
@@ -29198,11 +29990,11 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C25</f>
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="3"/>
@@ -29316,11 +30108,11 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C26</f>
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="3"/>
@@ -29426,7 +30218,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C29</f>
@@ -29662,7 +30454,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C40</f>
@@ -29774,11 +30566,11 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C44</f>
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="3"/>
@@ -29985,7 +30777,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C49</f>
@@ -30101,11 +30893,11 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C57</f>
-        <v>3.2</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="3"/>
@@ -31005,7 +31797,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C79</f>
@@ -31459,11 +32251,11 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C102</f>
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="6"/>
@@ -31573,11 +32365,11 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C104</f>
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="6"/>
@@ -31720,32 +32512,32 @@
       <c r="D4" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="E4" s="77" t="s">
+      <c r="E4" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="78" t="s">
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="79" t="s">
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="80" t="s">
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="80"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="27"/>
@@ -31982,32 +32774,32 @@
       <c r="D12" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="E12" s="77" t="s">
+      <c r="E12" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="78" t="s">
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79" t="s">
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="80" t="s">
+      <c r="N12" s="80"/>
+      <c r="O12" s="80"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R12" s="80"/>
-      <c r="S12" s="80"/>
-      <c r="T12" s="80"/>
-      <c r="U12" s="80"/>
-      <c r="V12" s="80"/>
+      <c r="R12" s="77"/>
+      <c r="S12" s="77"/>
+      <c r="T12" s="77"/>
+      <c r="U12" s="77"/>
+      <c r="V12" s="77"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
@@ -32251,32 +33043,32 @@
       <c r="D20" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78" t="s">
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="79" t="s">
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
-      <c r="Q20" s="80" t="s">
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="R20" s="80"/>
-      <c r="S20" s="80"/>
-      <c r="T20" s="80"/>
-      <c r="U20" s="80"/>
-      <c r="V20" s="80"/>
+      <c r="R20" s="77"/>
+      <c r="S20" s="77"/>
+      <c r="T20" s="77"/>
+      <c r="U20" s="77"/>
+      <c r="V20" s="77"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inhyu\OneDrive\바탕 화면\김인혁\김인혁_청년축구단\1. 출석부\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219FD164-3D60-4F5B-9642-3CD2DEA807DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76188C0-A49F-487D-9DC0-0AB1145910E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="402">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -1508,6 +1508,10 @@
   </si>
   <si>
     <t>홍서준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>입대</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2283,10 +2287,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2295,20 +2299,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2942,7 +2946,7 @@
     <row r="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D1" s="53">
         <f>COUNTIF(D4:D159,"발주")</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I1" s="18" t="s">
         <v>87</v>
@@ -3101,7 +3105,7 @@
     <row r="2" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D2" s="53">
         <f>COUNTIF(D4:D159,"지급")</f>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E2" s="53">
         <f>COUNTIF(E4:E142,"지급")</f>
@@ -3109,7 +3113,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>7.666666666666667</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3180,7 +3184,7 @@
       </c>
       <c r="Z2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA2" s="1">
         <f t="shared" si="0"/>
@@ -3391,7 +3395,9 @@
       <c r="Y3" s="4">
         <v>46156</v>
       </c>
-      <c r="Z3" s="4"/>
+      <c r="Z3" s="4">
+        <v>46170</v>
+      </c>
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -3597,7 +3603,7 @@
       </c>
       <c r="G5" s="2">
         <f>RANK(H5,$H$4:$H$123,0)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -4014,7 +4020,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="4"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
@@ -4125,15 +4131,15 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
-        <v>9.3000000000000007</v>
+        <v>10.3</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>352</v>
@@ -4165,7 +4171,9 @@
       <c r="Y10" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z10" s="2"/>
+      <c r="Z10" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
@@ -4242,7 +4250,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
@@ -4894,11 +4902,11 @@
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
@@ -4934,7 +4942,9 @@
         <v>352</v>
       </c>
       <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
+      <c r="Z17" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
@@ -5114,7 +5124,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="4"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
@@ -5225,7 +5235,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="4"/>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -5749,15 +5759,15 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -5779,7 +5789,9 @@
       <c r="Y25" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z25" s="2"/>
+      <c r="Z25" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
@@ -5973,11 +5985,11 @@
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
-        <v>19.100000000000001</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
@@ -6019,7 +6031,9 @@
         <v>352</v>
       </c>
       <c r="Y27" s="2"/>
-      <c r="Z27" s="2"/>
+      <c r="Z27" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
       <c r="AC27" s="2"/>
@@ -6311,7 +6325,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6420,7 +6434,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
@@ -6541,11 +6555,11 @@
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>352</v>
@@ -6583,7 +6597,9 @@
       <c r="Y32" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z32" s="2"/>
+      <c r="Z32" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
@@ -6775,15 +6791,15 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I34" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
@@ -6813,7 +6829,9 @@
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
       <c r="Y34" s="2"/>
-      <c r="Z34" s="2"/>
+      <c r="Z34" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA34" s="2"/>
       <c r="AB34" s="2"/>
       <c r="AC34" s="2"/>
@@ -7102,11 +7120,11 @@
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
-        <v>11.8</v>
+        <v>12.8</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -7140,7 +7158,9 @@
         <v>352</v>
       </c>
       <c r="Y37" s="2"/>
-      <c r="Z37" s="2"/>
+      <c r="Z37" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA37" s="2"/>
       <c r="AB37" s="2"/>
       <c r="AC37" s="2"/>
@@ -7209,7 +7229,7 @@
         <v>2023</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="E38" s="54"/>
       <c r="F38" s="2" t="s">
@@ -7217,15 +7237,15 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="4"/>
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="I38" s="6">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -7249,7 +7269,9 @@
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
       <c r="Y38" s="2"/>
-      <c r="Z38" s="2"/>
+      <c r="Z38" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA38" s="2"/>
       <c r="AB38" s="2"/>
       <c r="AC38" s="2"/>
@@ -7848,7 +7870,7 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
@@ -8175,7 +8197,7 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
@@ -8604,7 +8626,7 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
@@ -9025,7 +9047,7 @@
         <v>2023</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="E55" s="54"/>
       <c r="F55" s="2" t="s">
@@ -9037,11 +9059,11 @@
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
-        <v>8.8000000000000007</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I55" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -9073,7 +9095,9 @@
       <c r="Y55" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z55" s="2"/>
+      <c r="Z55" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA55" s="2"/>
       <c r="AB55" s="2"/>
       <c r="AC55" s="2"/>
@@ -9150,7 +9174,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
@@ -9696,15 +9720,15 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="4"/>
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="I61" s="6">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -9728,7 +9752,9 @@
       <c r="W61" s="2"/>
       <c r="X61" s="2"/>
       <c r="Y61" s="2"/>
-      <c r="Z61" s="2"/>
+      <c r="Z61" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA61" s="2"/>
       <c r="AB61" s="2"/>
       <c r="AC61" s="2"/>
@@ -10117,15 +10143,15 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="I65" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -10157,7 +10183,9 @@
       </c>
       <c r="X65" s="2"/>
       <c r="Y65" s="2"/>
-      <c r="Z65" s="2"/>
+      <c r="Z65" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA65" s="2"/>
       <c r="AB65" s="2"/>
       <c r="AC65" s="2"/>
@@ -10234,7 +10262,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
@@ -10343,7 +10371,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
@@ -10558,7 +10586,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
@@ -10667,7 +10695,7 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
@@ -10775,7 +10803,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="4"/>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -11085,9 +11113,8 @@
       <c r="C74" s="58">
         <v>2025</v>
       </c>
-      <c r="D74" s="54">
-        <f t="shared" si="16"/>
-        <v>5</v>
+      <c r="D74" s="54" t="s">
+        <v>227</v>
       </c>
       <c r="E74" s="54"/>
       <c r="F74" s="2" t="s">
@@ -11208,7 +11235,7 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="17"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
@@ -11319,15 +11346,15 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="17"/>
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
@@ -11351,7 +11378,9 @@
       <c r="Y76" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z76" s="2"/>
+      <c r="Z76" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA76" s="2"/>
       <c r="AB76" s="2"/>
       <c r="AC76" s="2"/>
@@ -11541,15 +11570,15 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="17"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
-        <v>4.5999999999999996</v>
+        <v>5.6</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
@@ -11575,7 +11604,9 @@
       </c>
       <c r="X78" s="2"/>
       <c r="Y78" s="2"/>
-      <c r="Z78" s="2"/>
+      <c r="Z78" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA78" s="2"/>
       <c r="AB78" s="2"/>
       <c r="AC78" s="2"/>
@@ -11652,7 +11683,7 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" si="17"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
@@ -11759,7 +11790,7 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="17"/>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
@@ -12074,7 +12105,7 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="17"/>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
@@ -12174,8 +12205,9 @@
       <c r="C84" s="58">
         <v>2024</v>
       </c>
-      <c r="D84" s="54" t="s">
-        <v>227</v>
+      <c r="D84" s="54">
+        <f t="shared" ref="D84" si="19">COUNTA(L84:AB84)</f>
+        <v>1</v>
       </c>
       <c r="E84" s="54"/>
       <c r="F84" s="2" t="s">
@@ -12288,7 +12320,7 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="17"/>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
@@ -12387,7 +12419,7 @@
         <v>322</v>
       </c>
       <c r="D86" s="54" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="E86" s="54"/>
       <c r="F86" s="2" t="s">
@@ -12498,7 +12530,7 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="17"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
@@ -12704,7 +12736,7 @@
         <v>2022</v>
       </c>
       <c r="D89" s="54">
-        <f t="shared" ref="D89" si="19">COUNTA(L89:AB89)</f>
+        <f t="shared" ref="D89" si="20">COUNTA(L89:AB89)</f>
         <v>0</v>
       </c>
       <c r="E89" s="54"/>
@@ -12816,7 +12848,7 @@
       </c>
       <c r="G90" s="2">
         <f t="shared" si="17"/>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
@@ -12917,7 +12949,7 @@
         <v>2022</v>
       </c>
       <c r="D91" s="54">
-        <f t="shared" ref="D91" si="20">COUNTA(L91:AB91)</f>
+        <f t="shared" ref="D91" si="21">COUNTA(L91:AB91)</f>
         <v>1</v>
       </c>
       <c r="E91" s="54"/>
@@ -13031,7 +13063,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="17"/>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
@@ -13140,15 +13172,15 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" si="17"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
-        <v>9.8000000000000007</v>
+        <v>10.8</v>
       </c>
       <c r="I93" s="6">
         <f t="shared" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
@@ -13180,7 +13212,9 @@
         <v>352</v>
       </c>
       <c r="Y93" s="2"/>
-      <c r="Z93" s="2"/>
+      <c r="Z93" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA93" s="2"/>
       <c r="AB93" s="2"/>
       <c r="AC93" s="2"/>
@@ -13257,7 +13291,7 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="17"/>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
@@ -13370,11 +13404,11 @@
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I95" s="6">
         <f t="shared" si="18"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>352</v>
@@ -13416,7 +13450,9 @@
       <c r="Y95" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z95" s="2"/>
+      <c r="Z95" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA95" s="2"/>
       <c r="AB95" s="2"/>
       <c r="AC95" s="2"/>
@@ -13493,15 +13529,15 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" si="17"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
-        <v>10.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="18"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>352</v>
@@ -13537,7 +13573,9 @@
       <c r="Y96" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z96" s="2"/>
+      <c r="Z96" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA96" s="2"/>
       <c r="AB96" s="2"/>
       <c r="AC96" s="2"/>
@@ -13727,7 +13765,7 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" si="17"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H98" s="6">
         <f>I98+개인기록Sheet!C98</f>
@@ -13832,7 +13870,7 @@
         <v>2021</v>
       </c>
       <c r="D99" s="54">
-        <f t="shared" ref="D99" si="21">COUNTA(L99:AB99)</f>
+        <f t="shared" ref="D99" si="22">COUNTA(L99:AB99)</f>
         <v>0</v>
       </c>
       <c r="E99" s="54"/>
@@ -13944,15 +13982,15 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="17"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
-        <v>4.5999999999999996</v>
+        <v>5.6</v>
       </c>
       <c r="I100" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>352</v>
@@ -13978,7 +14016,9 @@
       <c r="W100" s="2"/>
       <c r="X100" s="2"/>
       <c r="Y100" s="2"/>
-      <c r="Z100" s="2"/>
+      <c r="Z100" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA100" s="2"/>
       <c r="AB100" s="2"/>
       <c r="AC100" s="2"/>
@@ -14055,15 +14095,15 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="17"/>
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="I101" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>352</v>
@@ -14089,7 +14129,9 @@
       <c r="W101" s="2"/>
       <c r="X101" s="2"/>
       <c r="Y101" s="2"/>
-      <c r="Z101" s="2"/>
+      <c r="Z101" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA101" s="2"/>
       <c r="AB101" s="2"/>
       <c r="AC101" s="2"/>
@@ -14166,15 +14208,15 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="17"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I102" s="6">
         <f t="shared" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>352</v>
@@ -14206,7 +14248,9 @@
       <c r="Y102" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z102" s="2"/>
+      <c r="Z102" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA102" s="2"/>
       <c r="AB102" s="2"/>
       <c r="AC102" s="2"/>
@@ -14283,7 +14327,7 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="17"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
@@ -14390,15 +14434,15 @@
       </c>
       <c r="G104" s="2">
         <f t="shared" si="17"/>
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="I104" s="6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
@@ -14420,7 +14464,9 @@
       <c r="Y104" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z104" s="2"/>
+      <c r="Z104" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA104" s="2"/>
       <c r="AB104" s="2"/>
       <c r="AC104" s="2"/>
@@ -14497,7 +14543,7 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="17"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
@@ -14604,7 +14650,7 @@
       </c>
       <c r="G106" s="2">
         <f t="shared" si="17"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
@@ -14808,7 +14854,7 @@
         <v>2025</v>
       </c>
       <c r="D108" s="54">
-        <f t="shared" ref="D108:D120" si="22">COUNTA(L108:AB108)</f>
+        <f t="shared" ref="D108:D120" si="23">COUNTA(L108:AB108)</f>
         <v>1</v>
       </c>
       <c r="E108" s="54"/>
@@ -14914,7 +14960,7 @@
         <v>2026</v>
       </c>
       <c r="D109" s="54">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="E109" s="54"/>
@@ -15020,8 +15066,8 @@
         <v>2026</v>
       </c>
       <c r="D110" s="54">
-        <f t="shared" si="22"/>
-        <v>2</v>
+        <f t="shared" si="23"/>
+        <v>3</v>
       </c>
       <c r="E110" s="54"/>
       <c r="F110" s="2" t="s">
@@ -15029,15 +15075,15 @@
       </c>
       <c r="G110" s="2">
         <f t="shared" si="17"/>
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I110" s="6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
@@ -15059,7 +15105,9 @@
       </c>
       <c r="X110" s="2"/>
       <c r="Y110" s="2"/>
-      <c r="Z110" s="2"/>
+      <c r="Z110" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA110" s="2"/>
       <c r="AB110" s="2"/>
       <c r="AC110" s="2"/>
@@ -15128,7 +15176,7 @@
         <v>2026</v>
       </c>
       <c r="D111" s="54">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
       <c r="E111" s="54"/>
@@ -15137,7 +15185,7 @@
       </c>
       <c r="G111" s="2">
         <f t="shared" si="17"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
@@ -15235,9 +15283,8 @@
       <c r="C112" s="58">
         <v>2026</v>
       </c>
-      <c r="D112" s="54">
-        <f t="shared" si="22"/>
-        <v>4</v>
+      <c r="D112" s="54" t="s">
+        <v>227</v>
       </c>
       <c r="E112" s="54"/>
       <c r="F112" s="2" t="s">
@@ -15245,15 +15292,15 @@
       </c>
       <c r="G112" s="2">
         <f t="shared" si="17"/>
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="I112" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2"/>
@@ -15279,7 +15326,9 @@
       <c r="Y112" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="Z112" s="2"/>
+      <c r="Z112" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA112" s="2"/>
       <c r="AB112" s="2"/>
       <c r="AC112" s="2"/>
@@ -15348,7 +15397,7 @@
         <v>2026</v>
       </c>
       <c r="D113" s="54">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
       <c r="E113" s="54"/>
@@ -15357,7 +15406,7 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="17"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
@@ -15456,7 +15505,7 @@
         <v>2026</v>
       </c>
       <c r="D114" s="54">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4</v>
       </c>
       <c r="E114" s="54"/>
@@ -15568,7 +15617,7 @@
         <v>2026</v>
       </c>
       <c r="D115" s="54">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4</v>
       </c>
       <c r="E115" s="54"/>
@@ -15577,7 +15626,7 @@
       </c>
       <c r="G115" s="2">
         <f t="shared" si="17"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
@@ -15680,7 +15729,7 @@
         <v>2026</v>
       </c>
       <c r="D116" s="54">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4</v>
       </c>
       <c r="E116" s="54"/>
@@ -15689,7 +15738,7 @@
       </c>
       <c r="G116" s="2">
         <f t="shared" si="17"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H116" s="6">
         <f>I116+개인기록Sheet!C116</f>
@@ -15792,7 +15841,7 @@
         <v>2026</v>
       </c>
       <c r="D117" s="54">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4</v>
       </c>
       <c r="E117" s="54"/>
@@ -15801,7 +15850,7 @@
       </c>
       <c r="G117" s="2">
         <f t="shared" si="17"/>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H117" s="6">
         <f>I117+개인기록Sheet!C117</f>
@@ -15904,8 +15953,8 @@
         <v>2026</v>
       </c>
       <c r="D118" s="54">
-        <f t="shared" si="22"/>
-        <v>2</v>
+        <f t="shared" si="23"/>
+        <v>3</v>
       </c>
       <c r="E118" s="54"/>
       <c r="F118" s="2" t="s">
@@ -15913,15 +15962,15 @@
       </c>
       <c r="G118" s="2">
         <f t="shared" si="17"/>
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="I118" s="6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
@@ -15943,7 +15992,9 @@
         <v>352</v>
       </c>
       <c r="Y118" s="2"/>
-      <c r="Z118" s="2"/>
+      <c r="Z118" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA118" s="2"/>
       <c r="AB118" s="2"/>
       <c r="AC118" s="2"/>
@@ -16012,7 +16063,7 @@
         <v>2026</v>
       </c>
       <c r="D119" s="54">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4</v>
       </c>
       <c r="E119" s="54"/>
@@ -16021,7 +16072,7 @@
       </c>
       <c r="G119" s="2">
         <f t="shared" si="17"/>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H119" s="6">
         <f>I119+개인기록Sheet!C119</f>
@@ -16123,9 +16174,8 @@
       <c r="C120" s="58">
         <v>2026</v>
       </c>
-      <c r="D120" s="54">
-        <f t="shared" si="22"/>
-        <v>5</v>
+      <c r="D120" s="54" t="s">
+        <v>401</v>
       </c>
       <c r="E120" s="54"/>
       <c r="F120" s="2" t="s">
@@ -16133,7 +16183,7 @@
       </c>
       <c r="G120" s="2">
         <f t="shared" si="17"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H120" s="6">
         <f>I120+개인기록Sheet!C120</f>
@@ -16341,7 +16391,7 @@
         <v>2024</v>
       </c>
       <c r="D122" s="54">
-        <f t="shared" ref="D122" si="23">COUNTA(L122:AB122)</f>
+        <f t="shared" ref="D122" si="24">COUNTA(L122:AB122)</f>
         <v>0</v>
       </c>
       <c r="E122" s="54"/>
@@ -16453,15 +16503,15 @@
       </c>
       <c r="G123" s="2">
         <f t="shared" si="17"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H123" s="6">
         <f>I123+개인기록Sheet!C123</f>
-        <v>4.5999999999999996</v>
+        <v>5.6</v>
       </c>
       <c r="I123" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J123" s="2"/>
       <c r="K123" s="2" t="s">
@@ -16485,7 +16535,9 @@
       <c r="W123" s="2"/>
       <c r="X123" s="2"/>
       <c r="Y123" s="2"/>
-      <c r="Z123" s="2"/>
+      <c r="Z123" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AA123" s="2"/>
       <c r="AB123" s="2"/>
       <c r="AC123" s="2"/>
@@ -16544,6 +16596,7 @@
       <c r="CD123" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:CT123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:E123">
     <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="지급">
@@ -20220,38 +20273,120 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="Q89:V89"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="M89:P89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="M77:P77"/>
-    <mergeCell ref="Q77:V77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="Q113:V113"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="M101:P101"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
     <mergeCell ref="Q2:V2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -20275,120 +20410,38 @@
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E13:H13"/>
     <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="M101:P101"/>
-    <mergeCell ref="Q101:V101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="M113:P113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="Q113:V113"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="Q77:V77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -24728,7 +24781,7 @@
         <v>한상규</v>
       </c>
       <c r="C100" s="2">
-        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f t="shared" ref="C100:C123" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D100" s="14">
@@ -24752,7 +24805,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
+        <f t="shared" ref="I100:I123" si="12">SUM(D100:H100)</f>
         <v>3</v>
       </c>
       <c r="J100" s="15"/>
@@ -27223,10 +27276,10 @@
       <c r="G2" s="47" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="98" t="s">
+      <c r="I2" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="98"/>
+      <c r="J2" s="93"/>
       <c r="K2" s="65" t="s">
         <v>277</v>
       </c>
@@ -27251,7 +27304,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="92" t="s">
         <v>338</v>
       </c>
       <c r="C3" s="72">
@@ -27262,14 +27315,14 @@
       </c>
       <c r="E3" s="70">
         <f>VLOOKUP(D3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="70" t="s">
         <v>299</v>
       </c>
       <c r="G3" s="61">
         <f>VLOOKUP(F3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.3000000000000007</v>
+        <v>10.3</v>
       </c>
       <c r="I3" s="94" t="s">
         <v>333</v>
@@ -27294,14 +27347,14 @@
       </c>
       <c r="Q3" s="62">
         <f>VLOOKUP(P3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>299</v>
       </c>
       <c r="S3" s="63">
         <f>VLOOKUP(R3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.3000000000000007</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
@@ -27342,14 +27395,14 @@
       </c>
       <c r="Q4" s="62">
         <f>VLOOKUP(P4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>222</v>
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>19.100000000000001</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -27362,14 +27415,14 @@
       </c>
       <c r="E5" s="47">
         <f>VLOOKUP(D5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>222</v>
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>19.100000000000001</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="I5" s="95"/>
       <c r="J5" s="66">
@@ -27390,14 +27443,14 @@
       </c>
       <c r="Q5" s="62">
         <f>VLOOKUP(P5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>305</v>
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -27410,7 +27463,7 @@
       </c>
       <c r="E6" s="47">
         <f>VLOOKUP(D6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>233</v>
@@ -27438,14 +27491,14 @@
       </c>
       <c r="Q6" s="69">
         <f>VLOOKUP(P6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>231</v>
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.8000000000000007</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -27465,9 +27518,9 @@
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15</v>
-      </c>
-      <c r="I7" s="96"/>
+        <v>16</v>
+      </c>
+      <c r="I7" s="97"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -27486,14 +27539,14 @@
       </c>
       <c r="Q7" s="69">
         <f>VLOOKUP(P7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R7" s="65" t="s">
         <v>325</v>
       </c>
       <c r="S7" s="71">
         <f>VLOOKUP(R7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
@@ -27551,12 +27604,12 @@
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>3</v>
-      </c>
-      <c r="I9" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="J9" s="98"/>
+      <c r="J9" s="93"/>
       <c r="K9" s="65" t="s">
         <v>277</v>
       </c>
@@ -27642,7 +27695,7 @@
       </c>
       <c r="E11" s="65">
         <f>VLOOKUP(D11,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="70" t="s">
         <v>48</v>
@@ -27709,7 +27762,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="97"/>
+      <c r="N12" s="100"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -27774,16 +27827,16 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>229</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11.6</v>
-      </c>
-      <c r="I14" s="96"/>
+        <v>12.6</v>
+      </c>
+      <c r="I14" s="97"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -27836,20 +27889,20 @@
       </c>
       <c r="E16" s="65">
         <f>VLOOKUP(D16,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>231</v>
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.8000000000000007</v>
+        <v>10.8</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="98" t="s">
+      <c r="I16" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="J16" s="98"/>
+      <c r="J16" s="93"/>
       <c r="K16" s="65" t="s">
         <v>277</v>
       </c>
@@ -27872,7 +27925,7 @@
       </c>
       <c r="G17" s="63">
         <f>VLOOKUP(F17,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="H17" s="37"/>
       <c r="I17" s="94" t="s">
@@ -27910,10 +27963,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="C19" s="98"/>
+      <c r="C19" s="93"/>
       <c r="D19" s="65" t="s">
         <v>277</v>
       </c>
@@ -27964,7 +28017,7 @@
       <c r="E21" s="65" t="s">
         <v>341</v>
       </c>
-      <c r="I21" s="96"/>
+      <c r="I21" s="97"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -27976,7 +28029,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="100"/>
+      <c r="B22" s="96"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -27988,10 +28041,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="92" t="s">
+      <c r="I23" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="J23" s="93"/>
+      <c r="J23" s="99"/>
       <c r="K23" s="65" t="s">
         <v>277</v>
       </c>
@@ -28074,7 +28127,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="96"/>
+      <c r="I30" s="97"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -28087,12 +28140,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -28101,6 +28148,12 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B1FE1CE8-63DE-413D-AEDF-7D70F3B7BC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F625402-0C2E-4D60-948F-B78D1D7CCF8F}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69531D03-DFD6-4D56-BAFC-61812D3C9D24}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="408">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -1519,6 +1519,21 @@
   </si>
   <si>
     <t>박태현</t>
+  </si>
+  <si>
+    <t>게스트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤원택</t>
+  </si>
+  <si>
+    <t>황숵원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>노미준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2248,9 +2263,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2258,6 +2270,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3119,7 +3134,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>8.6666666666666661</v>
+        <v>9.0444444444444443</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3198,7 +3213,7 @@
       </c>
       <c r="AB2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="0"/>
@@ -3407,7 +3422,9 @@
       <c r="AA3" s="4">
         <v>46177</v>
       </c>
-      <c r="AB3" s="4"/>
+      <c r="AB3" s="4">
+        <v>46184</v>
+      </c>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
@@ -3486,11 +3503,11 @@
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>15.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4" si="2">(COUNTIF(J4:CD4,"출전")*1)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>352</v>
@@ -3538,7 +3555,9 @@
       <c r="AA4" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AB4" s="2"/>
+      <c r="AB4" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
@@ -4030,7 +4049,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
@@ -4143,7 +4162,7 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
@@ -4264,15 +4283,15 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
-        <v>11.4</v>
+        <v>13.1</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>352</v>
@@ -4308,7 +4327,9 @@
       <c r="AA11" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AB11" s="2"/>
+      <c r="AB11" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -4801,7 +4822,7 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
@@ -4918,11 +4939,11 @@
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
-        <v>13.6</v>
+        <v>15</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
@@ -4964,7 +4985,9 @@
       <c r="AA17" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AB17" s="2"/>
+      <c r="AB17" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
       <c r="AE17" s="2"/>
@@ -5142,7 +5165,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
@@ -5253,7 +5276,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -5777,15 +5800,15 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -5811,7 +5834,9 @@
         <v>352</v>
       </c>
       <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
+      <c r="AB25" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC25" s="2"/>
       <c r="AD25" s="2"/>
       <c r="AE25" s="2"/>
@@ -5886,7 +5911,7 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
@@ -6130,7 +6155,7 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
@@ -6347,7 +6372,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6456,7 +6481,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
@@ -6577,11 +6602,11 @@
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>13</v>
+        <v>14.6</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>352</v>
@@ -6623,7 +6648,9 @@
         <v>352</v>
       </c>
       <c r="AA32" s="2"/>
-      <c r="AB32" s="2"/>
+      <c r="AB32" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC32" s="2"/>
       <c r="AD32" s="2"/>
       <c r="AE32" s="2"/>
@@ -6698,7 +6725,7 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
@@ -6817,11 +6844,11 @@
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
-        <v>8.1999999999999993</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="I34" s="6">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
@@ -6855,7 +6882,9 @@
         <v>352</v>
       </c>
       <c r="AA34" s="2"/>
-      <c r="AB34" s="2"/>
+      <c r="AB34" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC34" s="2"/>
       <c r="AD34" s="2"/>
       <c r="AE34" s="2"/>
@@ -7142,11 +7171,11 @@
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
-        <v>15</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -7186,7 +7215,9 @@
       <c r="AA37" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AB37" s="2"/>
+      <c r="AB37" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
       <c r="AE37" s="2"/>
@@ -7261,7 +7292,7 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
@@ -7894,15 +7925,15 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
-        <v>11.2</v>
+        <v>12.8</v>
       </c>
       <c r="I44" s="6">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -7940,7 +7971,9 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
-      <c r="AB44" s="2"/>
+      <c r="AB44" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC44" s="2"/>
       <c r="AD44" s="2"/>
       <c r="AE44" s="2"/>
@@ -8016,7 +8049,7 @@
       </c>
       <c r="G45" s="2">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H45" s="6">
         <f>I45+개인기록Sheet!C45</f>
@@ -8331,7 +8364,7 @@
       </c>
       <c r="G48" s="2">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H48" s="6">
         <f>I48+개인기록Sheet!C48</f>
@@ -8762,15 +8795,15 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H52" s="6">
         <f>I52+개인기록Sheet!C52</f>
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="I52" s="6">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
@@ -8806,7 +8839,9 @@
       <c r="AA52" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AB52" s="2"/>
+      <c r="AB52" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC52" s="2"/>
       <c r="AD52" s="2"/>
       <c r="AE52" s="2"/>
@@ -9093,7 +9128,7 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
@@ -9414,15 +9449,15 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H58" s="6">
         <f>I58+개인기록Sheet!C58</f>
-        <v>9.8000000000000007</v>
+        <v>11</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
@@ -9458,7 +9493,9 @@
         <v>352</v>
       </c>
       <c r="AA58" s="2"/>
-      <c r="AB58" s="2"/>
+      <c r="AB58" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC58" s="2"/>
       <c r="AD58" s="2"/>
       <c r="AE58" s="2"/>
@@ -9533,7 +9570,7 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
@@ -9640,7 +9677,7 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
@@ -9964,7 +10001,7 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H63" s="6">
         <f>I63+개인기록Sheet!C63</f>
@@ -10080,7 +10117,7 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H64" s="6">
         <f>I64+개인기록Sheet!C64</f>
@@ -10192,7 +10229,7 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
@@ -10303,7 +10340,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
@@ -10726,15 +10763,15 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="14"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="I70" s="6">
         <f t="shared" si="15"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -10772,7 +10809,9 @@
       <c r="AA70" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AB70" s="2"/>
+      <c r="AB70" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC70" s="2"/>
       <c r="AD70" s="2"/>
       <c r="AE70" s="2"/>
@@ -10848,7 +10887,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="14"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -10959,7 +10998,7 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" si="14"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H72" s="6">
         <f>I72+개인기록Sheet!C72</f>
@@ -11068,7 +11107,7 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" si="14"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H73" s="6">
         <f>I73+개인기록Sheet!C73</f>
@@ -11283,15 +11322,15 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="14"/>
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
-        <v>3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I75" s="6">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
@@ -11317,7 +11356,9 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
-      <c r="AB75" s="2"/>
+      <c r="AB75" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC75" s="2"/>
       <c r="AD75" s="2"/>
       <c r="AE75" s="2"/>
@@ -11392,15 +11433,15 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="14"/>
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
-        <v>2.6</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
@@ -11424,7 +11465,9 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
       <c r="AA76" s="2"/>
-      <c r="AB76" s="2"/>
+      <c r="AB76" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC76" s="2"/>
       <c r="AD76" s="2"/>
       <c r="AE76" s="2"/>
@@ -11500,7 +11543,7 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="14"/>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
@@ -11819,7 +11862,7 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="14"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
@@ -11932,7 +11975,7 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" si="14"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
@@ -12043,15 +12086,15 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="14"/>
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="I82" s="6">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
@@ -12079,7 +12122,9 @@
         <v>352</v>
       </c>
       <c r="AA82" s="2"/>
-      <c r="AB82" s="2"/>
+      <c r="AB82" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC82" s="2"/>
       <c r="AD82" s="2"/>
       <c r="AE82" s="2"/>
@@ -12154,7 +12199,7 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="14"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
@@ -12269,7 +12314,7 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="14"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
@@ -12384,7 +12429,7 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="14"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
@@ -12493,7 +12538,7 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" si="14"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
@@ -12603,7 +12648,7 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="14"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
@@ -13023,7 +13068,7 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" si="14"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
@@ -13132,7 +13177,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="14"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
@@ -13347,7 +13392,7 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="14"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
@@ -13557,7 +13602,7 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" si="14"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
@@ -13877,7 +13922,7 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" si="14"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H99" s="6">
         <f>I99+개인기록Sheet!C99</f>
@@ -14094,7 +14139,7 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="14"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
@@ -14203,7 +14248,7 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="14"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
@@ -14324,7 +14369,7 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="14"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
@@ -14539,7 +14584,7 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="14"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
@@ -14654,11 +14699,11 @@
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
-        <v>16</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="I106" s="6">
         <f t="shared" si="15"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>352</v>
@@ -14704,7 +14749,9 @@
         <v>352</v>
       </c>
       <c r="AA106" s="2"/>
-      <c r="AB106" s="2"/>
+      <c r="AB106" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC106" s="2"/>
       <c r="AD106" s="2"/>
       <c r="AE106" s="2"/>
@@ -14779,7 +14826,7 @@
       </c>
       <c r="G107" s="2">
         <f t="shared" si="14"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H107" s="6">
         <f>I107+개인기록Sheet!C107</f>
@@ -14904,7 +14951,7 @@
       </c>
       <c r="G108" s="2">
         <f t="shared" si="14"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
@@ -15017,15 +15064,15 @@
       </c>
       <c r="G109" s="2">
         <f t="shared" si="14"/>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I109" s="6">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>352</v>
@@ -15055,7 +15102,9 @@
       </c>
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
-      <c r="AB109" s="2"/>
+      <c r="AB109" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC109" s="2"/>
       <c r="AD109" s="2"/>
       <c r="AE109" s="2"/>
@@ -15234,7 +15283,7 @@
       </c>
       <c r="G111" s="2">
         <f t="shared" si="14"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
@@ -15349,7 +15398,7 @@
       </c>
       <c r="G112" s="2">
         <f t="shared" si="14"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
@@ -15462,7 +15511,7 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="14"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
@@ -15583,7 +15632,7 @@
       </c>
       <c r="G114" s="2">
         <f t="shared" si="14"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
@@ -15692,7 +15741,7 @@
       </c>
       <c r="G115" s="2">
         <f t="shared" si="14"/>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
@@ -15908,7 +15957,7 @@
       </c>
       <c r="G117" s="2">
         <f t="shared" si="14"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H117" s="6">
         <f>I117+개인기록Sheet!C117</f>
@@ -16021,15 +16070,15 @@
       </c>
       <c r="G118" s="2">
         <f t="shared" si="14"/>
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="I118" s="6">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
@@ -16055,7 +16104,9 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
-      <c r="AB118" s="2"/>
+      <c r="AB118" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AC118" s="2"/>
       <c r="AD118" s="2"/>
       <c r="AE118" s="2"/>
@@ -16548,7 +16599,7 @@
       </c>
       <c r="G123" s="2">
         <f t="shared" si="14"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H123" s="6">
         <f>I123+개인기록Sheet!C123</f>
@@ -16664,7 +16715,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:V144"/>
+  <dimension ref="A2:V156"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -16683,32 +16734,32 @@
       <c r="D2" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="79" t="s">
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="80" t="s">
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="77" t="s">
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
@@ -17055,32 +17106,32 @@
       <c r="D13" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="E13" s="78" t="s">
+      <c r="E13" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="79" t="s">
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="80" t="s">
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N13" s="80"/>
-      <c r="O13" s="80"/>
-      <c r="P13" s="80"/>
-      <c r="Q13" s="77" t="s">
+      <c r="N13" s="79"/>
+      <c r="O13" s="79"/>
+      <c r="P13" s="79"/>
+      <c r="Q13" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R13" s="77"/>
-      <c r="S13" s="77"/>
-      <c r="T13" s="77"/>
-      <c r="U13" s="77"/>
-      <c r="V13" s="77"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="80"/>
+      <c r="U13" s="80"/>
+      <c r="V13" s="80"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
@@ -17373,32 +17424,32 @@
       <c r="D24" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="E24" s="78" t="s">
+      <c r="E24" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="79" t="s">
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="80" t="s">
+      <c r="J24" s="78"/>
+      <c r="K24" s="78"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N24" s="80"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="80"/>
-      <c r="Q24" s="77" t="s">
+      <c r="N24" s="79"/>
+      <c r="O24" s="79"/>
+      <c r="P24" s="79"/>
+      <c r="Q24" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R24" s="77"/>
-      <c r="S24" s="77"/>
-      <c r="T24" s="77"/>
-      <c r="U24" s="77"/>
-      <c r="V24" s="77"/>
+      <c r="R24" s="80"/>
+      <c r="S24" s="80"/>
+      <c r="T24" s="80"/>
+      <c r="U24" s="80"/>
+      <c r="V24" s="80"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
@@ -17809,32 +17860,32 @@
       <c r="D37" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="E37" s="78" t="s">
+      <c r="E37" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="79" t="s">
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J37" s="79"/>
-      <c r="K37" s="79"/>
-      <c r="L37" s="79"/>
-      <c r="M37" s="80" t="s">
+      <c r="J37" s="78"/>
+      <c r="K37" s="78"/>
+      <c r="L37" s="78"/>
+      <c r="M37" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N37" s="80"/>
-      <c r="O37" s="80"/>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="77" t="s">
+      <c r="N37" s="79"/>
+      <c r="O37" s="79"/>
+      <c r="P37" s="79"/>
+      <c r="Q37" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="77"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="80"/>
+      <c r="T37" s="80"/>
+      <c r="U37" s="80"/>
+      <c r="V37" s="80"/>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B38" s="73" t="s">
@@ -18095,32 +18146,32 @@
       <c r="D49" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="E49" s="78" t="s">
+      <c r="E49" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F49" s="78"/>
-      <c r="G49" s="78"/>
-      <c r="H49" s="78"/>
-      <c r="I49" s="79" t="s">
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="77"/>
+      <c r="I49" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J49" s="79"/>
-      <c r="K49" s="79"/>
-      <c r="L49" s="79"/>
-      <c r="M49" s="80" t="s">
+      <c r="J49" s="78"/>
+      <c r="K49" s="78"/>
+      <c r="L49" s="78"/>
+      <c r="M49" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N49" s="80"/>
-      <c r="O49" s="80"/>
-      <c r="P49" s="80"/>
-      <c r="Q49" s="77" t="s">
+      <c r="N49" s="79"/>
+      <c r="O49" s="79"/>
+      <c r="P49" s="79"/>
+      <c r="Q49" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R49" s="77"/>
-      <c r="S49" s="77"/>
-      <c r="T49" s="77"/>
-      <c r="U49" s="77"/>
-      <c r="V49" s="77"/>
+      <c r="R49" s="80"/>
+      <c r="S49" s="80"/>
+      <c r="T49" s="80"/>
+      <c r="U49" s="80"/>
+      <c r="V49" s="80"/>
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="73" t="s">
@@ -18513,32 +18564,32 @@
       <c r="D63" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="E63" s="78" t="s">
+      <c r="E63" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F63" s="78"/>
-      <c r="G63" s="78"/>
-      <c r="H63" s="78"/>
-      <c r="I63" s="79" t="s">
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="77"/>
+      <c r="I63" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J63" s="79"/>
-      <c r="K63" s="79"/>
-      <c r="L63" s="79"/>
-      <c r="M63" s="80" t="s">
+      <c r="J63" s="78"/>
+      <c r="K63" s="78"/>
+      <c r="L63" s="78"/>
+      <c r="M63" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N63" s="80"/>
-      <c r="O63" s="80"/>
-      <c r="P63" s="80"/>
-      <c r="Q63" s="77" t="s">
+      <c r="N63" s="79"/>
+      <c r="O63" s="79"/>
+      <c r="P63" s="79"/>
+      <c r="Q63" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R63" s="77"/>
-      <c r="S63" s="77"/>
-      <c r="T63" s="77"/>
-      <c r="U63" s="77"/>
-      <c r="V63" s="77"/>
+      <c r="R63" s="80"/>
+      <c r="S63" s="80"/>
+      <c r="T63" s="80"/>
+      <c r="U63" s="80"/>
+      <c r="V63" s="80"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="73" t="s">
@@ -18939,32 +18990,32 @@
       <c r="D77" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="E77" s="78" t="s">
+      <c r="E77" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F77" s="78"/>
-      <c r="G77" s="78"/>
-      <c r="H77" s="78"/>
-      <c r="I77" s="79" t="s">
+      <c r="F77" s="77"/>
+      <c r="G77" s="77"/>
+      <c r="H77" s="77"/>
+      <c r="I77" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J77" s="79"/>
-      <c r="K77" s="79"/>
-      <c r="L77" s="79"/>
-      <c r="M77" s="80" t="s">
+      <c r="J77" s="78"/>
+      <c r="K77" s="78"/>
+      <c r="L77" s="78"/>
+      <c r="M77" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N77" s="80"/>
-      <c r="O77" s="80"/>
-      <c r="P77" s="80"/>
-      <c r="Q77" s="77" t="s">
+      <c r="N77" s="79"/>
+      <c r="O77" s="79"/>
+      <c r="P77" s="79"/>
+      <c r="Q77" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R77" s="77"/>
-      <c r="S77" s="77"/>
-      <c r="T77" s="77"/>
-      <c r="U77" s="77"/>
-      <c r="V77" s="77"/>
+      <c r="R77" s="80"/>
+      <c r="S77" s="80"/>
+      <c r="T77" s="80"/>
+      <c r="U77" s="80"/>
+      <c r="V77" s="80"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="73" t="s">
@@ -19265,32 +19316,32 @@
       <c r="D89" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="E89" s="78" t="s">
+      <c r="E89" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F89" s="78"/>
-      <c r="G89" s="78"/>
-      <c r="H89" s="78"/>
-      <c r="I89" s="79" t="s">
+      <c r="F89" s="77"/>
+      <c r="G89" s="77"/>
+      <c r="H89" s="77"/>
+      <c r="I89" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J89" s="79"/>
-      <c r="K89" s="79"/>
-      <c r="L89" s="79"/>
-      <c r="M89" s="80" t="s">
+      <c r="J89" s="78"/>
+      <c r="K89" s="78"/>
+      <c r="L89" s="78"/>
+      <c r="M89" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N89" s="80"/>
-      <c r="O89" s="80"/>
-      <c r="P89" s="80"/>
-      <c r="Q89" s="77" t="s">
+      <c r="N89" s="79"/>
+      <c r="O89" s="79"/>
+      <c r="P89" s="79"/>
+      <c r="Q89" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R89" s="77"/>
-      <c r="S89" s="77"/>
-      <c r="T89" s="77"/>
-      <c r="U89" s="77"/>
-      <c r="V89" s="77"/>
+      <c r="R89" s="80"/>
+      <c r="S89" s="80"/>
+      <c r="T89" s="80"/>
+      <c r="U89" s="80"/>
+      <c r="V89" s="80"/>
     </row>
     <row r="90" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B90" s="73" t="s">
@@ -19627,32 +19678,32 @@
       <c r="D101" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="E101" s="78" t="s">
+      <c r="E101" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F101" s="78"/>
-      <c r="G101" s="78"/>
-      <c r="H101" s="78"/>
-      <c r="I101" s="79" t="s">
+      <c r="F101" s="77"/>
+      <c r="G101" s="77"/>
+      <c r="H101" s="77"/>
+      <c r="I101" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J101" s="79"/>
-      <c r="K101" s="79"/>
-      <c r="L101" s="79"/>
-      <c r="M101" s="80" t="s">
+      <c r="J101" s="78"/>
+      <c r="K101" s="78"/>
+      <c r="L101" s="78"/>
+      <c r="M101" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N101" s="80"/>
-      <c r="O101" s="80"/>
-      <c r="P101" s="80"/>
-      <c r="Q101" s="77" t="s">
+      <c r="N101" s="79"/>
+      <c r="O101" s="79"/>
+      <c r="P101" s="79"/>
+      <c r="Q101" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R101" s="77"/>
-      <c r="S101" s="77"/>
-      <c r="T101" s="77"/>
-      <c r="U101" s="77"/>
-      <c r="V101" s="77"/>
+      <c r="R101" s="80"/>
+      <c r="S101" s="80"/>
+      <c r="T101" s="80"/>
+      <c r="U101" s="80"/>
+      <c r="V101" s="80"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B102" s="73" t="s">
@@ -19989,32 +20040,32 @@
       <c r="D113" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="E113" s="78" t="s">
+      <c r="E113" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F113" s="78"/>
-      <c r="G113" s="78"/>
-      <c r="H113" s="78"/>
-      <c r="I113" s="79" t="s">
+      <c r="F113" s="77"/>
+      <c r="G113" s="77"/>
+      <c r="H113" s="77"/>
+      <c r="I113" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J113" s="79"/>
-      <c r="K113" s="79"/>
-      <c r="L113" s="79"/>
-      <c r="M113" s="80" t="s">
+      <c r="J113" s="78"/>
+      <c r="K113" s="78"/>
+      <c r="L113" s="78"/>
+      <c r="M113" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N113" s="80"/>
-      <c r="O113" s="80"/>
-      <c r="P113" s="80"/>
-      <c r="Q113" s="77" t="s">
+      <c r="N113" s="79"/>
+      <c r="O113" s="79"/>
+      <c r="P113" s="79"/>
+      <c r="Q113" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R113" s="77"/>
-      <c r="S113" s="77"/>
-      <c r="T113" s="77"/>
-      <c r="U113" s="77"/>
-      <c r="V113" s="77"/>
+      <c r="R113" s="80"/>
+      <c r="S113" s="80"/>
+      <c r="T113" s="80"/>
+      <c r="U113" s="80"/>
+      <c r="V113" s="80"/>
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B114" s="73" t="s">
@@ -20325,32 +20376,32 @@
       <c r="D125" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="E125" s="78" t="s">
+      <c r="E125" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F125" s="78"/>
-      <c r="G125" s="78"/>
-      <c r="H125" s="78"/>
-      <c r="I125" s="79" t="s">
+      <c r="F125" s="77"/>
+      <c r="G125" s="77"/>
+      <c r="H125" s="77"/>
+      <c r="I125" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J125" s="79"/>
-      <c r="K125" s="79"/>
-      <c r="L125" s="79"/>
-      <c r="M125" s="80" t="s">
+      <c r="J125" s="78"/>
+      <c r="K125" s="78"/>
+      <c r="L125" s="78"/>
+      <c r="M125" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N125" s="80"/>
-      <c r="O125" s="80"/>
-      <c r="P125" s="80"/>
-      <c r="Q125" s="77" t="s">
+      <c r="N125" s="79"/>
+      <c r="O125" s="79"/>
+      <c r="P125" s="79"/>
+      <c r="Q125" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R125" s="77"/>
-      <c r="S125" s="77"/>
-      <c r="T125" s="77"/>
-      <c r="U125" s="77"/>
-      <c r="V125" s="77"/>
+      <c r="R125" s="80"/>
+      <c r="S125" s="80"/>
+      <c r="T125" s="80"/>
+      <c r="U125" s="80"/>
+      <c r="V125" s="80"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B126" s="73" t="s">
@@ -20609,32 +20660,32 @@
       <c r="D135" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="E135" s="78" t="s">
+      <c r="E135" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F135" s="78"/>
-      <c r="G135" s="78"/>
-      <c r="H135" s="78"/>
-      <c r="I135" s="79" t="s">
+      <c r="F135" s="77"/>
+      <c r="G135" s="77"/>
+      <c r="H135" s="77"/>
+      <c r="I135" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J135" s="79"/>
-      <c r="K135" s="79"/>
-      <c r="L135" s="79"/>
-      <c r="M135" s="80" t="s">
+      <c r="J135" s="78"/>
+      <c r="K135" s="78"/>
+      <c r="L135" s="78"/>
+      <c r="M135" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N135" s="80"/>
-      <c r="O135" s="80"/>
-      <c r="P135" s="80"/>
-      <c r="Q135" s="77" t="s">
+      <c r="N135" s="79"/>
+      <c r="O135" s="79"/>
+      <c r="P135" s="79"/>
+      <c r="Q135" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R135" s="77"/>
-      <c r="S135" s="77"/>
-      <c r="T135" s="77"/>
-      <c r="U135" s="77"/>
-      <c r="V135" s="77"/>
+      <c r="R135" s="80"/>
+      <c r="S135" s="80"/>
+      <c r="T135" s="80"/>
+      <c r="U135" s="80"/>
+      <c r="V135" s="80"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B136" s="73" t="s">
@@ -20929,8 +20980,362 @@
       <c r="U144" s="2"/>
       <c r="V144" s="2"/>
     </row>
+    <row r="147" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B147" s="11">
+        <v>46184</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="E147" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="F147" s="77"/>
+      <c r="G147" s="77"/>
+      <c r="H147" s="77"/>
+      <c r="I147" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="J147" s="78"/>
+      <c r="K147" s="78"/>
+      <c r="L147" s="78"/>
+      <c r="M147" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="N147" s="79"/>
+      <c r="O147" s="79"/>
+      <c r="P147" s="79"/>
+      <c r="Q147" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="R147" s="80"/>
+      <c r="S147" s="80"/>
+      <c r="T147" s="80"/>
+      <c r="U147" s="80"/>
+      <c r="V147" s="80"/>
+    </row>
+    <row r="148" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B148" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C148" s="75">
+        <v>1</v>
+      </c>
+      <c r="D148" s="75">
+        <v>0</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+      <c r="I148" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="J148" s="8"/>
+      <c r="K148" s="8"/>
+      <c r="L148" s="8"/>
+      <c r="M148" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="N148" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="O148" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="P148" s="20"/>
+      <c r="Q148" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="R148" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="S148" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="T148" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="U148" s="9"/>
+      <c r="V148" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="149" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B149" s="74"/>
+      <c r="C149" s="76"/>
+      <c r="D149" s="76"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+      <c r="I149" s="8"/>
+      <c r="J149" s="8"/>
+      <c r="K149" s="8"/>
+      <c r="L149" s="8"/>
+      <c r="M149" s="20"/>
+      <c r="N149" s="20"/>
+      <c r="O149" s="20"/>
+      <c r="P149" s="20"/>
+      <c r="Q149" s="9"/>
+      <c r="R149" s="9"/>
+      <c r="S149" s="9"/>
+      <c r="T149" s="9"/>
+      <c r="U149" s="9"/>
+      <c r="V149" s="13"/>
+    </row>
+    <row r="150" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B150" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C150" s="75">
+        <v>0</v>
+      </c>
+      <c r="D150" s="75">
+        <v>0</v>
+      </c>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
+      <c r="I150" s="8"/>
+      <c r="J150" s="8"/>
+      <c r="K150" s="8"/>
+      <c r="L150" s="8"/>
+      <c r="M150" s="20"/>
+      <c r="N150" s="20"/>
+      <c r="O150" s="20"/>
+      <c r="P150" s="20"/>
+      <c r="Q150" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="R150" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="S150" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="T150" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="U150" s="9"/>
+      <c r="V150" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="151" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B151" s="74"/>
+      <c r="C151" s="76"/>
+      <c r="D151" s="76"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
+      <c r="I151" s="8"/>
+      <c r="J151" s="8"/>
+      <c r="K151" s="8"/>
+      <c r="L151" s="8"/>
+      <c r="M151" s="20"/>
+      <c r="N151" s="20"/>
+      <c r="O151" s="20"/>
+      <c r="P151" s="20"/>
+      <c r="Q151" s="9"/>
+      <c r="R151" s="9"/>
+      <c r="S151" s="9"/>
+      <c r="T151" s="9"/>
+      <c r="U151" s="9"/>
+      <c r="V151" s="13"/>
+    </row>
+    <row r="152" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B152" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C152" s="75">
+        <v>1</v>
+      </c>
+      <c r="D152" s="75">
+        <v>0</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+      <c r="I152" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="J152" s="8"/>
+      <c r="K152" s="8"/>
+      <c r="L152" s="8"/>
+      <c r="M152" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="N152" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="O152" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="P152" s="20"/>
+      <c r="Q152" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="R152" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="S152" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="T152" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="U152" s="9"/>
+      <c r="V152" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="153" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B153" s="74"/>
+      <c r="C153" s="76"/>
+      <c r="D153" s="76"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+      <c r="I153" s="8"/>
+      <c r="J153" s="8"/>
+      <c r="K153" s="8"/>
+      <c r="L153" s="8"/>
+      <c r="M153" s="20"/>
+      <c r="N153" s="20"/>
+      <c r="O153" s="20"/>
+      <c r="P153" s="20"/>
+      <c r="Q153" s="9"/>
+      <c r="R153" s="9"/>
+      <c r="S153" s="9"/>
+      <c r="T153" s="9"/>
+      <c r="U153" s="9"/>
+      <c r="V153" s="13"/>
+    </row>
+    <row r="154" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B154" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C154" s="75">
+        <v>4</v>
+      </c>
+      <c r="D154" s="75">
+        <v>0</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="I154" s="8"/>
+      <c r="J154" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K154" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="L154" s="8"/>
+      <c r="M154" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="N154" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="O154" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="P154" s="20"/>
+      <c r="Q154" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="R154" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="S154" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="T154" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="U154" s="9"/>
+      <c r="V154" s="13" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="155" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B155" s="74"/>
+      <c r="C155" s="76"/>
+      <c r="D155" s="76"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+      <c r="I155" s="8"/>
+      <c r="J155" s="8"/>
+      <c r="K155" s="8"/>
+      <c r="L155" s="8"/>
+      <c r="M155" s="20"/>
+      <c r="N155" s="20"/>
+      <c r="O155" s="20"/>
+      <c r="P155" s="20"/>
+      <c r="Q155" s="9"/>
+      <c r="R155" s="9"/>
+      <c r="S155" s="9"/>
+      <c r="T155" s="9"/>
+      <c r="U155" s="9"/>
+      <c r="V155" s="13"/>
+    </row>
+    <row r="156" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B156" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C156" s="2">
+        <f>SUM(C148:C155)</f>
+        <v>6</v>
+      </c>
+      <c r="D156" s="2">
+        <f>SUM(D148:D155)</f>
+        <v>0</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="2"/>
+      <c r="J156" s="2"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
+      <c r="M156" s="2"/>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" s="2"/>
+      <c r="Q156" s="2"/>
+      <c r="R156" s="2"/>
+      <c r="S156" s="2"/>
+      <c r="T156" s="2"/>
+      <c r="U156" s="2"/>
+      <c r="V156" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="214">
     <mergeCell ref="Q113:V113"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="C114:C115"/>
@@ -21116,9 +21521,6 @@
     <mergeCell ref="E125:H125"/>
     <mergeCell ref="I125:L125"/>
     <mergeCell ref="M125:P125"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
     <mergeCell ref="Q135:V135"/>
     <mergeCell ref="B136:B137"/>
     <mergeCell ref="C136:C137"/>
@@ -21129,6 +21531,25 @@
     <mergeCell ref="B140:B141"/>
     <mergeCell ref="C140:C141"/>
     <mergeCell ref="D140:D141"/>
+    <mergeCell ref="Q147:V147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="E147:H147"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M147:P147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -21170,23 +21591,23 @@
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -21300,7 +21721,7 @@
       </c>
       <c r="M4" s="21">
         <f t="shared" ref="M4:M15" si="2">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>354</v>
@@ -21313,14 +21734,14 @@
         <v>222</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q16" si="4">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
+        <f t="shared" ref="Q4:Q18" si="4">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
         <v>11</v>
       </c>
       <c r="R4" s="35" t="s">
-        <v>231</v>
+        <v>325</v>
       </c>
       <c r="S4" s="55">
-        <f t="shared" ref="S4:S17" si="5">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
+        <f t="shared" ref="S4:S18" si="5">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
         <v>16</v>
       </c>
       <c r="T4" s="36" t="s">
@@ -21328,7 +21749,7 @@
       </c>
       <c r="U4" s="56">
         <f t="shared" ref="U4:U7" si="6">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -21377,10 +21798,10 @@
       </c>
       <c r="M5" s="21">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>53</v>
+        <v>360</v>
       </c>
       <c r="O5" s="22">
         <f t="shared" si="3"/>
@@ -21394,11 +21815,11 @@
         <v>8</v>
       </c>
       <c r="R5" s="35" t="s">
-        <v>325</v>
+        <v>231</v>
       </c>
       <c r="S5" s="55">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T5" s="36" t="s">
         <v>221</v>
@@ -21457,25 +21878,25 @@
         <v>8</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>360</v>
+        <v>53</v>
       </c>
       <c r="O6" s="22">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="Q6" s="23">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R6" s="35" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="S6" s="55">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" s="36" t="s">
         <v>42</v>
@@ -21541,25 +21962,25 @@
         <v>4</v>
       </c>
       <c r="P7" s="34" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="Q7" s="23">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R7" s="35" t="s">
-        <v>62</v>
+        <v>357</v>
       </c>
       <c r="S7" s="55">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T7" s="36" t="s">
         <v>357</v>
       </c>
       <c r="U7" s="56">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -21625,11 +22046,11 @@
         <v>5</v>
       </c>
       <c r="R8" s="35" t="s">
-        <v>364</v>
+        <v>242</v>
       </c>
       <c r="S8" s="55">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" s="36"/>
       <c r="U8" s="56"/>
@@ -21676,7 +22097,7 @@
         <v>6</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>389</v>
+        <v>221</v>
       </c>
       <c r="M9" s="21">
         <f t="shared" si="2"/>
@@ -21697,11 +22118,11 @@
         <v>5</v>
       </c>
       <c r="R9" s="35" t="s">
-        <v>222</v>
+        <v>62</v>
       </c>
       <c r="S9" s="55">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T9" s="36"/>
       <c r="U9" s="56"/>
@@ -21748,14 +22169,14 @@
         <v>7</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>50</v>
+        <v>389</v>
       </c>
       <c r="M10" s="21">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>14</v>
+        <v>224</v>
       </c>
       <c r="O10" s="22">
         <f t="shared" si="3"/>
@@ -21769,7 +22190,7 @@
         <v>5</v>
       </c>
       <c r="R10" s="35" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="S10" s="55">
         <f t="shared" si="5"/>
@@ -21789,19 +22210,19 @@
       </c>
       <c r="C11" s="2">
         <f t="shared" si="0"/>
-        <v>3.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D11" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B11)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B11)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B11)</f>
@@ -21813,21 +22234,21 @@
       </c>
       <c r="I11" s="14">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="2">
         <v>8</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
       <c r="M11" s="21">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>356</v>
+        <v>14</v>
       </c>
       <c r="O11" s="22">
         <f t="shared" si="3"/>
@@ -21841,7 +22262,7 @@
         <v>5</v>
       </c>
       <c r="R11" s="35" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="S11" s="55">
         <f t="shared" si="5"/>
@@ -21892,28 +22313,28 @@
         <v>9</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>356</v>
+        <v>299</v>
       </c>
       <c r="M12" s="21">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="O12" s="22">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P12" s="34" t="s">
-        <v>314</v>
+        <v>7</v>
       </c>
       <c r="Q12" s="23">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R12" s="35" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="S12" s="55">
         <f t="shared" si="5"/>
@@ -21964,14 +22385,14 @@
         <v>10</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>221</v>
+        <v>356</v>
       </c>
       <c r="M13" s="21">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>221</v>
+        <v>403</v>
       </c>
       <c r="O13" s="22">
         <f t="shared" si="3"/>
@@ -21982,14 +22403,14 @@
       </c>
       <c r="Q13" s="23">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R13" s="35" t="s">
-        <v>388</v>
+        <v>67</v>
       </c>
       <c r="S13" s="55">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" s="36"/>
       <c r="U13" s="56"/>
@@ -22043,25 +22464,25 @@
         <v>3</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>314</v>
+        <v>221</v>
       </c>
       <c r="O14" s="22">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P14" s="34" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="Q14" s="23">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" s="55" t="s">
-        <v>365</v>
+        <v>303</v>
       </c>
       <c r="S14" s="55">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" s="36"/>
       <c r="U14" s="56"/>
@@ -22115,21 +22536,21 @@
         <v>3</v>
       </c>
       <c r="N15" s="22" t="s">
-        <v>395</v>
+        <v>314</v>
       </c>
       <c r="O15" s="22">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P15" s="23" t="s">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="Q15" s="23">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R15" s="55" t="s">
-        <v>34</v>
+        <v>388</v>
       </c>
       <c r="S15" s="55">
         <f t="shared" si="5"/>
@@ -22182,21 +22603,21 @@
       <c r="L16" s="21"/>
       <c r="M16" s="21"/>
       <c r="N16" s="22" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="O16" s="22">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P16" s="23" t="s">
-        <v>225</v>
+        <v>361</v>
       </c>
       <c r="Q16" s="23">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="R16" s="55" t="s">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="S16" s="55">
         <f t="shared" si="5"/>
@@ -22216,7 +22637,7 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B17)</f>
@@ -22224,7 +22645,7 @@
       </c>
       <c r="E17" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B17)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B17)</f>
@@ -22236,11 +22657,11 @@
       </c>
       <c r="H17" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B17)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="2">
@@ -22249,16 +22670,21 @@
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
       <c r="N17" s="22" t="s">
-        <v>231</v>
+        <v>387</v>
       </c>
       <c r="O17" s="22">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
+      <c r="P17" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q17" s="23">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
       <c r="R17" s="55" t="s">
-        <v>303</v>
+        <v>34</v>
       </c>
       <c r="S17" s="55">
         <f t="shared" si="5"/>
@@ -22311,16 +22737,26 @@
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
       <c r="N18" s="22" t="s">
-        <v>390</v>
+        <v>231</v>
       </c>
       <c r="O18" s="22">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
+      <c r="P18" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q18" s="23">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="R18" s="55" t="s">
+        <v>402</v>
+      </c>
+      <c r="S18" s="55">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
       <c r="T18" s="56"/>
       <c r="U18" s="56"/>
     </row>
@@ -22362,6 +22798,9 @@
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
+      <c r="N19" s="1" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -22569,11 +23008,11 @@
       </c>
       <c r="C25" s="2">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="D25" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B25)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B25)</f>
@@ -22593,7 +23032,7 @@
       </c>
       <c r="I25" s="14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" s="15"/>
     </row>
@@ -22842,7 +23281,7 @@
       </c>
       <c r="C32" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="D32" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B32)</f>
@@ -22858,15 +23297,15 @@
       </c>
       <c r="G32" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B32)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B32)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I32" s="14">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J32" s="15"/>
     </row>
@@ -23037,11 +23476,11 @@
       </c>
       <c r="C37" s="2">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="D37" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B37)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E37" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B37)</f>
@@ -23061,7 +23500,7 @@
       </c>
       <c r="I37" s="14">
         <f t="shared" si="8"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J37" s="15"/>
     </row>
@@ -23310,11 +23749,11 @@
       </c>
       <c r="C44" s="2">
         <f t="shared" si="7"/>
-        <v>2.2000000000000002</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D44" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B44)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B44)</f>
@@ -23326,15 +23765,15 @@
       </c>
       <c r="G44" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B44)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H44" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B44)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" s="14">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J44" s="15"/>
     </row>
@@ -23622,7 +24061,7 @@
       </c>
       <c r="C52" s="2">
         <f t="shared" si="7"/>
-        <v>1.4000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="D52" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B52)</f>
@@ -23638,7 +24077,7 @@
       </c>
       <c r="G52" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B52)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H52" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B52)</f>
@@ -23646,7 +24085,7 @@
       </c>
       <c r="I52" s="14">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J52" s="15"/>
     </row>
@@ -23856,11 +24295,11 @@
       </c>
       <c r="C58" s="2">
         <f t="shared" si="7"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D58" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B58)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B58)</f>
@@ -23880,7 +24319,7 @@
       </c>
       <c r="I58" s="14">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J58" s="15"/>
     </row>
@@ -24324,7 +24763,7 @@
       </c>
       <c r="C70" s="2">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D70" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B70)</f>
@@ -24340,7 +24779,7 @@
       </c>
       <c r="G70" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B70)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H70" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B70)</f>
@@ -24348,7 +24787,7 @@
       </c>
       <c r="I70" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J70" s="15"/>
     </row>
@@ -24519,7 +24958,7 @@
       </c>
       <c r="C75" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D75" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B75)</f>
@@ -24531,7 +24970,7 @@
       </c>
       <c r="F75" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B75)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B75)</f>
@@ -24543,7 +24982,7 @@
       </c>
       <c r="I75" s="14">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J75" s="15"/>
     </row>
@@ -24558,7 +24997,7 @@
       </c>
       <c r="C76" s="2">
         <f t="shared" si="9"/>
-        <v>0.60000000000000009</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D76" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B76)</f>
@@ -24566,7 +25005,7 @@
       </c>
       <c r="E76" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B76)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B76)</f>
@@ -24574,7 +25013,7 @@
       </c>
       <c r="G76" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B76)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H76" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B76)</f>
@@ -24582,7 +25021,7 @@
       </c>
       <c r="I76" s="14">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J76" s="15"/>
     </row>
@@ -24792,7 +25231,7 @@
       </c>
       <c r="C82" s="2">
         <f t="shared" si="9"/>
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="D82" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B82)</f>
@@ -24800,11 +25239,11 @@
       </c>
       <c r="E82" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B82)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B82)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G82" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B82)</f>
@@ -24816,7 +25255,7 @@
       </c>
       <c r="I82" s="14">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J82" s="15"/>
     </row>
@@ -25727,7 +26166,7 @@
       </c>
       <c r="C106" s="2">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D106" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B106)</f>
@@ -25739,7 +26178,7 @@
       </c>
       <c r="F106" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B106)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G106" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B106)</f>
@@ -25751,7 +26190,7 @@
       </c>
       <c r="I106" s="14">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -25841,7 +26280,7 @@
       </c>
       <c r="C109" s="2">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="D109" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B109)</f>
@@ -25857,7 +26296,7 @@
       </c>
       <c r="G109" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B109)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H109" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B109)</f>
@@ -25865,7 +26304,7 @@
       </c>
       <c r="I109" s="14">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -26183,7 +26622,7 @@
       </c>
       <c r="C118" s="2">
         <f t="shared" si="11"/>
-        <v>1.2000000000000002</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="D118" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B118)</f>
@@ -26195,11 +26634,11 @@
       </c>
       <c r="F118" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B118)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B118)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H118" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B118)</f>
@@ -26207,7 +26646,7 @@
       </c>
       <c r="I118" s="14">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -26401,6 +26840,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I123">
+      <sortCondition ref="A3"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:D123">
     <cfRule type="top10" dxfId="9" priority="862" rank="7"/>
@@ -28074,7 +28518,7 @@
       </c>
       <c r="E4" s="62">
         <f>VLOOKUP(D4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="70" t="s">
         <v>225</v>
@@ -28150,14 +28594,14 @@
       </c>
       <c r="Q5" s="62">
         <f>VLOOKUP(P5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>305</v>
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>16</v>
+        <v>17.600000000000001</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -28170,7 +28614,7 @@
       </c>
       <c r="E6" s="47">
         <f>VLOOKUP(D6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>233</v>
@@ -28225,7 +28669,7 @@
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>16</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="I7" s="97"/>
       <c r="J7" s="66">
@@ -28246,14 +28690,14 @@
       </c>
       <c r="Q7" s="69">
         <f>VLOOKUP(P7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R7" s="65" t="s">
         <v>325</v>
       </c>
       <c r="S7" s="71">
         <f>VLOOKUP(R7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>12</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
@@ -28273,7 +28717,7 @@
       </c>
       <c r="G8" s="63">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="N8" s="85"/>
       <c r="O8" s="48">
@@ -28311,7 +28755,7 @@
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="I9" s="93" t="s">
         <v>249</v>
@@ -28402,7 +28846,7 @@
       </c>
       <c r="E11" s="65">
         <f>VLOOKUP(D11,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="70" t="s">
         <v>48</v>
@@ -28450,14 +28894,14 @@
       </c>
       <c r="E12" s="65">
         <f>VLOOKUP(D12,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="70" t="s">
         <v>224</v>
       </c>
       <c r="G12" s="61">
         <f>VLOOKUP(F12,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11.4</v>
+        <v>13.1</v>
       </c>
       <c r="I12" s="95"/>
       <c r="J12" s="66">
@@ -28505,7 +28949,7 @@
       </c>
       <c r="G13" s="61">
         <f>VLOOKUP(F13,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="I13" s="95"/>
       <c r="J13" s="66">
@@ -28534,14 +28978,14 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>229</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>13</v>
+        <v>14.6</v>
       </c>
       <c r="I14" s="97"/>
       <c r="J14" s="66">
@@ -28570,7 +29014,7 @@
       </c>
       <c r="E15" s="65">
         <f>VLOOKUP(D15,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="62" t="s">
         <v>300</v>
@@ -29401,7 +29845,7 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ref="G4:G37" si="2">RANK(H4,$H$4:$H$37,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
@@ -30085,7 +30529,7 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C16</f>
@@ -30203,7 +30647,7 @@
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C17</f>
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="3"/>
@@ -30754,7 +31198,7 @@
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C25</f>
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="3"/>
@@ -31326,11 +31770,11 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C44</f>
-        <v>4.2</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="3"/>
@@ -33011,7 +33455,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C102</f>
@@ -33272,32 +33716,32 @@
       <c r="D4" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="E4" s="78" t="s">
+      <c r="E4" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="79" t="s">
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="80" t="s">
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="77" t="s">
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="27"/>
@@ -33534,32 +33978,32 @@
       <c r="D12" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="79" t="s">
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="80" t="s">
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N12" s="80"/>
-      <c r="O12" s="80"/>
-      <c r="P12" s="80"/>
-      <c r="Q12" s="77" t="s">
+      <c r="N12" s="79"/>
+      <c r="O12" s="79"/>
+      <c r="P12" s="79"/>
+      <c r="Q12" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R12" s="77"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="77"/>
-      <c r="U12" s="77"/>
-      <c r="V12" s="77"/>
+      <c r="R12" s="80"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="80"/>
+      <c r="U12" s="80"/>
+      <c r="V12" s="80"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
@@ -33803,32 +34247,32 @@
       <c r="D20" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="79" t="s">
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="80" t="s">
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N20" s="80"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="80"/>
-      <c r="Q20" s="77" t="s">
+      <c r="N20" s="79"/>
+      <c r="O20" s="79"/>
+      <c r="P20" s="79"/>
+      <c r="Q20" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="R20" s="77"/>
-      <c r="S20" s="77"/>
-      <c r="T20" s="77"/>
-      <c r="U20" s="77"/>
-      <c r="V20" s="77"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
+      <c r="T20" s="80"/>
+      <c r="U20" s="80"/>
+      <c r="V20" s="80"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABBC6EB2-5EE7-45E1-8B8D-E9DEC4D6C5F0}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{230EABB8-D342-42F1-B5FC-1416A7390ACB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2310,10 +2310,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2322,20 +2322,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3507,11 +3507,11 @@
       </c>
       <c r="G4" s="2">
         <f>RANK(H4,$H$4:$H$123,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>20</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4" si="2">(COUNTIF(J4:CD4,"출전")*1)</f>
@@ -3642,11 +3642,11 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ref="G5:G68" si="3">RANK(H5,$H$4:$H$123,0)</f>
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
-        <v>6.8000000000000007</v>
+        <v>3.7</v>
       </c>
       <c r="I5" s="6">
         <f t="shared" ref="I5:I68" si="4">(COUNTIF(J5:CD5,"출전")*1)</f>
@@ -3751,11 +3751,11 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6">
         <f t="shared" si="4"/>
@@ -3855,11 +3855,11 @@
       </c>
       <c r="G7" s="2">
         <f t="shared" si="3"/>
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C7</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" s="6">
         <f t="shared" si="4"/>
@@ -3958,11 +3958,11 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" si="3"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C8</f>
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I8" s="6">
         <f t="shared" si="4"/>
@@ -4061,11 +4061,11 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="I9" s="6">
         <f t="shared" si="4"/>
@@ -4174,11 +4174,11 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="4"/>
@@ -4297,11 +4297,11 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
-        <v>11.4</v>
+        <v>14.5</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="4"/>
@@ -4421,11 +4421,11 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C12</f>
-        <v>8.6</v>
+        <v>1</v>
       </c>
       <c r="I12" s="6">
         <f t="shared" si="4"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C13</f>
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I13" s="6">
         <f t="shared" si="4"/>
@@ -4631,11 +4631,11 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C14</f>
-        <v>1.4000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6">
         <f t="shared" si="4"/>
@@ -4735,11 +4735,11 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
-        <v>1.4000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I15" s="6">
         <f t="shared" si="4"/>
@@ -4838,11 +4838,11 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="4"/>
@@ -4951,11 +4951,11 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
-        <v>13.4</v>
+        <v>15</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="4"/>
@@ -5078,11 +5078,11 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C18</f>
-        <v>1.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6">
         <f t="shared" si="4"/>
@@ -5181,11 +5181,11 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I19" s="6">
         <f t="shared" si="4"/>
@@ -5292,11 +5292,11 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I20" s="6">
         <f t="shared" si="4"/>
@@ -5400,11 +5400,11 @@
       <c r="F21" s="60"/>
       <c r="G21" s="2">
         <f t="shared" si="3"/>
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C21</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="4"/>
@@ -5504,11 +5504,11 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" si="3"/>
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H22" s="6">
         <f>I22+개인기록Sheet!C22</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6">
         <f t="shared" si="4"/>
@@ -5608,11 +5608,11 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="3"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C23</f>
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="I23" s="6">
         <f t="shared" si="4"/>
@@ -5711,11 +5711,11 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="3"/>
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="4"/>
@@ -5816,11 +5816,11 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="4"/>
@@ -5927,11 +5927,11 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="4"/>
@@ -6042,11 +6042,11 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
-        <v>15.4</v>
+        <v>22.6</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="4"/>
@@ -6175,11 +6175,11 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="4"/>
@@ -6289,11 +6289,11 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="3"/>
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C29</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="6">
         <f t="shared" si="4"/>
@@ -6392,11 +6392,11 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I30" s="6">
         <f t="shared" si="4"/>
@@ -6501,11 +6501,11 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="I31" s="6">
         <f t="shared" si="4"/>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="4"/>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
@@ -6866,11 +6866,11 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
-        <v>10</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="I34" s="6">
         <f t="shared" si="4"/>
@@ -6986,11 +6986,11 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="3"/>
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C35</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="4"/>
@@ -7090,11 +7090,11 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="3"/>
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C36</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="4"/>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
-        <v>12.7</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="4"/>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
@@ -7432,11 +7432,11 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" si="3"/>
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="H39" s="6">
         <f>I39+개인기록Sheet!C39</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6">
         <f t="shared" si="4"/>
@@ -7535,11 +7535,11 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="3"/>
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="H40" s="6">
         <f>I40+개인기록Sheet!C40</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I40" s="6">
         <f t="shared" si="4"/>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="H41" s="6">
         <f>I41+개인기록Sheet!C41</f>
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="4"/>
@@ -7745,11 +7745,11 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" si="3"/>
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H42" s="6">
         <f>I42+개인기록Sheet!C42</f>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6">
         <f t="shared" si="4"/>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="3"/>
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
@@ -7953,11 +7953,11 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
-        <v>11</v>
+        <v>14.2</v>
       </c>
       <c r="I44" s="6">
         <f t="shared" si="4"/>
@@ -8079,11 +8079,11 @@
       </c>
       <c r="G45" s="2">
         <f t="shared" si="3"/>
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H45" s="6">
         <f>I45+개인기록Sheet!C45</f>
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I45" s="6">
         <f t="shared" si="4"/>
@@ -8189,11 +8189,11 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6">
         <f t="shared" si="4"/>
@@ -8291,11 +8291,11 @@
       <c r="F47" s="60"/>
       <c r="G47" s="2">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6">
         <f t="shared" si="4"/>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="H48" s="6">
         <f>I48+개인기록Sheet!C48</f>
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="I48" s="6">
         <f t="shared" si="4"/>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="G49" s="2">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H49" s="6">
         <f>I49+개인기록Sheet!C49</f>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H50" s="6">
         <f>I50+개인기록Sheet!C50</f>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="H52" s="6">
         <f>I52+개인기록Sheet!C52</f>
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="I52" s="6">
         <f t="shared" si="4"/>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H53" s="6">
         <f>I53+개인기록Sheet!C53</f>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" si="3"/>
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H54" s="6">
         <f>I54+개인기록Sheet!C54</f>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I55" s="6">
         <f t="shared" si="4"/>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
@@ -9481,11 +9481,11 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H58" s="6">
         <f>I58+개인기록Sheet!C58</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="4"/>
@@ -9602,11 +9602,11 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="3"/>
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="I59" s="6">
         <f t="shared" si="4"/>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I60" s="6">
         <f t="shared" si="4"/>
@@ -9825,11 +9825,11 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I61" s="6">
         <f t="shared" si="4"/>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G62" s="2">
         <f t="shared" si="3"/>
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="H62" s="6">
         <f>I62+개인기록Sheet!C62</f>
@@ -10033,11 +10033,11 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H63" s="6">
         <f>I63+개인기록Sheet!C63</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I63" s="6">
         <f t="shared" si="4"/>
@@ -10149,11 +10149,11 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H64" s="6">
         <f>I64+개인기록Sheet!C64</f>
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="I64" s="6">
         <f t="shared" si="4"/>
@@ -10261,11 +10261,11 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="I65" s="6">
         <f t="shared" si="4"/>
@@ -10372,11 +10372,11 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="I66" s="6">
         <f t="shared" si="4"/>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
@@ -10590,11 +10590,11 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="H68" s="6">
         <f>I68+개인기록Sheet!C68</f>
-        <v>5.6000000000000005</v>
+        <v>0</v>
       </c>
       <c r="I68" s="6">
         <f t="shared" si="4"/>
@@ -10694,11 +10694,11 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" ref="G69:G123" si="14">RANK(H69,$H$4:$H$123,0)</f>
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I69" s="6">
         <f t="shared" ref="I69:I123" si="15">(COUNTIF(J69:CD69,"출전")*1)</f>
@@ -10797,11 +10797,11 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="14"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
-        <v>11</v>
+        <v>14.8</v>
       </c>
       <c r="I70" s="6">
         <f t="shared" si="15"/>
@@ -10923,11 +10923,11 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I71" s="6">
         <f t="shared" si="15"/>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" si="14"/>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H72" s="6">
         <f>I72+개인기록Sheet!C72</f>
@@ -11143,11 +11143,11 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H73" s="6">
         <f>I73+개인기록Sheet!C73</f>
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="I73" s="6">
         <f t="shared" si="15"/>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="14"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
@@ -11358,11 +11358,11 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="14"/>
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
-        <v>4.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I75" s="6">
         <f t="shared" si="15"/>
@@ -11469,11 +11469,11 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="15"/>
@@ -11581,11 +11581,11 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="14"/>
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I77" s="6">
         <f t="shared" si="15"/>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="14"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" si="14"/>
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
@@ -11900,11 +11900,11 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="14"/>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="15"/>
@@ -12013,11 +12013,11 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I81" s="6">
         <f t="shared" si="15"/>
@@ -12124,11 +12124,11 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="I82" s="6">
         <f t="shared" si="15"/>
@@ -12237,11 +12237,11 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="14"/>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" si="15"/>
@@ -12352,11 +12352,11 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="14"/>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="I84" s="6">
         <f t="shared" si="15"/>
@@ -12467,11 +12467,11 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="14"/>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="I85" s="6">
         <f t="shared" si="15"/>
@@ -12578,11 +12578,11 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" si="14"/>
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I86" s="6">
         <f t="shared" si="15"/>
@@ -12688,11 +12688,11 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I87" s="6">
         <f t="shared" si="15"/>
@@ -12799,11 +12799,11 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" si="14"/>
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="I88" s="6">
         <f t="shared" si="15"/>
@@ -12904,11 +12904,11 @@
       </c>
       <c r="G89" s="2">
         <f t="shared" si="14"/>
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="H89" s="6">
         <f>I89+개인기록Sheet!C89</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I89" s="6">
         <f t="shared" si="15"/>
@@ -13006,11 +13006,11 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2">
         <f t="shared" si="14"/>
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I90" s="6">
         <f t="shared" si="15"/>
@@ -13110,11 +13110,11 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" si="14"/>
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I91" s="6">
         <f t="shared" si="15"/>
@@ -13219,11 +13219,11 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="14"/>
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I92" s="6">
         <f t="shared" si="15"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" si="14"/>
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
@@ -13434,11 +13434,11 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="14"/>
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="I94" s="6">
         <f t="shared" si="15"/>
@@ -13541,11 +13541,11 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" si="14"/>
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
-        <v>1.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="I95" s="6">
         <f t="shared" si="15"/>
@@ -13644,11 +13644,11 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" si="14"/>
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
-        <v>5</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="15"/>
@@ -13757,11 +13757,11 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="15"/>
@@ -13863,11 +13863,11 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" si="14"/>
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H98" s="6">
         <f>I98+개인기록Sheet!C98</f>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="15"/>
@@ -13966,11 +13966,11 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" si="14"/>
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H99" s="6">
         <f>I99+개인기록Sheet!C99</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I99" s="6">
         <f t="shared" si="15"/>
@@ -14080,11 +14080,11 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="14"/>
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I100" s="6">
         <f t="shared" si="15"/>
@@ -14185,11 +14185,11 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="14"/>
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
-        <v>4.5999999999999996</v>
+        <v>3.4</v>
       </c>
       <c r="I101" s="6">
         <f t="shared" si="15"/>
@@ -14294,11 +14294,11 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="14"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
-        <v>10.4</v>
+        <v>14</v>
       </c>
       <c r="I102" s="6">
         <f t="shared" si="15"/>
@@ -14417,11 +14417,11 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I103" s="6">
         <f t="shared" si="15"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="G104" s="2">
         <f t="shared" si="14"/>
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
@@ -14632,11 +14632,11 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
-        <v>4</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I105" s="6">
         <f t="shared" si="15"/>
@@ -14743,11 +14743,11 @@
       </c>
       <c r="G106" s="2">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
-        <v>15</v>
+        <v>19.2</v>
       </c>
       <c r="I106" s="6">
         <f t="shared" si="15"/>
@@ -14876,11 +14876,11 @@
       </c>
       <c r="G107" s="2">
         <f t="shared" si="14"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H107" s="6">
         <f>I107+개인기록Sheet!C107</f>
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="I107" s="6">
         <f t="shared" si="15"/>
@@ -15001,11 +15001,11 @@
       </c>
       <c r="G108" s="2">
         <f t="shared" si="14"/>
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I108" s="6">
         <f t="shared" si="15"/>
@@ -15114,11 +15114,11 @@
       </c>
       <c r="G109" s="2">
         <f t="shared" si="14"/>
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I109" s="6">
         <f t="shared" si="15"/>
@@ -15232,11 +15232,11 @@
       </c>
       <c r="G110" s="2">
         <f t="shared" si="14"/>
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="6">
         <f t="shared" si="15"/>
@@ -15335,11 +15335,11 @@
       </c>
       <c r="G111" s="2">
         <f t="shared" si="14"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="I111" s="6">
         <f t="shared" si="15"/>
@@ -15452,11 +15452,11 @@
       </c>
       <c r="G112" s="2">
         <f t="shared" si="14"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="I112" s="6">
         <f t="shared" si="15"/>
@@ -15565,11 +15565,11 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="14"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="I113" s="6">
         <f t="shared" si="15"/>
@@ -15686,11 +15686,11 @@
       </c>
       <c r="G114" s="2">
         <f t="shared" si="14"/>
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
-        <v>3.9000000000000004</v>
+        <v>3.4</v>
       </c>
       <c r="I114" s="6">
         <f t="shared" si="15"/>
@@ -15795,11 +15795,11 @@
       </c>
       <c r="G115" s="2">
         <f t="shared" si="14"/>
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
-        <v>7.2</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="I115" s="6">
         <f t="shared" si="15"/>
@@ -15904,11 +15904,11 @@
       </c>
       <c r="G116" s="2">
         <f t="shared" si="14"/>
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H116" s="6">
         <f>I116+개인기록Sheet!C116</f>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I116" s="6">
         <f t="shared" si="15"/>
@@ -16011,11 +16011,11 @@
       </c>
       <c r="G117" s="2">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H117" s="6">
         <f>I117+개인기록Sheet!C117</f>
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="I117" s="6">
         <f t="shared" si="15"/>
@@ -16124,11 +16124,11 @@
       </c>
       <c r="G118" s="2">
         <f t="shared" si="14"/>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="I118" s="6">
         <f t="shared" si="15"/>
@@ -16237,11 +16237,11 @@
       </c>
       <c r="G119" s="2">
         <f t="shared" si="14"/>
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H119" s="6">
         <f>I119+개인기록Sheet!C119</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I119" s="6">
         <f t="shared" si="15"/>
@@ -16341,11 +16341,11 @@
       </c>
       <c r="G120" s="2">
         <f t="shared" si="14"/>
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H120" s="6">
         <f>I120+개인기록Sheet!C120</f>
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I120" s="6">
         <f t="shared" si="15"/>
@@ -16448,11 +16448,11 @@
       </c>
       <c r="G121" s="2">
         <f t="shared" si="14"/>
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="H121" s="6">
         <f>I121+개인기록Sheet!C121</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I121" s="6">
         <f t="shared" si="15"/>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="G122" s="2">
         <f t="shared" si="14"/>
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H122" s="6">
         <f>I122+개인기록Sheet!C122</f>
@@ -16655,11 +16655,11 @@
       </c>
       <c r="G123" s="2">
         <f t="shared" si="14"/>
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="H123" s="6">
         <f>I123+개인기록Sheet!C123</f>
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="I123" s="6">
         <f t="shared" si="15"/>
@@ -21732,131 +21732,80 @@
     </row>
   </sheetData>
   <mergeCells count="230">
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="E159:H159"/>
-    <mergeCell ref="I159:L159"/>
-    <mergeCell ref="M159:P159"/>
-    <mergeCell ref="Q159:V159"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="D160:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="D162:D163"/>
-    <mergeCell ref="Q113:V113"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="M113:P113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="E147:H147"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M147:P147"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="Q147:V147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:L135"/>
+    <mergeCell ref="M135:P135"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:L125"/>
+    <mergeCell ref="M125:P125"/>
+    <mergeCell ref="Q135:V135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="M101:P101"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="M77:P77"/>
     <mergeCell ref="Q77:V77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -21881,25 +21830,122 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="I2:L2"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="M77:P77"/>
-    <mergeCell ref="Q89:V89"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="Q159:V159"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="Q113:V113"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
     <mergeCell ref="Q125:V125"/>
     <mergeCell ref="B126:B127"/>
     <mergeCell ref="C126:C127"/>
@@ -21907,61 +21953,15 @@
     <mergeCell ref="B128:B129"/>
     <mergeCell ref="C128:C129"/>
     <mergeCell ref="D128:D129"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="M101:P101"/>
-    <mergeCell ref="Q101:V101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="I135:L135"/>
-    <mergeCell ref="M135:P135"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="I125:L125"/>
-    <mergeCell ref="M125:P125"/>
-    <mergeCell ref="Q135:V135"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="Q147:V147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="E147:H147"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="M147:P147"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="E159:H159"/>
+    <mergeCell ref="I159:L159"/>
+    <mergeCell ref="M159:P159"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -22007,19 +22007,19 @@
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -22089,24 +22089,24 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <f>종합Sheet!A102</f>
-        <v>99</v>
+        <f>종합Sheet!A4</f>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="str">
-        <f>종합Sheet!B102</f>
-        <v>정민수</v>
+        <f>종합Sheet!B4</f>
+        <v>김인혁</v>
       </c>
       <c r="C4" s="2">
         <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="D4" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B4)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B4)</f>
@@ -22114,15 +22114,15 @@
       </c>
       <c r="G4" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B4)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H4" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="14">
         <f>SUM(D4:H4)</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="2">
@@ -22146,7 +22146,7 @@
         <v>222</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q18" si="2">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
+        <f t="shared" ref="Q4:Q14" si="2">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
         <v>12</v>
       </c>
       <c r="R4" s="35" t="s">
@@ -22166,32 +22166,32 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <f>종합Sheet!A70</f>
-        <v>67</v>
+        <f>종합Sheet!A5</f>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="str">
-        <f>종합Sheet!B70</f>
-        <v>유상근</v>
+        <f>종합Sheet!B5</f>
+        <v>신재경</v>
       </c>
       <c r="C5" s="2">
         <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
-        <v>3.8000000000000003</v>
+        <v>0.7</v>
       </c>
       <c r="D5" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B5)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H5" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B5)</f>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="I5" s="14">
         <f>SUM(D5:H5)</f>
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="2">
@@ -22243,24 +22243,24 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <f>종합Sheet!A44</f>
-        <v>41</v>
+        <f>종합Sheet!A6</f>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="str">
-        <f>종합Sheet!B44</f>
-        <v>노민준</v>
+        <f>종합Sheet!B6</f>
+        <v>정효태</v>
       </c>
       <c r="C6" s="2">
         <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="D6" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B6)</f>
@@ -22268,15 +22268,15 @@
       </c>
       <c r="G6" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B6)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H6" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B6)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="14">
         <f>SUM(D6:H6)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="2">
@@ -22320,24 +22320,24 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>종합Sheet!A109</f>
-        <v>106</v>
+        <f>종합Sheet!A7</f>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="str">
-        <f>종합Sheet!B109</f>
-        <v>최령창</v>
+        <f>종합Sheet!B7</f>
+        <v>이승민</v>
       </c>
       <c r="C7" s="2">
         <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B7)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B7)</f>
@@ -22345,15 +22345,15 @@
       </c>
       <c r="G7" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B7)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="14">
         <f>SUM(D7:H7)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="2">
@@ -22397,16 +22397,16 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <f>종합Sheet!A48</f>
-        <v>45</v>
+        <f>종합Sheet!A8</f>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="str">
-        <f>종합Sheet!B48</f>
-        <v>문준수</v>
+        <f>종합Sheet!B8</f>
+        <v>이정석</v>
       </c>
       <c r="C8" s="2">
         <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D8" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B8)</f>
@@ -22422,15 +22422,15 @@
       </c>
       <c r="G8" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B8)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H8" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B8)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="14">
         <f>SUM(D8:H8)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="2">
@@ -22469,20 +22469,20 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <f>종합Sheet!A52</f>
-        <v>49</v>
+        <f>종합Sheet!A9</f>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="str">
-        <f>종합Sheet!B52</f>
-        <v>박주연</v>
+        <f>종합Sheet!B9</f>
+        <v>강종찬</v>
       </c>
       <c r="C9" s="2">
         <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="D9" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B9)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B9)</f>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="G9" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B9)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H9" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B9)</f>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="I9" s="14">
         <f>SUM(D9:H9)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="2">
@@ -22541,32 +22541,32 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <f>종합Sheet!A118</f>
-        <v>115</v>
+        <f>종합Sheet!A10</f>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="str">
-        <f>종합Sheet!B118</f>
-        <v>황석원</v>
+        <f>종합Sheet!B10</f>
+        <v>강관석</v>
       </c>
       <c r="C10" s="2">
         <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="D10" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B10)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B10)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G10" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B10)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H10" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B10)</f>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="I10" s="14">
         <f>SUM(D10:H10)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="2">
@@ -22613,32 +22613,32 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <f>종합Sheet!A107</f>
-        <v>104</v>
+        <f>종합Sheet!A11</f>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="str">
-        <f>종합Sheet!B107</f>
-        <v>조현우</v>
+        <f>종합Sheet!B11</f>
+        <v>강기혁</v>
       </c>
       <c r="C11" s="2">
         <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
-        <v>1.4000000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="D11" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B11)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E11" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B11)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B11)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B11)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B11)</f>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="I11" s="14">
         <f>SUM(D11:H11)</f>
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="2">
@@ -22685,40 +22685,40 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <f>종합Sheet!A27</f>
-        <v>24</v>
+        <f>종합Sheet!A12</f>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="str">
-        <f>종합Sheet!B27</f>
-        <v>김성준</v>
+        <f>종합Sheet!B12</f>
+        <v>강도일</v>
       </c>
       <c r="C12" s="2">
         <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="D12" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B12)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E12" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B12)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B12)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B12)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H12" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B12)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="14">
         <f>SUM(D12:H12)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="2">
@@ -22757,16 +22757,16 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <f>종합Sheet!A76</f>
-        <v>73</v>
+        <f>종합Sheet!A13</f>
+        <v>10</v>
       </c>
       <c r="B13" s="2" t="str">
-        <f>종합Sheet!B76</f>
-        <v>윤창현</v>
+        <f>종합Sheet!B13</f>
+        <v>강일수</v>
       </c>
       <c r="C13" s="2">
         <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="D13" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B13)</f>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="E13" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B13)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B13)</f>
@@ -22782,7 +22782,7 @@
       </c>
       <c r="G13" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B13)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B13)</f>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="I13" s="14">
         <f>SUM(D13:H13)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="2">
@@ -22829,20 +22829,20 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <f>종합Sheet!A111</f>
-        <v>108</v>
+        <f>종합Sheet!A14</f>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="str">
-        <f>종합Sheet!B111</f>
-        <v>한상규</v>
+        <f>종합Sheet!B14</f>
+        <v>구교훈</v>
       </c>
       <c r="C14" s="2">
         <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
-        <v>1.4000000000000001</v>
+        <v>0</v>
       </c>
       <c r="D14" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B14)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B14)</f>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="G14" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B14)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B14)</f>
@@ -22862,7 +22862,7 @@
       </c>
       <c r="I14" s="14">
         <f>SUM(D14:H14)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="2">
@@ -22901,16 +22901,16 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <f>종합Sheet!A113</f>
-        <v>110</v>
+        <f>종합Sheet!A15</f>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="str">
-        <f>종합Sheet!B113</f>
-        <v>한중희</v>
+        <f>종합Sheet!B15</f>
+        <v>권주용</v>
       </c>
       <c r="C15" s="2">
         <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
-        <v>1.4000000000000001</v>
+        <v>0</v>
       </c>
       <c r="D15" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B15)</f>
@@ -22926,15 +22926,15 @@
       </c>
       <c r="G15" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B15)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H15" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B15)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <f>SUM(D15:H15)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="2">
@@ -22968,20 +22968,20 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <f>종합Sheet!A60</f>
-        <v>57</v>
+        <f>종합Sheet!A16</f>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="str">
-        <f>종합Sheet!B60</f>
-        <v>신기웅</v>
+        <f>종합Sheet!B16</f>
+        <v>김기문</v>
       </c>
       <c r="C16" s="2">
         <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
-        <v>1.9000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="D16" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B16)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B16)</f>
@@ -22989,19 +22989,19 @@
       </c>
       <c r="F16" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B16)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="14">
         <f>SUM(D16:H16)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="2">
@@ -23030,24 +23030,24 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <f>종합Sheet!A83</f>
-        <v>80</v>
+        <f>종합Sheet!A17</f>
+        <v>14</v>
       </c>
       <c r="B17" s="2" t="str">
-        <f>종합Sheet!B83</f>
-        <v>이새샘</v>
+        <f>종합Sheet!B17</f>
+        <v>김기태</v>
       </c>
       <c r="C17" s="2">
         <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
-        <v>1.4000000000000001</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B17)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B17)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F17" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B17)</f>
@@ -23055,7 +23055,7 @@
       </c>
       <c r="G17" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B17)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B17)</f>
@@ -23063,7 +23063,7 @@
       </c>
       <c r="I17" s="14">
         <f>SUM(D17:H17)</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="2">
@@ -23092,16 +23092,16 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <f>종합Sheet!A84</f>
-        <v>81</v>
+        <f>종합Sheet!A18</f>
+        <v>15</v>
       </c>
       <c r="B18" s="2" t="str">
-        <f>종합Sheet!B84</f>
-        <v>이성관</v>
+        <f>종합Sheet!B18</f>
+        <v>김덕준</v>
       </c>
       <c r="C18" s="2">
         <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
-        <v>1.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="D18" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B18)</f>
@@ -23117,15 +23117,15 @@
       </c>
       <c r="G18" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B18)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B18)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
         <f>SUM(D18:H18)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="2">
@@ -23154,16 +23154,16 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <f>종합Sheet!A85</f>
-        <v>82</v>
+        <f>종합Sheet!A19</f>
+        <v>16</v>
       </c>
       <c r="B19" s="2" t="str">
-        <f>종합Sheet!B85</f>
-        <v>이승윤</v>
+        <f>종합Sheet!B19</f>
+        <v>김동인</v>
       </c>
       <c r="C19" s="2">
         <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D19" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B19)</f>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="G19" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B19)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B19)</f>
@@ -23187,7 +23187,7 @@
       </c>
       <c r="I19" s="14">
         <f>SUM(D19:H19)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J19" s="15"/>
       <c r="N19" s="1" t="s">
@@ -23196,16 +23196,16 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <f>종합Sheet!A108</f>
-        <v>105</v>
+        <f>종합Sheet!A20</f>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="str">
-        <f>종합Sheet!B108</f>
-        <v>차승원</v>
+        <f>종합Sheet!B20</f>
+        <v>김민섭</v>
       </c>
       <c r="C20" s="2">
         <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D20" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B20)</f>
@@ -23221,7 +23221,7 @@
       </c>
       <c r="G20" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B20)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B20)</f>
@@ -23229,7 +23229,7 @@
       </c>
       <c r="I20" s="14">
         <f>SUM(D20:H20)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" s="15"/>
       <c r="N20" s="1" t="s">
@@ -23238,16 +23238,16 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <f>종합Sheet!A94</f>
-        <v>91</v>
+        <f>종합Sheet!A21</f>
+        <v>18</v>
       </c>
       <c r="B21" s="2" t="str">
-        <f>종합Sheet!B94</f>
-        <v>이호행</v>
+        <f>종합Sheet!B21</f>
+        <v>김민준</v>
       </c>
       <c r="C21" s="2">
         <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="D21" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B21)</f>
@@ -23263,7 +23263,7 @@
       </c>
       <c r="G21" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B21)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B21)</f>
@@ -23271,7 +23271,7 @@
       </c>
       <c r="I21" s="14">
         <f>SUM(D21:H21)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="15"/>
       <c r="N21" s="1" t="s">
@@ -23280,16 +23280,16 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <f>종합Sheet!A112</f>
-        <v>109</v>
+        <f>종합Sheet!A22</f>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="str">
-        <f>종합Sheet!B112</f>
-        <v>한의현</v>
+        <f>종합Sheet!B22</f>
+        <v>김민찬</v>
       </c>
       <c r="C22" s="2">
         <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D22" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B22)</f>
@@ -23297,7 +23297,7 @@
       </c>
       <c r="E22" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B22)</f>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="G22" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B22)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B22)</f>
@@ -23313,30 +23313,30 @@
       </c>
       <c r="I22" s="14">
         <f>SUM(D22:H22)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <f>종합Sheet!A123</f>
-        <v>120</v>
+        <f>종합Sheet!A23</f>
+        <v>20</v>
       </c>
       <c r="B23" s="2" t="str">
-        <f>종합Sheet!B123</f>
-        <v>최경영</v>
+        <f>종합Sheet!B23</f>
+        <v>김범기</v>
       </c>
       <c r="C23" s="2">
         <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="D23" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B23)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B23)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B23)</f>
@@ -23344,30 +23344,30 @@
       </c>
       <c r="G23" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B23)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B23)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <f>SUM(D23:H23)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J23" s="15"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <f>종합Sheet!A9</f>
-        <v>6</v>
+        <f>종합Sheet!A24</f>
+        <v>21</v>
       </c>
       <c r="B24" s="2" t="str">
-        <f>종합Sheet!B9</f>
-        <v>강종찬</v>
+        <f>종합Sheet!B24</f>
+        <v>김병준</v>
       </c>
       <c r="C24" s="2">
         <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D24" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B24)</f>
@@ -23383,7 +23383,7 @@
       </c>
       <c r="G24" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B24)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B24)</f>
@@ -23391,65 +23391,65 @@
       </c>
       <c r="I24" s="14">
         <f>SUM(D24:H24)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="15"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <f>종합Sheet!A16</f>
-        <v>13</v>
+        <f>종합Sheet!A25</f>
+        <v>22</v>
       </c>
       <c r="B25" s="2" t="str">
-        <f>종합Sheet!B16</f>
-        <v>김기문</v>
+        <f>종합Sheet!B25</f>
+        <v>김부건</v>
       </c>
       <c r="C25" s="2">
         <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="D25" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B25)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B25)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B25)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B25)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
         <f>SUM(D25:H25)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <f>종합Sheet!A32</f>
-        <v>29</v>
+        <f>종합Sheet!A26</f>
+        <v>23</v>
       </c>
       <c r="B26" s="2" t="str">
-        <f>종합Sheet!B32</f>
-        <v>김우인</v>
+        <f>종합Sheet!B26</f>
+        <v>김성수</v>
       </c>
       <c r="C26" s="2">
         <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
-        <v>2.6</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D26" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B26)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B26)</f>
@@ -23457,73 +23457,73 @@
       </c>
       <c r="F26" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B26)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G26" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B26)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B26)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
         <f>SUM(D26:H26)</f>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J26" s="15"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <f>종합Sheet!A71</f>
-        <v>68</v>
+        <f>종합Sheet!A27</f>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="str">
-        <f>종합Sheet!B71</f>
-        <v>유우진</v>
+        <f>종합Sheet!B27</f>
+        <v>김성준</v>
       </c>
       <c r="C27" s="2">
         <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
-        <v>0.4</v>
+        <v>7.6</v>
       </c>
       <c r="D27" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B27)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E27" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B27)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B27)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G27" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B27)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H27" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="14">
         <f>SUM(D27:H27)</f>
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J27" s="15"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <f>종합Sheet!A80</f>
-        <v>77</v>
+        <f>종합Sheet!A28</f>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="str">
-        <f>종합Sheet!B80</f>
-        <v>이병현</v>
+        <f>종합Sheet!B28</f>
+        <v>김송환</v>
       </c>
       <c r="C28" s="2">
         <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
-        <v>0.60000000000000009</v>
+        <v>2.6</v>
       </c>
       <c r="D28" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B28)</f>
@@ -23531,38 +23531,38 @@
       </c>
       <c r="E28" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B28)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B28)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B28)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="14">
         <f>SUM(D28:H28)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <f>종합Sheet!A91</f>
-        <v>88</v>
+        <f>종합Sheet!A29</f>
+        <v>26</v>
       </c>
       <c r="B29" s="2" t="str">
-        <f>종합Sheet!B91</f>
-        <v>이찬솔</v>
+        <f>종합Sheet!B29</f>
+        <v>김영태</v>
       </c>
       <c r="C29" s="2">
         <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B29)</f>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="E29" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B29)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B29)</f>
@@ -23578,30 +23578,30 @@
       </c>
       <c r="G29" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B29)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B29)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <f>SUM(D29:H29)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J29" s="15"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <f>종합Sheet!A92</f>
-        <v>89</v>
+        <f>종합Sheet!A30</f>
+        <v>27</v>
       </c>
       <c r="B30" s="2" t="str">
-        <f>종합Sheet!B92</f>
-        <v>이찬영</v>
+        <f>종합Sheet!B30</f>
+        <v>김용빈</v>
       </c>
       <c r="C30" s="2">
         <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D30" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B30)</f>
@@ -23617,7 +23617,7 @@
       </c>
       <c r="G30" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B30)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B30)</f>
@@ -23625,26 +23625,26 @@
       </c>
       <c r="I30" s="14">
         <f>SUM(D30:H30)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <f>종합Sheet!A17</f>
-        <v>14</v>
+        <f>종합Sheet!A31</f>
+        <v>28</v>
       </c>
       <c r="B31" s="2" t="str">
-        <f>종합Sheet!B17</f>
-        <v>김기태</v>
+        <f>종합Sheet!B31</f>
+        <v>김용현</v>
       </c>
       <c r="C31" s="2">
         <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
-        <v>3</v>
+        <v>2.9000000000000004</v>
       </c>
       <c r="D31" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B31)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E31" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B31)</f>
@@ -23652,69 +23652,69 @@
       </c>
       <c r="F31" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B31)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G31" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B31)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B31)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <f>SUM(D31:H31)</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
+        <f>종합Sheet!A32</f>
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="str">
+        <f>종합Sheet!B32</f>
+        <v>김우인</v>
+      </c>
+      <c r="C32" s="2">
+        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
+        <v>2.6</v>
+      </c>
+      <c r="D32" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B32)</f>
+        <v>2</v>
+      </c>
+      <c r="E32" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B32)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B32)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B32)</f>
+        <v>2</v>
+      </c>
+      <c r="H32" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B32)</f>
+        <v>9</v>
+      </c>
+      <c r="I32" s="14">
+        <f>SUM(D32:H32)</f>
+        <v>13</v>
+      </c>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <f>종합Sheet!A33</f>
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="str">
+      <c r="B33" s="2" t="str">
         <f>종합Sheet!B33</f>
         <v>김종준</v>
-      </c>
-      <c r="C32" s="2">
-        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
-        <v>0.2</v>
-      </c>
-      <c r="D32" s="14">
-        <f>COUNTIF(경기기록Sheet!$E:$H,B32)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="14">
-        <f>COUNTIF(경기기록Sheet!$I:$L,B32)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="14">
-        <f>COUNTIF(경기기록Sheet!$M:$P,B32)</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="14">
-        <f>COUNTIF(경기기록Sheet!$Q:$U,B32)</f>
-        <v>1</v>
-      </c>
-      <c r="H32" s="14">
-        <f>COUNTIF(경기기록Sheet!$V:$V,B32)</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="14">
-        <f>SUM(D32:H32)</f>
-        <v>1</v>
-      </c>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <f>종합Sheet!A54</f>
-        <v>51</v>
-      </c>
-      <c r="B33" s="2" t="str">
-        <f>종합Sheet!B54</f>
-        <v>박준영</v>
       </c>
       <c r="C33" s="2">
         <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
@@ -23748,20 +23748,20 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <f>종합Sheet!A58</f>
-        <v>55</v>
+        <f>종합Sheet!A34</f>
+        <v>31</v>
       </c>
       <c r="B34" s="2" t="str">
-        <f>종합Sheet!B58</f>
-        <v>손경호</v>
+        <f>종합Sheet!B34</f>
+        <v>김종혁</v>
       </c>
       <c r="C34" s="2">
         <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
-        <v>2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D34" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B34)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B34)</f>
@@ -23773,30 +23773,30 @@
       </c>
       <c r="G34" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B34)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B34)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" s="14">
         <f>SUM(D34:H34)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J34" s="15"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <f>종합Sheet!A63</f>
-        <v>60</v>
+        <f>종합Sheet!A35</f>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="str">
-        <f>종합Sheet!B63</f>
-        <v>양진웅</v>
+        <f>종합Sheet!B35</f>
+        <v>김준영</v>
       </c>
       <c r="C35" s="2">
         <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D35" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B35)</f>
@@ -23808,11 +23808,11 @@
       </c>
       <c r="F35" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B35)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B35)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B35)</f>
@@ -23820,26 +23820,26 @@
       </c>
       <c r="I35" s="14">
         <f>SUM(D35:H35)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <f>종합Sheet!A81</f>
-        <v>78</v>
+        <f>종합Sheet!A36</f>
+        <v>33</v>
       </c>
       <c r="B36" s="2" t="str">
-        <f>종합Sheet!B81</f>
-        <v>이상민</v>
+        <f>종합Sheet!B36</f>
+        <v>김진형</v>
       </c>
       <c r="C36" s="2">
         <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D36" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B36)</f>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="G36" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B36)</f>
@@ -23859,38 +23859,38 @@
       </c>
       <c r="I36" s="14">
         <f>SUM(D36:H36)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="15"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <f>종합Sheet!A87</f>
-        <v>84</v>
+        <f>종합Sheet!A37</f>
+        <v>34</v>
       </c>
       <c r="B37" s="2" t="str">
-        <f>종합Sheet!B87</f>
-        <v>이영준</v>
+        <f>종합Sheet!B37</f>
+        <v>김진호</v>
       </c>
       <c r="C37" s="2">
         <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
-        <v>0.7</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D37" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B37)</f>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E37" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B37)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F37" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B37)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B37)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B37)</f>
@@ -23898,18 +23898,18 @@
       </c>
       <c r="I37" s="14">
         <f>SUM(D37:H37)</f>
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="J37" s="15"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <f>종합Sheet!A88</f>
-        <v>85</v>
+        <f>종합Sheet!A38</f>
+        <v>35</v>
       </c>
       <c r="B38" s="2" t="str">
-        <f>종합Sheet!B88</f>
-        <v>이정범</v>
+        <f>종합Sheet!B38</f>
+        <v>김태성</v>
       </c>
       <c r="C38" s="2">
         <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
@@ -23917,11 +23917,11 @@
       </c>
       <c r="D38" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B38)</f>
@@ -23929,11 +23929,11 @@
       </c>
       <c r="G38" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B38)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B38)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="14">
         <f>SUM(D38:H38)</f>
@@ -23943,16 +23943,16 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <f>종합Sheet!A101</f>
-        <v>98</v>
+        <f>종합Sheet!A39</f>
+        <v>36</v>
       </c>
       <c r="B39" s="2" t="str">
-        <f>종합Sheet!B101</f>
-        <v>전하늘</v>
+        <f>종합Sheet!B39</f>
+        <v>김태양</v>
       </c>
       <c r="C39" s="2">
         <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D39" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B39)</f>
@@ -23960,7 +23960,7 @@
       </c>
       <c r="E39" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B39)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B39)</f>
@@ -23968,7 +23968,7 @@
       </c>
       <c r="G39" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B39)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B39)</f>
@@ -23976,22 +23976,22 @@
       </c>
       <c r="I39" s="14">
         <f>SUM(D39:H39)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" s="15"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <f>종합Sheet!A116</f>
-        <v>113</v>
+        <f>종합Sheet!A40</f>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="str">
-        <f>종합Sheet!B116</f>
-        <v>홍현석</v>
+        <f>종합Sheet!B40</f>
+        <v>김태완</v>
       </c>
       <c r="C40" s="2">
         <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D40" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B40)</f>
@@ -24007,7 +24007,7 @@
       </c>
       <c r="G40" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B40)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B40)</f>
@@ -24015,30 +24015,30 @@
       </c>
       <c r="I40" s="14">
         <f>SUM(D40:H40)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="15"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <f>종합Sheet!A4</f>
-        <v>1</v>
+        <f>종합Sheet!A41</f>
+        <v>38</v>
       </c>
       <c r="B41" s="2" t="str">
-        <f>종합Sheet!B4</f>
-        <v>김인혁</v>
+        <f>종합Sheet!B41</f>
+        <v>김태호</v>
       </c>
       <c r="C41" s="2">
         <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="D41" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B41)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E41" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B41)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F41" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B41)</f>
@@ -24050,30 +24050,30 @@
       </c>
       <c r="H41" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B41)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="14">
         <f>SUM(D41:H41)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J41" s="15"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <f>종합Sheet!A5</f>
-        <v>2</v>
+        <f>종합Sheet!A42</f>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="str">
-        <f>종합Sheet!B5</f>
-        <v>신재경</v>
+        <f>종합Sheet!B42</f>
+        <v>김현우</v>
       </c>
       <c r="C42" s="2">
         <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D42" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B42)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B42)</f>
@@ -24081,7 +24081,7 @@
       </c>
       <c r="F42" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B42)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B42)</f>
@@ -24089,22 +24089,22 @@
       </c>
       <c r="H42" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B42)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="14">
         <f>SUM(D42:H42)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J42" s="15"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <f>종합Sheet!A6</f>
-        <v>3</v>
+        <f>종합Sheet!A43</f>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="str">
-        <f>종합Sheet!B6</f>
-        <v>정효태</v>
+        <f>종합Sheet!B43</f>
+        <v>김형원</v>
       </c>
       <c r="C43" s="2">
         <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
@@ -24138,24 +24138,24 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <f>종합Sheet!A7</f>
-        <v>4</v>
+        <f>종합Sheet!A44</f>
+        <v>41</v>
       </c>
       <c r="B44" s="2" t="str">
-        <f>종합Sheet!B7</f>
-        <v>이승민</v>
+        <f>종합Sheet!B44</f>
+        <v>노민준</v>
       </c>
       <c r="C44" s="2">
         <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="D44" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B44)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B44)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B44)</f>
@@ -24163,30 +24163,30 @@
       </c>
       <c r="G44" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B44)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H44" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B44)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44" s="14">
         <f>SUM(D44:H44)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J44" s="15"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <f>종합Sheet!A8</f>
-        <v>5</v>
+        <f>종합Sheet!A45</f>
+        <v>42</v>
       </c>
       <c r="B45" s="2" t="str">
-        <f>종합Sheet!B8</f>
-        <v>이정석</v>
+        <f>종합Sheet!B45</f>
+        <v>노성호</v>
       </c>
       <c r="C45" s="2">
         <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D45" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B45)</f>
@@ -24194,7 +24194,7 @@
       </c>
       <c r="E45" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B45)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B45)</f>
@@ -24210,34 +24210,34 @@
       </c>
       <c r="I45" s="14">
         <f>SUM(D45:H45)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="15"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <f>종합Sheet!A10</f>
-        <v>7</v>
+        <f>종합Sheet!A46</f>
+        <v>43</v>
       </c>
       <c r="B46" s="2" t="str">
-        <f>종합Sheet!B10</f>
-        <v>강관석</v>
+        <f>종합Sheet!B46</f>
+        <v>류서진</v>
       </c>
       <c r="C46" s="2">
         <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="D46" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B46)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E46" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B46)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B46)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G46" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B46)</f>
@@ -24245,38 +24245,38 @@
       </c>
       <c r="H46" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B46)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="14">
         <f>SUM(D46:H46)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J46" s="15"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <f>종합Sheet!A11</f>
-        <v>8</v>
+        <f>종합Sheet!A47</f>
+        <v>44</v>
       </c>
       <c r="B47" s="2" t="str">
-        <f>종합Sheet!B11</f>
-        <v>강기혁</v>
+        <f>종합Sheet!B47</f>
+        <v>마창기</v>
       </c>
       <c r="C47" s="2">
         <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="D47" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B47)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E47" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B47)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F47" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B47)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G47" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B47)</f>
@@ -24288,22 +24288,22 @@
       </c>
       <c r="I47" s="14">
         <f>SUM(D47:H47)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J47" s="15"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <f>종합Sheet!A12</f>
-        <v>9</v>
+        <f>종합Sheet!A48</f>
+        <v>45</v>
       </c>
       <c r="B48" s="2" t="str">
-        <f>종합Sheet!B12</f>
-        <v>강도일</v>
+        <f>종합Sheet!B48</f>
+        <v>문준수</v>
       </c>
       <c r="C48" s="2">
         <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="D48" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B48)</f>
@@ -24319,26 +24319,26 @@
       </c>
       <c r="G48" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B48)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H48" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B48)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="14">
         <f>SUM(D48:H48)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J48" s="15"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <f>종합Sheet!A13</f>
-        <v>10</v>
+        <f>종합Sheet!A49</f>
+        <v>46</v>
       </c>
       <c r="B49" s="2" t="str">
-        <f>종합Sheet!B13</f>
-        <v>강일수</v>
+        <f>종합Sheet!B49</f>
+        <v>민건호</v>
       </c>
       <c r="C49" s="2">
         <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
@@ -24372,12 +24372,12 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <f>종합Sheet!A14</f>
-        <v>11</v>
+        <f>종합Sheet!A50</f>
+        <v>47</v>
       </c>
       <c r="B50" s="2" t="str">
-        <f>종합Sheet!B14</f>
-        <v>구교훈</v>
+        <f>종합Sheet!B50</f>
+        <v>박수천</v>
       </c>
       <c r="C50" s="2">
         <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
@@ -24411,12 +24411,12 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <f>종합Sheet!A15</f>
-        <v>12</v>
+        <f>종합Sheet!A51</f>
+        <v>48</v>
       </c>
       <c r="B51" s="2" t="str">
-        <f>종합Sheet!B15</f>
-        <v>권주용</v>
+        <f>종합Sheet!B51</f>
+        <v>박정호</v>
       </c>
       <c r="C51" s="2">
         <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
@@ -24450,20 +24450,20 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <f>종합Sheet!A18</f>
-        <v>15</v>
+        <f>종합Sheet!A52</f>
+        <v>49</v>
       </c>
       <c r="B52" s="2" t="str">
-        <f>종합Sheet!B18</f>
-        <v>김덕준</v>
+        <f>종합Sheet!B52</f>
+        <v>박주연</v>
       </c>
       <c r="C52" s="2">
         <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="D52" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B52)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B52)</f>
@@ -24475,7 +24475,7 @@
       </c>
       <c r="G52" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B52)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H52" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B52)</f>
@@ -24483,18 +24483,18 @@
       </c>
       <c r="I52" s="14">
         <f>SUM(D52:H52)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J52" s="15"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <f>종합Sheet!A19</f>
-        <v>16</v>
+        <f>종합Sheet!A53</f>
+        <v>50</v>
       </c>
       <c r="B53" s="2" t="str">
-        <f>종합Sheet!B19</f>
-        <v>김동인</v>
+        <f>종합Sheet!B53</f>
+        <v>박주현</v>
       </c>
       <c r="C53" s="2">
         <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
@@ -24528,12 +24528,12 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <f>종합Sheet!A20</f>
-        <v>17</v>
+        <f>종합Sheet!A54</f>
+        <v>51</v>
       </c>
       <c r="B54" s="2" t="str">
-        <f>종합Sheet!B20</f>
-        <v>김민섭</v>
+        <f>종합Sheet!B54</f>
+        <v>박준영</v>
       </c>
       <c r="C54" s="2">
         <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
@@ -24545,7 +24545,7 @@
       </c>
       <c r="E54" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B54)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B54)</f>
@@ -24553,7 +24553,7 @@
       </c>
       <c r="G54" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B54)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B54)</f>
@@ -24567,16 +24567,16 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <f>종합Sheet!A21</f>
-        <v>18</v>
+        <f>종합Sheet!A55</f>
+        <v>52</v>
       </c>
       <c r="B55" s="2" t="str">
-        <f>종합Sheet!B21</f>
-        <v>김민준</v>
+        <f>종합Sheet!B55</f>
+        <v>박태현</v>
       </c>
       <c r="C55" s="2">
         <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D55" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B55)</f>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="E55" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B55)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F55" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B55)</f>
@@ -24600,18 +24600,18 @@
       </c>
       <c r="I55" s="14">
         <f>SUM(D55:H55)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" s="15"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <f>종합Sheet!A22</f>
-        <v>19</v>
+        <f>종합Sheet!A56</f>
+        <v>53</v>
       </c>
       <c r="B56" s="2" t="str">
-        <f>종합Sheet!B22</f>
-        <v>김민찬</v>
+        <f>종합Sheet!B56</f>
+        <v>박하빈</v>
       </c>
       <c r="C56" s="2">
         <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
@@ -24645,12 +24645,12 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <f>종합Sheet!A23</f>
-        <v>20</v>
+        <f>종합Sheet!A57</f>
+        <v>54</v>
       </c>
       <c r="B57" s="2" t="str">
-        <f>종합Sheet!B23</f>
-        <v>김범기</v>
+        <f>종합Sheet!B57</f>
+        <v>박형기</v>
       </c>
       <c r="C57" s="2">
         <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
@@ -24684,24 +24684,24 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <f>종합Sheet!A24</f>
-        <v>21</v>
+        <f>종합Sheet!A58</f>
+        <v>55</v>
       </c>
       <c r="B58" s="2" t="str">
-        <f>종합Sheet!B24</f>
-        <v>김병준</v>
+        <f>종합Sheet!B58</f>
+        <v>손경호</v>
       </c>
       <c r="C58" s="2">
         <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B58)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E58" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B58)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B58)</f>
@@ -24709,42 +24709,42 @@
       </c>
       <c r="G58" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B58)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B58)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I58" s="14">
         <f>SUM(D58:H58)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J58" s="15"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <f>종합Sheet!A25</f>
-        <v>22</v>
+        <f>종합Sheet!A59</f>
+        <v>56</v>
       </c>
       <c r="B59" s="2" t="str">
-        <f>종합Sheet!B25</f>
-        <v>김부건</v>
+        <f>종합Sheet!B59</f>
+        <v>송윤상</v>
       </c>
       <c r="C59" s="2">
         <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D59" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B59)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E59" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B59)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F59" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B59)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B59)</f>
@@ -24756,26 +24756,26 @@
       </c>
       <c r="I59" s="14">
         <f>SUM(D59:H59)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J59" s="15"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <f>종합Sheet!A26</f>
-        <v>23</v>
+        <f>종합Sheet!A60</f>
+        <v>57</v>
       </c>
       <c r="B60" s="2" t="str">
-        <f>종합Sheet!B26</f>
-        <v>김성수</v>
+        <f>종합Sheet!B60</f>
+        <v>신기웅</v>
       </c>
       <c r="C60" s="2">
         <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
-        <v>1.7999999999999998</v>
+        <v>1.9000000000000001</v>
       </c>
       <c r="D60" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B60)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E60" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B60)</f>
@@ -24783,11 +24783,11 @@
       </c>
       <c r="F60" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B60)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G60" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B60)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H60" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B60)</f>
@@ -24795,22 +24795,22 @@
       </c>
       <c r="I60" s="14">
         <f>SUM(D60:H60)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J60" s="15"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <f>종합Sheet!A28</f>
-        <v>25</v>
+        <f>종합Sheet!A61</f>
+        <v>58</v>
       </c>
       <c r="B61" s="2" t="str">
-        <f>종합Sheet!B28</f>
-        <v>김송환</v>
+        <f>종합Sheet!B61</f>
+        <v>신종훈</v>
       </c>
       <c r="C61" s="2">
         <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="D61" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B61)</f>
@@ -24822,7 +24822,7 @@
       </c>
       <c r="F61" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B61)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G61" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B61)</f>
@@ -24830,22 +24830,22 @@
       </c>
       <c r="H61" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B61)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="14">
         <f>SUM(D61:H61)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J61" s="15"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <f>종합Sheet!A29</f>
-        <v>26</v>
+        <f>종합Sheet!A62</f>
+        <v>59</v>
       </c>
       <c r="B62" s="2" t="str">
-        <f>종합Sheet!B29</f>
-        <v>김영태</v>
+        <f>종합Sheet!B62</f>
+        <v>안진혁</v>
       </c>
       <c r="C62" s="2">
         <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
@@ -24879,16 +24879,16 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <f>종합Sheet!A30</f>
-        <v>27</v>
+        <f>종합Sheet!A63</f>
+        <v>60</v>
       </c>
       <c r="B63" s="2" t="str">
-        <f>종합Sheet!B30</f>
-        <v>김용빈</v>
+        <f>종합Sheet!B63</f>
+        <v>양진웅</v>
       </c>
       <c r="C63" s="2">
         <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D63" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B63)</f>
@@ -24900,11 +24900,11 @@
       </c>
       <c r="F63" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B63)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B63)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B63)</f>
@@ -24912,30 +24912,30 @@
       </c>
       <c r="I63" s="14">
         <f>SUM(D63:H63)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="15"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <f>종합Sheet!A31</f>
-        <v>28</v>
+        <f>종합Sheet!A64</f>
+        <v>61</v>
       </c>
       <c r="B64" s="2" t="str">
-        <f>종합Sheet!B31</f>
-        <v>김용현</v>
+        <f>종합Sheet!B64</f>
+        <v>오상준</v>
       </c>
       <c r="C64" s="2">
         <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
-        <v>2.9000000000000004</v>
+        <v>2.1</v>
       </c>
       <c r="D64" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B64)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B64)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F64" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B64)</f>
@@ -24951,34 +24951,34 @@
       </c>
       <c r="I64" s="14">
         <f>SUM(D64:H64)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J64" s="15"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <f>종합Sheet!A34</f>
-        <v>31</v>
+        <f>종합Sheet!A65</f>
+        <v>62</v>
       </c>
       <c r="B65" s="2" t="str">
-        <f>종합Sheet!B34</f>
-        <v>김종혁</v>
+        <f>종합Sheet!B65</f>
+        <v>오성찬</v>
       </c>
       <c r="C65" s="2">
         <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
-        <v>1.2000000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="D65" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B65)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E65" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B65)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B65)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B65)</f>
@@ -24986,38 +24986,38 @@
       </c>
       <c r="H65" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B65)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" s="14">
         <f>SUM(D65:H65)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J65" s="15"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <f>종합Sheet!A35</f>
-        <v>32</v>
+        <f>종합Sheet!A66</f>
+        <v>63</v>
       </c>
       <c r="B66" s="2" t="str">
-        <f>종합Sheet!B35</f>
-        <v>김준영</v>
+        <f>종합Sheet!B66</f>
+        <v>오우영</v>
       </c>
       <c r="C66" s="2">
         <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D66" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B66)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B66)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B66)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G66" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B66)</f>
@@ -25029,18 +25029,18 @@
       </c>
       <c r="I66" s="14">
         <f>SUM(D66:H66)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J66" s="15"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <f>종합Sheet!A36</f>
-        <v>33</v>
+        <f>종합Sheet!A67</f>
+        <v>64</v>
       </c>
       <c r="B67" s="2" t="str">
-        <f>종합Sheet!B36</f>
-        <v>김진형</v>
+        <f>종합Sheet!B67</f>
+        <v>오운용</v>
       </c>
       <c r="C67" s="2">
         <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
@@ -25074,24 +25074,24 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <f>종합Sheet!A37</f>
-        <v>34</v>
+        <f>종합Sheet!A68</f>
+        <v>65</v>
       </c>
       <c r="B68" s="2" t="str">
-        <f>종합Sheet!B37</f>
-        <v>김진호</v>
+        <f>종합Sheet!B68</f>
+        <v>오진환</v>
       </c>
       <c r="C68" s="2">
         <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
-        <v>5.6000000000000005</v>
+        <v>0</v>
       </c>
       <c r="D68" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B68)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E68" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B68)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F68" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B68)</f>
@@ -25107,30 +25107,30 @@
       </c>
       <c r="I68" s="14">
         <f>SUM(D68:H68)</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J68" s="15"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <f>종합Sheet!A38</f>
-        <v>35</v>
+        <f>종합Sheet!A69</f>
+        <v>66</v>
       </c>
       <c r="B69" s="2" t="str">
-        <f>종합Sheet!B38</f>
-        <v>김태성</v>
+        <f>종합Sheet!B69</f>
+        <v>우보광</v>
       </c>
       <c r="C69" s="2">
         <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D69" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B69)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B69)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B69)</f>
@@ -25146,22 +25146,22 @@
       </c>
       <c r="I69" s="14">
         <f>SUM(D69:H69)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" s="15"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <f>종합Sheet!A39</f>
-        <v>36</v>
+        <f>종합Sheet!A70</f>
+        <v>67</v>
       </c>
       <c r="B70" s="2" t="str">
-        <f>종합Sheet!B39</f>
-        <v>김태양</v>
+        <f>종합Sheet!B70</f>
+        <v>유상근</v>
       </c>
       <c r="C70" s="2">
         <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
-        <v>0</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="D70" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B70)</f>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="E70" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B70)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B70)</f>
@@ -25177,30 +25177,30 @@
       </c>
       <c r="G70" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B70)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H70" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B70)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="14">
         <f>SUM(D70:H70)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J70" s="15"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <f>종합Sheet!A40</f>
-        <v>37</v>
+        <f>종합Sheet!A71</f>
+        <v>68</v>
       </c>
       <c r="B71" s="2" t="str">
-        <f>종합Sheet!B40</f>
-        <v>김태완</v>
+        <f>종합Sheet!B71</f>
+        <v>유우진</v>
       </c>
       <c r="C71" s="2">
         <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D71" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B71)</f>
@@ -25216,7 +25216,7 @@
       </c>
       <c r="G71" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B71)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B71)</f>
@@ -25224,18 +25224,18 @@
       </c>
       <c r="I71" s="14">
         <f>SUM(D71:H71)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" s="15"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <f>종합Sheet!A41</f>
-        <v>38</v>
+        <f>종합Sheet!A72</f>
+        <v>69</v>
       </c>
       <c r="B72" s="2" t="str">
-        <f>종합Sheet!B41</f>
-        <v>김태호</v>
+        <f>종합Sheet!B72</f>
+        <v>유인상</v>
       </c>
       <c r="C72" s="2">
         <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
@@ -25269,16 +25269,16 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <f>종합Sheet!A42</f>
-        <v>39</v>
+        <f>종합Sheet!A73</f>
+        <v>70</v>
       </c>
       <c r="B73" s="2" t="str">
-        <f>종합Sheet!B42</f>
-        <v>김현우</v>
+        <f>종합Sheet!B73</f>
+        <v>유정훈</v>
       </c>
       <c r="C73" s="2">
         <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
-        <v>0</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D73" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B73)</f>
@@ -25286,11 +25286,11 @@
       </c>
       <c r="E73" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B73)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B73)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B73)</f>
@@ -25302,18 +25302,18 @@
       </c>
       <c r="I73" s="14">
         <f>SUM(D73:H73)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J73" s="15"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <f>종합Sheet!A43</f>
-        <v>40</v>
+        <f>종합Sheet!A74</f>
+        <v>71</v>
       </c>
       <c r="B74" s="2" t="str">
-        <f>종합Sheet!B43</f>
-        <v>김형원</v>
+        <f>종합Sheet!B74</f>
+        <v>유진효</v>
       </c>
       <c r="C74" s="2">
         <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
@@ -25347,16 +25347,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <f>종합Sheet!A45</f>
-        <v>42</v>
+        <f>종합Sheet!A75</f>
+        <v>72</v>
       </c>
       <c r="B75" s="2" t="str">
-        <f>종합Sheet!B45</f>
-        <v>노성호</v>
+        <f>종합Sheet!B75</f>
+        <v>윤원택</v>
       </c>
       <c r="C75" s="2">
         <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D75" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B75)</f>
@@ -25364,11 +25364,11 @@
       </c>
       <c r="E75" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B75)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B75)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B75)</f>
@@ -25380,22 +25380,22 @@
       </c>
       <c r="I75" s="14">
         <f>SUM(D75:H75)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J75" s="15"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <f>종합Sheet!A46</f>
-        <v>43</v>
+        <f>종합Sheet!A76</f>
+        <v>73</v>
       </c>
       <c r="B76" s="2" t="str">
-        <f>종합Sheet!B46</f>
-        <v>류서진</v>
+        <f>종합Sheet!B76</f>
+        <v>윤창현</v>
       </c>
       <c r="C76" s="2">
         <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="D76" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B76)</f>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="E76" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B76)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B76)</f>
@@ -25411,7 +25411,7 @@
       </c>
       <c r="G76" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B76)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H76" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B76)</f>
@@ -25419,26 +25419,26 @@
       </c>
       <c r="I76" s="14">
         <f>SUM(D76:H76)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J76" s="15"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <f>종합Sheet!A47</f>
-        <v>44</v>
+        <f>종합Sheet!A77</f>
+        <v>74</v>
       </c>
       <c r="B77" s="2" t="str">
-        <f>종합Sheet!B47</f>
-        <v>마창기</v>
+        <f>종합Sheet!B77</f>
+        <v>윤현기</v>
       </c>
       <c r="C77" s="2">
         <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D77" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B77)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B77)</f>
@@ -25446,7 +25446,7 @@
       </c>
       <c r="F77" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B77)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B77)</f>
@@ -25458,18 +25458,18 @@
       </c>
       <c r="I77" s="14">
         <f>SUM(D77:H77)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J77" s="15"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <f>종합Sheet!A49</f>
-        <v>46</v>
+        <f>종합Sheet!A78</f>
+        <v>75</v>
       </c>
       <c r="B78" s="2" t="str">
-        <f>종합Sheet!B49</f>
-        <v>민건호</v>
+        <f>종합Sheet!B78</f>
+        <v>이경석</v>
       </c>
       <c r="C78" s="2">
         <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
@@ -25503,12 +25503,12 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <f>종합Sheet!A50</f>
-        <v>47</v>
+        <f>종합Sheet!A79</f>
+        <v>76</v>
       </c>
       <c r="B79" s="2" t="str">
-        <f>종합Sheet!B50</f>
-        <v>박수천</v>
+        <f>종합Sheet!B79</f>
+        <v>이민재</v>
       </c>
       <c r="C79" s="2">
         <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
@@ -25542,16 +25542,16 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <f>종합Sheet!A51</f>
-        <v>48</v>
+        <f>종합Sheet!A80</f>
+        <v>77</v>
       </c>
       <c r="B80" s="2" t="str">
-        <f>종합Sheet!B51</f>
-        <v>박정호</v>
+        <f>종합Sheet!B80</f>
+        <v>이병현</v>
       </c>
       <c r="C80" s="2">
         <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D80" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B80)</f>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="E80" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B80)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B80)</f>
@@ -25567,7 +25567,7 @@
       </c>
       <c r="G80" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B80)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H80" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B80)</f>
@@ -25575,26 +25575,26 @@
       </c>
       <c r="I80" s="14">
         <f>SUM(D80:H80)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J80" s="15"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <f>종합Sheet!A53</f>
-        <v>50</v>
+        <f>종합Sheet!A81</f>
+        <v>78</v>
       </c>
       <c r="B81" s="2" t="str">
-        <f>종합Sheet!B53</f>
-        <v>박주현</v>
+        <f>종합Sheet!B81</f>
+        <v>이상민</v>
       </c>
       <c r="C81" s="2">
         <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D81" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B81)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B81)</f>
@@ -25606,7 +25606,7 @@
       </c>
       <c r="G81" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B81)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B81)</f>
@@ -25614,34 +25614,34 @@
       </c>
       <c r="I81" s="14">
         <f>SUM(D81:H81)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J81" s="15"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <f>종합Sheet!A55</f>
-        <v>52</v>
+        <f>종합Sheet!A82</f>
+        <v>79</v>
       </c>
       <c r="B82" s="2" t="str">
-        <f>종합Sheet!B55</f>
-        <v>박태현</v>
+        <f>종합Sheet!B82</f>
+        <v>이상현</v>
       </c>
       <c r="C82" s="2">
         <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="D82" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B82)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B82)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B82)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G82" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B82)</f>
@@ -25653,22 +25653,22 @@
       </c>
       <c r="I82" s="14">
         <f>SUM(D82:H82)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J82" s="15"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <f>종합Sheet!A56</f>
-        <v>53</v>
+        <f>종합Sheet!A83</f>
+        <v>80</v>
       </c>
       <c r="B83" s="2" t="str">
-        <f>종합Sheet!B56</f>
-        <v>박하빈</v>
+        <f>종합Sheet!B83</f>
+        <v>이새샘</v>
       </c>
       <c r="C83" s="2">
         <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
-        <v>0</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D83" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B83)</f>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="E83" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B83)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B83)</f>
@@ -25684,30 +25684,30 @@
       </c>
       <c r="G83" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B83)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H83" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B83)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" s="14">
         <f>SUM(D83:H83)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J83" s="15"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <f>종합Sheet!A57</f>
-        <v>54</v>
+        <f>종합Sheet!A84</f>
+        <v>81</v>
       </c>
       <c r="B84" s="2" t="str">
-        <f>종합Sheet!B57</f>
-        <v>박형기</v>
+        <f>종합Sheet!B84</f>
+        <v>이성관</v>
       </c>
       <c r="C84" s="2">
         <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
-        <v>0</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D84" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B84)</f>
@@ -25723,30 +25723,30 @@
       </c>
       <c r="G84" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B84)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H84" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B84)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" s="14">
         <f>SUM(D84:H84)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J84" s="15"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <f>종합Sheet!A59</f>
-        <v>56</v>
+        <f>종합Sheet!A85</f>
+        <v>82</v>
       </c>
       <c r="B85" s="2" t="str">
-        <f>종합Sheet!B59</f>
-        <v>송윤상</v>
+        <f>종합Sheet!B85</f>
+        <v>이승윤</v>
       </c>
       <c r="C85" s="2">
         <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D85" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B85)</f>
@@ -25758,11 +25758,11 @@
       </c>
       <c r="F85" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B85)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G85" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B85)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H85" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B85)</f>
@@ -25770,30 +25770,30 @@
       </c>
       <c r="I85" s="14">
         <f>SUM(D85:H85)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J85" s="15"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <f>종합Sheet!A61</f>
-        <v>58</v>
+        <f>종합Sheet!A86</f>
+        <v>83</v>
       </c>
       <c r="B86" s="2" t="str">
-        <f>종합Sheet!B61</f>
-        <v>신종훈</v>
+        <f>종합Sheet!B86</f>
+        <v>이연길</v>
       </c>
       <c r="C86" s="2">
         <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D86" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B86)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B86)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B86)</f>
@@ -25809,26 +25809,26 @@
       </c>
       <c r="I86" s="14">
         <f>SUM(D86:H86)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" s="15"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <f>종합Sheet!A62</f>
-        <v>59</v>
+        <f>종합Sheet!A87</f>
+        <v>84</v>
       </c>
       <c r="B87" s="2" t="str">
-        <f>종합Sheet!B62</f>
-        <v>안진혁</v>
+        <f>종합Sheet!B87</f>
+        <v>이영준</v>
       </c>
       <c r="C87" s="2">
         <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D87" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B87)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B87)</f>
@@ -25836,11 +25836,11 @@
       </c>
       <c r="F87" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B87)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B87)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B87)</f>
@@ -25848,61 +25848,61 @@
       </c>
       <c r="I87" s="14">
         <f>SUM(D87:H87)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J87" s="15"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <f>종합Sheet!A64</f>
-        <v>61</v>
+        <f>종합Sheet!A88</f>
+        <v>85</v>
       </c>
       <c r="B88" s="2" t="str">
-        <f>종합Sheet!B64</f>
-        <v>오상준</v>
+        <f>종합Sheet!B88</f>
+        <v>이정범</v>
       </c>
       <c r="C88" s="2">
         <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="D88" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B88)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E88" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B88)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B88)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G88" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B88)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B88)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="14">
         <f>SUM(D88:H88)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J88" s="15"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <f>종합Sheet!A65</f>
-        <v>62</v>
+        <f>종합Sheet!A89</f>
+        <v>86</v>
       </c>
       <c r="B89" s="2" t="str">
-        <f>종합Sheet!B65</f>
-        <v>오성찬</v>
+        <f>종합Sheet!B89</f>
+        <v>이종수</v>
       </c>
       <c r="C89" s="2">
         <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D89" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B89)</f>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="F89" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B89)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B89)</f>
@@ -25926,34 +25926,34 @@
       </c>
       <c r="I89" s="14">
         <f>SUM(D89:H89)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="15"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <f>종합Sheet!A66</f>
-        <v>63</v>
+        <f>종합Sheet!A90</f>
+        <v>87</v>
       </c>
       <c r="B90" s="2" t="str">
-        <f>종합Sheet!B66</f>
-        <v>오우영</v>
+        <f>종합Sheet!B90</f>
+        <v>이지섭</v>
       </c>
       <c r="C90" s="2">
         <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D90" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B90)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B90)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F90" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B90)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G90" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B90)</f>
@@ -25965,22 +25965,22 @@
       </c>
       <c r="I90" s="14">
         <f>SUM(D90:H90)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J90" s="15"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <f>종합Sheet!A67</f>
-        <v>64</v>
+        <f>종합Sheet!A91</f>
+        <v>88</v>
       </c>
       <c r="B91" s="2" t="str">
-        <f>종합Sheet!B67</f>
-        <v>오운용</v>
+        <f>종합Sheet!B91</f>
+        <v>이찬솔</v>
       </c>
       <c r="C91" s="2">
         <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B91)</f>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="E91" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B91)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B91)</f>
@@ -25996,30 +25996,30 @@
       </c>
       <c r="G91" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B91)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B91)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="14">
         <f>SUM(D91:H91)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J91" s="15"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <f>종합Sheet!A68</f>
-        <v>65</v>
+        <f>종합Sheet!A92</f>
+        <v>89</v>
       </c>
       <c r="B92" s="2" t="str">
-        <f>종합Sheet!B68</f>
-        <v>오진환</v>
+        <f>종합Sheet!B92</f>
+        <v>이찬영</v>
       </c>
       <c r="C92" s="2">
         <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D92" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B92)</f>
@@ -26035,7 +26035,7 @@
       </c>
       <c r="G92" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B92)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B92)</f>
@@ -26043,18 +26043,18 @@
       </c>
       <c r="I92" s="14">
         <f>SUM(D92:H92)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" s="15"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <f>종합Sheet!A69</f>
-        <v>66</v>
+        <f>종합Sheet!A93</f>
+        <v>90</v>
       </c>
       <c r="B93" s="2" t="str">
-        <f>종합Sheet!B69</f>
-        <v>우보광</v>
+        <f>종합Sheet!B93</f>
+        <v>이태한</v>
       </c>
       <c r="C93" s="2">
         <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
@@ -26088,16 +26088,16 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <f>종합Sheet!A72</f>
-        <v>69</v>
+        <f>종합Sheet!A94</f>
+        <v>91</v>
       </c>
       <c r="B94" s="2" t="str">
-        <f>종합Sheet!B72</f>
-        <v>유인상</v>
+        <f>종합Sheet!B94</f>
+        <v>이호행</v>
       </c>
       <c r="C94" s="2">
         <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D94" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B94)</f>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="G94" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B94)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H94" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B94)</f>
@@ -26121,22 +26121,22 @@
       </c>
       <c r="I94" s="14">
         <f>SUM(D94:H94)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J94" s="15"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <f>종합Sheet!A73</f>
-        <v>70</v>
+        <f>종합Sheet!A95</f>
+        <v>92</v>
       </c>
       <c r="B95" s="2" t="str">
-        <f>종합Sheet!B73</f>
-        <v>유정훈</v>
+        <f>종합Sheet!B95</f>
+        <v>임수철</v>
       </c>
       <c r="C95" s="2">
         <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
-        <v>1.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="D95" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B95)</f>
@@ -26144,11 +26144,11 @@
       </c>
       <c r="E95" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B95)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F95" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B95)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G95" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B95)</f>
@@ -26160,34 +26160,34 @@
       </c>
       <c r="I95" s="14">
         <f>SUM(D95:H95)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J95" s="15"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <f>종합Sheet!A74</f>
-        <v>71</v>
+        <f>종합Sheet!A96</f>
+        <v>93</v>
       </c>
       <c r="B96" s="2" t="str">
-        <f>종합Sheet!B74</f>
-        <v>유진효</v>
+        <f>종합Sheet!B96</f>
+        <v>임태환</v>
       </c>
       <c r="C96" s="2">
         <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
-        <v>0</v>
+        <v>1.8000000000000003</v>
       </c>
       <c r="D96" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B96)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E96" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B96)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B96)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B96)</f>
@@ -26195,26 +26195,26 @@
       </c>
       <c r="H96" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B96)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" s="14">
         <f>SUM(D96:H96)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J96" s="15"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <f>종합Sheet!A75</f>
-        <v>72</v>
+        <f>종합Sheet!A97</f>
+        <v>94</v>
       </c>
       <c r="B97" s="2" t="str">
-        <f>종합Sheet!B75</f>
-        <v>윤원택</v>
+        <f>종합Sheet!B97</f>
+        <v>장희도</v>
       </c>
       <c r="C97" s="2">
         <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D97" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B97)</f>
@@ -26226,7 +26226,7 @@
       </c>
       <c r="F97" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B97)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G97" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B97)</f>
@@ -26238,26 +26238,26 @@
       </c>
       <c r="I97" s="14">
         <f>SUM(D97:H97)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J97" s="15"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <f>종합Sheet!A77</f>
-        <v>74</v>
+        <f>종합Sheet!A98</f>
+        <v>95</v>
       </c>
       <c r="B98" s="2" t="str">
-        <f>종합Sheet!B77</f>
-        <v>윤현기</v>
+        <f>종합Sheet!B98</f>
+        <v>장희준</v>
       </c>
       <c r="C98" s="2">
         <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D98" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B98)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E98" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B98)</f>
@@ -26265,7 +26265,7 @@
       </c>
       <c r="F98" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B98)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B98)</f>
@@ -26277,22 +26277,22 @@
       </c>
       <c r="I98" s="14">
         <f>SUM(D98:H98)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J98" s="15"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <f>종합Sheet!A78</f>
-        <v>75</v>
+        <f>종합Sheet!A99</f>
+        <v>96</v>
       </c>
       <c r="B99" s="2" t="str">
-        <f>종합Sheet!B78</f>
-        <v>이경석</v>
+        <f>종합Sheet!B99</f>
+        <v>전나현</v>
       </c>
       <c r="C99" s="2">
         <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B99)</f>
@@ -26300,11 +26300,11 @@
       </c>
       <c r="E99" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B99)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B99)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G99" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B99)</f>
@@ -26316,26 +26316,26 @@
       </c>
       <c r="I99" s="14">
         <f>SUM(D99:H99)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J99" s="15"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <f>종합Sheet!A79</f>
-        <v>76</v>
+        <f>종합Sheet!A100</f>
+        <v>97</v>
       </c>
       <c r="B100" s="2" t="str">
-        <f>종합Sheet!B79</f>
-        <v>이민재</v>
+        <f>종합Sheet!B100</f>
+        <v>전성환</v>
       </c>
       <c r="C100" s="2">
         <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D100" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B100)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B100)</f>
@@ -26355,26 +26355,26 @@
       </c>
       <c r="I100" s="14">
         <f>SUM(D100:H100)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="15"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <f>종합Sheet!A82</f>
-        <v>79</v>
+        <f>종합Sheet!A101</f>
+        <v>98</v>
       </c>
       <c r="B101" s="2" t="str">
-        <f>종합Sheet!B82</f>
-        <v>이상현</v>
+        <f>종합Sheet!B101</f>
+        <v>전하늘</v>
       </c>
       <c r="C101" s="2">
         <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="D101" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B101)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B101)</f>
@@ -26382,11 +26382,11 @@
       </c>
       <c r="F101" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B101)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G101" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B101)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B101)</f>
@@ -26394,30 +26394,30 @@
       </c>
       <c r="I101" s="14">
         <f>SUM(D101:H101)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J101" s="15"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <f>종합Sheet!A86</f>
-        <v>83</v>
+        <f>종합Sheet!A102</f>
+        <v>99</v>
       </c>
       <c r="B102" s="2" t="str">
-        <f>종합Sheet!B86</f>
-        <v>이연길</v>
+        <f>종합Sheet!B102</f>
+        <v>정민수</v>
       </c>
       <c r="C102" s="2">
         <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="D102" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B102)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B102)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B102)</f>
@@ -26425,7 +26425,7 @@
       </c>
       <c r="G102" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B102)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H102" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B102)</f>
@@ -26433,26 +26433,26 @@
       </c>
       <c r="I102" s="14">
         <f>SUM(D102:H102)</f>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J102" s="15"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <f>종합Sheet!A89</f>
-        <v>86</v>
+        <f>종합Sheet!A103</f>
+        <v>100</v>
       </c>
       <c r="B103" s="2" t="str">
-        <f>종합Sheet!B89</f>
-        <v>이종수</v>
+        <f>종합Sheet!B103</f>
+        <v>정재명</v>
       </c>
       <c r="C103" s="2">
         <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D103" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B103)</f>
@@ -26472,18 +26472,18 @@
       </c>
       <c r="I103" s="14">
         <f>SUM(D103:H103)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" s="15"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <f>종합Sheet!A90</f>
-        <v>87</v>
+        <f>종합Sheet!A104</f>
+        <v>101</v>
       </c>
       <c r="B104" s="2" t="str">
-        <f>종합Sheet!B90</f>
-        <v>이지섭</v>
+        <f>종합Sheet!B104</f>
+        <v>정진억</v>
       </c>
       <c r="C104" s="2">
         <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
@@ -26517,28 +26517,28 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <f>종합Sheet!A93</f>
-        <v>90</v>
+        <f>종합Sheet!A105</f>
+        <v>102</v>
       </c>
       <c r="B105" s="2" t="str">
-        <f>종합Sheet!B93</f>
-        <v>이태한</v>
+        <f>종합Sheet!B105</f>
+        <v>정현서</v>
       </c>
       <c r="C105" s="2">
         <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
-        <v>0</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="D105" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B105)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B105)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B105)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B105)</f>
@@ -26550,33 +26550,33 @@
       </c>
       <c r="I105" s="14">
         <f>SUM(D105:H105)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <f>종합Sheet!A95</f>
-        <v>92</v>
+        <f>종합Sheet!A106</f>
+        <v>103</v>
       </c>
       <c r="B106" s="2" t="str">
-        <f>종합Sheet!B95</f>
-        <v>임수철</v>
+        <f>종합Sheet!B106</f>
+        <v>조진한</v>
       </c>
       <c r="C106" s="2">
         <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="D106" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B106)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E106" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B106)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B106)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G106" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B106)</f>
@@ -26588,59 +26588,59 @@
       </c>
       <c r="I106" s="14">
         <f>SUM(D106:H106)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <f>종합Sheet!A96</f>
-        <v>93</v>
+        <f>종합Sheet!A107</f>
+        <v>104</v>
       </c>
       <c r="B107" s="2" t="str">
-        <f>종합Sheet!B96</f>
-        <v>임태환</v>
+        <f>종합Sheet!B107</f>
+        <v>조현우</v>
       </c>
       <c r="C107" s="2">
         <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
-        <v>1.8000000000000003</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D107" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B107)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E107" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B107)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B107)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G107" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B107)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H107" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B107)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I107" s="14">
         <f>SUM(D107:H107)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <f>종합Sheet!A97</f>
-        <v>94</v>
+        <f>종합Sheet!A108</f>
+        <v>105</v>
       </c>
       <c r="B108" s="2" t="str">
-        <f>종합Sheet!B97</f>
-        <v>장희도</v>
+        <f>종합Sheet!B108</f>
+        <v>차승원</v>
       </c>
       <c r="C108" s="2">
         <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B108)</f>
@@ -26648,7 +26648,7 @@
       </c>
       <c r="E108" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B108)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B108)</f>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="G108" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B108)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H108" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B108)</f>
@@ -26664,29 +26664,29 @@
       </c>
       <c r="I108" s="14">
         <f>SUM(D108:H108)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <f>종합Sheet!A98</f>
-        <v>95</v>
+        <f>종합Sheet!A109</f>
+        <v>106</v>
       </c>
       <c r="B109" s="2" t="str">
-        <f>종합Sheet!B98</f>
-        <v>장희준</v>
+        <f>종합Sheet!B109</f>
+        <v>최령창</v>
       </c>
       <c r="C109" s="2">
         <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D109" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B109)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B109)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F109" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B109)</f>
@@ -26694,29 +26694,29 @@
       </c>
       <c r="G109" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B109)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H109" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B109)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="14">
         <f>SUM(D109:H109)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <f>종합Sheet!A99</f>
-        <v>96</v>
+        <f>종합Sheet!A110</f>
+        <v>107</v>
       </c>
       <c r="B110" s="2" t="str">
-        <f>종합Sheet!B99</f>
-        <v>전나현</v>
+        <f>종합Sheet!B110</f>
+        <v>최승훈</v>
       </c>
       <c r="C110" s="2">
         <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B110)</f>
@@ -26724,11 +26724,11 @@
       </c>
       <c r="E110" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B110)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F110" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B110)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G110" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B110)</f>
@@ -26740,21 +26740,21 @@
       </c>
       <c r="I110" s="14">
         <f>SUM(D110:H110)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <f>종합Sheet!A100</f>
-        <v>97</v>
+        <f>종합Sheet!A111</f>
+        <v>108</v>
       </c>
       <c r="B111" s="2" t="str">
-        <f>종합Sheet!B100</f>
-        <v>전성환</v>
+        <f>종합Sheet!B111</f>
+        <v>한상규</v>
       </c>
       <c r="C111" s="2">
         <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
-        <v>0.2</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D111" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B111)</f>
@@ -26770,7 +26770,7 @@
       </c>
       <c r="G111" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B111)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H111" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B111)</f>
@@ -26778,29 +26778,29 @@
       </c>
       <c r="I111" s="14">
         <f>SUM(D111:H111)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <f>종합Sheet!A103</f>
-        <v>100</v>
+        <f>종합Sheet!A112</f>
+        <v>109</v>
       </c>
       <c r="B112" s="2" t="str">
-        <f>종합Sheet!B103</f>
-        <v>정재명</v>
+        <f>종합Sheet!B112</f>
+        <v>한의현</v>
       </c>
       <c r="C112" s="2">
         <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D112" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B112)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B112)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B112)</f>
@@ -26808,7 +26808,7 @@
       </c>
       <c r="G112" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B112)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H112" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B112)</f>
@@ -26816,21 +26816,21 @@
       </c>
       <c r="I112" s="14">
         <f>SUM(D112:H112)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <f>종합Sheet!A104</f>
-        <v>101</v>
+        <f>종합Sheet!A113</f>
+        <v>110</v>
       </c>
       <c r="B113" s="2" t="str">
-        <f>종합Sheet!B104</f>
-        <v>정진억</v>
+        <f>종합Sheet!B113</f>
+        <v>한중희</v>
       </c>
       <c r="C113" s="2">
         <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
-        <v>0</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D113" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B113)</f>
@@ -26846,29 +26846,29 @@
       </c>
       <c r="G113" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B113)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H113" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B113)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" s="14">
         <f>SUM(D113:H113)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <f>종합Sheet!A105</f>
-        <v>102</v>
+        <f>종합Sheet!A114</f>
+        <v>111</v>
       </c>
       <c r="B114" s="2" t="str">
-        <f>종합Sheet!B105</f>
-        <v>정현서</v>
+        <f>종합Sheet!B114</f>
+        <v>허동혁</v>
       </c>
       <c r="C114" s="2">
         <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
-        <v>0.90000000000000013</v>
+        <v>0.4</v>
       </c>
       <c r="D114" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B114)</f>
@@ -26876,11 +26876,11 @@
       </c>
       <c r="E114" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B114)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B114)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B114)</f>
@@ -26892,25 +26892,25 @@
       </c>
       <c r="I114" s="14">
         <f>SUM(D114:H114)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
-        <f>종합Sheet!A106</f>
-        <v>103</v>
+        <f>종합Sheet!A115</f>
+        <v>112</v>
       </c>
       <c r="B115" s="2" t="str">
-        <f>종합Sheet!B106</f>
-        <v>조진한</v>
+        <f>종합Sheet!B115</f>
+        <v>홍석준</v>
       </c>
       <c r="C115" s="2">
         <f>((D115+E115+G115+H115)*0.2)+(F115*0.3)</f>
-        <v>4.2</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="D115" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B115)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E115" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B115)</f>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="F115" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B115)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G115" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B115)</f>
@@ -26930,21 +26930,21 @@
       </c>
       <c r="I115" s="14">
         <f>SUM(D115:H115)</f>
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <f>종합Sheet!A110</f>
-        <v>107</v>
+        <f>종합Sheet!A116</f>
+        <v>113</v>
       </c>
       <c r="B116" s="2" t="str">
-        <f>종합Sheet!B110</f>
-        <v>최승훈</v>
+        <f>종합Sheet!B116</f>
+        <v>홍현석</v>
       </c>
       <c r="C116" s="2">
         <f>((D116+E116+G116+H116)*0.2)+(F116*0.3)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D116" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B116)</f>
@@ -26960,7 +26960,7 @@
       </c>
       <c r="G116" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B116)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B116)</f>
@@ -26968,25 +26968,25 @@
       </c>
       <c r="I116" s="14">
         <f>SUM(D116:H116)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <f>종합Sheet!A114</f>
-        <v>111</v>
+        <f>종합Sheet!A117</f>
+        <v>114</v>
       </c>
       <c r="B117" s="2" t="str">
-        <f>종합Sheet!B114</f>
-        <v>허동혁</v>
+        <f>종합Sheet!B117</f>
+        <v>황건호</v>
       </c>
       <c r="C117" s="2">
         <f>((D117+E117+G117+H117)*0.2)+(F117*0.3)</f>
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="D117" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B117)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E117" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B117)</f>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="F117" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B117)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G117" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B117)</f>
@@ -27006,29 +27006,29 @@
       </c>
       <c r="I117" s="14">
         <f>SUM(D117:H117)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <f>종합Sheet!A115</f>
-        <v>112</v>
+        <f>종합Sheet!A118</f>
+        <v>115</v>
       </c>
       <c r="B118" s="2" t="str">
-        <f>종합Sheet!B115</f>
-        <v>홍석준</v>
+        <f>종합Sheet!B118</f>
+        <v>황석원</v>
       </c>
       <c r="C118" s="2">
         <f>((D118+E118+G118+H118)*0.2)+(F118*0.3)</f>
-        <v>0.90000000000000013</v>
+        <v>2.1</v>
       </c>
       <c r="D118" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B118)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E118" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B118)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B118)</f>
@@ -27036,41 +27036,41 @@
       </c>
       <c r="G118" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B118)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H118" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B118)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="14">
         <f>SUM(D118:H118)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <f>종합Sheet!A117</f>
-        <v>114</v>
+        <f>종합Sheet!A119</f>
+        <v>116</v>
       </c>
       <c r="B119" s="2" t="str">
-        <f>종합Sheet!B117</f>
-        <v>황건호</v>
+        <f>종합Sheet!B119</f>
+        <v>황재순</v>
       </c>
       <c r="C119" s="2">
         <f>((D119+E119+G119+H119)*0.2)+(F119*0.3)</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D119" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B119)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E119" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B119)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B119)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G119" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B119)</f>
@@ -27082,25 +27082,25 @@
       </c>
       <c r="I119" s="14">
         <f>SUM(D119:H119)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <f>종합Sheet!A119</f>
-        <v>116</v>
+        <f>종합Sheet!A120</f>
+        <v>117</v>
       </c>
       <c r="B120" s="2" t="str">
-        <f>종합Sheet!B119</f>
-        <v>황재순</v>
+        <f>종합Sheet!B120</f>
+        <v>황철우</v>
       </c>
       <c r="C120" s="2">
         <f>((D120+E120+G120+H120)*0.2)+(F120*0.3)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D120" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B120)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E120" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B120)</f>
@@ -27120,25 +27120,25 @@
       </c>
       <c r="I120" s="14">
         <f>SUM(D120:H120)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <f>종합Sheet!A120</f>
-        <v>117</v>
+        <f>종합Sheet!A121</f>
+        <v>118</v>
       </c>
       <c r="B121" s="2" t="str">
-        <f>종합Sheet!B120</f>
-        <v>황철우</v>
+        <f>종합Sheet!B121</f>
+        <v>김민성</v>
       </c>
       <c r="C121" s="2">
         <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D121" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B121)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E121" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B121)</f>
@@ -27158,17 +27158,17 @@
       </c>
       <c r="I121" s="14">
         <f>SUM(D121:H121)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <f>종합Sheet!A121</f>
-        <v>118</v>
+        <f>종합Sheet!A122</f>
+        <v>119</v>
       </c>
       <c r="B122" s="2" t="str">
-        <f>종합Sheet!B121</f>
-        <v>김민성</v>
+        <f>종합Sheet!B122</f>
+        <v>송명섭</v>
       </c>
       <c r="C122" s="2">
         <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
@@ -27201,24 +27201,24 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <f>종합Sheet!A122</f>
-        <v>119</v>
+        <f>종합Sheet!A123</f>
+        <v>120</v>
       </c>
       <c r="B123" s="2" t="str">
-        <f>종합Sheet!B122</f>
-        <v>송명섭</v>
+        <f>종합Sheet!B123</f>
+        <v>최경영</v>
       </c>
       <c r="C123" s="2">
         <f>((D123+E123+G123+H123)*0.2)+(F123*0.3)</f>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D123" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B123)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E123" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B123)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B123)</f>
@@ -27226,21 +27226,21 @@
       </c>
       <c r="G123" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B123)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H123" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B123)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I123" s="14">
         <f>SUM(D123:H123)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I123">
-      <sortCondition descending="1" ref="G3"/>
+      <sortCondition ref="A3"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -28825,10 +28825,10 @@
       <c r="G2" s="47" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="93" t="s">
+      <c r="I2" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="93"/>
+      <c r="J2" s="98"/>
       <c r="K2" s="65" t="s">
         <v>277</v>
       </c>
@@ -28853,7 +28853,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="99" t="s">
         <v>338</v>
       </c>
       <c r="C3" s="72">
@@ -28871,7 +28871,7 @@
       </c>
       <c r="G3" s="61">
         <f>VLOOKUP(F3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="I3" s="94" t="s">
         <v>333</v>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="S3" s="63">
         <f>VLOOKUP(R3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
@@ -28923,7 +28923,7 @@
       </c>
       <c r="G4" s="61">
         <f>VLOOKUP(F4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="I4" s="95"/>
       <c r="J4" s="66">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15.4</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -28971,7 +28971,7 @@
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15.4</v>
+        <v>22.6</v>
       </c>
       <c r="I5" s="95"/>
       <c r="J5" s="66">
@@ -28999,7 +28999,7 @@
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -29019,7 +29019,7 @@
       </c>
       <c r="G6" s="61">
         <f>VLOOKUP(F6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="I6" s="95"/>
       <c r="J6" s="66">
@@ -29047,7 +29047,7 @@
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -29067,9 +29067,9 @@
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15</v>
-      </c>
-      <c r="I7" s="97"/>
+        <v>19.2</v>
+      </c>
+      <c r="I7" s="96"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="S7" s="71">
         <f>VLOOKUP(R7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="G8" s="63">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>20</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="N8" s="85"/>
       <c r="O8" s="48">
@@ -29133,7 +29133,7 @@
       </c>
       <c r="S8" s="71">
         <f>VLOOKUP(R8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
@@ -29153,12 +29153,12 @@
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>5.4</v>
-      </c>
-      <c r="I9" s="93" t="s">
+        <v>6.6</v>
+      </c>
+      <c r="I9" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="J9" s="93"/>
+      <c r="J9" s="98"/>
       <c r="K9" s="65" t="s">
         <v>277</v>
       </c>
@@ -29201,7 +29201,7 @@
       </c>
       <c r="G10" s="61">
         <f>VLOOKUP(F10,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="I10" s="94" t="s">
         <v>334</v>
@@ -29231,7 +29231,7 @@
       </c>
       <c r="S10" s="71">
         <f>VLOOKUP(R10,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
@@ -29251,7 +29251,7 @@
       </c>
       <c r="G11" s="61">
         <f>VLOOKUP(F11,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="I11" s="95"/>
       <c r="J11" s="66">
@@ -29279,7 +29279,7 @@
       </c>
       <c r="S11" s="71">
         <f>VLOOKUP(R11,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>3.9000000000000004</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
@@ -29299,7 +29299,7 @@
       </c>
       <c r="G12" s="61">
         <f>VLOOKUP(F12,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11.4</v>
+        <v>14.5</v>
       </c>
       <c r="I12" s="95"/>
       <c r="J12" s="66">
@@ -29311,7 +29311,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="100"/>
+      <c r="N12" s="97"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -29347,7 +29347,7 @@
       </c>
       <c r="G13" s="61">
         <f>VLOOKUP(F13,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="I13" s="95"/>
       <c r="J13" s="66">
@@ -29383,9 +29383,9 @@
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>13.2</v>
-      </c>
-      <c r="I14" s="97"/>
+        <v>15.6</v>
+      </c>
+      <c r="I14" s="96"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -29419,7 +29419,7 @@
       </c>
       <c r="G15" s="63">
         <f>VLOOKUP(F15,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="N15"/>
       <c r="O15"/>
@@ -29445,13 +29445,13 @@
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.4</v>
+        <v>14</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="93" t="s">
+      <c r="I16" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="J16" s="93"/>
+      <c r="J16" s="98"/>
       <c r="K16" s="65" t="s">
         <v>277</v>
       </c>
@@ -29474,7 +29474,7 @@
       </c>
       <c r="G17" s="63">
         <f>VLOOKUP(F17,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H17" s="37"/>
       <c r="I17" s="94" t="s">
@@ -29512,10 +29512,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="93" t="s">
+      <c r="B19" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="C19" s="93"/>
+      <c r="C19" s="98"/>
       <c r="D19" s="65" t="s">
         <v>277</v>
       </c>
@@ -29566,7 +29566,7 @@
       <c r="E21" s="65" t="s">
         <v>341</v>
       </c>
-      <c r="I21" s="97"/>
+      <c r="I21" s="96"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -29578,7 +29578,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="96"/>
+      <c r="B22" s="100"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -29590,10 +29590,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="98" t="s">
+      <c r="I23" s="92" t="s">
         <v>249</v>
       </c>
-      <c r="J23" s="99"/>
+      <c r="J23" s="93"/>
       <c r="K23" s="65" t="s">
         <v>277</v>
       </c>
@@ -29676,7 +29676,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="97"/>
+      <c r="I30" s="96"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -29689,6 +29689,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -29697,12 +29703,6 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30243,11 +30243,11 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ref="G4:G37" si="2">RANK(H4,$H$4:$H$37,0)</f>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4:I28" si="3">(COUNTIF(J4:CD4,"출전")*1)</f>
@@ -30357,11 +30357,11 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
-        <v>8.8000000000000007</v>
+        <v>5.7</v>
       </c>
       <c r="I5" s="6">
         <f t="shared" si="3"/>
@@ -30475,11 +30475,11 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="I6" s="6">
         <f t="shared" si="3"/>
@@ -30587,11 +30587,11 @@
       </c>
       <c r="G7" s="2">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C9</f>
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="I7" s="6">
         <f t="shared" si="3"/>
@@ -30695,11 +30695,11 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C10</f>
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I8" s="6">
         <f t="shared" si="3"/>
@@ -30813,11 +30813,11 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C15</f>
-        <v>4.4000000000000004</v>
+        <v>3</v>
       </c>
       <c r="I9" s="6">
         <f t="shared" si="3"/>
@@ -30927,11 +30927,11 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C16</f>
-        <v>4.9000000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="3"/>
@@ -31041,11 +31041,11 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C17</f>
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="3"/>
@@ -31157,11 +31157,11 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C18</f>
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="6">
         <f t="shared" si="3"/>
@@ -31275,7 +31275,7 @@
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C22</f>
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="I13" s="6">
         <f t="shared" si="3"/>
@@ -31383,11 +31383,11 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C23</f>
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="6">
         <f t="shared" si="3"/>
@@ -31592,11 +31592,11 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C25</f>
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="3"/>
@@ -31710,11 +31710,11 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C26</f>
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="3"/>
@@ -31820,11 +31820,11 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C29</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" s="6">
         <f t="shared" si="3"/>
@@ -31938,11 +31938,11 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C34</f>
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="I19" s="6">
         <f t="shared" si="3"/>
@@ -32056,11 +32056,11 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C40</f>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="I20" s="6">
         <f t="shared" si="3"/>
@@ -32168,11 +32168,11 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C44</f>
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="3"/>
@@ -32379,7 +32379,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C49</f>
@@ -32495,7 +32495,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C57</f>
@@ -32607,11 +32607,11 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C59</f>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="3"/>
@@ -32721,11 +32721,11 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C60</f>
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="3"/>
@@ -32837,7 +32837,7 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C62</f>
@@ -32951,11 +32951,11 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C63</f>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="3"/>
@@ -33065,11 +33065,11 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" ref="G29" si="4">RANK(H29,$H$4:$H$37,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C64</f>
-        <v>3.9000000000000004</v>
+        <v>3.1</v>
       </c>
       <c r="I29" s="6">
         <f t="shared" ref="I29" si="5">(COUNTIF(J29:CD29,"출전")*1)</f>
@@ -33175,11 +33175,11 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C69</f>
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I30" s="6">
         <f t="shared" ref="I30:I37" si="6">(COUNTIF(J30:CD30,"출전")*1)</f>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C72</f>
@@ -33399,7 +33399,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C79</f>
@@ -33515,11 +33515,11 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C83</f>
-        <v>1</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="6"/>
@@ -33625,11 +33625,11 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C90</f>
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I34" s="6">
         <f t="shared" si="6"/>
@@ -33735,11 +33735,11 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C97</f>
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="6"/>
@@ -33853,11 +33853,11 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C102</f>
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="6"/>
@@ -33967,7 +33967,7 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C104</f>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{230EABB8-D342-42F1-B5FC-1416A7390ACB}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25382BB3-14AB-40D6-ABB5-1AF221502C64}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="414">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -1458,16 +1458,10 @@
     <t>오상준</t>
   </si>
   <si>
-    <t>전나현</t>
-  </si>
-  <si>
     <t>신기웅</t>
   </si>
   <si>
     <t>황건호</t>
-  </si>
-  <si>
-    <t>정현서</t>
   </si>
   <si>
     <t>Red</t>
@@ -1485,9 +1479,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이찬솔</t>
-  </si>
-  <si>
     <t>노민진</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1531,6 +1522,42 @@
   </si>
   <si>
     <t>최경영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>손경호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오우영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전나현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유상근</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정민수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최령창</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>노민준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임태환</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3140,7 +3167,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>9.6</v>
+        <v>10.444444444444445</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3227,11 +3254,11 @@
       </c>
       <c r="AD2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF2" s="1">
         <f t="shared" si="0"/>
@@ -3434,8 +3461,12 @@
       <c r="AC3" s="4">
         <v>46191</v>
       </c>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
+      <c r="AD3" s="4">
+        <v>46198</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>46202</v>
+      </c>
       <c r="AF3" s="4"/>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
@@ -3511,11 +3542,11 @@
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>17.600000000000001</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4" si="2">(COUNTIF(J4:CD4,"출전")*1)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>352</v>
@@ -3570,7 +3601,9 @@
         <v>352</v>
       </c>
       <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
+      <c r="AE4" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF4" s="2"/>
       <c r="AG4" s="2"/>
       <c r="AH4" s="2"/>
@@ -3642,7 +3675,7 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ref="G5:G68" si="3">RANK(H5,$H$4:$H$123,0)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -3751,7 +3784,7 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
@@ -3855,7 +3888,7 @@
       </c>
       <c r="G7" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C7</f>
@@ -3958,7 +3991,7 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C8</f>
@@ -4061,7 +4094,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
@@ -4178,11 +4211,11 @@
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>352</v>
@@ -4224,7 +4257,9 @@
       <c r="AC10" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD10" s="2"/>
+      <c r="AD10" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE10" s="2"/>
       <c r="AF10" s="2"/>
       <c r="AG10" s="2"/>
@@ -4297,7 +4332,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
@@ -4421,7 +4456,7 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="3"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C12</f>
@@ -4527,7 +4562,7 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C13</f>
@@ -4631,7 +4666,7 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C14</f>
@@ -4735,7 +4770,7 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
@@ -4838,7 +4873,7 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
@@ -4951,7 +4986,7 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
@@ -5078,7 +5113,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C18</f>
@@ -5181,7 +5216,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
@@ -5292,7 +5327,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -5400,7 +5435,7 @@
       <c r="F21" s="60"/>
       <c r="G21" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C21</f>
@@ -5504,7 +5539,7 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" s="6">
         <f>I22+개인기록Sheet!C22</f>
@@ -5608,7 +5643,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C23</f>
@@ -5711,7 +5746,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="3"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
@@ -5816,7 +5851,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
@@ -5927,15 +5962,15 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
-        <v>7.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
@@ -5970,7 +6005,9 @@
         <v>352</v>
       </c>
       <c r="AD26" s="2"/>
-      <c r="AE26" s="2"/>
+      <c r="AE26" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF26" s="2"/>
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
@@ -6046,11 +6083,11 @@
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
@@ -6102,7 +6139,9 @@
       <c r="AC27" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD27" s="2"/>
+      <c r="AD27" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE27" s="2"/>
       <c r="AF27" s="2"/>
       <c r="AG27" s="2"/>
@@ -6175,7 +6214,7 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
@@ -6289,7 +6328,7 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C29</f>
@@ -6392,7 +6431,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6501,7 +6540,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
@@ -6624,11 +6663,11 @@
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>15.6</v>
+        <v>16.8</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>352</v>
@@ -6676,7 +6715,9 @@
       <c r="AC32" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD32" s="2"/>
+      <c r="AD32" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE32" s="2"/>
       <c r="AF32" s="2"/>
       <c r="AG32" s="2"/>
@@ -6749,7 +6790,7 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
@@ -6870,11 +6911,11 @@
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
-        <v>9.1999999999999993</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I34" s="6">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
@@ -6913,7 +6954,9 @@
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" s="2"/>
-      <c r="AE34" s="2"/>
+      <c r="AE34" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF34" s="2"/>
       <c r="AG34" s="2"/>
       <c r="AH34" s="2"/>
@@ -6986,7 +7029,7 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C35</f>
@@ -7090,7 +7133,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C36</f>
@@ -7193,7 +7236,7 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
@@ -7320,15 +7363,15 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
-        <v>4.4000000000000004</v>
+        <v>5.4</v>
       </c>
       <c r="I38" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -7359,7 +7402,9 @@
       <c r="AB38" s="2"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="2"/>
-      <c r="AE38" s="2"/>
+      <c r="AE38" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF38" s="2"/>
       <c r="AG38" s="2"/>
       <c r="AH38" s="2"/>
@@ -7432,7 +7477,7 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" s="6">
         <f>I39+개인기록Sheet!C39</f>
@@ -7535,7 +7580,7 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="3"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H40" s="6">
         <f>I40+개인기록Sheet!C40</f>
@@ -7641,7 +7686,7 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H41" s="6">
         <f>I41+개인기록Sheet!C41</f>
@@ -7745,7 +7790,7 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H42" s="6">
         <f>I42+개인기록Sheet!C42</f>
@@ -7848,7 +7893,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="3"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
@@ -7953,15 +7998,15 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
-        <v>14.2</v>
+        <v>15.2</v>
       </c>
       <c r="I44" s="6">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -8005,7 +8050,9 @@
       <c r="AC44" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD44" s="2"/>
+      <c r="AD44" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE44" s="2"/>
       <c r="AF44" s="2"/>
       <c r="AG44" s="2"/>
@@ -8079,7 +8126,7 @@
       </c>
       <c r="G45" s="2">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H45" s="6">
         <f>I45+개인기록Sheet!C45</f>
@@ -8189,15 +8236,15 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
-        <v>0</v>
+        <v>1.9000000000000001</v>
       </c>
       <c r="I46" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -8219,7 +8266,9 @@
       <c r="AA46" s="2"/>
       <c r="AB46" s="2"/>
       <c r="AC46" s="2"/>
-      <c r="AD46" s="2"/>
+      <c r="AD46" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE46" s="2"/>
       <c r="AF46" s="2"/>
       <c r="AG46" s="2"/>
@@ -8291,7 +8340,7 @@
       <c r="F47" s="60"/>
       <c r="G47" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
@@ -8398,11 +8447,11 @@
       </c>
       <c r="H48" s="6">
         <f>I48+개인기록Sheet!C48</f>
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="I48" s="6">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
@@ -8442,7 +8491,9 @@
       <c r="AC48" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD48" s="2"/>
+      <c r="AD48" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE48" s="2"/>
       <c r="AF48" s="2"/>
       <c r="AG48" s="2"/>
@@ -8516,7 +8567,7 @@
       </c>
       <c r="G49" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H49" s="6">
         <f>I49+개인기록Sheet!C49</f>
@@ -8620,7 +8671,7 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H50" s="6">
         <f>I50+개인기록Sheet!C50</f>
@@ -8724,7 +8775,7 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
@@ -8827,15 +8878,15 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52" s="6">
         <f>I52+개인기록Sheet!C52</f>
-        <v>10.8</v>
+        <v>13</v>
       </c>
       <c r="I52" s="6">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
@@ -8875,8 +8926,12 @@
         <v>352</v>
       </c>
       <c r="AC52" s="2"/>
-      <c r="AD52" s="2"/>
-      <c r="AE52" s="2"/>
+      <c r="AD52" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE52" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF52" s="2"/>
       <c r="AG52" s="2"/>
       <c r="AH52" s="2"/>
@@ -8949,7 +9004,7 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H53" s="6">
         <f>I53+개인기록Sheet!C53</f>
@@ -9053,15 +9108,15 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" si="3"/>
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H54" s="6">
         <f>I54+개인기록Sheet!C54</f>
-        <v>2.2000000000000002</v>
+        <v>4.2</v>
       </c>
       <c r="I54" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -9087,8 +9142,12 @@
       <c r="AA54" s="2"/>
       <c r="AB54" s="2"/>
       <c r="AC54" s="2"/>
-      <c r="AD54" s="2"/>
-      <c r="AE54" s="2"/>
+      <c r="AD54" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE54" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF54" s="2"/>
       <c r="AG54" s="2"/>
       <c r="AH54" s="2"/>
@@ -9160,7 +9219,7 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
@@ -9274,7 +9333,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
@@ -9378,7 +9437,7 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
@@ -9485,11 +9544,11 @@
       </c>
       <c r="H58" s="6">
         <f>I58+개인기록Sheet!C58</f>
-        <v>11</v>
+        <v>13.2</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
@@ -9529,8 +9588,12 @@
         <v>352</v>
       </c>
       <c r="AC58" s="2"/>
-      <c r="AD58" s="2"/>
-      <c r="AE58" s="2"/>
+      <c r="AD58" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE58" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF58" s="2"/>
       <c r="AG58" s="2"/>
       <c r="AH58" s="2"/>
@@ -9602,7 +9665,7 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="3"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
@@ -9709,15 +9772,15 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="I60" s="6">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -9752,7 +9815,9 @@
       <c r="AB60" s="2"/>
       <c r="AC60" s="2"/>
       <c r="AD60" s="2"/>
-      <c r="AE60" s="2"/>
+      <c r="AE60" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF60" s="2"/>
       <c r="AG60" s="2"/>
       <c r="AH60" s="2"/>
@@ -9825,7 +9890,7 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
@@ -9928,7 +9993,7 @@
       </c>
       <c r="G62" s="2">
         <f t="shared" si="3"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H62" s="6">
         <f>I62+개인기록Sheet!C62</f>
@@ -10033,7 +10098,7 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H63" s="6">
         <f>I63+개인기록Sheet!C63</f>
@@ -10149,7 +10214,7 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H64" s="6">
         <f>I64+개인기록Sheet!C64</f>
@@ -10261,7 +10326,7 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
@@ -10372,15 +10437,15 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="I66" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -10412,7 +10477,9 @@
       <c r="AC66" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD66" s="2"/>
+      <c r="AD66" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE66" s="2"/>
       <c r="AF66" s="2"/>
       <c r="AG66" s="2"/>
@@ -10486,7 +10553,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
@@ -10590,7 +10657,7 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H68" s="6">
         <f>I68+개인기록Sheet!C68</f>
@@ -10694,7 +10761,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" ref="G69:G123" si="14">RANK(H69,$H$4:$H$123,0)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
@@ -10797,15 +10864,15 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="14"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
-        <v>14.8</v>
+        <v>16.2</v>
       </c>
       <c r="I70" s="6">
         <f t="shared" si="15"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -10849,7 +10916,9 @@
       <c r="AC70" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD70" s="2"/>
+      <c r="AD70" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE70" s="2"/>
       <c r="AF70" s="2"/>
       <c r="AG70" s="2"/>
@@ -10923,7 +10992,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="14"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -11034,7 +11103,7 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" si="14"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H72" s="6">
         <f>I72+개인기록Sheet!C72</f>
@@ -11143,7 +11212,7 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" si="14"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H73" s="6">
         <f>I73+개인기록Sheet!C73</f>
@@ -11255,7 +11324,7 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
@@ -11358,7 +11427,7 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="14"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
@@ -11469,7 +11538,7 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="14"/>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
@@ -11581,7 +11650,7 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="14"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
@@ -11691,7 +11760,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
@@ -11795,7 +11864,7 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" si="14"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
@@ -11900,15 +11969,15 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="14"/>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
@@ -11941,7 +12010,9 @@
       <c r="AB80" s="2"/>
       <c r="AC80" s="2"/>
       <c r="AD80" s="2"/>
-      <c r="AE80" s="2"/>
+      <c r="AE80" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF80" s="2"/>
       <c r="AG80" s="2"/>
       <c r="AH80" s="2"/>
@@ -12013,7 +12084,7 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" si="14"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
@@ -12124,15 +12195,15 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="14"/>
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="I82" s="6">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
@@ -12164,8 +12235,12 @@
         <v>352</v>
       </c>
       <c r="AC82" s="2"/>
-      <c r="AD82" s="2"/>
-      <c r="AE82" s="2"/>
+      <c r="AD82" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE82" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF82" s="2"/>
       <c r="AG82" s="2"/>
       <c r="AH82" s="2"/>
@@ -12237,7 +12312,7 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="14"/>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
@@ -12352,7 +12427,7 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
@@ -12467,15 +12542,15 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="14"/>
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="I85" s="6">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
@@ -12505,8 +12580,12 @@
       <c r="AC85" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD85" s="2"/>
-      <c r="AE85" s="2"/>
+      <c r="AD85" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE85" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF85" s="2"/>
       <c r="AG85" s="2"/>
       <c r="AH85" s="2"/>
@@ -12578,7 +12657,7 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" si="14"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
@@ -12688,15 +12767,15 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="14"/>
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="I87" s="6">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
@@ -12727,7 +12806,9 @@
       <c r="AB87" s="2"/>
       <c r="AC87" s="2"/>
       <c r="AD87" s="2"/>
-      <c r="AE87" s="2"/>
+      <c r="AE87" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF87" s="2"/>
       <c r="AG87" s="2"/>
       <c r="AH87" s="2"/>
@@ -12799,7 +12880,7 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" si="14"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
@@ -12904,7 +12985,7 @@
       </c>
       <c r="G89" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H89" s="6">
         <f>I89+개인기록Sheet!C89</f>
@@ -12993,7 +13074,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C90" s="58">
         <v>2026</v>
@@ -13006,7 +13087,7 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
@@ -13110,7 +13191,7 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
@@ -13219,7 +13300,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="14"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
@@ -13329,7 +13410,7 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" si="14"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
@@ -13434,7 +13515,7 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="14"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
@@ -13541,7 +13622,7 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
@@ -13644,15 +13725,15 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" si="14"/>
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
-        <v>6.8000000000000007</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
@@ -13684,8 +13765,12 @@
       <c r="AC96" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD96" s="2"/>
-      <c r="AE96" s="2"/>
+      <c r="AD96" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE96" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF96" s="2"/>
       <c r="AG96" s="2"/>
       <c r="AH96" s="2"/>
@@ -13757,7 +13842,7 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" si="14"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
@@ -13863,7 +13948,7 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H98" s="6">
         <f>I98+개인기록Sheet!C98</f>
@@ -13966,15 +14051,15 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H99" s="6">
         <f>I99+개인기록Sheet!C99</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I99" s="6">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -14007,7 +14092,9 @@
         <v>352</v>
       </c>
       <c r="AD99" s="2"/>
-      <c r="AE99" s="2"/>
+      <c r="AE99" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF99" s="2"/>
       <c r="AG99" s="2"/>
       <c r="AH99" s="2"/>
@@ -14080,7 +14167,7 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="14"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
@@ -14185,7 +14272,7 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="14"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
@@ -14294,15 +14381,15 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="14"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="I102" s="6">
         <f t="shared" si="15"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
@@ -14344,7 +14431,9 @@
       <c r="AC102" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD102" s="2"/>
+      <c r="AD102" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE102" s="2"/>
       <c r="AF102" s="2"/>
       <c r="AG102" s="2"/>
@@ -14417,15 +14506,15 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="14"/>
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="I103" s="6">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
@@ -14455,8 +14544,12 @@
       </c>
       <c r="AB103" s="2"/>
       <c r="AC103" s="2"/>
-      <c r="AD103" s="2"/>
-      <c r="AE103" s="2"/>
+      <c r="AD103" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE103" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF103" s="2"/>
       <c r="AG103" s="2"/>
       <c r="AH103" s="2"/>
@@ -14514,7 +14607,7 @@
         <v>101</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C104" s="58">
         <v>2026</v>
@@ -14526,7 +14619,7 @@
       </c>
       <c r="G104" s="2">
         <f t="shared" si="14"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
@@ -14632,15 +14725,15 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="14"/>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
-        <v>4.9000000000000004</v>
+        <v>6.9</v>
       </c>
       <c r="I105" s="6">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
@@ -14670,8 +14763,12 @@
       <c r="AA105" s="2"/>
       <c r="AB105" s="2"/>
       <c r="AC105" s="2"/>
-      <c r="AD105" s="2"/>
-      <c r="AE105" s="2"/>
+      <c r="AD105" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE105" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF105" s="2"/>
       <c r="AG105" s="2"/>
       <c r="AH105" s="2"/>
@@ -14880,11 +14977,11 @@
       </c>
       <c r="H107" s="6">
         <f>I107+개인기록Sheet!C107</f>
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="I107" s="6">
         <f t="shared" si="15"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>352</v>
@@ -14929,7 +15026,9 @@
       <c r="AB107" s="2"/>
       <c r="AC107" s="2"/>
       <c r="AD107" s="2"/>
-      <c r="AE107" s="2"/>
+      <c r="AE107" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF107" s="2"/>
       <c r="AG107" s="2"/>
       <c r="AH107" s="2"/>
@@ -15001,7 +15100,7 @@
       </c>
       <c r="G108" s="2">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
@@ -15114,15 +15213,15 @@
       </c>
       <c r="G109" s="2">
         <f t="shared" si="14"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="I109" s="6">
         <f t="shared" si="15"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>352</v>
@@ -15158,7 +15257,9 @@
       <c r="AC109" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD109" s="2"/>
+      <c r="AD109" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE109" s="2"/>
       <c r="AF109" s="2"/>
       <c r="AG109" s="2"/>
@@ -15232,7 +15333,7 @@
       </c>
       <c r="G110" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
@@ -15339,11 +15440,11 @@
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="I111" s="6">
         <f t="shared" si="15"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>352</v>
@@ -15380,7 +15481,9 @@
         <v>352</v>
       </c>
       <c r="AD111" s="2"/>
-      <c r="AE111" s="2"/>
+      <c r="AE111" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF111" s="2"/>
       <c r="AG111" s="2"/>
       <c r="AH111" s="2"/>
@@ -15452,15 +15555,15 @@
       </c>
       <c r="G112" s="2">
         <f t="shared" si="14"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="I112" s="6">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>352</v>
@@ -15493,7 +15596,9 @@
       <c r="AB112" s="2"/>
       <c r="AC112" s="2"/>
       <c r="AD112" s="2"/>
-      <c r="AE112" s="2"/>
+      <c r="AE112" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AF112" s="2"/>
       <c r="AG112" s="2"/>
       <c r="AH112" s="2"/>
@@ -15565,7 +15670,7 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="14"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
@@ -15686,7 +15791,7 @@
       </c>
       <c r="G114" s="2">
         <f t="shared" si="14"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
@@ -15795,7 +15900,7 @@
       </c>
       <c r="G115" s="2">
         <f t="shared" si="14"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
@@ -15904,7 +16009,7 @@
       </c>
       <c r="G116" s="2">
         <f t="shared" si="14"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H116" s="6">
         <f>I116+개인기록Sheet!C116</f>
@@ -16003,7 +16108,7 @@
         <v>2026</v>
       </c>
       <c r="D117" s="54" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E117" s="54"/>
       <c r="F117" s="2" t="s">
@@ -16011,7 +16116,7 @@
       </c>
       <c r="G117" s="2">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H117" s="6">
         <f>I117+개인기록Sheet!C117</f>
@@ -16124,15 +16229,15 @@
       </c>
       <c r="G118" s="2">
         <f t="shared" si="14"/>
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I118" s="6">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
@@ -16164,7 +16269,9 @@
       <c r="AC118" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AD118" s="2"/>
+      <c r="AD118" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AE118" s="2"/>
       <c r="AF118" s="2"/>
       <c r="AG118" s="2"/>
@@ -16237,7 +16344,7 @@
       </c>
       <c r="G119" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H119" s="6">
         <f>I119+개인기록Sheet!C119</f>
@@ -16341,7 +16448,7 @@
       </c>
       <c r="G120" s="2">
         <f t="shared" si="14"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H120" s="6">
         <f>I120+개인기록Sheet!C120</f>
@@ -16448,7 +16555,7 @@
       </c>
       <c r="G121" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H121" s="6">
         <f>I121+개인기록Sheet!C121</f>
@@ -16552,7 +16659,7 @@
       </c>
       <c r="G122" s="2">
         <f t="shared" si="14"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H122" s="6">
         <f>I122+개인기록Sheet!C122</f>
@@ -16655,7 +16762,7 @@
       </c>
       <c r="G123" s="2">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H123" s="6">
         <f>I123+개인기록Sheet!C123</f>
@@ -16773,7 +16880,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:V168"/>
+  <dimension ref="A2:V192"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -18620,7 +18727,7 @@
         <v>378</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E63" s="77" t="s">
         <v>82</v>
@@ -19046,7 +19153,7 @@
         <v>378</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E77" s="77" t="s">
         <v>82</v>
@@ -19369,10 +19476,10 @@
         <v>46149</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E89" s="77" t="s">
         <v>82</v>
@@ -19734,7 +19841,7 @@
         <v>358</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E101" s="77" t="s">
         <v>82</v>
@@ -19959,7 +20066,7 @@
       </c>
       <c r="U106" s="9"/>
       <c r="V106" s="13" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.25">
@@ -20093,10 +20200,10 @@
         <v>46156</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E113" s="77" t="s">
         <v>82</v>
@@ -20169,7 +20276,7 @@
       </c>
       <c r="U114" s="9"/>
       <c r="V114" s="13" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
@@ -20206,7 +20313,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
@@ -20239,7 +20346,7 @@
       </c>
       <c r="U116" s="9"/>
       <c r="V116" s="13" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="117" spans="2:22" x14ac:dyDescent="0.25">
@@ -20432,7 +20539,7 @@
         <v>378</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E125" s="77" t="s">
         <v>82</v>
@@ -20716,7 +20823,7 @@
         <v>378</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E135" s="77" t="s">
         <v>82</v>
@@ -21046,7 +21153,7 @@
         <v>358</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E147" s="77" t="s">
         <v>82</v>
@@ -21397,10 +21504,10 @@
         <v>46191</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E159" s="77" t="s">
         <v>82</v>
@@ -21730,8 +21837,628 @@
       <c r="U168" s="2"/>
       <c r="V168" s="2"/>
     </row>
+    <row r="171" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B171" s="11">
+        <v>46198</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="E171" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="F171" s="77"/>
+      <c r="G171" s="77"/>
+      <c r="H171" s="77"/>
+      <c r="I171" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="J171" s="78"/>
+      <c r="K171" s="78"/>
+      <c r="L171" s="78"/>
+      <c r="M171" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="N171" s="79"/>
+      <c r="O171" s="79"/>
+      <c r="P171" s="79"/>
+      <c r="Q171" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="R171" s="80"/>
+      <c r="S171" s="80"/>
+      <c r="T171" s="80"/>
+      <c r="U171" s="80"/>
+      <c r="V171" s="80"/>
+    </row>
+    <row r="172" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B172" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C172" s="75">
+        <v>1</v>
+      </c>
+      <c r="D172" s="75">
+        <v>0</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F172" s="7"/>
+      <c r="G172" s="7"/>
+      <c r="H172" s="7"/>
+      <c r="I172" s="8"/>
+      <c r="J172" s="8"/>
+      <c r="K172" s="8"/>
+      <c r="L172" s="8"/>
+      <c r="M172" s="20"/>
+      <c r="N172" s="20"/>
+      <c r="O172" s="20"/>
+      <c r="P172" s="20"/>
+      <c r="Q172" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="R172" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="S172" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="T172" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="U172" s="9"/>
+      <c r="V172" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="173" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B173" s="74"/>
+      <c r="C173" s="76"/>
+      <c r="D173" s="76"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
+      <c r="I173" s="8"/>
+      <c r="J173" s="8"/>
+      <c r="K173" s="8"/>
+      <c r="L173" s="8"/>
+      <c r="M173" s="20"/>
+      <c r="N173" s="20"/>
+      <c r="O173" s="20"/>
+      <c r="P173" s="20"/>
+      <c r="Q173" s="9"/>
+      <c r="R173" s="9"/>
+      <c r="S173" s="9"/>
+      <c r="T173" s="9"/>
+      <c r="U173" s="9"/>
+      <c r="V173" s="13"/>
+    </row>
+    <row r="174" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B174" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C174" s="75">
+        <v>0</v>
+      </c>
+      <c r="D174" s="75">
+        <v>1</v>
+      </c>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
+      <c r="I174" s="8"/>
+      <c r="J174" s="8"/>
+      <c r="K174" s="8"/>
+      <c r="L174" s="8"/>
+      <c r="M174" s="20"/>
+      <c r="N174" s="20"/>
+      <c r="O174" s="20"/>
+      <c r="P174" s="20"/>
+      <c r="Q174" s="9"/>
+      <c r="R174" s="9"/>
+      <c r="S174" s="9"/>
+      <c r="T174" s="9"/>
+      <c r="U174" s="9"/>
+      <c r="V174" s="13"/>
+    </row>
+    <row r="175" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B175" s="74"/>
+      <c r="C175" s="76"/>
+      <c r="D175" s="76"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
+      <c r="I175" s="8"/>
+      <c r="J175" s="8"/>
+      <c r="K175" s="8"/>
+      <c r="L175" s="8"/>
+      <c r="M175" s="20"/>
+      <c r="N175" s="20"/>
+      <c r="O175" s="20"/>
+      <c r="P175" s="20"/>
+      <c r="Q175" s="9"/>
+      <c r="R175" s="9"/>
+      <c r="S175" s="9"/>
+      <c r="T175" s="9"/>
+      <c r="U175" s="9"/>
+      <c r="V175" s="13"/>
+    </row>
+    <row r="176" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B176" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C176" s="75">
+        <v>1</v>
+      </c>
+      <c r="D176" s="75">
+        <v>0</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F176" s="7"/>
+      <c r="G176" s="7"/>
+      <c r="H176" s="7"/>
+      <c r="I176" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="J176" s="8"/>
+      <c r="K176" s="8"/>
+      <c r="L176" s="8"/>
+      <c r="M176" s="20"/>
+      <c r="N176" s="20"/>
+      <c r="O176" s="20"/>
+      <c r="P176" s="20"/>
+      <c r="Q176" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="R176" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="S176" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="T176" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="U176" s="9"/>
+      <c r="V176" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="177" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B177" s="74"/>
+      <c r="C177" s="76"/>
+      <c r="D177" s="76"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="7"/>
+      <c r="H177" s="7"/>
+      <c r="I177" s="8"/>
+      <c r="J177" s="8"/>
+      <c r="K177" s="8"/>
+      <c r="L177" s="8"/>
+      <c r="M177" s="20"/>
+      <c r="N177" s="20"/>
+      <c r="O177" s="20"/>
+      <c r="P177" s="20"/>
+      <c r="Q177" s="9"/>
+      <c r="R177" s="9"/>
+      <c r="S177" s="9"/>
+      <c r="T177" s="9"/>
+      <c r="U177" s="9"/>
+      <c r="V177" s="13"/>
+    </row>
+    <row r="178" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B178" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C178" s="75">
+        <v>1</v>
+      </c>
+      <c r="D178" s="75">
+        <v>1</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="7"/>
+      <c r="I178" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J178" s="8"/>
+      <c r="K178" s="8"/>
+      <c r="L178" s="8"/>
+      <c r="M178" s="20"/>
+      <c r="N178" s="20"/>
+      <c r="O178" s="20"/>
+      <c r="P178" s="20"/>
+      <c r="Q178" s="9"/>
+      <c r="R178" s="9"/>
+      <c r="S178" s="9"/>
+      <c r="T178" s="9"/>
+      <c r="U178" s="9"/>
+      <c r="V178" s="13"/>
+    </row>
+    <row r="179" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B179" s="74"/>
+      <c r="C179" s="76"/>
+      <c r="D179" s="76"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
+      <c r="G179" s="7"/>
+      <c r="H179" s="7"/>
+      <c r="I179" s="8"/>
+      <c r="J179" s="8"/>
+      <c r="K179" s="8"/>
+      <c r="L179" s="8"/>
+      <c r="M179" s="20"/>
+      <c r="N179" s="20"/>
+      <c r="O179" s="20"/>
+      <c r="P179" s="20"/>
+      <c r="Q179" s="9"/>
+      <c r="R179" s="9"/>
+      <c r="S179" s="9"/>
+      <c r="T179" s="9"/>
+      <c r="U179" s="9"/>
+      <c r="V179" s="13"/>
+    </row>
+    <row r="180" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B180" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C180" s="2">
+        <f>SUM(C172:C179)</f>
+        <v>3</v>
+      </c>
+      <c r="D180" s="2">
+        <f>SUM(D172:D179)</f>
+        <v>2</v>
+      </c>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+      <c r="I180" s="2"/>
+      <c r="J180" s="2"/>
+      <c r="K180" s="2"/>
+      <c r="L180" s="2"/>
+      <c r="M180" s="2"/>
+      <c r="N180" s="2"/>
+      <c r="O180" s="2"/>
+      <c r="P180" s="2"/>
+      <c r="Q180" s="2"/>
+      <c r="R180" s="2"/>
+      <c r="S180" s="2"/>
+      <c r="T180" s="2"/>
+      <c r="U180" s="2"/>
+      <c r="V180" s="2"/>
+    </row>
+    <row r="183" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B183" s="11">
+        <v>46202</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="E183" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="F183" s="77"/>
+      <c r="G183" s="77"/>
+      <c r="H183" s="77"/>
+      <c r="I183" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="J183" s="78"/>
+      <c r="K183" s="78"/>
+      <c r="L183" s="78"/>
+      <c r="M183" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="N183" s="79"/>
+      <c r="O183" s="79"/>
+      <c r="P183" s="79"/>
+      <c r="Q183" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="R183" s="80"/>
+      <c r="S183" s="80"/>
+      <c r="T183" s="80"/>
+      <c r="U183" s="80"/>
+      <c r="V183" s="80"/>
+    </row>
+    <row r="184" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B184" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C184" s="75">
+        <v>0</v>
+      </c>
+      <c r="D184" s="75">
+        <v>2</v>
+      </c>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="7"/>
+      <c r="H184" s="7"/>
+      <c r="I184" s="8"/>
+      <c r="J184" s="8"/>
+      <c r="K184" s="8"/>
+      <c r="L184" s="8"/>
+      <c r="M184" s="20"/>
+      <c r="N184" s="20"/>
+      <c r="O184" s="20"/>
+      <c r="P184" s="20"/>
+      <c r="Q184" s="9"/>
+      <c r="R184" s="9"/>
+      <c r="S184" s="9"/>
+      <c r="T184" s="9"/>
+      <c r="U184" s="9"/>
+      <c r="V184" s="13"/>
+    </row>
+    <row r="185" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B185" s="74"/>
+      <c r="C185" s="76"/>
+      <c r="D185" s="76"/>
+      <c r="E185" s="7"/>
+      <c r="F185" s="7"/>
+      <c r="G185" s="7"/>
+      <c r="H185" s="7"/>
+      <c r="I185" s="8"/>
+      <c r="J185" s="8"/>
+      <c r="K185" s="8"/>
+      <c r="L185" s="8"/>
+      <c r="M185" s="20"/>
+      <c r="N185" s="20"/>
+      <c r="O185" s="20"/>
+      <c r="P185" s="20"/>
+      <c r="Q185" s="9"/>
+      <c r="R185" s="9"/>
+      <c r="S185" s="9"/>
+      <c r="T185" s="9"/>
+      <c r="U185" s="9"/>
+      <c r="V185" s="13"/>
+    </row>
+    <row r="186" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B186" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C186" s="75">
+        <v>4</v>
+      </c>
+      <c r="D186" s="75">
+        <v>2</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G186" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H186" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I186" s="8"/>
+      <c r="J186" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="K186" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="L186" s="8"/>
+      <c r="M186" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="N186" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="O186" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="P186" s="20"/>
+      <c r="Q186" s="9"/>
+      <c r="R186" s="9"/>
+      <c r="S186" s="9"/>
+      <c r="T186" s="9"/>
+      <c r="U186" s="9"/>
+      <c r="V186" s="13"/>
+    </row>
+    <row r="187" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B187" s="74"/>
+      <c r="C187" s="76"/>
+      <c r="D187" s="76"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
+      <c r="I187" s="8"/>
+      <c r="J187" s="8"/>
+      <c r="K187" s="8"/>
+      <c r="L187" s="8"/>
+      <c r="M187" s="20"/>
+      <c r="N187" s="20"/>
+      <c r="O187" s="20"/>
+      <c r="P187" s="20"/>
+      <c r="Q187" s="9"/>
+      <c r="R187" s="9"/>
+      <c r="S187" s="9"/>
+      <c r="T187" s="9"/>
+      <c r="U187" s="9"/>
+      <c r="V187" s="13"/>
+    </row>
+    <row r="188" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B188" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C188" s="75">
+        <v>0</v>
+      </c>
+      <c r="D188" s="75">
+        <v>4</v>
+      </c>
+      <c r="E188" s="7"/>
+      <c r="F188" s="7"/>
+      <c r="G188" s="7"/>
+      <c r="H188" s="7"/>
+      <c r="I188" s="8"/>
+      <c r="J188" s="8"/>
+      <c r="K188" s="8"/>
+      <c r="L188" s="8"/>
+      <c r="M188" s="20"/>
+      <c r="N188" s="20"/>
+      <c r="O188" s="20"/>
+      <c r="P188" s="20"/>
+      <c r="Q188" s="9"/>
+      <c r="R188" s="9"/>
+      <c r="S188" s="9"/>
+      <c r="T188" s="9"/>
+      <c r="U188" s="9"/>
+      <c r="V188" s="13"/>
+    </row>
+    <row r="189" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B189" s="74"/>
+      <c r="C189" s="76"/>
+      <c r="D189" s="76"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
+      <c r="I189" s="8"/>
+      <c r="J189" s="8"/>
+      <c r="K189" s="8"/>
+      <c r="L189" s="8"/>
+      <c r="M189" s="20"/>
+      <c r="N189" s="20"/>
+      <c r="O189" s="20"/>
+      <c r="P189" s="20"/>
+      <c r="Q189" s="9"/>
+      <c r="R189" s="9"/>
+      <c r="S189" s="9"/>
+      <c r="T189" s="9"/>
+      <c r="U189" s="9"/>
+      <c r="V189" s="13"/>
+    </row>
+    <row r="190" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B190" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C190" s="75">
+        <v>1</v>
+      </c>
+      <c r="D190" s="75">
+        <v>2</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F190" s="7"/>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+      <c r="I190" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="J190" s="8"/>
+      <c r="K190" s="8"/>
+      <c r="L190" s="8"/>
+      <c r="M190" s="20"/>
+      <c r="N190" s="20"/>
+      <c r="O190" s="20"/>
+      <c r="P190" s="20"/>
+      <c r="Q190" s="9"/>
+      <c r="R190" s="9"/>
+      <c r="S190" s="9"/>
+      <c r="T190" s="9"/>
+      <c r="U190" s="9"/>
+      <c r="V190" s="13"/>
+    </row>
+    <row r="191" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B191" s="74"/>
+      <c r="C191" s="76"/>
+      <c r="D191" s="76"/>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="7"/>
+      <c r="H191" s="7"/>
+      <c r="I191" s="8"/>
+      <c r="J191" s="8"/>
+      <c r="K191" s="8"/>
+      <c r="L191" s="8"/>
+      <c r="M191" s="20"/>
+      <c r="N191" s="20"/>
+      <c r="O191" s="20"/>
+      <c r="P191" s="20"/>
+      <c r="Q191" s="9"/>
+      <c r="R191" s="9"/>
+      <c r="S191" s="9"/>
+      <c r="T191" s="9"/>
+      <c r="U191" s="9"/>
+      <c r="V191" s="13"/>
+    </row>
+    <row r="192" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B192" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C192" s="2">
+        <f>SUM(C184:C191)</f>
+        <v>5</v>
+      </c>
+      <c r="D192" s="2">
+        <f>SUM(D184:D191)</f>
+        <v>10</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+      <c r="I192" s="2"/>
+      <c r="J192" s="2"/>
+      <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
+      <c r="M192" s="2"/>
+      <c r="N192" s="2"/>
+      <c r="O192" s="2"/>
+      <c r="P192" s="2"/>
+      <c r="Q192" s="2"/>
+      <c r="R192" s="2"/>
+      <c r="S192" s="2"/>
+      <c r="T192" s="2"/>
+      <c r="U192" s="2"/>
+      <c r="V192" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="230">
+  <mergeCells count="262">
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="D188:D189"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
+    <mergeCell ref="E183:H183"/>
+    <mergeCell ref="I183:L183"/>
+    <mergeCell ref="M183:P183"/>
+    <mergeCell ref="Q183:V183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
     <mergeCell ref="B154:B155"/>
     <mergeCell ref="C154:C155"/>
     <mergeCell ref="D154:D155"/>
@@ -21741,9 +22468,6 @@
     <mergeCell ref="B150:B151"/>
     <mergeCell ref="C150:C151"/>
     <mergeCell ref="D150:D151"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
     <mergeCell ref="B152:B153"/>
     <mergeCell ref="C152:C153"/>
     <mergeCell ref="D152:D153"/>
@@ -21767,7 +22491,9 @@
     <mergeCell ref="B136:B137"/>
     <mergeCell ref="C136:C137"/>
     <mergeCell ref="D136:D137"/>
-    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
     <mergeCell ref="B102:B103"/>
     <mergeCell ref="C102:C103"/>
     <mergeCell ref="D102:D103"/>
@@ -21778,7 +22504,14 @@
     <mergeCell ref="B130:B131"/>
     <mergeCell ref="C130:C131"/>
     <mergeCell ref="D130:D131"/>
-    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
     <mergeCell ref="C94:C95"/>
     <mergeCell ref="D94:D95"/>
     <mergeCell ref="B96:B97"/>
@@ -21787,7 +22520,17 @@
     <mergeCell ref="E101:H101"/>
     <mergeCell ref="I101:L101"/>
     <mergeCell ref="M101:P101"/>
-    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
     <mergeCell ref="B82:B83"/>
     <mergeCell ref="C82:C83"/>
     <mergeCell ref="D82:D83"/>
@@ -21796,25 +22539,6 @@
     <mergeCell ref="D84:D85"/>
     <mergeCell ref="E89:H89"/>
     <mergeCell ref="I89:L89"/>
-    <mergeCell ref="M89:P89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="M77:P77"/>
-    <mergeCell ref="Q77:V77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="M13:P13"/>
@@ -21828,8 +22552,13 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
     <mergeCell ref="M2:P2"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
@@ -21845,19 +22574,20 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="D18:D19"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="D29:D30"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
     <mergeCell ref="Q37:V37"/>
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="C38:C39"/>
@@ -21865,21 +22595,6 @@
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="C33:C34"/>
     <mergeCell ref="D33:D34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
     <mergeCell ref="Q49:V49"/>
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="C50:C51"/>
@@ -21887,18 +22602,21 @@
     <mergeCell ref="B44:B45"/>
     <mergeCell ref="C44:C45"/>
     <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
     <mergeCell ref="Q63:V63"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="C64:C65"/>
@@ -21906,36 +22624,42 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
     <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="Q125:V125"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
     <mergeCell ref="B70:B71"/>
     <mergeCell ref="C70:C71"/>
     <mergeCell ref="D70:D71"/>
     <mergeCell ref="B72:B73"/>
     <mergeCell ref="C72:C73"/>
     <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="M113:P113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="Q159:V159"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="D160:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="Q77:V77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B94:B95"/>
     <mergeCell ref="Q113:V113"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="C114:C115"/>
@@ -21946,22 +22670,41 @@
     <mergeCell ref="B118:B119"/>
     <mergeCell ref="C118:C119"/>
     <mergeCell ref="D118:D119"/>
-    <mergeCell ref="Q125:V125"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="E159:H159"/>
+    <mergeCell ref="I159:L159"/>
+    <mergeCell ref="M159:P159"/>
+    <mergeCell ref="Q159:V159"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="Q171:V171"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
     <mergeCell ref="B164:B165"/>
     <mergeCell ref="C164:C165"/>
     <mergeCell ref="D164:D165"/>
     <mergeCell ref="B166:B167"/>
     <mergeCell ref="C166:C167"/>
     <mergeCell ref="D166:D167"/>
-    <mergeCell ref="E159:H159"/>
-    <mergeCell ref="I159:L159"/>
-    <mergeCell ref="M159:P159"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="D176:D177"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="D178:D179"/>
+    <mergeCell ref="E171:H171"/>
+    <mergeCell ref="I171:L171"/>
+    <mergeCell ref="M171:P171"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -22003,23 +22746,23 @@
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -22097,7 +22840,7 @@
         <v>김인혁</v>
       </c>
       <c r="C4" s="2">
-        <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
+        <f t="shared" ref="C4:C35" si="0">((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
         <v>1.6</v>
       </c>
       <c r="D4" s="14">
@@ -22121,7 +22864,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="14">
-        <f>SUM(D4:H4)</f>
+        <f t="shared" ref="I4:I35" si="1">SUM(D4:H4)</f>
         <v>8</v>
       </c>
       <c r="J4" s="15"/>
@@ -22132,35 +22875,35 @@
         <v>354</v>
       </c>
       <c r="M4" s="21">
-        <f t="shared" ref="M4:M15" si="0">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
+        <f t="shared" ref="M4:M15" si="2">VLOOKUP(L4,$B$4:$H$141,3,FALSE)</f>
         <v>20</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>354</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O18" si="1">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
+        <f t="shared" ref="O4:O18" si="3">VLOOKUP(N4,$B$4:$H$141,4,FALSE)</f>
         <v>8</v>
       </c>
       <c r="P4" s="34" t="s">
         <v>222</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q14" si="2">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
+        <f t="shared" ref="Q4:Q14" si="4">VLOOKUP(P4,$B$4:$H$141,5,FALSE)</f>
         <v>12</v>
       </c>
       <c r="R4" s="35" t="s">
-        <v>231</v>
+        <v>407</v>
       </c>
       <c r="S4" s="55">
-        <f t="shared" ref="S4:S18" si="3">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
-        <v>18</v>
+        <f t="shared" ref="S4:S18" si="5">VLOOKUP(R4,$B$4:$H$141,6,FALSE)</f>
+        <v>19</v>
       </c>
       <c r="T4" s="36" t="s">
         <v>229</v>
       </c>
       <c r="U4" s="56">
-        <f t="shared" ref="U4:U7" si="4">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
+        <f t="shared" ref="U4:U7" si="6">VLOOKUP(T4,$B$4:$H$141,7,FALSE)</f>
         <v>9</v>
       </c>
     </row>
@@ -22174,7 +22917,7 @@
         <v>신재경</v>
       </c>
       <c r="C5" s="2">
-        <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
       <c r="D5" s="14">
@@ -22198,7 +22941,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="14">
-        <f>SUM(D5:H5)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J5" s="15"/>
@@ -22209,35 +22952,35 @@
         <v>224</v>
       </c>
       <c r="M5" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="N5" s="33" t="s">
         <v>360</v>
       </c>
       <c r="O5" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="P5" s="34" t="s">
         <v>305</v>
       </c>
       <c r="Q5" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="R5" s="35" t="s">
-        <v>325</v>
+        <v>408</v>
       </c>
       <c r="S5" s="55">
-        <f t="shared" si="3"/>
-        <v>17</v>
+        <f t="shared" si="5"/>
+        <v>18</v>
       </c>
       <c r="T5" s="36" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="U5" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
     </row>
@@ -22251,7 +22994,7 @@
         <v>정효태</v>
       </c>
       <c r="C6" s="2">
-        <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D6" s="14">
@@ -22275,7 +23018,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="14">
-        <f>SUM(D6:H6)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J6" s="15"/>
@@ -22286,36 +23029,36 @@
         <v>222</v>
       </c>
       <c r="M6" s="21">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
       <c r="N6" s="33" t="s">
         <v>53</v>
       </c>
       <c r="O6" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="P6" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Q6" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="R6" s="35" t="s">
-        <v>357</v>
+        <v>409</v>
       </c>
       <c r="S6" s="55">
-        <f t="shared" si="3"/>
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="T6" s="36" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="U6" s="56">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -22328,7 +23071,7 @@
         <v>이승민</v>
       </c>
       <c r="C7" s="2">
-        <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7" s="14">
@@ -22352,7 +23095,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f>SUM(D7:H7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J7" s="15"/>
@@ -22363,35 +23106,35 @@
         <v>360</v>
       </c>
       <c r="M7" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="N7" s="33" t="s">
         <v>50</v>
       </c>
       <c r="O7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P7" s="34" t="s">
         <v>299</v>
       </c>
       <c r="Q7" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="R7" s="35" t="s">
-        <v>363</v>
+        <v>410</v>
       </c>
       <c r="S7" s="55">
-        <f t="shared" si="3"/>
-        <v>10</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="T7" s="36" t="s">
         <v>357</v>
       </c>
       <c r="U7" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -22405,7 +23148,7 @@
         <v>이정석</v>
       </c>
       <c r="C8" s="2">
-        <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D8" s="14">
@@ -22429,7 +23172,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f>SUM(D8:H8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="15"/>
@@ -22440,29 +23183,29 @@
         <v>305</v>
       </c>
       <c r="M8" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>222</v>
       </c>
       <c r="O8" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P8" s="34" t="s">
         <v>379</v>
       </c>
       <c r="Q8" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="R8" s="35" t="s">
         <v>233</v>
       </c>
       <c r="S8" s="55">
-        <f t="shared" si="3"/>
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
       <c r="T8" s="36"/>
       <c r="U8" s="56"/>
@@ -22477,7 +23220,7 @@
         <v>강종찬</v>
       </c>
       <c r="C9" s="2">
-        <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D9" s="14">
@@ -22501,7 +23244,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="14">
-        <f>SUM(D9:H9)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J9" s="15"/>
@@ -22509,31 +23252,31 @@
         <v>6</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="M9" s="21">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>224</v>
       </c>
       <c r="O9" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P9" s="34" t="s">
         <v>53</v>
       </c>
       <c r="Q9" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R9" s="35" t="s">
         <v>242</v>
       </c>
       <c r="S9" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="T9" s="36"/>
@@ -22549,8 +23292,8 @@
         <v>강관석</v>
       </c>
       <c r="C10" s="2">
-        <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
-        <v>3.1</v>
+        <f t="shared" si="0"/>
+        <v>3.3000000000000003</v>
       </c>
       <c r="D10" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B10)</f>
@@ -22570,42 +23313,42 @@
       </c>
       <c r="H10" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="14">
-        <f>SUM(D10:H10)</f>
-        <v>12</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="2">
         <v>7</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>232</v>
+        <v>413</v>
       </c>
       <c r="M10" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N10" s="33" t="s">
         <v>225</v>
       </c>
       <c r="O10" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P10" s="34" t="s">
         <v>385</v>
       </c>
       <c r="Q10" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R10" s="35" t="s">
         <v>303</v>
       </c>
       <c r="S10" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="T10" s="36"/>
@@ -22621,7 +23364,7 @@
         <v>강기혁</v>
       </c>
       <c r="C11" s="2">
-        <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
       <c r="D11" s="14">
@@ -22645,7 +23388,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f>SUM(D11:H11)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="J11" s="15"/>
@@ -22653,31 +23396,31 @@
         <v>8</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M11" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N11" s="33" t="s">
         <v>363</v>
       </c>
       <c r="O11" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q11" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R11" s="35" t="s">
         <v>62</v>
       </c>
       <c r="S11" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="T11" s="36"/>
@@ -22693,7 +23436,7 @@
         <v>강도일</v>
       </c>
       <c r="C12" s="2">
-        <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D12" s="14">
@@ -22717,7 +23460,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="14">
-        <f>SUM(D12:H12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J12" s="15"/>
@@ -22728,28 +23471,28 @@
         <v>50</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>14</v>
+        <v>405</v>
       </c>
       <c r="O12" s="22">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="P12" s="34" t="s">
         <v>7</v>
       </c>
       <c r="Q12" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="R12" s="35" t="s">
         <v>222</v>
       </c>
       <c r="S12" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T12" s="36"/>
@@ -22765,7 +23508,7 @@
         <v>강일수</v>
       </c>
       <c r="C13" s="2">
-        <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D13" s="14">
@@ -22789,7 +23532,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f>SUM(D13:H13)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -22800,28 +23543,28 @@
         <v>299</v>
       </c>
       <c r="M13" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>356</v>
+        <v>14</v>
       </c>
       <c r="O13" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P13" s="34" t="s">
         <v>224</v>
       </c>
       <c r="Q13" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R13" s="35" t="s">
         <v>75</v>
       </c>
       <c r="S13" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T13" s="36"/>
@@ -22837,7 +23580,7 @@
         <v>구교훈</v>
       </c>
       <c r="C14" s="2">
-        <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D14" s="14">
@@ -22861,7 +23604,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f>SUM(D14:H14)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="15"/>
@@ -22872,28 +23615,28 @@
         <v>356</v>
       </c>
       <c r="M14" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>402</v>
+        <v>356</v>
       </c>
       <c r="O14" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P14" s="34" t="s">
         <v>314</v>
       </c>
       <c r="Q14" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R14" s="55" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="S14" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T14" s="36"/>
@@ -22909,7 +23652,7 @@
         <v>권주용</v>
       </c>
       <c r="C15" s="2">
-        <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D15" s="14">
@@ -22933,7 +23676,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f>SUM(D15:H15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J15" s="15"/>
@@ -22941,17 +23684,17 @@
         <v>12</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M15" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="N15" s="22" t="s">
-        <v>221</v>
+      <c r="N15" s="33" t="s">
+        <v>399</v>
       </c>
       <c r="O15" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P15" s="23"/>
@@ -22960,7 +23703,7 @@
         <v>67</v>
       </c>
       <c r="S15" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T15" s="56"/>
@@ -22976,7 +23719,7 @@
         <v>김기문</v>
       </c>
       <c r="C16" s="2">
-        <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
       <c r="D16" s="14">
@@ -23000,7 +23743,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="14">
-        <f>SUM(D16:H16)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J16" s="15"/>
@@ -23010,19 +23753,19 @@
       <c r="L16" s="21"/>
       <c r="M16" s="21"/>
       <c r="N16" s="22" t="s">
-        <v>314</v>
+        <v>221</v>
       </c>
       <c r="O16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P16" s="23"/>
       <c r="Q16" s="23"/>
       <c r="R16" s="55" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="S16" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T16" s="56"/>
@@ -23038,7 +23781,7 @@
         <v>김기태</v>
       </c>
       <c r="C17" s="2">
-        <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D17" s="14">
@@ -23062,7 +23805,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="14">
-        <f>SUM(D17:H17)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="J17" s="15"/>
@@ -23072,10 +23815,10 @@
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
       <c r="N17" s="22" t="s">
-        <v>75</v>
+        <v>406</v>
       </c>
       <c r="O17" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P17" s="23"/>
@@ -23084,7 +23827,7 @@
         <v>364</v>
       </c>
       <c r="S17" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T17" s="56"/>
@@ -23100,7 +23843,7 @@
         <v>김덕준</v>
       </c>
       <c r="C18" s="2">
-        <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D18" s="14">
@@ -23124,7 +23867,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f>SUM(D18:H18)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="15"/>
@@ -23134,10 +23877,10 @@
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
       <c r="N18" s="22" t="s">
-        <v>394</v>
+        <v>75</v>
       </c>
       <c r="O18" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P18" s="23"/>
@@ -23146,7 +23889,7 @@
         <v>34</v>
       </c>
       <c r="S18" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T18" s="56"/>
@@ -23162,7 +23905,7 @@
         <v>김동인</v>
       </c>
       <c r="C19" s="2">
-        <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D19" s="14">
@@ -23186,13 +23929,10 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f>SUM(D19:H19)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
-      <c r="N19" s="1" t="s">
-        <v>386</v>
-      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -23204,7 +23944,7 @@
         <v>김민섭</v>
       </c>
       <c r="C20" s="2">
-        <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="D20" s="14">
@@ -23228,13 +23968,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f>SUM(D20:H20)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J20" s="15"/>
-      <c r="N20" s="1" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -23246,7 +23983,7 @@
         <v>김민준</v>
       </c>
       <c r="C21" s="2">
-        <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D21" s="14">
@@ -23270,13 +24007,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="14">
-        <f>SUM(D21:H21)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21" s="15"/>
-      <c r="N21" s="1" t="s">
-        <v>389</v>
-      </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -23288,7 +24022,7 @@
         <v>김민찬</v>
       </c>
       <c r="C22" s="2">
-        <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D22" s="14">
@@ -23312,7 +24046,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f>SUM(D22:H22)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J22" s="15"/>
@@ -23327,7 +24061,7 @@
         <v>김범기</v>
       </c>
       <c r="C23" s="2">
-        <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D23" s="14">
@@ -23351,7 +24085,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f>SUM(D23:H23)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="15"/>
@@ -23366,7 +24100,7 @@
         <v>김병준</v>
       </c>
       <c r="C24" s="2">
-        <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D24" s="14">
@@ -23390,7 +24124,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f>SUM(D24:H24)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="15"/>
@@ -23405,7 +24139,7 @@
         <v>김부건</v>
       </c>
       <c r="C25" s="2">
-        <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="D25" s="14">
@@ -23429,7 +24163,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f>SUM(D25:H25)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="J25" s="15"/>
@@ -23444,7 +24178,7 @@
         <v>김성수</v>
       </c>
       <c r="C26" s="2">
-        <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="D26" s="14">
@@ -23468,7 +24202,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="14">
-        <f>SUM(D26:H26)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J26" s="15"/>
@@ -23483,12 +24217,12 @@
         <v>김성준</v>
       </c>
       <c r="C27" s="2">
-        <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
-        <v>7.6</v>
+        <f t="shared" si="0"/>
+        <v>7.8</v>
       </c>
       <c r="D27" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B27)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B27)</f>
@@ -23507,8 +24241,8 @@
         <v>1</v>
       </c>
       <c r="I27" s="14">
-        <f>SUM(D27:H27)</f>
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>33</v>
       </c>
       <c r="J27" s="15"/>
     </row>
@@ -23522,7 +24256,7 @@
         <v>김송환</v>
       </c>
       <c r="C28" s="2">
-        <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.6</v>
       </c>
       <c r="D28" s="14">
@@ -23546,7 +24280,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="14">
-        <f>SUM(D28:H28)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="J28" s="15"/>
@@ -23561,7 +24295,7 @@
         <v>김영태</v>
       </c>
       <c r="C29" s="2">
-        <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D29" s="14">
@@ -23585,7 +24319,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <f>SUM(D29:H29)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J29" s="15"/>
@@ -23600,7 +24334,7 @@
         <v>김용빈</v>
       </c>
       <c r="C30" s="2">
-        <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D30" s="14">
@@ -23624,7 +24358,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <f>SUM(D30:H30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J30" s="15"/>
@@ -23639,7 +24373,7 @@
         <v>김용현</v>
       </c>
       <c r="C31" s="2">
-        <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.9000000000000004</v>
       </c>
       <c r="D31" s="14">
@@ -23663,7 +24397,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <f>SUM(D31:H31)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="J31" s="15"/>
@@ -23678,8 +24412,8 @@
         <v>김우인</v>
       </c>
       <c r="C32" s="2">
-        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
-        <v>2.6</v>
+        <f t="shared" si="0"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D32" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B32)</f>
@@ -23687,7 +24421,7 @@
       </c>
       <c r="E32" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B32)</f>
@@ -23702,8 +24436,8 @@
         <v>9</v>
       </c>
       <c r="I32" s="14">
-        <f>SUM(D32:H32)</f>
-        <v>13</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="J32" s="15"/>
     </row>
@@ -23717,7 +24451,7 @@
         <v>김종준</v>
       </c>
       <c r="C33" s="2">
-        <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="D33" s="14">
@@ -23741,7 +24475,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="14">
-        <f>SUM(D33:H33)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J33" s="15"/>
@@ -23756,7 +24490,7 @@
         <v>김종혁</v>
       </c>
       <c r="C34" s="2">
-        <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D34" s="14">
@@ -23780,7 +24514,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="14">
-        <f>SUM(D34:H34)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J34" s="15"/>
@@ -23795,7 +24529,7 @@
         <v>김준영</v>
       </c>
       <c r="C35" s="2">
-        <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D35" s="14">
@@ -23819,7 +24553,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="14">
-        <f>SUM(D35:H35)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J35" s="15"/>
@@ -23834,7 +24568,7 @@
         <v>김진형</v>
       </c>
       <c r="C36" s="2">
-        <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
         <v>0</v>
       </c>
       <c r="D36" s="14">
@@ -23858,7 +24592,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="14">
-        <f>SUM(D36:H36)</f>
+        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
         <v>0</v>
       </c>
       <c r="J36" s="15"/>
@@ -23873,7 +24607,7 @@
         <v>김진호</v>
       </c>
       <c r="C37" s="2">
-        <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
+        <f t="shared" si="7"/>
         <v>5.6000000000000005</v>
       </c>
       <c r="D37" s="14">
@@ -23897,7 +24631,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="14">
-        <f>SUM(D37:H37)</f>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="J37" s="15"/>
@@ -23912,7 +24646,7 @@
         <v>김태성</v>
       </c>
       <c r="C38" s="2">
-        <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D38" s="14">
@@ -23936,7 +24670,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="14">
-        <f>SUM(D38:H38)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J38" s="15"/>
@@ -23951,7 +24685,7 @@
         <v>김태양</v>
       </c>
       <c r="C39" s="2">
-        <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D39" s="14">
@@ -23975,7 +24709,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="14">
-        <f>SUM(D39:H39)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J39" s="15"/>
@@ -23990,7 +24724,7 @@
         <v>김태완</v>
       </c>
       <c r="C40" s="2">
-        <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D40" s="14">
@@ -24014,7 +24748,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="14">
-        <f>SUM(D40:H40)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J40" s="15"/>
@@ -24029,7 +24763,7 @@
         <v>김태호</v>
       </c>
       <c r="C41" s="2">
-        <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D41" s="14">
@@ -24053,7 +24787,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="14">
-        <f>SUM(D41:H41)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J41" s="15"/>
@@ -24068,7 +24802,7 @@
         <v>김현우</v>
       </c>
       <c r="C42" s="2">
-        <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D42" s="14">
@@ -24092,7 +24826,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="14">
-        <f>SUM(D42:H42)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J42" s="15"/>
@@ -24107,7 +24841,7 @@
         <v>김형원</v>
       </c>
       <c r="C43" s="2">
-        <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D43" s="14">
@@ -24131,7 +24865,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="14">
-        <f>SUM(D43:H43)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J43" s="15"/>
@@ -24146,7 +24880,7 @@
         <v>노민준</v>
       </c>
       <c r="C44" s="2">
-        <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
+        <f t="shared" si="7"/>
         <v>3.2</v>
       </c>
       <c r="D44" s="14">
@@ -24170,7 +24904,7 @@
         <v>3</v>
       </c>
       <c r="I44" s="14">
-        <f>SUM(D44:H44)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="J44" s="15"/>
@@ -24185,7 +24919,7 @@
         <v>노성호</v>
       </c>
       <c r="C45" s="2">
-        <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="D45" s="14">
@@ -24209,7 +24943,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="14">
-        <f>SUM(D45:H45)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J45" s="15"/>
@@ -24224,20 +24958,20 @@
         <v>류서진</v>
       </c>
       <c r="C46" s="2">
-        <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.90000000000000013</v>
       </c>
       <c r="D46" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B46)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B46)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B46)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B46)</f>
@@ -24248,8 +24982,8 @@
         <v>0</v>
       </c>
       <c r="I46" s="14">
-        <f>SUM(D46:H46)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="J46" s="15"/>
     </row>
@@ -24263,7 +24997,7 @@
         <v>마창기</v>
       </c>
       <c r="C47" s="2">
-        <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D47" s="14">
@@ -24287,7 +25021,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="14">
-        <f>SUM(D47:H47)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J47" s="15"/>
@@ -24302,8 +25036,8 @@
         <v>문준수</v>
       </c>
       <c r="C48" s="2">
-        <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
-        <v>1.8</v>
+        <f t="shared" si="7"/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D48" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B48)</f>
@@ -24319,15 +25053,15 @@
       </c>
       <c r="G48" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B48)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H48" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B48)</f>
         <v>1</v>
       </c>
       <c r="I48" s="14">
-        <f>SUM(D48:H48)</f>
-        <v>9</v>
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="J48" s="15"/>
     </row>
@@ -24341,7 +25075,7 @@
         <v>민건호</v>
       </c>
       <c r="C49" s="2">
-        <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D49" s="14">
@@ -24365,7 +25099,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="14">
-        <f>SUM(D49:H49)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J49" s="15"/>
@@ -24380,7 +25114,7 @@
         <v>박수천</v>
       </c>
       <c r="C50" s="2">
-        <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D50" s="14">
@@ -24404,7 +25138,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="14">
-        <f>SUM(D50:H50)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J50" s="15"/>
@@ -24419,7 +25153,7 @@
         <v>박정호</v>
       </c>
       <c r="C51" s="2">
-        <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D51" s="14">
@@ -24443,7 +25177,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="14">
-        <f>SUM(D51:H51)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J51" s="15"/>
@@ -24458,8 +25192,8 @@
         <v>박주연</v>
       </c>
       <c r="C52" s="2">
-        <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
-        <v>1.8</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="D52" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B52)</f>
@@ -24467,7 +25201,7 @@
       </c>
       <c r="E52" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B52)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B52)</f>
@@ -24482,8 +25216,8 @@
         <v>0</v>
       </c>
       <c r="I52" s="14">
-        <f>SUM(D52:H52)</f>
-        <v>9</v>
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="J52" s="15"/>
     </row>
@@ -24497,7 +25231,7 @@
         <v>박주현</v>
       </c>
       <c r="C53" s="2">
-        <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D53" s="14">
@@ -24521,7 +25255,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="14">
-        <f>SUM(D53:H53)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J53" s="15"/>
@@ -24536,7 +25270,7 @@
         <v>박준영</v>
       </c>
       <c r="C54" s="2">
-        <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="D54" s="14">
@@ -24560,7 +25294,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="14">
-        <f>SUM(D54:H54)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J54" s="15"/>
@@ -24575,7 +25309,7 @@
         <v>박태현</v>
       </c>
       <c r="C55" s="2">
-        <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D55" s="14">
@@ -24599,7 +25333,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="14">
-        <f>SUM(D55:H55)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J55" s="15"/>
@@ -24614,7 +25348,7 @@
         <v>박하빈</v>
       </c>
       <c r="C56" s="2">
-        <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D56" s="14">
@@ -24638,7 +25372,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="14">
-        <f>SUM(D56:H56)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J56" s="15"/>
@@ -24653,7 +25387,7 @@
         <v>박형기</v>
       </c>
       <c r="C57" s="2">
-        <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D57" s="14">
@@ -24677,7 +25411,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="14">
-        <f>SUM(D57:H57)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J57" s="15"/>
@@ -24692,8 +25426,8 @@
         <v>손경호</v>
       </c>
       <c r="C58" s="2">
-        <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D58" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B58)</f>
@@ -24713,11 +25447,11 @@
       </c>
       <c r="H58" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B58)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58" s="14">
-        <f>SUM(D58:H58)</f>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="J58" s="15"/>
     </row>
@@ -24731,7 +25465,7 @@
         <v>송윤상</v>
       </c>
       <c r="C59" s="2">
-        <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="D59" s="14">
@@ -24755,7 +25489,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="14">
-        <f>SUM(D59:H59)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J59" s="15"/>
@@ -24770,7 +25504,7 @@
         <v>신기웅</v>
       </c>
       <c r="C60" s="2">
-        <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.9000000000000001</v>
       </c>
       <c r="D60" s="14">
@@ -24794,7 +25528,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="14">
-        <f>SUM(D60:H60)</f>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="J60" s="15"/>
@@ -24809,7 +25543,7 @@
         <v>신종훈</v>
       </c>
       <c r="C61" s="2">
-        <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D61" s="14">
@@ -24833,7 +25567,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="14">
-        <f>SUM(D61:H61)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J61" s="15"/>
@@ -24848,7 +25582,7 @@
         <v>안진혁</v>
       </c>
       <c r="C62" s="2">
-        <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D62" s="14">
@@ -24872,7 +25606,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="14">
-        <f>SUM(D62:H62)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J62" s="15"/>
@@ -24887,7 +25621,7 @@
         <v>양진웅</v>
       </c>
       <c r="C63" s="2">
-        <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="D63" s="14">
@@ -24911,7 +25645,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f>SUM(D63:H63)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J63" s="15"/>
@@ -24926,7 +25660,7 @@
         <v>오상준</v>
       </c>
       <c r="C64" s="2">
-        <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.1</v>
       </c>
       <c r="D64" s="14">
@@ -24950,7 +25684,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="14">
-        <f>SUM(D64:H64)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="J64" s="15"/>
@@ -24965,7 +25699,7 @@
         <v>오성찬</v>
       </c>
       <c r="C65" s="2">
-        <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.3</v>
       </c>
       <c r="D65" s="14">
@@ -24989,7 +25723,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="14">
-        <f>SUM(D65:H65)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J65" s="15"/>
@@ -25004,8 +25738,8 @@
         <v>오우영</v>
       </c>
       <c r="C66" s="2">
-        <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
-        <v>1.5</v>
+        <f t="shared" si="7"/>
+        <v>1.7</v>
       </c>
       <c r="D66" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B66)</f>
@@ -25013,7 +25747,7 @@
       </c>
       <c r="E66" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B66)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B66)</f>
@@ -25028,8 +25762,8 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f>SUM(D66:H66)</f>
-        <v>6</v>
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="J66" s="15"/>
     </row>
@@ -25043,7 +25777,7 @@
         <v>오운용</v>
       </c>
       <c r="C67" s="2">
-        <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D67" s="14">
@@ -25067,7 +25801,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f>SUM(D67:H67)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J67" s="15"/>
@@ -25082,7 +25816,7 @@
         <v>오진환</v>
       </c>
       <c r="C68" s="2">
-        <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
         <v>0</v>
       </c>
       <c r="D68" s="14">
@@ -25106,7 +25840,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="14">
-        <f>SUM(D68:H68)</f>
+        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
         <v>0</v>
       </c>
       <c r="J68" s="15"/>
@@ -25121,7 +25855,7 @@
         <v>우보광</v>
       </c>
       <c r="C69" s="2">
-        <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D69" s="14">
@@ -25145,7 +25879,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f>SUM(D69:H69)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J69" s="15"/>
@@ -25160,8 +25894,8 @@
         <v>유상근</v>
       </c>
       <c r="C70" s="2">
-        <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
-        <v>3.8000000000000003</v>
+        <f t="shared" si="9"/>
+        <v>4.2</v>
       </c>
       <c r="D70" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B70)</f>
@@ -25177,15 +25911,15 @@
       </c>
       <c r="G70" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B70)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H70" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B70)</f>
         <v>1</v>
       </c>
       <c r="I70" s="14">
-        <f>SUM(D70:H70)</f>
-        <v>19</v>
+        <f t="shared" si="10"/>
+        <v>21</v>
       </c>
       <c r="J70" s="15"/>
     </row>
@@ -25199,7 +25933,7 @@
         <v>유우진</v>
       </c>
       <c r="C71" s="2">
-        <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D71" s="14">
@@ -25223,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <f>SUM(D71:H71)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J71" s="15"/>
@@ -25238,7 +25972,7 @@
         <v>유인상</v>
       </c>
       <c r="C72" s="2">
-        <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D72" s="14">
@@ -25262,7 +25996,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f>SUM(D72:H72)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J72" s="15"/>
@@ -25277,7 +26011,7 @@
         <v>유정훈</v>
       </c>
       <c r="C73" s="2">
-        <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D73" s="14">
@@ -25301,7 +26035,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f>SUM(D73:H73)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J73" s="15"/>
@@ -25316,7 +26050,7 @@
         <v>유진효</v>
       </c>
       <c r="C74" s="2">
-        <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D74" s="14">
@@ -25340,7 +26074,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="14">
-        <f>SUM(D74:H74)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J74" s="15"/>
@@ -25355,7 +26089,7 @@
         <v>윤원택</v>
       </c>
       <c r="C75" s="2">
-        <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
       <c r="D75" s="14">
@@ -25379,7 +26113,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="14">
-        <f>SUM(D75:H75)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J75" s="15"/>
@@ -25394,7 +26128,7 @@
         <v>윤창현</v>
       </c>
       <c r="C76" s="2">
-        <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.6</v>
       </c>
       <c r="D76" s="14">
@@ -25418,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="14">
-        <f>SUM(D76:H76)</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="J76" s="15"/>
@@ -25433,7 +26167,7 @@
         <v>윤현기</v>
       </c>
       <c r="C77" s="2">
-        <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
       <c r="D77" s="14">
@@ -25457,7 +26191,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="14">
-        <f>SUM(D77:H77)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J77" s="15"/>
@@ -25472,7 +26206,7 @@
         <v>이경석</v>
       </c>
       <c r="C78" s="2">
-        <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D78" s="14">
@@ -25496,7 +26230,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="14">
-        <f>SUM(D78:H78)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J78" s="15"/>
@@ -25511,7 +26245,7 @@
         <v>이민재</v>
       </c>
       <c r="C79" s="2">
-        <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D79" s="14">
@@ -25535,7 +26269,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="14">
-        <f>SUM(D79:H79)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J79" s="15"/>
@@ -25550,7 +26284,7 @@
         <v>이병현</v>
       </c>
       <c r="C80" s="2">
-        <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D80" s="14">
@@ -25574,7 +26308,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="14">
-        <f>SUM(D80:H80)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J80" s="15"/>
@@ -25589,7 +26323,7 @@
         <v>이상민</v>
       </c>
       <c r="C81" s="2">
-        <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D81" s="14">
@@ -25613,7 +26347,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="14">
-        <f>SUM(D81:H81)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J81" s="15"/>
@@ -25628,7 +26362,7 @@
         <v>이상현</v>
       </c>
       <c r="C82" s="2">
-        <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.6</v>
       </c>
       <c r="D82" s="14">
@@ -25652,7 +26386,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="14">
-        <f>SUM(D82:H82)</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="J82" s="15"/>
@@ -25667,7 +26401,7 @@
         <v>이새샘</v>
       </c>
       <c r="C83" s="2">
-        <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="D83" s="14">
@@ -25691,7 +26425,7 @@
         <v>1</v>
       </c>
       <c r="I83" s="14">
-        <f>SUM(D83:H83)</f>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="J83" s="15"/>
@@ -25706,7 +26440,7 @@
         <v>이성관</v>
       </c>
       <c r="C84" s="2">
-        <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D84" s="14">
@@ -25730,7 +26464,7 @@
         <v>1</v>
       </c>
       <c r="I84" s="14">
-        <f>SUM(D84:H84)</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="J84" s="15"/>
@@ -25745,12 +26479,12 @@
         <v>이승윤</v>
       </c>
       <c r="C85" s="2">
-        <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
-        <v>0.8</v>
+        <f t="shared" si="9"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D85" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B85)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B85)</f>
@@ -25762,15 +26496,15 @@
       </c>
       <c r="G85" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B85)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H85" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B85)</f>
         <v>0</v>
       </c>
       <c r="I85" s="14">
-        <f>SUM(D85:H85)</f>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="J85" s="15"/>
     </row>
@@ -25784,7 +26518,7 @@
         <v>이연길</v>
       </c>
       <c r="C86" s="2">
-        <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D86" s="14">
@@ -25808,7 +26542,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="14">
-        <f>SUM(D86:H86)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J86" s="15"/>
@@ -25823,7 +26557,7 @@
         <v>이영준</v>
       </c>
       <c r="C87" s="2">
-        <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
       <c r="D87" s="14">
@@ -25847,7 +26581,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="14">
-        <f>SUM(D87:H87)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J87" s="15"/>
@@ -25862,7 +26596,7 @@
         <v>이정범</v>
       </c>
       <c r="C88" s="2">
-        <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D88" s="14">
@@ -25886,7 +26620,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="14">
-        <f>SUM(D88:H88)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J88" s="15"/>
@@ -25901,7 +26635,7 @@
         <v>이종수</v>
       </c>
       <c r="C89" s="2">
-        <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D89" s="14">
@@ -25925,7 +26659,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="14">
-        <f>SUM(D89:H89)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J89" s="15"/>
@@ -25940,7 +26674,7 @@
         <v>이지섭</v>
       </c>
       <c r="C90" s="2">
-        <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D90" s="14">
@@ -25964,7 +26698,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="14">
-        <f>SUM(D90:H90)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J90" s="15"/>
@@ -25979,7 +26713,7 @@
         <v>이찬솔</v>
       </c>
       <c r="C91" s="2">
-        <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D91" s="14">
@@ -26003,7 +26737,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="14">
-        <f>SUM(D91:H91)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J91" s="15"/>
@@ -26018,7 +26752,7 @@
         <v>이찬영</v>
       </c>
       <c r="C92" s="2">
-        <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D92" s="14">
@@ -26042,7 +26776,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="14">
-        <f>SUM(D92:H92)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J92" s="15"/>
@@ -26057,7 +26791,7 @@
         <v>이태한</v>
       </c>
       <c r="C93" s="2">
-        <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D93" s="14">
@@ -26081,7 +26815,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="14">
-        <f>SUM(D93:H93)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J93" s="15"/>
@@ -26096,7 +26830,7 @@
         <v>이호행</v>
       </c>
       <c r="C94" s="2">
-        <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D94" s="14">
@@ -26120,7 +26854,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="14">
-        <f>SUM(D94:H94)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J94" s="15"/>
@@ -26135,7 +26869,7 @@
         <v>임수철</v>
       </c>
       <c r="C95" s="2">
-        <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D95" s="14">
@@ -26159,7 +26893,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="14">
-        <f>SUM(D95:H95)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J95" s="15"/>
@@ -26174,12 +26908,12 @@
         <v>임태환</v>
       </c>
       <c r="C96" s="2">
-        <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
-        <v>1.8000000000000003</v>
+        <f t="shared" si="9"/>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D96" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B96)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E96" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B96)</f>
@@ -26187,7 +26921,7 @@
       </c>
       <c r="F96" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B96)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B96)</f>
@@ -26198,8 +26932,8 @@
         <v>1</v>
       </c>
       <c r="I96" s="14">
-        <f>SUM(D96:H96)</f>
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="J96" s="15"/>
     </row>
@@ -26213,7 +26947,7 @@
         <v>장희도</v>
       </c>
       <c r="C97" s="2">
-        <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D97" s="14">
@@ -26237,7 +26971,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="14">
-        <f>SUM(D97:H97)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J97" s="15"/>
@@ -26252,7 +26986,7 @@
         <v>장희준</v>
       </c>
       <c r="C98" s="2">
-        <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D98" s="14">
@@ -26276,7 +27010,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="14">
-        <f>SUM(D98:H98)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J98" s="15"/>
@@ -26291,12 +27025,12 @@
         <v>전나현</v>
       </c>
       <c r="C99" s="2">
-        <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>1.5</v>
       </c>
       <c r="D99" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B99)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B99)</f>
@@ -26304,7 +27038,7 @@
       </c>
       <c r="F99" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B99)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G99" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B99)</f>
@@ -26315,8 +27049,8 @@
         <v>0</v>
       </c>
       <c r="I99" s="14">
-        <f>SUM(D99:H99)</f>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>6</v>
       </c>
       <c r="J99" s="15"/>
     </row>
@@ -26330,7 +27064,7 @@
         <v>전성환</v>
       </c>
       <c r="C100" s="2">
-        <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f t="shared" ref="C100:C123" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D100" s="14">
@@ -26354,7 +27088,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f>SUM(D100:H100)</f>
+        <f t="shared" ref="I100:I123" si="12">SUM(D100:H100)</f>
         <v>1</v>
       </c>
       <c r="J100" s="15"/>
@@ -26369,7 +27103,7 @@
         <v>전하늘</v>
       </c>
       <c r="C101" s="2">
-        <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D101" s="14">
@@ -26393,7 +27127,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f>SUM(D101:H101)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="J101" s="15"/>
@@ -26408,12 +27142,12 @@
         <v>정민수</v>
       </c>
       <c r="C102" s="2">
-        <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
-        <v>4</v>
+        <f t="shared" si="11"/>
+        <v>4.2</v>
       </c>
       <c r="D102" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B102)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B102)</f>
@@ -26432,8 +27166,8 @@
         <v>0</v>
       </c>
       <c r="I102" s="14">
-        <f>SUM(D102:H102)</f>
-        <v>20</v>
+        <f t="shared" si="12"/>
+        <v>21</v>
       </c>
       <c r="J102" s="15"/>
     </row>
@@ -26447,12 +27181,12 @@
         <v>정재명</v>
       </c>
       <c r="C103" s="2">
-        <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
-        <v>0.2</v>
+        <f t="shared" si="11"/>
+        <v>0.4</v>
       </c>
       <c r="D103" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B103)</f>
@@ -26471,8 +27205,8 @@
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f>SUM(D103:H103)</f>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="J103" s="15"/>
     </row>
@@ -26486,7 +27220,7 @@
         <v>정진억</v>
       </c>
       <c r="C104" s="2">
-        <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D104" s="14">
@@ -26510,7 +27244,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f>SUM(D104:H104)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J104" s="15"/>
@@ -26525,7 +27259,7 @@
         <v>정현서</v>
       </c>
       <c r="C105" s="2">
-        <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D105" s="14">
@@ -26549,7 +27283,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="14">
-        <f>SUM(D105:H105)</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
     </row>
@@ -26563,7 +27297,7 @@
         <v>조진한</v>
       </c>
       <c r="C106" s="2">
-        <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
+        <f t="shared" si="11"/>
         <v>4.2</v>
       </c>
       <c r="D106" s="14">
@@ -26587,7 +27321,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="14">
-        <f>SUM(D106:H106)</f>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
     </row>
@@ -26601,7 +27335,7 @@
         <v>조현우</v>
       </c>
       <c r="C107" s="2">
-        <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="D107" s="14">
@@ -26625,7 +27359,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f>SUM(D107:H107)</f>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
     </row>
@@ -26639,7 +27373,7 @@
         <v>차승원</v>
       </c>
       <c r="C108" s="2">
-        <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="D108" s="14">
@@ -26663,7 +27397,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f>SUM(D108:H108)</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
     </row>
@@ -26677,8 +27411,8 @@
         <v>최령창</v>
       </c>
       <c r="C109" s="2">
-        <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
-        <v>3</v>
+        <f t="shared" si="11"/>
+        <v>3.4000000000000004</v>
       </c>
       <c r="D109" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B109)</f>
@@ -26694,15 +27428,15 @@
       </c>
       <c r="G109" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B109)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H109" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B109)</f>
         <v>1</v>
       </c>
       <c r="I109" s="14">
-        <f>SUM(D109:H109)</f>
-        <v>15</v>
+        <f t="shared" si="12"/>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -26715,7 +27449,7 @@
         <v>최승훈</v>
       </c>
       <c r="C110" s="2">
-        <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D110" s="14">
@@ -26739,7 +27473,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="14">
-        <f>SUM(D110:H110)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -26753,7 +27487,7 @@
         <v>한상규</v>
       </c>
       <c r="C111" s="2">
-        <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="D111" s="14">
@@ -26777,7 +27511,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f>SUM(D111:H111)</f>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
     </row>
@@ -26791,8 +27525,8 @@
         <v>한의현</v>
       </c>
       <c r="C112" s="2">
-        <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
-        <v>0.8</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="D112" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B112)</f>
@@ -26800,7 +27534,7 @@
       </c>
       <c r="E112" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B112)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B112)</f>
@@ -26815,8 +27549,8 @@
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f>SUM(D112:H112)</f>
-        <v>4</v>
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -26829,7 +27563,7 @@
         <v>한중희</v>
       </c>
       <c r="C113" s="2">
-        <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="D113" s="14">
@@ -26853,7 +27587,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="14">
-        <f>SUM(D113:H113)</f>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
     </row>
@@ -26867,7 +27601,7 @@
         <v>허동혁</v>
       </c>
       <c r="C114" s="2">
-        <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D114" s="14">
@@ -26891,7 +27625,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="14">
-        <f>SUM(D114:H114)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -26905,7 +27639,7 @@
         <v>홍석준</v>
       </c>
       <c r="C115" s="2">
-        <f>((D115+E115+G115+H115)*0.2)+(F115*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D115" s="14">
@@ -26929,7 +27663,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="14">
-        <f>SUM(D115:H115)</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
     </row>
@@ -26943,7 +27677,7 @@
         <v>홍현석</v>
       </c>
       <c r="C116" s="2">
-        <f>((D116+E116+G116+H116)*0.2)+(F116*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D116" s="14">
@@ -26967,7 +27701,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="14">
-        <f>SUM(D116:H116)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -26981,7 +27715,7 @@
         <v>황건호</v>
       </c>
       <c r="C117" s="2">
-        <f>((D117+E117+G117+H117)*0.2)+(F117*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
       <c r="D117" s="14">
@@ -27005,7 +27739,7 @@
         <v>0</v>
       </c>
       <c r="I117" s="14">
-        <f>SUM(D117:H117)</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
     </row>
@@ -27019,7 +27753,7 @@
         <v>황석원</v>
       </c>
       <c r="C118" s="2">
-        <f>((D118+E118+G118+H118)*0.2)+(F118*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.1</v>
       </c>
       <c r="D118" s="14">
@@ -27043,7 +27777,7 @@
         <v>1</v>
       </c>
       <c r="I118" s="14">
-        <f>SUM(D118:H118)</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
     </row>
@@ -27057,7 +27791,7 @@
         <v>황재순</v>
       </c>
       <c r="C119" s="2">
-        <f>((D119+E119+G119+H119)*0.2)+(F119*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D119" s="14">
@@ -27081,7 +27815,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f>SUM(D119:H119)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -27095,7 +27829,7 @@
         <v>황철우</v>
       </c>
       <c r="C120" s="2">
-        <f>((D120+E120+G120+H120)*0.2)+(F120*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D120" s="14">
@@ -27119,7 +27853,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="14">
-        <f>SUM(D120:H120)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -27133,7 +27867,7 @@
         <v>김민성</v>
       </c>
       <c r="C121" s="2">
-        <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D121" s="14">
@@ -27157,7 +27891,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="14">
-        <f>SUM(D121:H121)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -27171,7 +27905,7 @@
         <v>송명섭</v>
       </c>
       <c r="C122" s="2">
-        <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D122" s="14">
@@ -27195,7 +27929,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f>SUM(D122:H122)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -27209,7 +27943,7 @@
         <v>최경영</v>
       </c>
       <c r="C123" s="2">
-        <f>((D123+E123+G123+H123)*0.2)+(F123*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="D123" s="14">
@@ -27233,7 +27967,7 @@
         <v>5</v>
       </c>
       <c r="I123" s="14">
-        <f>SUM(D123:H123)</f>
+        <f t="shared" si="12"/>
         <v>11</v>
       </c>
     </row>
@@ -28864,14 +29598,14 @@
       </c>
       <c r="E3" s="70">
         <f>VLOOKUP(D3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" s="70" t="s">
         <v>299</v>
       </c>
       <c r="G3" s="61">
         <f>VLOOKUP(F3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="I3" s="94" t="s">
         <v>333</v>
@@ -28896,14 +29630,14 @@
       </c>
       <c r="Q3" s="62">
         <f>VLOOKUP(P3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>299</v>
       </c>
       <c r="S3" s="63">
         <f>VLOOKUP(R3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
@@ -28916,7 +29650,7 @@
       </c>
       <c r="E4" s="62">
         <f>VLOOKUP(D4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="70" t="s">
         <v>225</v>
@@ -28944,14 +29678,14 @@
       </c>
       <c r="Q4" s="62">
         <f>VLOOKUP(P4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>222</v>
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -28964,14 +29698,14 @@
       </c>
       <c r="E5" s="47">
         <f>VLOOKUP(D5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>222</v>
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="I5" s="95"/>
       <c r="J5" s="66">
@@ -29019,7 +29753,7 @@
       </c>
       <c r="G6" s="61">
         <f>VLOOKUP(F6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="I6" s="95"/>
       <c r="J6" s="66">
@@ -29040,14 +29774,14 @@
       </c>
       <c r="Q6" s="69">
         <f>VLOOKUP(P6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>231</v>
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>14</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -29060,7 +29794,7 @@
       </c>
       <c r="E7" s="47">
         <f>VLOOKUP(D7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" s="70" t="s">
         <v>305</v>
@@ -29088,14 +29822,14 @@
       </c>
       <c r="Q7" s="69">
         <f>VLOOKUP(P7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R7" s="65" t="s">
         <v>325</v>
       </c>
       <c r="S7" s="71">
         <f>VLOOKUP(R7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>14.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
@@ -29115,7 +29849,7 @@
       </c>
       <c r="G8" s="63">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>17.600000000000001</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="N8" s="85"/>
       <c r="O8" s="48">
@@ -29153,7 +29887,7 @@
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="I9" s="98" t="s">
         <v>249</v>
@@ -29174,7 +29908,7 @@
       </c>
       <c r="Q9" s="69">
         <f>VLOOKUP(P9,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R9" s="65" t="s">
         <v>310</v>
@@ -29231,7 +29965,7 @@
       </c>
       <c r="S10" s="71">
         <f>VLOOKUP(R10,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
@@ -29244,7 +29978,7 @@
       </c>
       <c r="E11" s="65">
         <f>VLOOKUP(D11,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="70" t="s">
         <v>48</v>
@@ -29347,7 +30081,7 @@
       </c>
       <c r="G13" s="61">
         <f>VLOOKUP(F13,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.8</v>
+        <v>13</v>
       </c>
       <c r="I13" s="95"/>
       <c r="J13" s="66">
@@ -29376,14 +30110,14 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>229</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15.6</v>
+        <v>16.8</v>
       </c>
       <c r="I14" s="96"/>
       <c r="J14" s="66">
@@ -29412,7 +30146,7 @@
       </c>
       <c r="E15" s="65">
         <f>VLOOKUP(D15,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F15" s="62" t="s">
         <v>300</v>
@@ -29438,14 +30172,14 @@
       </c>
       <c r="E16" s="65">
         <f>VLOOKUP(D16,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>231</v>
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="H16" s="37"/>
       <c r="I16" s="98" t="s">
@@ -29474,7 +30208,7 @@
       </c>
       <c r="G17" s="63">
         <f>VLOOKUP(F17,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H17" s="37"/>
       <c r="I17" s="94" t="s">
@@ -30699,7 +31433,7 @@
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C10</f>
-        <v>8.1</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I8" s="6">
         <f t="shared" si="3"/>
@@ -31041,7 +31775,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C17</f>
@@ -33857,7 +34591,7 @@
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C102</f>
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="6"/>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="897" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD9E4079-AF11-4013-987B-47D51B246F19}"/>
+  <xr:revisionPtr revIDLastSave="985" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77A34C4D-EF5C-4AF0-A3BD-D981598623DB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2746" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="416">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -2347,10 +2347,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2359,20 +2359,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>14.2</v>
+        <v>14.688888888888888</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="AJ2" s="1">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AK2" s="1">
         <f t="shared" si="0"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AL2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AM2" s="1">
         <f t="shared" si="0"/>
@@ -3495,7 +3495,9 @@
       <c r="AK3" s="4">
         <v>46246</v>
       </c>
-      <c r="AL3" s="4"/>
+      <c r="AL3" s="4">
+        <v>46254</v>
+      </c>
       <c r="AM3" s="4"/>
       <c r="AN3" s="4"/>
       <c r="AO3" s="4"/>
@@ -3564,11 +3566,11 @@
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="6">
         <f>(COUNTIF(J4:CD4,"출전")*1)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>349</v>
@@ -3640,7 +3642,9 @@
       <c r="AK4" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AL4" s="2"/>
+      <c r="AL4" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ref="G5:G68" si="2">RANK(H5,$H$4:$H$124,0)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -4128,15 +4132,15 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="I9" s="6">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
@@ -4176,7 +4180,9 @@
       <c r="AI9" s="2"/>
       <c r="AJ9" s="2"/>
       <c r="AK9" s="2"/>
-      <c r="AL9" s="2"/>
+      <c r="AL9" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM9" s="2"/>
       <c r="AN9" s="2"/>
       <c r="AO9" s="2"/>
@@ -4245,11 +4251,11 @@
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
-        <v>18.600000000000001</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>349</v>
@@ -4309,7 +4315,9 @@
       </c>
       <c r="AJ10" s="2"/>
       <c r="AK10" s="2"/>
-      <c r="AL10" s="2"/>
+      <c r="AL10" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM10" s="2"/>
       <c r="AN10" s="2"/>
       <c r="AO10" s="2"/>
@@ -4374,7 +4382,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
@@ -4814,7 +4822,7 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="2"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
@@ -4919,7 +4927,7 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
@@ -5038,7 +5046,7 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
@@ -5373,7 +5381,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -5485,7 +5493,7 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C21</f>
@@ -5590,7 +5598,7 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H22" s="6">
         <f>I22+개인기록Sheet!C22</f>
@@ -6254,11 +6262,11 @@
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
@@ -6332,7 +6340,9 @@
       <c r="AK28" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AL28" s="2"/>
+      <c r="AL28" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM28" s="2"/>
       <c r="AN28" s="2"/>
       <c r="AO28" s="2"/>
@@ -6397,7 +6407,7 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C29</f>
@@ -6727,7 +6737,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
@@ -6858,11 +6868,11 @@
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>349</v>
@@ -6932,7 +6942,9 @@
       <c r="AK33" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AL33" s="2"/>
+      <c r="AL33" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM33" s="2"/>
       <c r="AN33" s="2"/>
       <c r="AO33" s="2"/>
@@ -7118,15 +7130,15 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C35</f>
-        <v>18.2</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
@@ -7186,7 +7198,9 @@
       <c r="AK35" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AL35" s="2"/>
+      <c r="AL35" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM35" s="2"/>
       <c r="AN35" s="2"/>
       <c r="AO35" s="2"/>
@@ -7594,15 +7608,15 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H39" s="6">
         <f>I39+개인기록Sheet!C39</f>
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="I39" s="6">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
@@ -7644,7 +7658,9 @@
       </c>
       <c r="AJ39" s="2"/>
       <c r="AK39" s="2"/>
-      <c r="AL39" s="2"/>
+      <c r="AL39" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM39" s="2"/>
       <c r="AN39" s="2"/>
       <c r="AO39" s="2"/>
@@ -7813,7 +7829,7 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" si="2"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H41" s="6">
         <f>I41+개인기록Sheet!C41</f>
@@ -8128,7 +8144,7 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="2"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
@@ -8372,15 +8388,15 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="I46" s="6">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -8422,7 +8438,9 @@
       </c>
       <c r="AJ46" s="2"/>
       <c r="AK46" s="2"/>
-      <c r="AL46" s="2"/>
+      <c r="AL46" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM46" s="2"/>
       <c r="AN46" s="2"/>
       <c r="AO46" s="2"/>
@@ -8487,7 +8505,7 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
@@ -8834,7 +8852,7 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" si="2"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H50" s="6">
         <f>I50+개인기록Sheet!C50</f>
@@ -9149,15 +9167,15 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H53" s="6">
         <f>I53+개인기록Sheet!C53</f>
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="I53" s="6">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -9213,7 +9231,9 @@
       <c r="AI53" s="2"/>
       <c r="AJ53" s="2"/>
       <c r="AK53" s="2"/>
-      <c r="AL53" s="2"/>
+      <c r="AL53" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM53" s="2"/>
       <c r="AN53" s="2"/>
       <c r="AO53" s="2"/>
@@ -9383,7 +9403,7 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
@@ -9495,7 +9515,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
@@ -9816,15 +9836,15 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
-        <v>19.2</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="I59" s="6">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
@@ -9886,7 +9906,9 @@
       <c r="AK59" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AL59" s="2"/>
+      <c r="AL59" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM59" s="2"/>
       <c r="AN59" s="2"/>
       <c r="AO59" s="2"/>
@@ -10058,7 +10080,7 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
@@ -10388,15 +10410,15 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H64" s="6">
         <f>I64+개인기록Sheet!C64</f>
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="I64" s="6">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>349</v>
@@ -10442,7 +10464,9 @@
         <v>349</v>
       </c>
       <c r="AK64" s="2"/>
-      <c r="AL64" s="2"/>
+      <c r="AL64" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM64" s="2"/>
       <c r="AN64" s="2"/>
       <c r="AO64" s="2"/>
@@ -10507,7 +10531,7 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
@@ -10627,7 +10651,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
@@ -11160,7 +11184,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -11294,7 +11318,7 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" si="12"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H72" s="6">
         <f>I72+개인기록Sheet!C72</f>
@@ -11518,7 +11542,7 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="12"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
@@ -11737,7 +11761,7 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="12"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
@@ -11850,7 +11874,7 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="12"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
@@ -11961,7 +11985,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="12"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
@@ -12407,7 +12431,7 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="12"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
@@ -12518,15 +12542,15 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="12"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" si="13"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
@@ -12572,7 +12596,9 @@
         <v>349</v>
       </c>
       <c r="AK83" s="2"/>
-      <c r="AL83" s="2"/>
+      <c r="AL83" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM83" s="2"/>
       <c r="AN83" s="2"/>
       <c r="AO83" s="2"/>
@@ -12637,7 +12663,7 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="12"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
@@ -12877,15 +12903,15 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" si="12"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
-        <v>9.8000000000000007</v>
+        <v>11</v>
       </c>
       <c r="I86" s="6">
         <f t="shared" si="13"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
@@ -12931,7 +12957,9 @@
       <c r="AI86" s="2"/>
       <c r="AJ86" s="2"/>
       <c r="AK86" s="2"/>
-      <c r="AL86" s="2"/>
+      <c r="AL86" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM86" s="2"/>
       <c r="AN86" s="2"/>
       <c r="AO86" s="2"/>
@@ -12996,15 +13024,15 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="12"/>
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
-        <v>3.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I87" s="6">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
@@ -13040,7 +13068,9 @@
       <c r="AI87" s="2"/>
       <c r="AJ87" s="2"/>
       <c r="AK87" s="2"/>
-      <c r="AL87" s="2"/>
+      <c r="AL87" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM87" s="2"/>
       <c r="AN87" s="2"/>
       <c r="AO87" s="2"/>
@@ -13105,7 +13135,7 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" si="12"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
@@ -13435,7 +13465,7 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" si="12"/>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
@@ -13544,7 +13574,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="12"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
@@ -13865,15 +13895,15 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" si="12"/>
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="I95" s="6">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -13909,7 +13939,9 @@
       <c r="AI95" s="2"/>
       <c r="AJ95" s="2"/>
       <c r="AK95" s="2"/>
-      <c r="AL95" s="2"/>
+      <c r="AL95" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM95" s="2"/>
       <c r="AN95" s="2"/>
       <c r="AO95" s="2"/>
@@ -14077,7 +14109,7 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
@@ -14409,15 +14441,15 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="12"/>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="I100" s="6">
         <f t="shared" si="13"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -14465,7 +14497,9 @@
       <c r="AI100" s="2"/>
       <c r="AJ100" s="2"/>
       <c r="AK100" s="2"/>
-      <c r="AL100" s="2"/>
+      <c r="AL100" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM100" s="2"/>
       <c r="AN100" s="2"/>
       <c r="AO100" s="2"/>
@@ -14636,7 +14670,7 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="12"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
@@ -14747,15 +14781,15 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
-        <v>18.600000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="I103" s="6">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
@@ -14811,7 +14845,9 @@
       <c r="AI103" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AJ103" s="2"/>
+      <c r="AJ103" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AK103" s="2"/>
       <c r="AL103" s="2"/>
       <c r="AM103" s="2"/>
@@ -14878,15 +14914,15 @@
       </c>
       <c r="G104" s="2">
         <f t="shared" si="12"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
-        <v>12.8</v>
+        <v>14.4</v>
       </c>
       <c r="I104" s="6">
         <f t="shared" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
@@ -14938,7 +14974,9 @@
         <v>349</v>
       </c>
       <c r="AK104" s="2"/>
-      <c r="AL104" s="2"/>
+      <c r="AL104" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM104" s="2"/>
       <c r="AN104" s="2"/>
       <c r="AO104" s="2"/>
@@ -15003,7 +15041,7 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="12"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
@@ -15124,11 +15162,11 @@
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
-        <v>25</v>
+        <v>26.8</v>
       </c>
       <c r="I106" s="6">
         <f t="shared" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>349</v>
@@ -15198,7 +15236,9 @@
         <v>349</v>
       </c>
       <c r="AK106" s="2"/>
-      <c r="AL106" s="2"/>
+      <c r="AL106" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM106" s="2"/>
       <c r="AN106" s="2"/>
       <c r="AO106" s="2"/>
@@ -15267,11 +15307,11 @@
       </c>
       <c r="H107" s="6">
         <f>I107+개인기록Sheet!C107</f>
-        <v>18.399999999999999</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="I107" s="6">
         <f t="shared" si="13"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>349</v>
@@ -15333,7 +15373,9 @@
       <c r="AK107" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AL107" s="2"/>
+      <c r="AL107" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM107" s="2"/>
       <c r="AN107" s="2"/>
       <c r="AO107" s="2"/>
@@ -15398,7 +15440,7 @@
       </c>
       <c r="G108" s="2">
         <f t="shared" si="12"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
@@ -15738,7 +15780,7 @@
       </c>
       <c r="G111" s="2">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
@@ -15992,7 +16034,7 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
@@ -16115,15 +16157,15 @@
       </c>
       <c r="G114" s="2">
         <f t="shared" si="12"/>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="I114" s="6">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>349</v>
@@ -16163,7 +16205,9 @@
         <v>349</v>
       </c>
       <c r="AK114" s="2"/>
-      <c r="AL114" s="2"/>
+      <c r="AL114" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM114" s="2"/>
       <c r="AN114" s="2"/>
       <c r="AO114" s="2"/>
@@ -16228,7 +16272,7 @@
       </c>
       <c r="G115" s="2">
         <f t="shared" si="12"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
@@ -16341,7 +16385,7 @@
       </c>
       <c r="G116" s="2">
         <f t="shared" si="12"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H116" s="6">
         <f>I116+개인기록Sheet!C116</f>
@@ -16448,7 +16492,7 @@
       </c>
       <c r="G117" s="2">
         <f t="shared" si="12"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H117" s="6">
         <f>I117+개인기록Sheet!C117</f>
@@ -16561,7 +16605,7 @@
       </c>
       <c r="G118" s="2">
         <f t="shared" si="12"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
@@ -16684,7 +16728,7 @@
       </c>
       <c r="G119" s="2">
         <f t="shared" si="12"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H119" s="6">
         <f>I119+개인기록Sheet!C119</f>
@@ -16790,7 +16834,7 @@
       </c>
       <c r="G120" s="2">
         <f t="shared" si="12"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H120" s="6">
         <f>I120+개인기록Sheet!C120</f>
@@ -17106,7 +17150,7 @@
       </c>
       <c r="G123" s="2">
         <f t="shared" si="12"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H123" s="6">
         <f>I123+개인기록Sheet!C123</f>
@@ -17216,7 +17260,7 @@
       </c>
       <c r="D124" s="54">
         <f>COUNTA(W124:AN124)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="54"/>
       <c r="F124" s="2" t="s">
@@ -17224,15 +17268,15 @@
       </c>
       <c r="G124" s="2">
         <f t="shared" si="12"/>
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H124" s="6">
         <f>I124+개인기록Sheet!C124</f>
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="I124" s="6">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
@@ -17264,7 +17308,9 @@
       </c>
       <c r="AJ124" s="2"/>
       <c r="AK124" s="2"/>
-      <c r="AL124" s="2"/>
+      <c r="AL124" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM124" s="2"/>
       <c r="AN124" s="2"/>
       <c r="AO124" s="2"/>
@@ -17311,6 +17357,7 @@
       <c r="CD124" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:CT124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:E124">
     <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="지급">
@@ -17334,7 +17381,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:V266"/>
+  <dimension ref="A2:V276"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -24997,56 +25044,586 @@
       <c r="U266" s="2"/>
       <c r="V266" s="2"/>
     </row>
+    <row r="269" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B269" s="11">
+        <v>46254</v>
+      </c>
+      <c r="C269" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D269" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="E269" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="F269" s="77"/>
+      <c r="G269" s="77"/>
+      <c r="H269" s="77"/>
+      <c r="I269" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="J269" s="78"/>
+      <c r="K269" s="78"/>
+      <c r="L269" s="78"/>
+      <c r="M269" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="N269" s="79"/>
+      <c r="O269" s="79"/>
+      <c r="P269" s="79"/>
+      <c r="Q269" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="R269" s="80"/>
+      <c r="S269" s="80"/>
+      <c r="T269" s="80"/>
+      <c r="U269" s="80"/>
+      <c r="V269" s="80"/>
+    </row>
+    <row r="270" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B270" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C270" s="75">
+        <v>1</v>
+      </c>
+      <c r="D270" s="75">
+        <v>1</v>
+      </c>
+      <c r="E270" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F270" s="7"/>
+      <c r="G270" s="7"/>
+      <c r="H270" s="7"/>
+      <c r="I270" s="8"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="8"/>
+      <c r="L270" s="8"/>
+      <c r="M270" s="20"/>
+      <c r="N270" s="20"/>
+      <c r="O270" s="20"/>
+      <c r="P270" s="20"/>
+      <c r="Q270" s="9"/>
+      <c r="R270" s="9"/>
+      <c r="S270" s="9"/>
+      <c r="T270" s="9"/>
+      <c r="U270" s="9"/>
+      <c r="V270" s="13"/>
+    </row>
+    <row r="271" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B271" s="74"/>
+      <c r="C271" s="76"/>
+      <c r="D271" s="76"/>
+      <c r="E271" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="F271" s="7"/>
+      <c r="G271" s="7"/>
+      <c r="H271" s="7"/>
+      <c r="I271" s="8"/>
+      <c r="J271" s="8"/>
+      <c r="K271" s="8"/>
+      <c r="L271" s="8"/>
+      <c r="M271" s="20"/>
+      <c r="N271" s="20"/>
+      <c r="O271" s="20"/>
+      <c r="P271" s="20"/>
+      <c r="Q271" s="9"/>
+      <c r="R271" s="9"/>
+      <c r="S271" s="9"/>
+      <c r="T271" s="9"/>
+      <c r="U271" s="9"/>
+      <c r="V271" s="13"/>
+    </row>
+    <row r="272" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B272" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C272" s="75">
+        <v>0</v>
+      </c>
+      <c r="D272" s="75">
+        <v>1</v>
+      </c>
+      <c r="E272" s="7"/>
+      <c r="F272" s="7"/>
+      <c r="G272" s="7"/>
+      <c r="H272" s="7"/>
+      <c r="I272" s="8"/>
+      <c r="J272" s="8"/>
+      <c r="K272" s="8"/>
+      <c r="L272" s="8"/>
+      <c r="M272" s="20"/>
+      <c r="N272" s="20"/>
+      <c r="O272" s="20"/>
+      <c r="P272" s="20"/>
+      <c r="Q272" s="9"/>
+      <c r="R272" s="9"/>
+      <c r="S272" s="9"/>
+      <c r="T272" s="9"/>
+      <c r="U272" s="9"/>
+      <c r="V272" s="13"/>
+    </row>
+    <row r="273" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B273" s="74"/>
+      <c r="C273" s="76"/>
+      <c r="D273" s="76"/>
+      <c r="E273" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="F273" s="7"/>
+      <c r="G273" s="7"/>
+      <c r="H273" s="7"/>
+      <c r="I273" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="J273" s="8"/>
+      <c r="K273" s="8"/>
+      <c r="L273" s="8"/>
+      <c r="M273" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="N273" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="O273" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="P273" s="20"/>
+      <c r="Q273" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="R273" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="S273" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="T273" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="U273" s="9"/>
+      <c r="V273" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="274" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B274" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C274" s="75">
+        <v>2</v>
+      </c>
+      <c r="D274" s="75">
+        <v>4</v>
+      </c>
+      <c r="E274" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F274" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G274" s="7"/>
+      <c r="H274" s="7"/>
+      <c r="I274" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J274" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="K274" s="8"/>
+      <c r="L274" s="8"/>
+      <c r="M274" s="20"/>
+      <c r="N274" s="20"/>
+      <c r="O274" s="20"/>
+      <c r="P274" s="20"/>
+      <c r="Q274" s="9"/>
+      <c r="R274" s="9"/>
+      <c r="S274" s="9"/>
+      <c r="T274" s="9"/>
+      <c r="U274" s="9"/>
+      <c r="V274" s="13"/>
+    </row>
+    <row r="275" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B275" s="74"/>
+      <c r="C275" s="76"/>
+      <c r="D275" s="76"/>
+      <c r="E275" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F275" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G275" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H275" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="I275" s="8"/>
+      <c r="J275" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K275" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="L275" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="M275" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="N275" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="O275" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="P275" s="20"/>
+      <c r="Q275" s="9"/>
+      <c r="R275" s="9"/>
+      <c r="S275" s="9"/>
+      <c r="T275" s="9"/>
+      <c r="U275" s="9"/>
+      <c r="V275" s="13"/>
+    </row>
+    <row r="276" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B276" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C276" s="2">
+        <f>SUM(C270:C275)</f>
+        <v>3</v>
+      </c>
+      <c r="D276" s="2">
+        <f>SUM(D270:D275)</f>
+        <v>6</v>
+      </c>
+      <c r="E276" s="2"/>
+      <c r="F276" s="2"/>
+      <c r="G276" s="2"/>
+      <c r="H276" s="2"/>
+      <c r="I276" s="2"/>
+      <c r="J276" s="2"/>
+      <c r="K276" s="2"/>
+      <c r="L276" s="2"/>
+      <c r="M276" s="2"/>
+      <c r="N276" s="2"/>
+      <c r="O276" s="2"/>
+      <c r="P276" s="2"/>
+      <c r="Q276" s="2"/>
+      <c r="R276" s="2"/>
+      <c r="S276" s="2"/>
+      <c r="T276" s="2"/>
+      <c r="U276" s="2"/>
+      <c r="V276" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="361">
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="B264:B265"/>
-    <mergeCell ref="C264:C265"/>
-    <mergeCell ref="D264:D265"/>
-    <mergeCell ref="E257:H257"/>
-    <mergeCell ref="I257:L257"/>
-    <mergeCell ref="M257:P257"/>
-    <mergeCell ref="Q257:V257"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="C258:C259"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="C260:C261"/>
-    <mergeCell ref="D260:D261"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="C252:C253"/>
-    <mergeCell ref="D252:D253"/>
-    <mergeCell ref="Q245:V245"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="C246:C247"/>
-    <mergeCell ref="D246:D247"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="C248:C249"/>
-    <mergeCell ref="D248:D249"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="C250:C251"/>
-    <mergeCell ref="D250:D251"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="C238:C239"/>
-    <mergeCell ref="D238:D239"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="C240:C241"/>
-    <mergeCell ref="D240:D241"/>
-    <mergeCell ref="E245:H245"/>
-    <mergeCell ref="I245:L245"/>
-    <mergeCell ref="M245:P245"/>
-    <mergeCell ref="E233:H233"/>
-    <mergeCell ref="I233:L233"/>
-    <mergeCell ref="M233:P233"/>
-    <mergeCell ref="Q233:V233"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="C234:C235"/>
-    <mergeCell ref="D234:D235"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="C236:C237"/>
-    <mergeCell ref="D236:D237"/>
+  <mergeCells count="374">
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="C274:C275"/>
+    <mergeCell ref="D274:D275"/>
+    <mergeCell ref="E269:H269"/>
+    <mergeCell ref="I269:L269"/>
+    <mergeCell ref="M269:P269"/>
+    <mergeCell ref="Q269:V269"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="C270:C271"/>
+    <mergeCell ref="D270:D271"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="C272:C273"/>
+    <mergeCell ref="D272:D273"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="C226:C227"/>
+    <mergeCell ref="D226:D227"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="C228:C229"/>
+    <mergeCell ref="D228:D229"/>
+    <mergeCell ref="E221:H221"/>
+    <mergeCell ref="I221:L221"/>
+    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="Q221:V221"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="D222:D223"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="E211:H211"/>
+    <mergeCell ref="I211:L211"/>
+    <mergeCell ref="M211:P211"/>
+    <mergeCell ref="Q211:V211"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="D214:D215"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="D200:D201"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="D204:D205"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E195:H195"/>
+    <mergeCell ref="I195:L195"/>
+    <mergeCell ref="M195:P195"/>
+    <mergeCell ref="Q195:V195"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="D196:D197"/>
+    <mergeCell ref="Q183:V183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
+    <mergeCell ref="E183:H183"/>
+    <mergeCell ref="I183:L183"/>
+    <mergeCell ref="M183:P183"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="Q113:V113"/>
+    <mergeCell ref="Q77:V77"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="M101:P101"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:V13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:L135"/>
+    <mergeCell ref="M135:P135"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:L125"/>
+    <mergeCell ref="M125:P125"/>
+    <mergeCell ref="Q135:V135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="Q125:V125"/>
+    <mergeCell ref="Q159:V159"/>
+    <mergeCell ref="Q171:V171"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="Q147:V147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="E147:H147"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M147:P147"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
     <mergeCell ref="E159:H159"/>
     <mergeCell ref="I159:L159"/>
     <mergeCell ref="M159:P159"/>
@@ -25071,295 +25648,54 @@
     <mergeCell ref="E171:H171"/>
     <mergeCell ref="I171:L171"/>
     <mergeCell ref="M171:P171"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="Q159:V159"/>
-    <mergeCell ref="Q171:V171"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="Q147:V147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="E147:H147"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="M147:P147"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="I135:L135"/>
-    <mergeCell ref="M135:P135"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="I125:L125"/>
-    <mergeCell ref="M125:P125"/>
-    <mergeCell ref="Q135:V135"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="Q125:V125"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:V13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="M113:P113"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="M77:P77"/>
-    <mergeCell ref="Q89:V89"/>
-    <mergeCell ref="M89:P89"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="Q113:V113"/>
-    <mergeCell ref="Q77:V77"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="M101:P101"/>
-    <mergeCell ref="Q101:V101"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E195:H195"/>
-    <mergeCell ref="I195:L195"/>
-    <mergeCell ref="M195:P195"/>
-    <mergeCell ref="Q195:V195"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="D196:D197"/>
-    <mergeCell ref="Q183:V183"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="D190:D191"/>
-    <mergeCell ref="E183:H183"/>
-    <mergeCell ref="I183:L183"/>
-    <mergeCell ref="M183:P183"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="D200:D201"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="D202:D203"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="D204:D205"/>
-    <mergeCell ref="E211:H211"/>
-    <mergeCell ref="I211:L211"/>
-    <mergeCell ref="M211:P211"/>
-    <mergeCell ref="Q211:V211"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="D214:D215"/>
-    <mergeCell ref="Q221:V221"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="D222:D223"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="D216:D217"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="C228:C229"/>
-    <mergeCell ref="D228:D229"/>
-    <mergeCell ref="E221:H221"/>
-    <mergeCell ref="I221:L221"/>
-    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="E233:H233"/>
+    <mergeCell ref="I233:L233"/>
+    <mergeCell ref="M233:P233"/>
+    <mergeCell ref="Q233:V233"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="C234:C235"/>
+    <mergeCell ref="D234:D235"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="C236:C237"/>
+    <mergeCell ref="D236:D237"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="C238:C239"/>
+    <mergeCell ref="D238:D239"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="C240:C241"/>
+    <mergeCell ref="D240:D241"/>
+    <mergeCell ref="E245:H245"/>
+    <mergeCell ref="I245:L245"/>
+    <mergeCell ref="M245:P245"/>
+    <mergeCell ref="Q245:V245"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="C246:C247"/>
+    <mergeCell ref="D246:D247"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="C248:C249"/>
+    <mergeCell ref="D248:D249"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="C250:C251"/>
+    <mergeCell ref="D250:D251"/>
+    <mergeCell ref="Q257:V257"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="C258:C259"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="C260:C261"/>
+    <mergeCell ref="D260:D261"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="C252:C253"/>
+    <mergeCell ref="D252:D253"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="B264:B265"/>
+    <mergeCell ref="C264:C265"/>
+    <mergeCell ref="D264:D265"/>
+    <mergeCell ref="E257:H257"/>
+    <mergeCell ref="I257:L257"/>
+    <mergeCell ref="M257:P257"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -25401,23 +25737,23 @@
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -25537,7 +25873,7 @@
         <v>351</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O15" si="1">VLOOKUP(N4,$B$4:$H$137,4,FALSE)</f>
+        <f t="shared" ref="O4:O18" si="1">VLOOKUP(N4,$B$4:$H$137,4,FALSE)</f>
         <v>9</v>
       </c>
       <c r="P4" s="34" t="s">
@@ -25545,7 +25881,7 @@
       </c>
       <c r="Q4" s="23">
         <f t="shared" ref="Q4:Q18" si="2">VLOOKUP(P4,$B$4:$H$137,5,FALSE)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>322</v>
@@ -25558,7 +25894,7 @@
         <v>228</v>
       </c>
       <c r="U4" s="56">
-        <f t="shared" ref="U4:U12" si="4">VLOOKUP(T4,$B$4:$H$137,7,FALSE)</f>
+        <f t="shared" ref="U4:U13" si="4">VLOOKUP(T4,$B$4:$H$137,7,FALSE)</f>
         <v>12</v>
       </c>
     </row>
@@ -25622,7 +25958,7 @@
       </c>
       <c r="Q5" s="23">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>230</v>
@@ -25881,7 +26217,7 @@
       </c>
       <c r="C9" s="2">
         <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D9" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B9)</f>
@@ -25901,22 +26237,22 @@
       </c>
       <c r="H9" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="14">
         <f>SUM(D9:H9)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="2">
         <v>6</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="M9" s="21">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>223</v>
@@ -25926,11 +26262,11 @@
         <v>4</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>53</v>
+        <v>382</v>
       </c>
       <c r="Q9" s="23">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R9" s="35" t="s">
         <v>392</v>
@@ -25989,25 +26325,25 @@
         <v>7</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>228</v>
+        <v>398</v>
       </c>
       <c r="M10" s="21">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>353</v>
+        <v>403</v>
       </c>
       <c r="O10" s="22">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" s="34" t="s">
-        <v>382</v>
+        <v>53</v>
       </c>
       <c r="Q10" s="23">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R10" s="35" t="s">
         <v>62</v>
@@ -26017,7 +26353,7 @@
         <v>12</v>
       </c>
       <c r="T10" s="36" t="s">
-        <v>353</v>
+        <v>299</v>
       </c>
       <c r="U10" s="56">
         <f t="shared" si="4"/>
@@ -26066,14 +26402,14 @@
         <v>8</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>353</v>
+        <v>228</v>
       </c>
       <c r="M11" s="21">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="O11" s="22">
         <f t="shared" si="1"/>
@@ -26094,7 +26430,7 @@
         <v>10</v>
       </c>
       <c r="T11" s="36" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="U11" s="56">
         <f t="shared" si="4"/>
@@ -26150,7 +26486,7 @@
         <v>7</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>224</v>
+        <v>313</v>
       </c>
       <c r="O12" s="22">
         <f t="shared" si="1"/>
@@ -26164,14 +26500,14 @@
         <v>5</v>
       </c>
       <c r="R12" s="35" t="s">
-        <v>361</v>
+        <v>221</v>
       </c>
       <c r="S12" s="55">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T12" s="36" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U12" s="56">
         <f t="shared" si="4"/>
@@ -26220,21 +26556,21 @@
         <v>10</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M13" s="21">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>7</v>
+        <v>224</v>
       </c>
       <c r="O13" s="22">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="P13" s="34" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q13" s="23">
         <f t="shared" si="2"/>
@@ -26245,10 +26581,15 @@
       </c>
       <c r="S13" s="55">
         <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="T13" s="36"/>
-      <c r="U13" s="56"/>
+        <v>9</v>
+      </c>
+      <c r="T13" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="U13" s="56">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -26296,28 +26637,28 @@
       </c>
       <c r="M14" s="21">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>403</v>
+        <v>7</v>
       </c>
       <c r="O14" s="22">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="P14" s="34" t="s">
-        <v>403</v>
+        <v>313</v>
       </c>
       <c r="Q14" s="23">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="R14" s="55" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="S14" s="55">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" s="36"/>
       <c r="U14" s="56"/>
@@ -26364,32 +26705,32 @@
         <v>12</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="M15" s="21">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N15" s="33" t="s">
-        <v>360</v>
+        <v>230</v>
       </c>
       <c r="O15" s="22">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="P15" s="23" t="s">
-        <v>223</v>
+        <v>403</v>
       </c>
       <c r="Q15" s="23">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R15" s="55" t="s">
-        <v>67</v>
+        <v>308</v>
       </c>
       <c r="S15" s="55">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" s="56"/>
       <c r="U15" s="56"/>
@@ -26442,17 +26783,22 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
+      <c r="N16" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="O16" s="22">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
       <c r="P16" s="23" t="s">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="Q16" s="23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="R16" s="55" t="s">
-        <v>221</v>
+        <v>67</v>
       </c>
       <c r="S16" s="55">
         <f t="shared" si="3"/>
@@ -26504,10 +26850,15 @@
       </c>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
+      <c r="N17" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="O17" s="22">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
       <c r="P17" s="23" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="Q17" s="23">
         <f t="shared" si="2"/>
@@ -26561,8 +26912,13 @@
       </c>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
+      <c r="N18" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="O18" s="22">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
       <c r="P18" s="23" t="s">
         <v>231</v>
       </c>
@@ -26937,7 +27293,7 @@
       </c>
       <c r="C28" s="2">
         <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D28" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B28)</f>
@@ -26949,11 +27305,11 @@
       </c>
       <c r="F28" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B28)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B28)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B28)</f>
@@ -26961,7 +27317,7 @@
       </c>
       <c r="I28" s="14">
         <f>SUM(D28:H28)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J28" s="15"/>
     </row>
@@ -27132,11 +27488,11 @@
       </c>
       <c r="C33" s="2">
         <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D33" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B33)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E33" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B33)</f>
@@ -27156,7 +27512,7 @@
       </c>
       <c r="I33" s="14">
         <f>SUM(D33:H33)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J33" s="15"/>
     </row>
@@ -27210,11 +27566,11 @@
       </c>
       <c r="C35" s="2">
         <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D35" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B35)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B35)</f>
@@ -27234,7 +27590,7 @@
       </c>
       <c r="I35" s="14">
         <f>SUM(D35:H35)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J35" s="15"/>
     </row>
@@ -27366,7 +27722,7 @@
       </c>
       <c r="C39" s="2">
         <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D39" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B39)</f>
@@ -27374,7 +27730,7 @@
       </c>
       <c r="E39" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B39)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B39)</f>
@@ -27390,7 +27746,7 @@
       </c>
       <c r="I39" s="14">
         <f>SUM(D39:H39)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J39" s="15"/>
     </row>
@@ -27912,7 +28268,7 @@
       </c>
       <c r="C53" s="2">
         <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D53" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B53)</f>
@@ -27928,7 +28284,7 @@
       </c>
       <c r="G53" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B53)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H53" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B53)</f>
@@ -27936,7 +28292,7 @@
       </c>
       <c r="I53" s="14">
         <f>SUM(D53:H53)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J53" s="15"/>
     </row>
@@ -28146,11 +28502,11 @@
       </c>
       <c r="C59" s="2">
         <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
-        <v>3.2</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="D59" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B59)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B59)</f>
@@ -28170,7 +28526,7 @@
       </c>
       <c r="I59" s="14">
         <f>SUM(D59:H59)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J59" s="15"/>
     </row>
@@ -28341,7 +28697,7 @@
       </c>
       <c r="C64" s="2">
         <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D64" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B64)</f>
@@ -28349,11 +28705,11 @@
       </c>
       <c r="E64" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B64)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B64)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B64)</f>
@@ -28365,7 +28721,7 @@
       </c>
       <c r="I64" s="14">
         <f>SUM(D64:H64)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J64" s="15"/>
     </row>
@@ -29199,7 +29555,7 @@
       </c>
       <c r="C86" s="2">
         <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D86" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B86)</f>
@@ -29215,7 +29571,7 @@
       </c>
       <c r="G86" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B86)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H86" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B86)</f>
@@ -29223,7 +29579,7 @@
       </c>
       <c r="I86" s="14">
         <f>SUM(D86:H86)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J86" s="15"/>
     </row>
@@ -29745,7 +30101,7 @@
       </c>
       <c r="C100" s="2">
         <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D100" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B100)</f>
@@ -29753,7 +30109,7 @@
       </c>
       <c r="E100" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B100)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B100)</f>
@@ -29769,7 +30125,7 @@
       </c>
       <c r="I100" s="14">
         <f>SUM(D100:H100)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J100" s="15"/>
     </row>
@@ -29862,7 +30218,7 @@
       </c>
       <c r="C103" s="2">
         <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
-        <v>4.6000000000000005</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D103" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
@@ -29870,7 +30226,7 @@
       </c>
       <c r="E103" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B103)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B103)</f>
@@ -29886,7 +30242,7 @@
       </c>
       <c r="I103" s="14">
         <f>SUM(D103:H103)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J103" s="15"/>
     </row>
@@ -29901,15 +30257,15 @@
       </c>
       <c r="C104" s="2">
         <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
-        <v>1.8</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D104" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B104)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E104" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B104)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B104)</f>
@@ -29925,7 +30281,7 @@
       </c>
       <c r="I104" s="14">
         <f>SUM(D104:H104)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J104" s="15"/>
     </row>
@@ -29978,7 +30334,7 @@
       </c>
       <c r="C106" s="2">
         <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
-        <v>5</v>
+        <v>5.8000000000000007</v>
       </c>
       <c r="D106" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B106)</f>
@@ -29986,11 +30342,11 @@
       </c>
       <c r="E106" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B106)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B106)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G106" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B106)</f>
@@ -30002,7 +30358,7 @@
       </c>
       <c r="I106" s="14">
         <f>SUM(D106:H106)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -30282,11 +30638,11 @@
       </c>
       <c r="C114" s="2">
         <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
-        <v>1.4000000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="D114" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B114)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E114" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B114)</f>
@@ -30294,7 +30650,7 @@
       </c>
       <c r="F114" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B114)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G114" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B114)</f>
@@ -30306,7 +30662,7 @@
       </c>
       <c r="I114" s="14">
         <f>SUM(D114:H114)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -30662,7 +31018,7 @@
       </c>
       <c r="C124" s="2">
         <f>((D124+E124+G124+H124)*0.2)+(F124*0.3)</f>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D124" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B124)</f>
@@ -30678,7 +31034,7 @@
       </c>
       <c r="G124" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B124)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H124" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B124)</f>
@@ -30686,11 +31042,10 @@
       </c>
       <c r="I124" s="14">
         <f>SUM(D124:H124)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:D124">
     <cfRule type="top10" dxfId="9" priority="953" rank="7"/>
@@ -32273,10 +32628,10 @@
       <c r="G2" s="47" t="s">
         <v>329</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I2" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="99"/>
+      <c r="J2" s="94"/>
       <c r="K2" s="65" t="s">
         <v>276</v>
       </c>
@@ -32301,7 +32656,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="93" t="s">
         <v>335</v>
       </c>
       <c r="C3" s="72">
@@ -32312,14 +32667,14 @@
       </c>
       <c r="E3" s="70">
         <f>VLOOKUP(D3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="70" t="s">
         <v>298</v>
       </c>
       <c r="G3" s="61">
         <f>VLOOKUP(F3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>18.600000000000001</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I3" s="95" t="s">
         <v>330</v>
@@ -32344,14 +32699,14 @@
       </c>
       <c r="Q3" s="62">
         <f>VLOOKUP(P3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>298</v>
       </c>
       <c r="S3" s="63">
         <f>VLOOKUP(R3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>18.600000000000001</v>
+        <v>19.600000000000001</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
@@ -32364,7 +32719,7 @@
       </c>
       <c r="E4" s="62">
         <f>VLOOKUP(D4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="70" t="s">
         <v>224</v>
@@ -32392,14 +32747,14 @@
       </c>
       <c r="Q4" s="62">
         <f>VLOOKUP(P4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>221</v>
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -32412,14 +32767,14 @@
       </c>
       <c r="E5" s="47">
         <f>VLOOKUP(D5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>221</v>
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="I5" s="96"/>
       <c r="J5" s="66">
@@ -32440,14 +32795,14 @@
       </c>
       <c r="Q5" s="62">
         <f>VLOOKUP(P5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>304</v>
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>25</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -32460,7 +32815,7 @@
       </c>
       <c r="E6" s="47">
         <f>VLOOKUP(D6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>232</v>
@@ -32488,14 +32843,14 @@
       </c>
       <c r="Q6" s="69">
         <f>VLOOKUP(P6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>230</v>
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>18.600000000000001</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -32515,9 +32870,9 @@
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>25</v>
-      </c>
-      <c r="I7" s="97"/>
+        <v>26.8</v>
+      </c>
+      <c r="I7" s="98"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -32563,7 +32918,7 @@
       </c>
       <c r="G8" s="63">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" s="86"/>
       <c r="O8" s="48">
@@ -32574,14 +32929,14 @@
       </c>
       <c r="Q8" s="69">
         <f>VLOOKUP(P8,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R8" s="65" t="s">
         <v>316</v>
       </c>
       <c r="S8" s="71">
         <f>VLOOKUP(R8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
@@ -32594,19 +32949,19 @@
       </c>
       <c r="E9" s="65">
         <f>VLOOKUP(D9,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="70" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.5</v>
-      </c>
-      <c r="I9" s="99" t="s">
+        <v>11.5</v>
+      </c>
+      <c r="I9" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J9" s="99"/>
+      <c r="J9" s="94"/>
       <c r="K9" s="65" t="s">
         <v>276</v>
       </c>
@@ -32622,7 +32977,7 @@
       </c>
       <c r="Q9" s="69">
         <f>VLOOKUP(P9,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R9" s="65" t="s">
         <v>309</v>
@@ -32679,7 +33034,7 @@
       </c>
       <c r="S10" s="71">
         <f>VLOOKUP(R10,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>9.8000000000000007</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
@@ -32692,14 +33047,14 @@
       </c>
       <c r="E11" s="65">
         <f>VLOOKUP(D11,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="70" t="s">
         <v>48</v>
       </c>
       <c r="G11" s="61">
         <f>VLOOKUP(F11,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="I11" s="96"/>
       <c r="J11" s="66">
@@ -32720,14 +33075,14 @@
       </c>
       <c r="Q11" s="65">
         <f>VLOOKUP(P11,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R11" s="65" t="s">
         <v>314</v>
       </c>
       <c r="S11" s="71">
         <f>VLOOKUP(R11,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
@@ -32759,7 +33114,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="98"/>
+      <c r="N12" s="101"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -32795,7 +33150,7 @@
       </c>
       <c r="G13" s="61">
         <f>VLOOKUP(F13,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="66">
@@ -32824,16 +33179,16 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>228</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>24.4</v>
-      </c>
-      <c r="I14" s="97"/>
+        <v>25.8</v>
+      </c>
+      <c r="I14" s="98"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -32860,7 +33215,7 @@
       </c>
       <c r="E15" s="65">
         <f>VLOOKUP(D15,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="62" t="s">
         <v>299</v>
@@ -32886,20 +33241,20 @@
       </c>
       <c r="E16" s="65">
         <f>VLOOKUP(D16,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>230</v>
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>18.600000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="99" t="s">
+      <c r="I16" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J16" s="99"/>
+      <c r="J16" s="94"/>
       <c r="K16" s="65" t="s">
         <v>276</v>
       </c>
@@ -32960,10 +33315,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="C19" s="99"/>
+      <c r="C19" s="94"/>
       <c r="D19" s="65" t="s">
         <v>276</v>
       </c>
@@ -33014,7 +33369,7 @@
       <c r="E21" s="65" t="s">
         <v>338</v>
       </c>
-      <c r="I21" s="97"/>
+      <c r="I21" s="98"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -33026,7 +33381,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="101"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -33038,10 +33393,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="93" t="s">
+      <c r="I23" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J23" s="94"/>
+      <c r="J23" s="100"/>
       <c r="K23" s="65" t="s">
         <v>276</v>
       </c>
@@ -33124,7 +33479,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="97"/>
+      <c r="I30" s="98"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -33137,12 +33492,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -33151,6 +33500,12 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34039,7 +34394,7 @@
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C9</f>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="I7" s="6">
         <f t="shared" si="3"/>
@@ -35827,7 +36182,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C49</f>
@@ -36059,7 +36414,7 @@
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C59</f>
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="3"/>
@@ -36513,11 +36868,11 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" ref="G29" si="4">RANK(H29,$H$4:$H$37,0)</f>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C64</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I29" s="6">
         <f t="shared" ref="I29" si="5">(COUNTIF(J29:CD29,"출전")*1)</f>
@@ -37415,11 +37770,11 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C104</f>
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="6"/>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="985" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77A34C4D-EF5C-4AF0-A3BD-D981598623DB}"/>
+  <xr:revisionPtr revIDLastSave="986" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94AD0FD4-1BC1-4C96-9C14-CAA408460C5F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="416">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -2347,10 +2347,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2359,20 +2359,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16161,7 +16161,7 @@
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I114" s="6">
         <f t="shared" si="13"/>
@@ -25262,7 +25262,9 @@
       <c r="H275" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="I275" s="8"/>
+      <c r="I275" s="8" t="s">
+        <v>306</v>
+      </c>
       <c r="J275" s="8" t="s">
         <v>203</v>
       </c>
@@ -25322,125 +25324,237 @@
     </row>
   </sheetData>
   <mergeCells count="374">
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="C274:C275"/>
-    <mergeCell ref="D274:D275"/>
-    <mergeCell ref="E269:H269"/>
-    <mergeCell ref="I269:L269"/>
-    <mergeCell ref="M269:P269"/>
-    <mergeCell ref="Q269:V269"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="C270:C271"/>
-    <mergeCell ref="D270:D271"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="C272:C273"/>
-    <mergeCell ref="D272:D273"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="C228:C229"/>
-    <mergeCell ref="D228:D229"/>
-    <mergeCell ref="E221:H221"/>
-    <mergeCell ref="I221:L221"/>
-    <mergeCell ref="M221:P221"/>
-    <mergeCell ref="Q221:V221"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="D222:D223"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="D216:D217"/>
-    <mergeCell ref="E211:H211"/>
-    <mergeCell ref="I211:L211"/>
-    <mergeCell ref="M211:P211"/>
-    <mergeCell ref="Q211:V211"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="D214:D215"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="D200:D201"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="D202:D203"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="D204:D205"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E195:H195"/>
-    <mergeCell ref="I195:L195"/>
-    <mergeCell ref="M195:P195"/>
-    <mergeCell ref="Q195:V195"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="D196:D197"/>
-    <mergeCell ref="Q183:V183"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="D190:D191"/>
-    <mergeCell ref="E183:H183"/>
-    <mergeCell ref="I183:L183"/>
-    <mergeCell ref="M183:P183"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="M113:P113"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="M77:P77"/>
-    <mergeCell ref="Q89:V89"/>
-    <mergeCell ref="M89:P89"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="Q113:V113"/>
-    <mergeCell ref="Q77:V77"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="M101:P101"/>
-    <mergeCell ref="Q101:V101"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="B264:B265"/>
+    <mergeCell ref="C264:C265"/>
+    <mergeCell ref="D264:D265"/>
+    <mergeCell ref="E257:H257"/>
+    <mergeCell ref="I257:L257"/>
+    <mergeCell ref="M257:P257"/>
+    <mergeCell ref="Q257:V257"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="C258:C259"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="C260:C261"/>
+    <mergeCell ref="D260:D261"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="C252:C253"/>
+    <mergeCell ref="D252:D253"/>
+    <mergeCell ref="Q245:V245"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="C246:C247"/>
+    <mergeCell ref="D246:D247"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="C248:C249"/>
+    <mergeCell ref="D248:D249"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="C250:C251"/>
+    <mergeCell ref="D250:D251"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="C238:C239"/>
+    <mergeCell ref="D238:D239"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="C240:C241"/>
+    <mergeCell ref="D240:D241"/>
+    <mergeCell ref="E245:H245"/>
+    <mergeCell ref="I245:L245"/>
+    <mergeCell ref="M245:P245"/>
+    <mergeCell ref="E233:H233"/>
+    <mergeCell ref="I233:L233"/>
+    <mergeCell ref="M233:P233"/>
+    <mergeCell ref="Q233:V233"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="C234:C235"/>
+    <mergeCell ref="D234:D235"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="C236:C237"/>
+    <mergeCell ref="D236:D237"/>
+    <mergeCell ref="E159:H159"/>
+    <mergeCell ref="I159:L159"/>
+    <mergeCell ref="M159:P159"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="D188:D189"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="D176:D177"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="D178:D179"/>
+    <mergeCell ref="E171:H171"/>
+    <mergeCell ref="I171:L171"/>
+    <mergeCell ref="M171:P171"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="Q159:V159"/>
+    <mergeCell ref="Q171:V171"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="Q147:V147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="E147:H147"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M147:P147"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:L135"/>
+    <mergeCell ref="M135:P135"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:L125"/>
+    <mergeCell ref="M125:P125"/>
+    <mergeCell ref="Q135:V135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="Q125:V125"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:V13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="C114:C115"/>
     <mergeCell ref="D114:D115"/>
@@ -25465,237 +25579,125 @@
     <mergeCell ref="C104:C105"/>
     <mergeCell ref="D104:D105"/>
     <mergeCell ref="B106:B107"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:V13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="I135:L135"/>
-    <mergeCell ref="M135:P135"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="I125:L125"/>
-    <mergeCell ref="M125:P125"/>
-    <mergeCell ref="Q135:V135"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="Q125:V125"/>
-    <mergeCell ref="Q159:V159"/>
-    <mergeCell ref="Q171:V171"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="Q147:V147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="E147:H147"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="M147:P147"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="E159:H159"/>
-    <mergeCell ref="I159:L159"/>
-    <mergeCell ref="M159:P159"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="D160:D161"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="D188:D189"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="D162:D163"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="D172:D173"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="D176:D177"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="D178:D179"/>
-    <mergeCell ref="E171:H171"/>
-    <mergeCell ref="I171:L171"/>
-    <mergeCell ref="M171:P171"/>
-    <mergeCell ref="E233:H233"/>
-    <mergeCell ref="I233:L233"/>
-    <mergeCell ref="M233:P233"/>
-    <mergeCell ref="Q233:V233"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="C234:C235"/>
-    <mergeCell ref="D234:D235"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="C236:C237"/>
-    <mergeCell ref="D236:D237"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="C238:C239"/>
-    <mergeCell ref="D238:D239"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="C240:C241"/>
-    <mergeCell ref="D240:D241"/>
-    <mergeCell ref="E245:H245"/>
-    <mergeCell ref="I245:L245"/>
-    <mergeCell ref="M245:P245"/>
-    <mergeCell ref="Q245:V245"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="C246:C247"/>
-    <mergeCell ref="D246:D247"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="C248:C249"/>
-    <mergeCell ref="D248:D249"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="C250:C251"/>
-    <mergeCell ref="D250:D251"/>
-    <mergeCell ref="Q257:V257"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="C258:C259"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="C260:C261"/>
-    <mergeCell ref="D260:D261"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="C252:C253"/>
-    <mergeCell ref="D252:D253"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="B264:B265"/>
-    <mergeCell ref="C264:C265"/>
-    <mergeCell ref="D264:D265"/>
-    <mergeCell ref="E257:H257"/>
-    <mergeCell ref="I257:L257"/>
-    <mergeCell ref="M257:P257"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="Q113:V113"/>
+    <mergeCell ref="Q77:V77"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="M101:P101"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E195:H195"/>
+    <mergeCell ref="I195:L195"/>
+    <mergeCell ref="M195:P195"/>
+    <mergeCell ref="Q195:V195"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="D196:D197"/>
+    <mergeCell ref="Q183:V183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
+    <mergeCell ref="E183:H183"/>
+    <mergeCell ref="I183:L183"/>
+    <mergeCell ref="M183:P183"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="D200:D201"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="D204:D205"/>
+    <mergeCell ref="E211:H211"/>
+    <mergeCell ref="I211:L211"/>
+    <mergeCell ref="M211:P211"/>
+    <mergeCell ref="Q211:V211"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="D214:D215"/>
+    <mergeCell ref="Q221:V221"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="D222:D223"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="C226:C227"/>
+    <mergeCell ref="D226:D227"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="C228:C229"/>
+    <mergeCell ref="D228:D229"/>
+    <mergeCell ref="E221:H221"/>
+    <mergeCell ref="I221:L221"/>
+    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="C274:C275"/>
+    <mergeCell ref="D274:D275"/>
+    <mergeCell ref="E269:H269"/>
+    <mergeCell ref="I269:L269"/>
+    <mergeCell ref="M269:P269"/>
+    <mergeCell ref="Q269:V269"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="C270:C271"/>
+    <mergeCell ref="D270:D271"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="C272:C273"/>
+    <mergeCell ref="D272:D273"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -25831,7 +25833,7 @@
         <v>김인혁</v>
       </c>
       <c r="C4" s="2">
-        <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
+        <f t="shared" ref="C4:C35" si="0">((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
         <v>2</v>
       </c>
       <c r="D4" s="14">
@@ -25855,7 +25857,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="14">
-        <f>SUM(D4:H4)</f>
+        <f t="shared" ref="I4:I35" si="1">SUM(D4:H4)</f>
         <v>10</v>
       </c>
       <c r="J4" s="15"/>
@@ -25866,35 +25868,35 @@
         <v>351</v>
       </c>
       <c r="M4" s="21">
-        <f t="shared" ref="M4:M16" si="0">VLOOKUP(L4,$B$4:$H$137,3,FALSE)</f>
+        <f t="shared" ref="M4:M16" si="2">VLOOKUP(L4,$B$4:$H$137,3,FALSE)</f>
         <v>22</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>351</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O18" si="1">VLOOKUP(N4,$B$4:$H$137,4,FALSE)</f>
+        <f t="shared" ref="O4:O18" si="3">VLOOKUP(N4,$B$4:$H$137,4,FALSE)</f>
         <v>9</v>
       </c>
       <c r="P4" s="34" t="s">
         <v>221</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q18" si="2">VLOOKUP(P4,$B$4:$H$137,5,FALSE)</f>
+        <f t="shared" ref="Q4:Q18" si="4">VLOOKUP(P4,$B$4:$H$137,5,FALSE)</f>
         <v>16</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>322</v>
       </c>
       <c r="S4" s="55">
-        <f t="shared" ref="S4:S16" si="3">VLOOKUP(R4,$B$4:$H$137,6,FALSE)</f>
+        <f t="shared" ref="S4:S16" si="5">VLOOKUP(R4,$B$4:$H$137,6,FALSE)</f>
         <v>23</v>
       </c>
       <c r="T4" s="36" t="s">
         <v>228</v>
       </c>
       <c r="U4" s="56">
-        <f t="shared" ref="U4:U13" si="4">VLOOKUP(T4,$B$4:$H$137,7,FALSE)</f>
+        <f t="shared" ref="U4:U13" si="6">VLOOKUP(T4,$B$4:$H$137,7,FALSE)</f>
         <v>12</v>
       </c>
     </row>
@@ -25908,7 +25910,7 @@
         <v>신재경</v>
       </c>
       <c r="C5" s="2">
-        <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D5" s="14">
@@ -25932,7 +25934,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="14">
-        <f>SUM(D5:H5)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="J5" s="15"/>
@@ -25943,35 +25945,35 @@
         <v>223</v>
       </c>
       <c r="M5" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="N5" s="33" t="s">
         <v>357</v>
       </c>
       <c r="O5" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="P5" s="34" t="s">
         <v>304</v>
       </c>
       <c r="Q5" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>230</v>
       </c>
       <c r="S5" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="T5" s="36" t="s">
         <v>42</v>
       </c>
       <c r="U5" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
     </row>
@@ -25985,7 +25987,7 @@
         <v>정효태</v>
       </c>
       <c r="C6" s="2">
-        <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D6" s="14">
@@ -26009,7 +26011,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="14">
-        <f>SUM(D6:H6)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J6" s="15"/>
@@ -26020,35 +26022,35 @@
         <v>221</v>
       </c>
       <c r="M6" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="N6" s="33" t="s">
         <v>221</v>
       </c>
       <c r="O6" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="P6" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Q6" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="R6" s="35" t="s">
         <v>354</v>
       </c>
       <c r="S6" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="T6" s="36" t="s">
         <v>220</v>
       </c>
       <c r="U6" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
     </row>
@@ -26062,7 +26064,7 @@
         <v>이승민</v>
       </c>
       <c r="C7" s="2">
-        <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7" s="14">
@@ -26086,7 +26088,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f>SUM(D7:H7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J7" s="15"/>
@@ -26097,35 +26099,35 @@
         <v>231</v>
       </c>
       <c r="M7" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="N7" s="33" t="s">
         <v>53</v>
       </c>
       <c r="O7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="P7" s="34" t="s">
         <v>298</v>
       </c>
       <c r="Q7" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="R7" s="35" t="s">
         <v>360</v>
       </c>
       <c r="S7" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="T7" s="36" t="s">
         <v>354</v>
       </c>
       <c r="U7" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -26139,7 +26141,7 @@
         <v>이정석</v>
       </c>
       <c r="C8" s="2">
-        <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D8" s="14">
@@ -26163,7 +26165,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f>SUM(D8:H8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="15"/>
@@ -26174,35 +26176,35 @@
         <v>357</v>
       </c>
       <c r="M8" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>50</v>
       </c>
       <c r="O8" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P8" s="34" t="s">
         <v>376</v>
       </c>
       <c r="Q8" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="R8" s="35" t="s">
         <v>232</v>
       </c>
       <c r="S8" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="T8" s="36" t="s">
         <v>397</v>
       </c>
       <c r="U8" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -26216,7 +26218,7 @@
         <v>강종찬</v>
       </c>
       <c r="C9" s="2">
-        <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D9" s="14">
@@ -26240,7 +26242,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="14">
-        <f>SUM(D9:H9)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J9" s="15"/>
@@ -26251,35 +26253,35 @@
         <v>353</v>
       </c>
       <c r="M9" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>223</v>
       </c>
       <c r="O9" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P9" s="34" t="s">
         <v>382</v>
       </c>
       <c r="Q9" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="R9" s="35" t="s">
         <v>392</v>
       </c>
       <c r="S9" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="T9" s="36" t="s">
         <v>298</v>
       </c>
       <c r="U9" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -26293,7 +26295,7 @@
         <v>강관석</v>
       </c>
       <c r="C10" s="2">
-        <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
       <c r="D10" s="14">
@@ -26317,7 +26319,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="14">
-        <f>SUM(D10:H10)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="J10" s="15"/>
@@ -26328,35 +26330,35 @@
         <v>398</v>
       </c>
       <c r="M10" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="N10" s="33" t="s">
         <v>403</v>
       </c>
       <c r="O10" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P10" s="34" t="s">
         <v>53</v>
       </c>
       <c r="Q10" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="R10" s="35" t="s">
         <v>62</v>
       </c>
       <c r="S10" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T10" s="36" t="s">
         <v>299</v>
       </c>
       <c r="U10" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -26370,7 +26372,7 @@
         <v>강기혁</v>
       </c>
       <c r="C11" s="2">
-        <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
+        <f t="shared" si="0"/>
         <v>4.7</v>
       </c>
       <c r="D11" s="14">
@@ -26394,7 +26396,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f>SUM(D11:H11)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="J11" s="15"/>
@@ -26405,35 +26407,35 @@
         <v>228</v>
       </c>
       <c r="M11" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="N11" s="33" t="s">
         <v>353</v>
       </c>
       <c r="O11" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P11" s="34" t="s">
         <v>7</v>
       </c>
       <c r="Q11" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R11" s="35" t="s">
         <v>302</v>
       </c>
       <c r="S11" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="T11" s="36" t="s">
         <v>353</v>
       </c>
       <c r="U11" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -26447,7 +26449,7 @@
         <v>강도일</v>
       </c>
       <c r="C12" s="2">
-        <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D12" s="14">
@@ -26471,7 +26473,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="14">
-        <f>SUM(D12:H12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J12" s="15"/>
@@ -26482,35 +26484,35 @@
         <v>407</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="N12" s="33" t="s">
         <v>313</v>
       </c>
       <c r="O12" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P12" s="34" t="s">
         <v>383</v>
       </c>
       <c r="Q12" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R12" s="35" t="s">
         <v>221</v>
       </c>
       <c r="S12" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="T12" s="36" t="s">
         <v>361</v>
       </c>
       <c r="U12" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -26524,7 +26526,7 @@
         <v>강일수</v>
       </c>
       <c r="C13" s="2">
-        <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D13" s="14">
@@ -26548,7 +26550,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f>SUM(D13:H13)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -26559,35 +26561,35 @@
         <v>314</v>
       </c>
       <c r="M13" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="N13" s="33" t="s">
         <v>224</v>
       </c>
       <c r="O13" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P13" s="34" t="s">
         <v>316</v>
       </c>
       <c r="Q13" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="R13" s="35" t="s">
         <v>241</v>
       </c>
       <c r="S13" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="T13" s="36" t="s">
         <v>360</v>
       </c>
       <c r="U13" s="56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -26601,7 +26603,7 @@
         <v>구교훈</v>
       </c>
       <c r="C14" s="2">
-        <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D14" s="14">
@@ -26625,7 +26627,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f>SUM(D14:H14)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="15"/>
@@ -26636,28 +26638,28 @@
         <v>220</v>
       </c>
       <c r="M14" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="N14" s="33" t="s">
         <v>7</v>
       </c>
       <c r="O14" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P14" s="34" t="s">
         <v>313</v>
       </c>
       <c r="Q14" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="R14" s="55" t="s">
         <v>361</v>
       </c>
       <c r="S14" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="T14" s="36"/>
@@ -26673,7 +26675,7 @@
         <v>권민강</v>
       </c>
       <c r="C15" s="2">
-        <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D15" s="14">
@@ -26697,7 +26699,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f>SUM(D15:H15)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J15" s="15"/>
@@ -26708,28 +26710,28 @@
         <v>304</v>
       </c>
       <c r="M15" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="N15" s="33" t="s">
         <v>230</v>
       </c>
       <c r="O15" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P15" s="23" t="s">
         <v>403</v>
       </c>
       <c r="Q15" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="R15" s="55" t="s">
         <v>308</v>
       </c>
       <c r="S15" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="T15" s="56"/>
@@ -26745,7 +26747,7 @@
         <v>김기문</v>
       </c>
       <c r="C16" s="2">
-        <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
       <c r="D16" s="14">
@@ -26769,7 +26771,7 @@
         <v>2</v>
       </c>
       <c r="I16" s="14">
-        <f>SUM(D16:H16)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="J16" s="15"/>
@@ -26780,28 +26782,28 @@
         <v>383</v>
       </c>
       <c r="M16" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N16" s="22" t="s">
         <v>398</v>
       </c>
       <c r="O16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P16" s="23" t="s">
         <v>223</v>
       </c>
       <c r="Q16" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R16" s="55" t="s">
         <v>67</v>
       </c>
       <c r="S16" s="55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="T16" s="56"/>
@@ -26817,7 +26819,7 @@
         <v>김기태</v>
       </c>
       <c r="C17" s="2">
-        <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="D17" s="14">
@@ -26841,7 +26843,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="14">
-        <f>SUM(D17:H17)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="J17" s="15"/>
@@ -26854,14 +26856,14 @@
         <v>304</v>
       </c>
       <c r="O17" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P17" s="23" t="s">
         <v>299</v>
       </c>
       <c r="Q17" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R17" s="55"/>
@@ -26879,7 +26881,7 @@
         <v>김덕준</v>
       </c>
       <c r="C18" s="2">
-        <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D18" s="14">
@@ -26903,7 +26905,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f>SUM(D18:H18)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="15"/>
@@ -26916,14 +26918,14 @@
         <v>360</v>
       </c>
       <c r="O18" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P18" s="23" t="s">
         <v>231</v>
       </c>
       <c r="Q18" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R18" s="55"/>
@@ -26941,7 +26943,7 @@
         <v>김도원</v>
       </c>
       <c r="C19" s="2">
-        <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D19" s="14">
@@ -26965,7 +26967,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f>SUM(D19:H19)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
@@ -26980,7 +26982,7 @@
         <v>김동인</v>
       </c>
       <c r="C20" s="2">
-        <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D20" s="14">
@@ -27004,7 +27006,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f>SUM(D20:H20)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="15"/>
@@ -27019,7 +27021,7 @@
         <v>김류현</v>
       </c>
       <c r="C21" s="2">
-        <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D21" s="14">
@@ -27043,7 +27045,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="14">
-        <f>SUM(D21:H21)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J21" s="15"/>
@@ -27058,7 +27060,7 @@
         <v>김민섭</v>
       </c>
       <c r="C22" s="2">
-        <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D22" s="14">
@@ -27082,7 +27084,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f>SUM(D22:H22)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J22" s="15"/>
@@ -27097,7 +27099,7 @@
         <v>김민찬</v>
       </c>
       <c r="C23" s="2">
-        <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D23" s="14">
@@ -27121,7 +27123,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f>SUM(D23:H23)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="15"/>
@@ -27136,7 +27138,7 @@
         <v>김범기</v>
       </c>
       <c r="C24" s="2">
-        <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D24" s="14">
@@ -27160,7 +27162,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f>SUM(D24:H24)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="15"/>
@@ -27175,7 +27177,7 @@
         <v>김병준</v>
       </c>
       <c r="C25" s="2">
-        <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D25" s="14">
@@ -27199,7 +27201,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f>SUM(D25:H25)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J25" s="15"/>
@@ -27214,7 +27216,7 @@
         <v>김부건</v>
       </c>
       <c r="C26" s="2">
-        <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="D26" s="14">
@@ -27238,7 +27240,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="14">
-        <f>SUM(D26:H26)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="J26" s="15"/>
@@ -27253,7 +27255,7 @@
         <v>김성수</v>
       </c>
       <c r="C27" s="2">
-        <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
       <c r="D27" s="14">
@@ -27277,7 +27279,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <f>SUM(D27:H27)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="J27" s="15"/>
@@ -27292,7 +27294,7 @@
         <v>김성준</v>
       </c>
       <c r="C28" s="2">
-        <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
+        <f t="shared" si="0"/>
         <v>10.4</v>
       </c>
       <c r="D28" s="14">
@@ -27316,7 +27318,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="14">
-        <f>SUM(D28:H28)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="J28" s="15"/>
@@ -27331,7 +27333,7 @@
         <v>김송환</v>
       </c>
       <c r="C29" s="2">
-        <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.0999999999999996</v>
       </c>
       <c r="D29" s="14">
@@ -27355,7 +27357,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="14">
-        <f>SUM(D29:H29)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="J29" s="15"/>
@@ -27370,7 +27372,7 @@
         <v>김영태</v>
       </c>
       <c r="C30" s="2">
-        <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D30" s="14">
@@ -27394,7 +27396,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <f>SUM(D30:H30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J30" s="15"/>
@@ -27409,7 +27411,7 @@
         <v>김용빈</v>
       </c>
       <c r="C31" s="2">
-        <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D31" s="14">
@@ -27433,7 +27435,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <f>SUM(D31:H31)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J31" s="15"/>
@@ -27448,7 +27450,7 @@
         <v>김용현</v>
       </c>
       <c r="C32" s="2">
-        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="D32" s="14">
@@ -27472,7 +27474,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="14">
-        <f>SUM(D32:H32)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="J32" s="15"/>
@@ -27487,7 +27489,7 @@
         <v>김우인</v>
       </c>
       <c r="C33" s="2">
-        <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
+        <f t="shared" si="0"/>
         <v>4.8000000000000007</v>
       </c>
       <c r="D33" s="14">
@@ -27511,7 +27513,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="14">
-        <f>SUM(D33:H33)</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="J33" s="15"/>
@@ -27526,7 +27528,7 @@
         <v>김종준</v>
       </c>
       <c r="C34" s="2">
-        <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D34" s="14">
@@ -27550,7 +27552,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="14">
-        <f>SUM(D34:H34)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J34" s="15"/>
@@ -27565,7 +27567,7 @@
         <v>김종혁</v>
       </c>
       <c r="C35" s="2">
-        <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
       <c r="D35" s="14">
@@ -27589,7 +27591,7 @@
         <v>2</v>
       </c>
       <c r="I35" s="14">
-        <f>SUM(D35:H35)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="J35" s="15"/>
@@ -27604,7 +27606,7 @@
         <v>김준영</v>
       </c>
       <c r="C36" s="2">
-        <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
         <v>0</v>
       </c>
       <c r="D36" s="14">
@@ -27628,7 +27630,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="14">
-        <f>SUM(D36:H36)</f>
+        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
         <v>0</v>
       </c>
       <c r="J36" s="15"/>
@@ -27643,7 +27645,7 @@
         <v>김진형</v>
       </c>
       <c r="C37" s="2">
-        <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D37" s="14">
@@ -27667,7 +27669,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="14">
-        <f>SUM(D37:H37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J37" s="15"/>
@@ -27682,7 +27684,7 @@
         <v>김진호</v>
       </c>
       <c r="C38" s="2">
-        <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
+        <f t="shared" si="7"/>
         <v>6.2</v>
       </c>
       <c r="D38" s="14">
@@ -27706,7 +27708,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="14">
-        <f>SUM(D38:H38)</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="J38" s="15"/>
@@ -27721,7 +27723,7 @@
         <v>김태성</v>
       </c>
       <c r="C39" s="2">
-        <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D39" s="14">
@@ -27745,7 +27747,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="14">
-        <f>SUM(D39:H39)</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="J39" s="15"/>
@@ -27760,7 +27762,7 @@
         <v>김태양</v>
       </c>
       <c r="C40" s="2">
-        <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D40" s="14">
@@ -27784,7 +27786,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="14">
-        <f>SUM(D40:H40)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J40" s="15"/>
@@ -27799,7 +27801,7 @@
         <v>김태완</v>
       </c>
       <c r="C41" s="2">
-        <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D41" s="14">
@@ -27823,7 +27825,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="14">
-        <f>SUM(D41:H41)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J41" s="15"/>
@@ -27838,7 +27840,7 @@
         <v>김태호</v>
       </c>
       <c r="C42" s="2">
-        <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D42" s="14">
@@ -27862,7 +27864,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="14">
-        <f>SUM(D42:H42)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J42" s="15"/>
@@ -27877,7 +27879,7 @@
         <v>김현우</v>
       </c>
       <c r="C43" s="2">
-        <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D43" s="14">
@@ -27901,7 +27903,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="14">
-        <f>SUM(D43:H43)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J43" s="15"/>
@@ -27916,7 +27918,7 @@
         <v>김형원</v>
       </c>
       <c r="C44" s="2">
-        <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D44" s="14">
@@ -27940,7 +27942,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="14">
-        <f>SUM(D44:H44)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J44" s="15"/>
@@ -27955,7 +27957,7 @@
         <v>노민준</v>
       </c>
       <c r="C45" s="2">
-        <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
+        <f t="shared" si="7"/>
         <v>4.2</v>
       </c>
       <c r="D45" s="14">
@@ -27979,7 +27981,7 @@
         <v>3</v>
       </c>
       <c r="I45" s="14">
-        <f>SUM(D45:H45)</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="J45" s="15"/>
@@ -27994,7 +27996,7 @@
         <v>노성호</v>
       </c>
       <c r="C46" s="2">
-        <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="D46" s="14">
@@ -28018,7 +28020,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="14">
-        <f>SUM(D46:H46)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J46" s="15"/>
@@ -28033,7 +28035,7 @@
         <v>류서진</v>
       </c>
       <c r="C47" s="2">
-        <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.4</v>
       </c>
       <c r="D47" s="14">
@@ -28057,7 +28059,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="14">
-        <f>SUM(D47:H47)</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="J47" s="15"/>
@@ -28072,7 +28074,7 @@
         <v>마창기</v>
       </c>
       <c r="C48" s="2">
-        <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D48" s="14">
@@ -28096,7 +28098,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="14">
-        <f>SUM(D48:H48)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J48" s="15"/>
@@ -28111,7 +28113,7 @@
         <v>문준수</v>
       </c>
       <c r="C49" s="2">
-        <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
+        <f t="shared" si="7"/>
         <v>3.2</v>
       </c>
       <c r="D49" s="14">
@@ -28135,7 +28137,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="14">
-        <f>SUM(D49:H49)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="J49" s="15"/>
@@ -28150,7 +28152,7 @@
         <v>민건호</v>
       </c>
       <c r="C50" s="2">
-        <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D50" s="14">
@@ -28174,7 +28176,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="14">
-        <f>SUM(D50:H50)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J50" s="15"/>
@@ -28189,7 +28191,7 @@
         <v>박수천</v>
       </c>
       <c r="C51" s="2">
-        <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D51" s="14">
@@ -28213,7 +28215,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="14">
-        <f>SUM(D51:H51)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J51" s="15"/>
@@ -28228,7 +28230,7 @@
         <v>박정호</v>
       </c>
       <c r="C52" s="2">
-        <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D52" s="14">
@@ -28252,7 +28254,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="14">
-        <f>SUM(D52:H52)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J52" s="15"/>
@@ -28267,7 +28269,7 @@
         <v>박주연</v>
       </c>
       <c r="C53" s="2">
-        <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="D53" s="14">
@@ -28291,7 +28293,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="14">
-        <f>SUM(D53:H53)</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="J53" s="15"/>
@@ -28306,7 +28308,7 @@
         <v>박주현</v>
       </c>
       <c r="C54" s="2">
-        <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D54" s="14">
@@ -28330,7 +28332,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="14">
-        <f>SUM(D54:H54)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J54" s="15"/>
@@ -28345,7 +28347,7 @@
         <v>박준영</v>
       </c>
       <c r="C55" s="2">
-        <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="D55" s="14">
@@ -28369,7 +28371,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="14">
-        <f>SUM(D55:H55)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J55" s="15"/>
@@ -28384,7 +28386,7 @@
         <v>박태현</v>
       </c>
       <c r="C56" s="2">
-        <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D56" s="14">
@@ -28408,7 +28410,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="14">
-        <f>SUM(D56:H56)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J56" s="15"/>
@@ -28423,7 +28425,7 @@
         <v>박하빈</v>
       </c>
       <c r="C57" s="2">
-        <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D57" s="14">
@@ -28447,7 +28449,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="14">
-        <f>SUM(D57:H57)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J57" s="15"/>
@@ -28462,7 +28464,7 @@
         <v>박형기</v>
       </c>
       <c r="C58" s="2">
-        <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D58" s="14">
@@ -28486,7 +28488,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="14">
-        <f>SUM(D58:H58)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J58" s="15"/>
@@ -28501,7 +28503,7 @@
         <v>손경호</v>
       </c>
       <c r="C59" s="2">
-        <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
+        <f t="shared" si="7"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="D59" s="14">
@@ -28525,7 +28527,7 @@
         <v>5</v>
       </c>
       <c r="I59" s="14">
-        <f>SUM(D59:H59)</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="J59" s="15"/>
@@ -28540,7 +28542,7 @@
         <v>송윤상</v>
       </c>
       <c r="C60" s="2">
-        <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="D60" s="14">
@@ -28564,7 +28566,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="14">
-        <f>SUM(D60:H60)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J60" s="15"/>
@@ -28579,7 +28581,7 @@
         <v>신기웅</v>
       </c>
       <c r="C61" s="2">
-        <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
+        <f t="shared" si="7"/>
         <v>1.9000000000000001</v>
       </c>
       <c r="D61" s="14">
@@ -28603,7 +28605,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="14">
-        <f>SUM(D61:H61)</f>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="J61" s="15"/>
@@ -28618,7 +28620,7 @@
         <v>신종훈</v>
       </c>
       <c r="C62" s="2">
-        <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D62" s="14">
@@ -28642,7 +28644,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="14">
-        <f>SUM(D62:H62)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J62" s="15"/>
@@ -28657,7 +28659,7 @@
         <v>안진혁</v>
       </c>
       <c r="C63" s="2">
-        <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D63" s="14">
@@ -28681,7 +28683,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f>SUM(D63:H63)</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="J63" s="15"/>
@@ -28696,7 +28698,7 @@
         <v>양진웅</v>
       </c>
       <c r="C64" s="2">
-        <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="D64" s="14">
@@ -28720,7 +28722,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="14">
-        <f>SUM(D64:H64)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="J64" s="15"/>
@@ -28735,7 +28737,7 @@
         <v>오상준</v>
       </c>
       <c r="C65" s="2">
-        <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
+        <f t="shared" si="7"/>
         <v>3.3000000000000003</v>
       </c>
       <c r="D65" s="14">
@@ -28759,7 +28761,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="14">
-        <f>SUM(D65:H65)</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="J65" s="15"/>
@@ -28774,7 +28776,7 @@
         <v>오성찬</v>
       </c>
       <c r="C66" s="2">
-        <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.3</v>
       </c>
       <c r="D66" s="14">
@@ -28798,7 +28800,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f>SUM(D66:H66)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J66" s="15"/>
@@ -28813,7 +28815,7 @@
         <v>오우영</v>
       </c>
       <c r="C67" s="2">
-        <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="D67" s="14">
@@ -28837,7 +28839,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f>SUM(D67:H67)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="J67" s="15"/>
@@ -28852,7 +28854,7 @@
         <v>오운용</v>
       </c>
       <c r="C68" s="2">
-        <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
         <v>0</v>
       </c>
       <c r="D68" s="14">
@@ -28876,7 +28878,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="14">
-        <f>SUM(D68:H68)</f>
+        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
         <v>0</v>
       </c>
       <c r="J68" s="15"/>
@@ -28891,7 +28893,7 @@
         <v>오준서</v>
       </c>
       <c r="C69" s="2">
-        <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D69" s="14">
@@ -28915,7 +28917,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f>SUM(D69:H69)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J69" s="15"/>
@@ -28930,7 +28932,7 @@
         <v>우보광</v>
       </c>
       <c r="C70" s="2">
-        <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D70" s="14">
@@ -28954,7 +28956,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="14">
-        <f>SUM(D70:H70)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J70" s="15"/>
@@ -28969,7 +28971,7 @@
         <v>유상근</v>
       </c>
       <c r="C71" s="2">
-        <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="D71" s="14">
@@ -28993,7 +28995,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="14">
-        <f>SUM(D71:H71)</f>
+        <f t="shared" si="10"/>
         <v>25</v>
       </c>
       <c r="J71" s="15"/>
@@ -29008,7 +29010,7 @@
         <v>유우진</v>
       </c>
       <c r="C72" s="2">
-        <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D72" s="14">
@@ -29032,7 +29034,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f>SUM(D72:H72)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J72" s="15"/>
@@ -29047,7 +29049,7 @@
         <v>유인상</v>
       </c>
       <c r="C73" s="2">
-        <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D73" s="14">
@@ -29071,7 +29073,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f>SUM(D73:H73)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J73" s="15"/>
@@ -29086,7 +29088,7 @@
         <v>유정훈</v>
       </c>
       <c r="C74" s="2">
-        <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D74" s="14">
@@ -29110,7 +29112,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="14">
-        <f>SUM(D74:H74)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J74" s="15"/>
@@ -29125,7 +29127,7 @@
         <v>유진효</v>
       </c>
       <c r="C75" s="2">
-        <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D75" s="14">
@@ -29149,7 +29151,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="14">
-        <f>SUM(D75:H75)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J75" s="15"/>
@@ -29164,7 +29166,7 @@
         <v>윤원택</v>
       </c>
       <c r="C76" s="2">
-        <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D76" s="14">
@@ -29188,7 +29190,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="14">
-        <f>SUM(D76:H76)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J76" s="15"/>
@@ -29203,7 +29205,7 @@
         <v>윤창현</v>
       </c>
       <c r="C77" s="2">
-        <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.6</v>
       </c>
       <c r="D77" s="14">
@@ -29227,7 +29229,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="14">
-        <f>SUM(D77:H77)</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="J77" s="15"/>
@@ -29242,7 +29244,7 @@
         <v>윤현기</v>
       </c>
       <c r="C78" s="2">
-        <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="D78" s="14">
@@ -29266,7 +29268,7 @@
         <v>1</v>
       </c>
       <c r="I78" s="14">
-        <f>SUM(D78:H78)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J78" s="15"/>
@@ -29281,7 +29283,7 @@
         <v>이경석</v>
       </c>
       <c r="C79" s="2">
-        <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D79" s="14">
@@ -29305,7 +29307,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="14">
-        <f>SUM(D79:H79)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J79" s="15"/>
@@ -29320,7 +29322,7 @@
         <v>이민재</v>
       </c>
       <c r="C80" s="2">
-        <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D80" s="14">
@@ -29344,7 +29346,7 @@
         <v>3</v>
       </c>
       <c r="I80" s="14">
-        <f>SUM(D80:H80)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J80" s="15"/>
@@ -29359,7 +29361,7 @@
         <v>이병현</v>
       </c>
       <c r="C81" s="2">
-        <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D81" s="14">
@@ -29383,7 +29385,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="14">
-        <f>SUM(D81:H81)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J81" s="15"/>
@@ -29398,7 +29400,7 @@
         <v>이상민</v>
       </c>
       <c r="C82" s="2">
-        <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D82" s="14">
@@ -29422,7 +29424,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="14">
-        <f>SUM(D82:H82)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J82" s="15"/>
@@ -29437,7 +29439,7 @@
         <v>이상현</v>
       </c>
       <c r="C83" s="2">
-        <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
+        <f t="shared" si="9"/>
         <v>2.5</v>
       </c>
       <c r="D83" s="14">
@@ -29461,7 +29463,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="14">
-        <f>SUM(D83:H83)</f>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J83" s="15"/>
@@ -29476,7 +29478,7 @@
         <v>이새샘</v>
       </c>
       <c r="C84" s="2">
-        <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
+        <f t="shared" si="9"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="D84" s="14">
@@ -29500,7 +29502,7 @@
         <v>2</v>
       </c>
       <c r="I84" s="14">
-        <f>SUM(D84:H84)</f>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="J84" s="15"/>
@@ -29515,7 +29517,7 @@
         <v>이성관</v>
       </c>
       <c r="C85" s="2">
-        <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="D85" s="14">
@@ -29539,7 +29541,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="14">
-        <f>SUM(D85:H85)</f>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="J85" s="15"/>
@@ -29554,7 +29556,7 @@
         <v>이승윤</v>
       </c>
       <c r="C86" s="2">
-        <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D86" s="14">
@@ -29578,7 +29580,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="14">
-        <f>SUM(D86:H86)</f>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J86" s="15"/>
@@ -29593,7 +29595,7 @@
         <v>이연길</v>
       </c>
       <c r="C87" s="2">
-        <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D87" s="14">
@@ -29617,7 +29619,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="14">
-        <f>SUM(D87:H87)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J87" s="15"/>
@@ -29632,7 +29634,7 @@
         <v>이영준</v>
       </c>
       <c r="C88" s="2">
-        <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D88" s="14">
@@ -29656,7 +29658,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="14">
-        <f>SUM(D88:H88)</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="J88" s="15"/>
@@ -29671,7 +29673,7 @@
         <v>이정범</v>
       </c>
       <c r="C89" s="2">
-        <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D89" s="14">
@@ -29695,7 +29697,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="14">
-        <f>SUM(D89:H89)</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="J89" s="15"/>
@@ -29710,7 +29712,7 @@
         <v>이종수</v>
       </c>
       <c r="C90" s="2">
-        <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D90" s="14">
@@ -29734,7 +29736,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="14">
-        <f>SUM(D90:H90)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J90" s="15"/>
@@ -29749,7 +29751,7 @@
         <v>이찬솔</v>
       </c>
       <c r="C91" s="2">
-        <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D91" s="14">
@@ -29773,7 +29775,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="14">
-        <f>SUM(D91:H91)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J91" s="15"/>
@@ -29788,7 +29790,7 @@
         <v>이찬영</v>
       </c>
       <c r="C92" s="2">
-        <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D92" s="14">
@@ -29812,7 +29814,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="14">
-        <f>SUM(D92:H92)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J92" s="15"/>
@@ -29827,7 +29829,7 @@
         <v>이태한</v>
       </c>
       <c r="C93" s="2">
-        <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D93" s="14">
@@ -29851,7 +29853,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="14">
-        <f>SUM(D93:H93)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J93" s="15"/>
@@ -29866,7 +29868,7 @@
         <v>이현택</v>
       </c>
       <c r="C94" s="2">
-        <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D94" s="14">
@@ -29890,7 +29892,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="14">
-        <f>SUM(D94:H94)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J94" s="15"/>
@@ -29905,7 +29907,7 @@
         <v>이호행</v>
       </c>
       <c r="C95" s="2">
-        <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.8</v>
       </c>
       <c r="D95" s="14">
@@ -29929,7 +29931,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="14">
-        <f>SUM(D95:H95)</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="J95" s="15"/>
@@ -29944,7 +29946,7 @@
         <v>임수철</v>
       </c>
       <c r="C96" s="2">
-        <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D96" s="14">
@@ -29968,7 +29970,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="14">
-        <f>SUM(D96:H96)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J96" s="15"/>
@@ -29983,7 +29985,7 @@
         <v>임태환</v>
       </c>
       <c r="C97" s="2">
-        <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
+        <f t="shared" si="9"/>
         <v>3.7</v>
       </c>
       <c r="D97" s="14">
@@ -30007,7 +30009,7 @@
         <v>1</v>
       </c>
       <c r="I97" s="14">
-        <f>SUM(D97:H97)</f>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="J97" s="15"/>
@@ -30022,7 +30024,7 @@
         <v>장희도</v>
       </c>
       <c r="C98" s="2">
-        <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D98" s="14">
@@ -30046,7 +30048,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="14">
-        <f>SUM(D98:H98)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J98" s="15"/>
@@ -30061,7 +30063,7 @@
         <v>장희준</v>
       </c>
       <c r="C99" s="2">
-        <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D99" s="14">
@@ -30085,7 +30087,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="14">
-        <f>SUM(D99:H99)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J99" s="15"/>
@@ -30100,7 +30102,7 @@
         <v>전나현</v>
       </c>
       <c r="C100" s="2">
-        <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="D100" s="14">
@@ -30124,7 +30126,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f>SUM(D100:H100)</f>
+        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
         <v>9</v>
       </c>
       <c r="J100" s="15"/>
@@ -30139,7 +30141,7 @@
         <v>전성환</v>
       </c>
       <c r="C101" s="2">
-        <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D101" s="14">
@@ -30163,7 +30165,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f>SUM(D101:H101)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J101" s="15"/>
@@ -30178,7 +30180,7 @@
         <v>전하늘</v>
       </c>
       <c r="C102" s="2">
-        <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.7</v>
       </c>
       <c r="D102" s="14">
@@ -30202,7 +30204,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="14">
-        <f>SUM(D102:H102)</f>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="J102" s="15"/>
@@ -30217,7 +30219,7 @@
         <v>정민수</v>
       </c>
       <c r="C103" s="2">
-        <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
+        <f t="shared" si="11"/>
         <v>4.8000000000000007</v>
       </c>
       <c r="D103" s="14">
@@ -30241,7 +30243,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f>SUM(D103:H103)</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="J103" s="15"/>
@@ -30256,7 +30258,7 @@
         <v>정재명</v>
       </c>
       <c r="C104" s="2">
-        <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="D104" s="14">
@@ -30280,7 +30282,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f>SUM(D104:H104)</f>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="J104" s="15"/>
@@ -30295,7 +30297,7 @@
         <v>정현서</v>
       </c>
       <c r="C105" s="2">
-        <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D105" s="14">
@@ -30319,7 +30321,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="14">
-        <f>SUM(D105:H105)</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
     </row>
@@ -30333,7 +30335,7 @@
         <v>조진한</v>
       </c>
       <c r="C106" s="2">
-        <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
+        <f t="shared" si="11"/>
         <v>5.8000000000000007</v>
       </c>
       <c r="D106" s="14">
@@ -30357,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="14">
-        <f>SUM(D106:H106)</f>
+        <f t="shared" si="12"/>
         <v>22</v>
       </c>
     </row>
@@ -30371,7 +30373,7 @@
         <v>조현우</v>
       </c>
       <c r="C107" s="2">
-        <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="D107" s="14">
@@ -30395,7 +30397,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f>SUM(D107:H107)</f>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
     </row>
@@ -30409,7 +30411,7 @@
         <v>차승원</v>
       </c>
       <c r="C108" s="2">
-        <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="D108" s="14">
@@ -30433,7 +30435,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f>SUM(D108:H108)</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
     </row>
@@ -30447,7 +30449,7 @@
         <v>최령창</v>
       </c>
       <c r="C109" s="2">
-        <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
+        <f t="shared" si="11"/>
         <v>4.6000000000000005</v>
       </c>
       <c r="D109" s="14">
@@ -30471,7 +30473,7 @@
         <v>2</v>
       </c>
       <c r="I109" s="14">
-        <f>SUM(D109:H109)</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
     </row>
@@ -30485,7 +30487,7 @@
         <v>최승훈</v>
       </c>
       <c r="C110" s="2">
-        <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D110" s="14">
@@ -30509,7 +30511,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="14">
-        <f>SUM(D110:H110)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -30523,7 +30525,7 @@
         <v>한상규</v>
       </c>
       <c r="C111" s="2">
-        <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="D111" s="14">
@@ -30547,7 +30549,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f>SUM(D111:H111)</f>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
     </row>
@@ -30561,7 +30563,7 @@
         <v>한의현</v>
       </c>
       <c r="C112" s="2">
-        <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.6</v>
       </c>
       <c r="D112" s="14">
@@ -30585,7 +30587,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f>SUM(D112:H112)</f>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
     </row>
@@ -30599,7 +30601,7 @@
         <v>한중희</v>
       </c>
       <c r="C113" s="2">
-        <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.8</v>
       </c>
       <c r="D113" s="14">
@@ -30623,7 +30625,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="14">
-        <f>SUM(D113:H113)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
     </row>
@@ -30637,8 +30639,8 @@
         <v>허동혁</v>
       </c>
       <c r="C114" s="2">
-        <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
-        <v>2.4</v>
+        <f t="shared" si="11"/>
+        <v>2.6</v>
       </c>
       <c r="D114" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B114)</f>
@@ -30646,7 +30648,7 @@
       </c>
       <c r="E114" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B114)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B114)</f>
@@ -30661,8 +30663,8 @@
         <v>1</v>
       </c>
       <c r="I114" s="14">
-        <f>SUM(D114:H114)</f>
-        <v>11</v>
+        <f t="shared" si="12"/>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -30675,7 +30677,7 @@
         <v>홍석준</v>
       </c>
       <c r="C115" s="2">
-        <f>((D115+E115+G115+H115)*0.2)+(F115*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.6</v>
       </c>
       <c r="D115" s="14">
@@ -30699,7 +30701,7 @@
         <v>1</v>
       </c>
       <c r="I115" s="14">
-        <f>SUM(D115:H115)</f>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
     </row>
@@ -30713,7 +30715,7 @@
         <v>홍현석</v>
       </c>
       <c r="C116" s="2">
-        <f>((D116+E116+G116+H116)*0.2)+(F116*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D116" s="14">
@@ -30737,7 +30739,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="14">
-        <f>SUM(D116:H116)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -30751,7 +30753,7 @@
         <v>황건호</v>
       </c>
       <c r="C117" s="2">
-        <f>((D117+E117+G117+H117)*0.2)+(F117*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
       <c r="D117" s="14">
@@ -30775,7 +30777,7 @@
         <v>0</v>
       </c>
       <c r="I117" s="14">
-        <f>SUM(D117:H117)</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
     </row>
@@ -30789,7 +30791,7 @@
         <v>황석원</v>
       </c>
       <c r="C118" s="2">
-        <f>((D118+E118+G118+H118)*0.2)+(F118*0.3)</f>
+        <f t="shared" si="11"/>
         <v>3.0000000000000004</v>
       </c>
       <c r="D118" s="14">
@@ -30813,7 +30815,7 @@
         <v>1</v>
       </c>
       <c r="I118" s="14">
-        <f>SUM(D118:H118)</f>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
     </row>
@@ -30827,7 +30829,7 @@
         <v>황재순</v>
       </c>
       <c r="C119" s="2">
-        <f>((D119+E119+G119+H119)*0.2)+(F119*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D119" s="14">
@@ -30851,7 +30853,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f>SUM(D119:H119)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -30865,7 +30867,7 @@
         <v>황철우</v>
       </c>
       <c r="C120" s="2">
-        <f>((D120+E120+G120+H120)*0.2)+(F120*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D120" s="14">
@@ -30889,7 +30891,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="14">
-        <f>SUM(D120:H120)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -30903,7 +30905,7 @@
         <v>김민성</v>
       </c>
       <c r="C121" s="2">
-        <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D121" s="14">
@@ -30927,7 +30929,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="14">
-        <f>SUM(D121:H121)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -30941,7 +30943,7 @@
         <v>송명섭</v>
       </c>
       <c r="C122" s="2">
-        <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D122" s="14">
@@ -30965,7 +30967,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f>SUM(D122:H122)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -30979,7 +30981,7 @@
         <v>최경영</v>
       </c>
       <c r="C123" s="2">
-        <f>((D123+E123+G123+H123)*0.2)+(F123*0.3)</f>
+        <f t="shared" si="11"/>
         <v>3.2</v>
       </c>
       <c r="D123" s="14">
@@ -31003,7 +31005,7 @@
         <v>10</v>
       </c>
       <c r="I123" s="14">
-        <f>SUM(D123:H123)</f>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
     </row>
@@ -31017,7 +31019,7 @@
         <v>박지수</v>
       </c>
       <c r="C124" s="2">
-        <f>((D124+E124+G124+H124)*0.2)+(F124*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D124" s="14">
@@ -31041,7 +31043,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="14">
-        <f>SUM(D124:H124)</f>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
     </row>
@@ -32628,10 +32630,10 @@
       <c r="G2" s="47" t="s">
         <v>329</v>
       </c>
-      <c r="I2" s="94" t="s">
+      <c r="I2" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="94"/>
+      <c r="J2" s="99"/>
       <c r="K2" s="65" t="s">
         <v>276</v>
       </c>
@@ -32656,7 +32658,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="100" t="s">
         <v>335</v>
       </c>
       <c r="C3" s="72">
@@ -32872,7 +32874,7 @@
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
         <v>26.8</v>
       </c>
-      <c r="I7" s="98"/>
+      <c r="I7" s="97"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -32958,10 +32960,10 @@
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
         <v>11.5</v>
       </c>
-      <c r="I9" s="94" t="s">
+      <c r="I9" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J9" s="94"/>
+      <c r="J9" s="99"/>
       <c r="K9" s="65" t="s">
         <v>276</v>
       </c>
@@ -33082,7 +33084,7 @@
       </c>
       <c r="S11" s="71">
         <f>VLOOKUP(R11,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
@@ -33114,7 +33116,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="101"/>
+      <c r="N12" s="98"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -33188,7 +33190,7 @@
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
         <v>25.8</v>
       </c>
-      <c r="I14" s="98"/>
+      <c r="I14" s="97"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -33251,10 +33253,10 @@
         <v>19.8</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="94" t="s">
+      <c r="I16" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J16" s="94"/>
+      <c r="J16" s="99"/>
       <c r="K16" s="65" t="s">
         <v>276</v>
       </c>
@@ -33315,10 +33317,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="C19" s="94"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="65" t="s">
         <v>276</v>
       </c>
@@ -33369,7 +33371,7 @@
       <c r="E21" s="65" t="s">
         <v>338</v>
       </c>
-      <c r="I21" s="98"/>
+      <c r="I21" s="97"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -33381,7 +33383,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="97"/>
+      <c r="B22" s="101"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -33393,10 +33395,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="99" t="s">
+      <c r="I23" s="93" t="s">
         <v>248</v>
       </c>
-      <c r="J23" s="100"/>
+      <c r="J23" s="94"/>
       <c r="K23" s="65" t="s">
         <v>276</v>
       </c>
@@ -33479,7 +33481,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="98"/>
+      <c r="I30" s="97"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -33492,6 +33494,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -33500,12 +33508,6 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="986" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94AD0FD4-1BC1-4C96-9C14-CAA408460C5F}"/>
+  <xr:revisionPtr revIDLastSave="1131" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52BFECD-F442-41B8-BEC8-5AC9673C18EE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2900" uniqueCount="441">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -1560,15 +1560,115 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>대상</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>김도원</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>오준서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정재명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김진호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김성준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김부건</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김용현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강종찬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>황석원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정민수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이성관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최경영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이경석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오우영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유인상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김기문</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상민</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한상규</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강기혁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박주연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전나현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정현서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이승윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>노민준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이정범</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5Q</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6Q</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3010,7 +3110,7 @@
     <row r="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D1" s="53">
         <f>COUNTIF(D4:D159,"발주")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1" s="18" t="s">
         <v>87</v>
@@ -3169,7 +3269,7 @@
     <row r="2" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D2" s="53">
         <f>COUNTIF(D4:D159,"지급")</f>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E2" s="53">
         <f>COUNTIF(E4:E142,"지급")</f>
@@ -3177,7 +3277,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>14.688888888888888</v>
+        <v>15.377777777777778</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3300,7 +3400,7 @@
       </c>
       <c r="AM2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AN2" s="1">
         <f t="shared" si="0"/>
@@ -3498,7 +3598,9 @@
       <c r="AL3" s="4">
         <v>46254</v>
       </c>
-      <c r="AM3" s="4"/>
+      <c r="AM3" s="4">
+        <v>46261</v>
+      </c>
       <c r="AN3" s="4"/>
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
@@ -3709,7 +3811,7 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ref="G5:G68" si="2">RANK(H5,$H$4:$H$124,0)</f>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -3822,7 +3924,7 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
@@ -3917,7 +4019,7 @@
         <v>319</v>
       </c>
       <c r="D7" s="54">
-        <f>COUNTA(W7:AN7)</f>
+        <f>COUNTA(AF7:AS7)</f>
         <v>0</v>
       </c>
       <c r="E7" s="54"/>
@@ -3926,7 +4028,7 @@
       </c>
       <c r="G7" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C7</f>
@@ -4029,7 +4131,7 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C8</f>
@@ -4132,15 +4234,15 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I9" s="6">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
@@ -4183,7 +4285,9 @@
       <c r="AL9" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AM9" s="2"/>
+      <c r="AM9" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN9" s="2"/>
       <c r="AO9" s="2"/>
       <c r="AP9" s="2"/>
@@ -4382,15 +4486,15 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
-        <v>15.7</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>349</v>
@@ -4443,7 +4547,9 @@
       <c r="AJ11" s="2"/>
       <c r="AK11" s="2"/>
       <c r="AL11" s="2"/>
-      <c r="AM11" s="2"/>
+      <c r="AM11" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN11" s="2"/>
       <c r="AO11" s="2"/>
       <c r="AP11" s="2"/>
@@ -4499,7 +4605,7 @@
         <v>2025</v>
       </c>
       <c r="D12" s="54">
-        <f t="shared" ref="D12:D15" si="4">COUNTA(W12:AN12)</f>
+        <f t="shared" ref="D12:D15" si="4">COUNTA(AF12:AS12)</f>
         <v>0</v>
       </c>
       <c r="E12" s="54"/>
@@ -4508,7 +4614,7 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="2"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C12</f>
@@ -4614,7 +4720,7 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C13</f>
@@ -4718,7 +4824,7 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C14</f>
@@ -4927,15 +5033,15 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -4982,7 +5088,9 @@
         <v>349</v>
       </c>
       <c r="AL16" s="2"/>
-      <c r="AM16" s="2"/>
+      <c r="AM16" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN16" s="2"/>
       <c r="AO16" s="2"/>
       <c r="AP16" s="2"/>
@@ -5179,7 +5287,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C18</f>
@@ -5268,17 +5376,20 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C19" s="58">
         <v>2026</v>
       </c>
-      <c r="D19" s="54"/>
+      <c r="D19" s="54">
+        <f>COUNTA(AF19:AS19)</f>
+        <v>0</v>
+      </c>
       <c r="E19" s="54"/>
       <c r="F19" s="60"/>
       <c r="G19" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
@@ -5381,15 +5492,15 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="6">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>349</v>
@@ -5428,7 +5539,9 @@
       <c r="AJ20" s="2"/>
       <c r="AK20" s="2"/>
       <c r="AL20" s="2"/>
-      <c r="AM20" s="2"/>
+      <c r="AM20" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN20" s="2"/>
       <c r="AO20" s="2"/>
       <c r="AP20" s="2"/>
@@ -5484,7 +5597,7 @@
         <v>2026</v>
       </c>
       <c r="D21" s="54">
-        <f t="shared" ref="D21" si="5">COUNTA(W21:AN21)</f>
+        <f>COUNTA(AF21:AS21)</f>
         <v>1</v>
       </c>
       <c r="E21" s="54"/>
@@ -5493,7 +5606,7 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C21</f>
@@ -5598,7 +5711,7 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H22" s="6">
         <f>I22+개인기록Sheet!C22</f>
@@ -5703,7 +5816,7 @@
         <v>2024</v>
       </c>
       <c r="D23" s="54">
-        <f t="shared" ref="D23:D24" si="6">COUNTA(W23:AN23)</f>
+        <f t="shared" ref="D23:D24" si="5">COUNTA(AF23:AS23)</f>
         <v>0</v>
       </c>
       <c r="E23" s="54"/>
@@ -5712,7 +5825,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C23</f>
@@ -5807,7 +5920,7 @@
         <v>2022</v>
       </c>
       <c r="D24" s="54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E24" s="54"/>
@@ -5816,7 +5929,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
@@ -5919,7 +6032,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
@@ -6024,15 +6137,15 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="2"/>
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -6071,7 +6184,9 @@
       <c r="AJ26" s="2"/>
       <c r="AK26" s="2"/>
       <c r="AL26" s="2"/>
-      <c r="AM26" s="2"/>
+      <c r="AM26" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN26" s="2"/>
       <c r="AO26" s="2"/>
       <c r="AP26" s="2"/>
@@ -6135,7 +6250,7 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
@@ -6262,11 +6377,11 @@
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
-        <v>33.4</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
@@ -6343,7 +6458,9 @@
       <c r="AL28" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AM28" s="2"/>
+      <c r="AM28" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN28" s="2"/>
       <c r="AO28" s="2"/>
       <c r="AP28" s="2"/>
@@ -6407,15 +6524,15 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C29</f>
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="I29" s="6">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -6460,7 +6577,9 @@
         <v>349</v>
       </c>
       <c r="AL29" s="2"/>
-      <c r="AM29" s="2"/>
+      <c r="AM29" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN29" s="2"/>
       <c r="AO29" s="2"/>
       <c r="AP29" s="2"/>
@@ -6516,7 +6635,7 @@
         <v>2023</v>
       </c>
       <c r="D30" s="54">
-        <f>COUNTA(W30:AN30)</f>
+        <f>COUNTA(AF30:AS30)</f>
         <v>0</v>
       </c>
       <c r="E30" s="54"/>
@@ -6525,7 +6644,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6737,15 +6856,15 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>15.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
@@ -6800,7 +6919,9 @@
       </c>
       <c r="AK32" s="2"/>
       <c r="AL32" s="2"/>
-      <c r="AM32" s="2"/>
+      <c r="AM32" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN32" s="2"/>
       <c r="AO32" s="2"/>
       <c r="AP32" s="2"/>
@@ -6864,15 +6985,15 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
-        <v>25.8</v>
+        <v>26.8</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>349</v>
@@ -6945,7 +7066,9 @@
       <c r="AL33" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AM33" s="2"/>
+      <c r="AM33" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN33" s="2"/>
       <c r="AO33" s="2"/>
       <c r="AP33" s="2"/>
@@ -7009,7 +7132,7 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
@@ -7257,7 +7380,7 @@
         <v>2025</v>
       </c>
       <c r="D36" s="54">
-        <f t="shared" ref="D36:D37" si="7">COUNTA(W36:AN36)</f>
+        <f t="shared" ref="D36:D37" si="6">COUNTA(AF36:AS36)</f>
         <v>0</v>
       </c>
       <c r="E36" s="54"/>
@@ -7266,7 +7389,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C36</f>
@@ -7361,7 +7484,7 @@
         <v>2025</v>
       </c>
       <c r="D37" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E37" s="54"/>
@@ -7370,7 +7493,7 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
@@ -7477,11 +7600,11 @@
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="I38" s="6">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -7544,7 +7667,9 @@
         <v>349</v>
       </c>
       <c r="AL38" s="2"/>
-      <c r="AM38" s="2"/>
+      <c r="AM38" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN38" s="2"/>
       <c r="AO38" s="2"/>
       <c r="AP38" s="2"/>
@@ -7608,7 +7733,7 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H39" s="6">
         <f>I39+개인기록Sheet!C39</f>
@@ -7717,7 +7842,7 @@
         <v>2025</v>
       </c>
       <c r="D40" s="54">
-        <f>COUNTA(W40:AN40)</f>
+        <f>COUNTA(AF40:AS40)</f>
         <v>0</v>
       </c>
       <c r="E40" s="54"/>
@@ -7726,7 +7851,7 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H40" s="6">
         <f>I40+개인기록Sheet!C40</f>
@@ -7928,7 +8053,7 @@
         <v>319</v>
       </c>
       <c r="D42" s="54">
-        <f t="shared" ref="D42:D43" si="8">COUNTA(W42:AN42)</f>
+        <f t="shared" ref="D42:D43" si="7">COUNTA(AF42:AS42)</f>
         <v>0</v>
       </c>
       <c r="E42" s="54"/>
@@ -7937,7 +8062,7 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H42" s="6">
         <f>I42+개인기록Sheet!C42</f>
@@ -8032,7 +8157,7 @@
         <v>2024</v>
       </c>
       <c r="D43" s="54">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E43" s="54"/>
@@ -8041,7 +8166,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
@@ -8255,11 +8380,11 @@
       </c>
       <c r="H45" s="6">
         <f>I45+개인기록Sheet!C45</f>
-        <v>21.2</v>
+        <v>22.4</v>
       </c>
       <c r="I45" s="6">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
@@ -8324,7 +8449,9 @@
       </c>
       <c r="AK45" s="2"/>
       <c r="AL45" s="2"/>
-      <c r="AM45" s="2"/>
+      <c r="AM45" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN45" s="2"/>
       <c r="AO45" s="2"/>
       <c r="AP45" s="2"/>
@@ -8380,7 +8507,7 @@
         <v>2026</v>
       </c>
       <c r="D46" s="54" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="E46" s="54"/>
       <c r="F46" s="2" t="s">
@@ -8388,7 +8515,7 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
@@ -8497,7 +8624,7 @@
         <v>2024</v>
       </c>
       <c r="D47" s="54" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="E47" s="54"/>
       <c r="F47" s="2" t="s">
@@ -8505,7 +8632,7 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
@@ -8610,14 +8737,14 @@
         <v>2026</v>
       </c>
       <c r="D48" s="54">
-        <f>COUNTA(W48:AN48)</f>
+        <f>COUNTA(AF48:AS48)</f>
         <v>0</v>
       </c>
       <c r="E48" s="54"/>
       <c r="F48" s="60"/>
       <c r="G48" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H48" s="6">
         <f>I48+개인기록Sheet!C48</f>
@@ -8724,11 +8851,11 @@
       </c>
       <c r="H49" s="6">
         <f>I49+개인기록Sheet!C49</f>
-        <v>17.2</v>
+        <v>18.2</v>
       </c>
       <c r="I49" s="6">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
@@ -8787,7 +8914,9 @@
       </c>
       <c r="AK49" s="2"/>
       <c r="AL49" s="2"/>
-      <c r="AM49" s="2"/>
+      <c r="AM49" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN49" s="2"/>
       <c r="AO49" s="2"/>
       <c r="AP49" s="2"/>
@@ -8843,7 +8972,7 @@
         <v>2022</v>
       </c>
       <c r="D50" s="54">
-        <f t="shared" ref="D50:D52" si="9">COUNTA(W50:AN50)</f>
+        <f t="shared" ref="D50:D52" si="8">COUNTA(AF50:AS50)</f>
         <v>2</v>
       </c>
       <c r="E50" s="54"/>
@@ -8951,7 +9080,7 @@
         <v>2025</v>
       </c>
       <c r="D51" s="54">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E51" s="54"/>
@@ -8960,7 +9089,7 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
@@ -9055,7 +9184,7 @@
         <v>2022</v>
       </c>
       <c r="D52" s="54">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E52" s="54"/>
@@ -9064,7 +9193,7 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H52" s="6">
         <f>I52+개인기록Sheet!C52</f>
@@ -9167,15 +9296,15 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H53" s="6">
         <f>I53+개인기록Sheet!C53</f>
-        <v>16.2</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I53" s="6">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -9234,7 +9363,9 @@
       <c r="AL53" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AM53" s="2"/>
+      <c r="AM53" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN53" s="2"/>
       <c r="AO53" s="2"/>
       <c r="AP53" s="2"/>
@@ -9290,7 +9421,7 @@
         <v>2023</v>
       </c>
       <c r="D54" s="54">
-        <f t="shared" ref="D54:D58" si="10">COUNTA(W54:AN54)</f>
+        <f t="shared" ref="D54:D58" si="9">COUNTA(AF54:AS54)</f>
         <v>0</v>
       </c>
       <c r="E54" s="54"/>
@@ -9299,7 +9430,7 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H54" s="6">
         <f>I54+개인기록Sheet!C54</f>
@@ -9394,8 +9525,8 @@
         <v>2026</v>
       </c>
       <c r="D55" s="54">
-        <f t="shared" si="10"/>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="E55" s="54"/>
       <c r="F55" s="2" t="s">
@@ -9403,7 +9534,7 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="2"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
@@ -9506,8 +9637,8 @@
         <v>2026</v>
       </c>
       <c r="D56" s="54">
-        <f t="shared" si="10"/>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="E56" s="54"/>
       <c r="F56" s="2" t="s">
@@ -9515,7 +9646,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
@@ -9620,7 +9751,7 @@
         <v>2023</v>
       </c>
       <c r="D57" s="54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E57" s="54"/>
@@ -9629,7 +9760,7 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
@@ -9724,7 +9855,7 @@
         <v>2022</v>
       </c>
       <c r="D58" s="54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E58" s="54"/>
@@ -9733,7 +9864,7 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H58" s="6">
         <f>I58+개인기록Sheet!C58</f>
@@ -9836,7 +9967,7 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
@@ -10072,7 +10203,7 @@
         <v>2025</v>
       </c>
       <c r="D61" s="54" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="E61" s="54"/>
       <c r="F61" s="2" t="s">
@@ -10080,7 +10211,7 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
@@ -10191,7 +10322,7 @@
         <v>2024</v>
       </c>
       <c r="D62" s="54">
-        <f>COUNTA(W62:AN62)</f>
+        <f>COUNTA(AF62:AS62)</f>
         <v>0</v>
       </c>
       <c r="E62" s="54"/>
@@ -10200,7 +10331,7 @@
       </c>
       <c r="G62" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H62" s="6">
         <f>I62+개인기록Sheet!C62</f>
@@ -10410,7 +10541,7 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H64" s="6">
         <f>I64+개인기록Sheet!C64</f>
@@ -10523,7 +10654,7 @@
         <v>2026</v>
       </c>
       <c r="D65" s="54" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="E65" s="54"/>
       <c r="F65" s="2" t="s">
@@ -10531,7 +10662,7 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
@@ -10642,8 +10773,8 @@
         <v>2026</v>
       </c>
       <c r="D66" s="54">
-        <f>COUNTA(W66:AN66)</f>
-        <v>1</v>
+        <f>COUNTA(AF66:AS66)</f>
+        <v>0</v>
       </c>
       <c r="E66" s="54"/>
       <c r="F66" s="2" t="s">
@@ -10651,7 +10782,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
@@ -10762,15 +10893,15 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="I67" s="6">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
@@ -10815,7 +10946,9 @@
       <c r="AJ67" s="2"/>
       <c r="AK67" s="2"/>
       <c r="AL67" s="2"/>
-      <c r="AM67" s="2"/>
+      <c r="AM67" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN67" s="2"/>
       <c r="AO67" s="2"/>
       <c r="AP67" s="2"/>
@@ -10871,7 +11004,7 @@
         <v>319</v>
       </c>
       <c r="D68" s="54">
-        <f t="shared" ref="D68:D70" si="11">COUNTA(W68:AN68)</f>
+        <f t="shared" ref="D68:D70" si="10">COUNTA(AF68:AS68)</f>
         <v>0</v>
       </c>
       <c r="E68" s="54"/>
@@ -10880,7 +11013,7 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H68" s="6">
         <f>I68+개인기록Sheet!C68</f>
@@ -10969,22 +11102,25 @@
         <v>66</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C69" s="57"/>
-      <c r="D69" s="54"/>
+      <c r="D69" s="54">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="E69" s="54"/>
       <c r="F69" s="60"/>
       <c r="G69" s="2">
-        <f t="shared" ref="G69:G124" si="12">RANK(H69,$H$4:$H$124,0)</f>
-        <v>89</v>
+        <f t="shared" ref="G69:G124" si="11">RANK(H69,$H$4:$H$124,0)</f>
+        <v>90</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
         <v>0</v>
       </c>
       <c r="I69" s="6">
-        <f t="shared" ref="I69:I124" si="13">(COUNTIF(J69:CD69,"출전")*1)</f>
+        <f t="shared" ref="I69:I124" si="12">(COUNTIF(J69:CD69,"출전")*1)</f>
         <v>0</v>
       </c>
       <c r="J69" s="2"/>
@@ -11072,7 +11208,7 @@
         <v>2025</v>
       </c>
       <c r="D70" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E70" s="54"/>
@@ -11080,15 +11216,15 @@
         <v>37</v>
       </c>
       <c r="G70" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
         <v>0</v>
       </c>
       <c r="I70" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J70" s="2"/>
@@ -11183,15 +11319,15 @@
         <v>37</v>
       </c>
       <c r="G71" s="2">
-        <f t="shared" si="12"/>
-        <v>8</v>
+        <f t="shared" si="11"/>
+        <v>9</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
         <v>20</v>
       </c>
       <c r="I71" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="J71" s="2"/>
@@ -11309,23 +11445,23 @@
         <v>2026</v>
       </c>
       <c r="D72" s="54">
-        <f>COUNTA(W72:AN72)</f>
-        <v>3</v>
+        <f>COUNTA(AF72:AS72)</f>
+        <v>0</v>
       </c>
       <c r="E72" s="54"/>
       <c r="F72" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G72" s="2">
-        <f t="shared" si="12"/>
-        <v>62</v>
+        <f t="shared" si="11"/>
+        <v>64</v>
       </c>
       <c r="H72" s="6">
         <f>I72+개인기록Sheet!C72</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="I72" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="J72" s="2"/>
@@ -11428,16 +11564,16 @@
         <v>37</v>
       </c>
       <c r="G73" s="2">
-        <f t="shared" si="12"/>
-        <v>57</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="H73" s="6">
         <f>I73+개인기록Sheet!C73</f>
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" si="13"/>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>6</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -11478,7 +11614,9 @@
         <v>349</v>
       </c>
       <c r="AL73" s="2"/>
-      <c r="AM73" s="2"/>
+      <c r="AM73" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN73" s="2"/>
       <c r="AO73" s="2"/>
       <c r="AP73" s="2"/>
@@ -11541,16 +11679,16 @@
         <v>37</v>
       </c>
       <c r="G74" s="2">
-        <f t="shared" si="12"/>
-        <v>45</v>
+        <f t="shared" si="11"/>
+        <v>42</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
-        <v>7.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I74" s="6">
-        <f t="shared" si="13"/>
-        <v>6</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
@@ -11593,7 +11731,9 @@
       </c>
       <c r="AK74" s="2"/>
       <c r="AL74" s="2"/>
-      <c r="AM74" s="2"/>
+      <c r="AM74" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN74" s="2"/>
       <c r="AO74" s="2"/>
       <c r="AP74" s="2"/>
@@ -11649,7 +11789,7 @@
         <v>319</v>
       </c>
       <c r="D75" s="54">
-        <f>COUNTA(W75:AN75)</f>
+        <f>COUNTA(AF75:AS75)</f>
         <v>0</v>
       </c>
       <c r="E75" s="54"/>
@@ -11657,15 +11797,15 @@
         <v>37</v>
       </c>
       <c r="G75" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
         <v>0</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J75" s="2"/>
@@ -11760,15 +11900,15 @@
         <v>37</v>
       </c>
       <c r="G76" s="2">
-        <f t="shared" si="12"/>
-        <v>51</v>
+        <f t="shared" si="11"/>
+        <v>53</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
         <v>6.2</v>
       </c>
       <c r="I76" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="J76" s="2"/>
@@ -11873,15 +12013,15 @@
         <v>37</v>
       </c>
       <c r="G77" s="2">
-        <f t="shared" si="12"/>
-        <v>54</v>
+        <f t="shared" si="11"/>
+        <v>58</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
         <v>5.6</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="J77" s="2"/>
@@ -11977,22 +12117,22 @@
         <v>2026</v>
       </c>
       <c r="D78" s="54" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="E78" s="54"/>
       <c r="F78" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G78" s="2">
-        <f t="shared" si="12"/>
-        <v>47</v>
+        <f t="shared" si="11"/>
+        <v>49</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
         <v>7.1</v>
       </c>
       <c r="I78" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
       <c r="J78" s="2"/>
@@ -12092,24 +12232,24 @@
         <v>2025</v>
       </c>
       <c r="D79" s="54">
-        <f t="shared" ref="D79:D80" si="14">COUNTA(W79:AN79)</f>
-        <v>0</v>
+        <f t="shared" ref="D79:D80" si="13">COUNTA(AF79:AS79)</f>
+        <v>1</v>
       </c>
       <c r="E79" s="54"/>
       <c r="F79" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G79" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>80</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I79" s="6">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
@@ -12140,7 +12280,9 @@
       <c r="AJ79" s="2"/>
       <c r="AK79" s="2"/>
       <c r="AL79" s="2"/>
-      <c r="AM79" s="2"/>
+      <c r="AM79" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN79" s="2"/>
       <c r="AO79" s="2"/>
       <c r="AP79" s="2"/>
@@ -12196,15 +12338,15 @@
         <v>2023</v>
       </c>
       <c r="D80" s="54">
-        <f t="shared" si="14"/>
-        <v>2</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="E80" s="54"/>
       <c r="F80" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G80" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>72</v>
       </c>
       <c r="H80" s="6">
@@ -12212,7 +12354,7 @@
         <v>2.6</v>
       </c>
       <c r="I80" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="J80" s="2"/>
@@ -12311,15 +12453,15 @@
         <v>37</v>
       </c>
       <c r="G81" s="2">
-        <f t="shared" si="12"/>
-        <v>38</v>
+        <f t="shared" si="11"/>
+        <v>40</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
         <v>9</v>
       </c>
       <c r="I81" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="J81" s="2"/>
@@ -12430,16 +12572,16 @@
         <v>37</v>
       </c>
       <c r="G82" s="2">
-        <f t="shared" si="12"/>
-        <v>62</v>
+        <f t="shared" si="11"/>
+        <v>55</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
-        <v>4.4000000000000004</v>
+        <v>6</v>
       </c>
       <c r="I82" s="6">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
@@ -12478,7 +12620,9 @@
       <c r="AJ82" s="2"/>
       <c r="AK82" s="2"/>
       <c r="AL82" s="2"/>
-      <c r="AM82" s="2"/>
+      <c r="AM82" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN82" s="2"/>
       <c r="AO82" s="2"/>
       <c r="AP82" s="2"/>
@@ -12541,16 +12685,16 @@
         <v>37</v>
       </c>
       <c r="G83" s="2">
-        <f t="shared" si="12"/>
-        <v>27</v>
+        <f t="shared" si="11"/>
+        <v>24</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="I83" s="6">
-        <f t="shared" si="13"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
@@ -12599,7 +12743,9 @@
       <c r="AL83" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AM83" s="2"/>
+      <c r="AM83" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN83" s="2"/>
       <c r="AO83" s="2"/>
       <c r="AP83" s="2"/>
@@ -12662,15 +12808,15 @@
         <v>37</v>
       </c>
       <c r="G84" s="2">
-        <f t="shared" si="12"/>
-        <v>28</v>
+        <f t="shared" si="11"/>
+        <v>31</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
         <v>11.4</v>
       </c>
       <c r="I84" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="J84" s="2"/>
@@ -12783,16 +12929,16 @@
         <v>37</v>
       </c>
       <c r="G85" s="2">
-        <f t="shared" si="12"/>
-        <v>36</v>
+        <f t="shared" si="11"/>
+        <v>34</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="I85" s="6">
-        <f t="shared" si="13"/>
-        <v>8</v>
+        <f t="shared" si="12"/>
+        <v>9</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
@@ -12839,7 +12985,9 @@
       </c>
       <c r="AK85" s="2"/>
       <c r="AL85" s="2"/>
-      <c r="AM85" s="2"/>
+      <c r="AM85" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN85" s="2"/>
       <c r="AO85" s="2"/>
       <c r="AP85" s="2"/>
@@ -12902,16 +13050,16 @@
         <v>37</v>
       </c>
       <c r="G86" s="2">
-        <f t="shared" si="12"/>
-        <v>30</v>
+        <f t="shared" si="11"/>
+        <v>28</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="I86" s="6">
-        <f t="shared" si="13"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
@@ -12960,7 +13108,9 @@
       <c r="AL86" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AM86" s="2"/>
+      <c r="AM86" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN86" s="2"/>
       <c r="AO86" s="2"/>
       <c r="AP86" s="2"/>
@@ -13023,15 +13173,15 @@
         <v>37</v>
       </c>
       <c r="G87" s="2">
-        <f t="shared" si="12"/>
-        <v>62</v>
+        <f t="shared" si="11"/>
+        <v>64</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="I87" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="J87" s="2"/>
@@ -13127,23 +13277,23 @@
         <v>2026</v>
       </c>
       <c r="D88" s="54" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="E88" s="54"/>
       <c r="F88" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G88" s="2">
-        <f t="shared" si="12"/>
-        <v>48</v>
+        <f t="shared" si="11"/>
+        <v>43</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="I88" s="6">
-        <f t="shared" si="13"/>
-        <v>6</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
@@ -13186,7 +13336,9 @@
       <c r="AJ88" s="2"/>
       <c r="AK88" s="2"/>
       <c r="AL88" s="2"/>
-      <c r="AM88" s="2"/>
+      <c r="AM88" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN88" s="2"/>
       <c r="AO88" s="2"/>
       <c r="AP88" s="2"/>
@@ -13249,16 +13401,16 @@
         <v>37</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="12"/>
-        <v>57</v>
+        <f t="shared" si="11"/>
+        <v>52</v>
       </c>
       <c r="H89" s="6">
         <f>I89+개인기록Sheet!C89</f>
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="I89" s="6">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
@@ -13297,7 +13449,9 @@
       <c r="AJ89" s="2"/>
       <c r="AK89" s="2"/>
       <c r="AL89" s="2"/>
-      <c r="AM89" s="2"/>
+      <c r="AM89" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN89" s="2"/>
       <c r="AO89" s="2"/>
       <c r="AP89" s="2"/>
@@ -13360,15 +13514,15 @@
         <v>37</v>
       </c>
       <c r="G90" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
         <v>0</v>
       </c>
       <c r="I90" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J90" s="2"/>
@@ -13456,23 +13610,23 @@
         <v>2026</v>
       </c>
       <c r="D91" s="54">
-        <f t="shared" ref="D91" si="15">COUNTA(W91:AN91)</f>
-        <v>2</v>
+        <f>COUNTA(AF91:AS91)</f>
+        <v>0</v>
       </c>
       <c r="E91" s="54"/>
       <c r="F91" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="12"/>
-        <v>67</v>
+        <f t="shared" si="11"/>
+        <v>68</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
         <v>4</v>
       </c>
       <c r="I91" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="J91" s="2"/>
@@ -13573,7 +13727,7 @@
         <v>37</v>
       </c>
       <c r="G92" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>69</v>
       </c>
       <c r="H92" s="6">
@@ -13581,7 +13735,7 @@
         <v>3.4</v>
       </c>
       <c r="I92" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="J92" s="2"/>
@@ -13675,7 +13829,7 @@
         <v>2024</v>
       </c>
       <c r="D93" s="54">
-        <f t="shared" ref="D93:D94" si="16">COUNTA(W93:AN93)</f>
+        <f t="shared" ref="D93:D94" si="14">COUNTA(AF93:AS93)</f>
         <v>0</v>
       </c>
       <c r="E93" s="54"/>
@@ -13683,15 +13837,15 @@
         <v>37</v>
       </c>
       <c r="G93" s="2">
-        <f t="shared" si="12"/>
-        <v>84</v>
+        <f t="shared" si="11"/>
+        <v>85</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
         <v>1</v>
       </c>
       <c r="I93" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J93" s="2"/>
@@ -13781,7 +13935,7 @@
         <v>2026</v>
       </c>
       <c r="D94" s="54">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="E94" s="54"/>
@@ -13789,15 +13943,15 @@
         <v>37</v>
       </c>
       <c r="G94" s="2">
-        <f t="shared" si="12"/>
-        <v>84</v>
+        <f t="shared" si="11"/>
+        <v>85</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
         <v>1</v>
       </c>
       <c r="I94" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J94" s="2"/>
@@ -13894,15 +14048,15 @@
         <v>37</v>
       </c>
       <c r="G95" s="2">
-        <f t="shared" si="12"/>
-        <v>59</v>
+        <f t="shared" si="11"/>
+        <v>62</v>
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
         <v>4.8</v>
       </c>
       <c r="I95" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="J95" s="2"/>
@@ -14005,15 +14159,15 @@
         <v>37</v>
       </c>
       <c r="G96" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
         <v>0</v>
       </c>
       <c r="I96" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J96" s="2"/>
@@ -14108,15 +14262,15 @@
         <v>37</v>
       </c>
       <c r="G97" s="2">
-        <f t="shared" si="12"/>
-        <v>21</v>
+        <f t="shared" si="11"/>
+        <v>22</v>
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
         <v>13.7</v>
       </c>
       <c r="I97" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="J97" s="2"/>
@@ -14231,15 +14385,15 @@
         <v>37</v>
       </c>
       <c r="G98" s="2">
-        <f t="shared" si="12"/>
-        <v>84</v>
+        <f t="shared" si="11"/>
+        <v>85</v>
       </c>
       <c r="H98" s="6">
         <f>I98+개인기록Sheet!C98</f>
         <v>1</v>
       </c>
       <c r="I98" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J98" s="2"/>
@@ -14329,7 +14483,7 @@
         <v>2022</v>
       </c>
       <c r="D99" s="54">
-        <f>COUNTA(W99:AN99)</f>
+        <f>COUNTA(AF99:AS99)</f>
         <v>0</v>
       </c>
       <c r="E99" s="54"/>
@@ -14337,15 +14491,15 @@
         <v>37</v>
       </c>
       <c r="G99" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
       <c r="H99" s="6">
         <f>I99+개인기록Sheet!C99</f>
         <v>0</v>
       </c>
       <c r="I99" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J99" s="2"/>
@@ -14440,16 +14594,16 @@
         <v>37</v>
       </c>
       <c r="G100" s="2">
-        <f t="shared" si="12"/>
-        <v>25</v>
+        <f t="shared" si="11"/>
+        <v>23</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="I100" s="6">
-        <f t="shared" si="13"/>
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>11</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -14500,7 +14654,9 @@
       <c r="AL100" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AM100" s="2"/>
+      <c r="AM100" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN100" s="2"/>
       <c r="AO100" s="2"/>
       <c r="AP100" s="2"/>
@@ -14556,7 +14712,7 @@
         <v>2022</v>
       </c>
       <c r="D101" s="54">
-        <f>COUNTA(W101:AN101)</f>
+        <f>COUNTA(AF101:AS101)</f>
         <v>0</v>
       </c>
       <c r="E101" s="54"/>
@@ -14564,15 +14720,15 @@
         <v>37</v>
       </c>
       <c r="G101" s="2">
-        <f t="shared" si="12"/>
-        <v>83</v>
+        <f t="shared" si="11"/>
+        <v>84</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
         <v>1.2</v>
       </c>
       <c r="I101" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J101" s="2"/>
@@ -14669,15 +14825,15 @@
         <v>37</v>
       </c>
       <c r="G102" s="2">
-        <f t="shared" si="12"/>
-        <v>61</v>
+        <f t="shared" si="11"/>
+        <v>63</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
         <v>4.7</v>
       </c>
       <c r="I102" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="J102" s="2"/>
@@ -14780,16 +14936,16 @@
         <v>37</v>
       </c>
       <c r="G103" s="2">
-        <f t="shared" si="12"/>
-        <v>9</v>
+        <f t="shared" si="11"/>
+        <v>7</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="I103" s="6">
-        <f t="shared" si="13"/>
-        <v>15</v>
+        <f t="shared" si="12"/>
+        <v>16</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
@@ -14850,7 +15006,9 @@
       </c>
       <c r="AK103" s="2"/>
       <c r="AL103" s="2"/>
-      <c r="AM103" s="2"/>
+      <c r="AM103" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN103" s="2"/>
       <c r="AO103" s="2"/>
       <c r="AP103" s="2"/>
@@ -14913,16 +15071,16 @@
         <v>37</v>
       </c>
       <c r="G104" s="2">
-        <f t="shared" si="12"/>
-        <v>20</v>
+        <f t="shared" si="11"/>
+        <v>19</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
-        <v>14.4</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="I104" s="6">
-        <f t="shared" si="13"/>
-        <v>12</v>
+        <f t="shared" si="12"/>
+        <v>13</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
@@ -14977,7 +15135,9 @@
       <c r="AL104" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AM104" s="2"/>
+      <c r="AM104" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN104" s="2"/>
       <c r="AO104" s="2"/>
       <c r="AP104" s="2"/>
@@ -15040,16 +15200,16 @@
         <v>37</v>
       </c>
       <c r="G105" s="2">
-        <f t="shared" si="12"/>
-        <v>41</v>
+        <f t="shared" si="11"/>
+        <v>38</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
-        <v>8.1999999999999993</v>
+        <v>9.5</v>
       </c>
       <c r="I105" s="6">
-        <f t="shared" si="13"/>
-        <v>7</v>
+        <f t="shared" si="12"/>
+        <v>8</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
@@ -15094,7 +15254,9 @@
       <c r="AJ105" s="2"/>
       <c r="AK105" s="2"/>
       <c r="AL105" s="2"/>
-      <c r="AM105" s="2"/>
+      <c r="AM105" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN105" s="2"/>
       <c r="AO105" s="2"/>
       <c r="AP105" s="2"/>
@@ -15157,7 +15319,7 @@
         <v>37</v>
       </c>
       <c r="G106" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H106" s="6">
@@ -15165,7 +15327,7 @@
         <v>26.8</v>
       </c>
       <c r="I106" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>21</v>
       </c>
       <c r="J106" s="2" t="s">
@@ -15302,7 +15464,7 @@
         <v>37</v>
       </c>
       <c r="G107" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="H107" s="6">
@@ -15310,7 +15472,7 @@
         <v>19.399999999999999</v>
       </c>
       <c r="I107" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>17</v>
       </c>
       <c r="J107" s="2" t="s">
@@ -15439,15 +15601,15 @@
         <v>37</v>
       </c>
       <c r="G108" s="2">
-        <f t="shared" si="12"/>
-        <v>52</v>
+        <f t="shared" si="11"/>
+        <v>55</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
         <v>6</v>
       </c>
       <c r="I108" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="J108" s="2" t="s">
@@ -15552,16 +15714,16 @@
         <v>37</v>
       </c>
       <c r="G109" s="2">
-        <f t="shared" si="12"/>
-        <v>19</v>
+        <f t="shared" si="11"/>
+        <v>20</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
-        <v>14.600000000000001</v>
+        <v>15.600000000000001</v>
       </c>
       <c r="I109" s="6">
-        <f t="shared" si="13"/>
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>11</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>349</v>
@@ -15612,7 +15774,9 @@
       </c>
       <c r="AK109" s="2"/>
       <c r="AL109" s="2"/>
-      <c r="AM109" s="2"/>
+      <c r="AM109" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN109" s="2"/>
       <c r="AO109" s="2"/>
       <c r="AP109" s="2"/>
@@ -15668,7 +15832,7 @@
         <v>2021</v>
       </c>
       <c r="D110" s="54">
-        <f>COUNTA(W110:AN110)</f>
+        <f>COUNTA(AF110:AS110)</f>
         <v>0</v>
       </c>
       <c r="E110" s="54"/>
@@ -15676,15 +15840,15 @@
         <v>37</v>
       </c>
       <c r="G110" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
         <v>0</v>
       </c>
       <c r="I110" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J110" s="2"/>
@@ -15779,16 +15943,16 @@
         <v>37</v>
       </c>
       <c r="G111" s="2">
-        <f t="shared" si="12"/>
-        <v>16</v>
+        <f t="shared" si="11"/>
+        <v>17</v>
       </c>
       <c r="H111" s="6">
         <f>I111+개인기록Sheet!C111</f>
-        <v>15.8</v>
+        <v>17.2</v>
       </c>
       <c r="I111" s="6">
-        <f t="shared" si="13"/>
-        <v>13</v>
+        <f t="shared" si="12"/>
+        <v>14</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>349</v>
@@ -15845,7 +16009,9 @@
         <v>349</v>
       </c>
       <c r="AL111" s="2"/>
-      <c r="AM111" s="2"/>
+      <c r="AM111" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN111" s="2"/>
       <c r="AO111" s="2"/>
       <c r="AP111" s="2"/>
@@ -15908,15 +16074,15 @@
         <v>37</v>
       </c>
       <c r="G112" s="2">
-        <f t="shared" si="12"/>
-        <v>23</v>
+        <f t="shared" si="11"/>
+        <v>25</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
         <v>12.6</v>
       </c>
       <c r="I112" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>11</v>
       </c>
       <c r="J112" s="2" t="s">
@@ -16033,15 +16199,15 @@
         <v>37</v>
       </c>
       <c r="G113" s="2">
-        <f t="shared" si="12"/>
-        <v>26</v>
+        <f t="shared" si="11"/>
+        <v>30</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
         <v>11.8</v>
       </c>
       <c r="I113" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="J113" s="2" t="s">
@@ -16156,15 +16322,15 @@
         <v>37</v>
       </c>
       <c r="G114" s="2">
-        <f t="shared" si="12"/>
-        <v>40</v>
+        <f t="shared" si="11"/>
+        <v>41</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
         <v>8.6</v>
       </c>
       <c r="I114" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
       <c r="J114" s="2" t="s">
@@ -16271,15 +16437,15 @@
         <v>37</v>
       </c>
       <c r="G115" s="2">
-        <f t="shared" si="12"/>
-        <v>49</v>
+        <f t="shared" si="11"/>
+        <v>51</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
         <v>6.6</v>
       </c>
       <c r="I115" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="J115" s="2"/>
@@ -16384,7 +16550,7 @@
         <v>37</v>
       </c>
       <c r="G116" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>78</v>
       </c>
       <c r="H116" s="6">
@@ -16392,7 +16558,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="I116" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="J116" s="2"/>
@@ -16491,15 +16657,15 @@
         <v>37</v>
       </c>
       <c r="G117" s="2">
-        <f t="shared" si="12"/>
-        <v>43</v>
+        <f t="shared" si="11"/>
+        <v>46</v>
       </c>
       <c r="H117" s="6">
         <f>I117+개인기록Sheet!C117</f>
         <v>7.5</v>
       </c>
       <c r="I117" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="J117" s="2"/>
@@ -16604,16 +16770,16 @@
         <v>37</v>
       </c>
       <c r="G118" s="2">
-        <f t="shared" si="12"/>
-        <v>22</v>
+        <f t="shared" si="11"/>
+        <v>21</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="I118" s="6">
-        <f t="shared" si="13"/>
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>11</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
@@ -16664,7 +16830,9 @@
         <v>349</v>
       </c>
       <c r="AL118" s="2"/>
-      <c r="AM118" s="2"/>
+      <c r="AM118" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN118" s="2"/>
       <c r="AO118" s="2"/>
       <c r="AP118" s="2"/>
@@ -16727,15 +16895,15 @@
         <v>37</v>
       </c>
       <c r="G119" s="2">
-        <f t="shared" si="12"/>
-        <v>81</v>
+        <f t="shared" si="11"/>
+        <v>82</v>
       </c>
       <c r="H119" s="6">
         <f>I119+개인기록Sheet!C119</f>
         <v>1.4</v>
       </c>
       <c r="I119" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J119" s="2"/>
@@ -16825,15 +16993,15 @@
         <v>2025</v>
       </c>
       <c r="D120" s="54">
-        <f>COUNTA(W120:AN120)</f>
-        <v>2</v>
+        <f>COUNTA(AF120:AS120)</f>
+        <v>1</v>
       </c>
       <c r="E120" s="54"/>
       <c r="F120" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G120" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>69</v>
       </c>
       <c r="H120" s="6">
@@ -16841,7 +17009,7 @@
         <v>3.4</v>
       </c>
       <c r="I120" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="J120" s="2"/>
@@ -16942,15 +17110,15 @@
         <v>37</v>
       </c>
       <c r="G121" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
       <c r="H121" s="6">
         <f>I121+개인기록Sheet!C121</f>
         <v>0</v>
       </c>
       <c r="I121" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J121" s="2"/>
@@ -17038,7 +17206,7 @@
         <v>2024</v>
       </c>
       <c r="D122" s="54">
-        <f>COUNTA(W122:AN122)</f>
+        <f>COUNTA(AF122:AS122)</f>
         <v>0</v>
       </c>
       <c r="E122" s="54"/>
@@ -17046,15 +17214,15 @@
         <v>37</v>
       </c>
       <c r="G122" s="2">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
       <c r="H122" s="6">
         <f>I122+개인기록Sheet!C122</f>
         <v>0</v>
       </c>
       <c r="I122" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J122" s="2"/>
@@ -17149,16 +17317,16 @@
         <v>37</v>
       </c>
       <c r="G123" s="2">
-        <f t="shared" si="12"/>
-        <v>33</v>
+        <f t="shared" si="11"/>
+        <v>29</v>
       </c>
       <c r="H123" s="6">
         <f>I123+개인기록Sheet!C123</f>
-        <v>10.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="I123" s="6">
-        <f t="shared" si="13"/>
-        <v>7</v>
+        <f t="shared" si="12"/>
+        <v>8</v>
       </c>
       <c r="J123" s="2"/>
       <c r="K123" s="2" t="s">
@@ -17203,7 +17371,9 @@
       <c r="AJ123" s="2"/>
       <c r="AK123" s="2"/>
       <c r="AL123" s="2"/>
-      <c r="AM123" s="2"/>
+      <c r="AM123" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN123" s="2"/>
       <c r="AO123" s="2"/>
       <c r="AP123" s="2"/>
@@ -17259,7 +17429,7 @@
         <v>2026</v>
       </c>
       <c r="D124" s="54">
-        <f>COUNTA(W124:AN124)</f>
+        <f>COUNTA(AF124:AS124)</f>
         <v>2</v>
       </c>
       <c r="E124" s="54"/>
@@ -17267,7 +17437,7 @@
         <v>37</v>
       </c>
       <c r="G124" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>72</v>
       </c>
       <c r="H124" s="6">
@@ -17275,7 +17445,7 @@
         <v>2.6</v>
       </c>
       <c r="I124" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="J124" s="2"/>
@@ -17357,7 +17527,6 @@
       <c r="CD124" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:CT124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:E124">
     <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="지급">
@@ -17381,7 +17550,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:V276"/>
+  <dimension ref="A2:V292"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -25322,8 +25491,490 @@
       <c r="U276" s="2"/>
       <c r="V276" s="2"/>
     </row>
+    <row r="279" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B279" s="11">
+        <v>46261</v>
+      </c>
+      <c r="C279" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D279" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="E279" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="F279" s="77"/>
+      <c r="G279" s="77"/>
+      <c r="H279" s="77"/>
+      <c r="I279" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="J279" s="78"/>
+      <c r="K279" s="78"/>
+      <c r="L279" s="78"/>
+      <c r="M279" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="N279" s="79"/>
+      <c r="O279" s="79"/>
+      <c r="P279" s="79"/>
+      <c r="Q279" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="R279" s="80"/>
+      <c r="S279" s="80"/>
+      <c r="T279" s="80"/>
+      <c r="U279" s="80"/>
+      <c r="V279" s="80"/>
+    </row>
+    <row r="280" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B280" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C280" s="75">
+        <v>2</v>
+      </c>
+      <c r="D280" s="75">
+        <v>0</v>
+      </c>
+      <c r="E280" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="F280" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="G280" s="7"/>
+      <c r="H280" s="7"/>
+      <c r="I280" s="8"/>
+      <c r="J280" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="K280" s="8"/>
+      <c r="L280" s="8"/>
+      <c r="M280" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="N280" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="O280" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="P280" s="20"/>
+      <c r="Q280" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="R280" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="S280" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="T280" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="U280" s="9"/>
+      <c r="V280" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="281" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B281" s="74"/>
+      <c r="C281" s="76"/>
+      <c r="D281" s="76"/>
+      <c r="E281" s="7"/>
+      <c r="F281" s="7"/>
+      <c r="G281" s="7"/>
+      <c r="H281" s="7"/>
+      <c r="I281" s="8"/>
+      <c r="J281" s="8"/>
+      <c r="K281" s="8"/>
+      <c r="L281" s="8"/>
+      <c r="M281" s="20"/>
+      <c r="N281" s="20"/>
+      <c r="O281" s="20"/>
+      <c r="P281" s="20"/>
+      <c r="Q281" s="9"/>
+      <c r="R281" s="9"/>
+      <c r="S281" s="9"/>
+      <c r="T281" s="9"/>
+      <c r="U281" s="9"/>
+      <c r="V281" s="13"/>
+    </row>
+    <row r="282" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B282" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C282" s="75">
+        <v>1</v>
+      </c>
+      <c r="D282" s="75">
+        <v>0</v>
+      </c>
+      <c r="E282" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="F282" s="7"/>
+      <c r="G282" s="7"/>
+      <c r="H282" s="7"/>
+      <c r="I282" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="J282" s="8"/>
+      <c r="K282" s="8"/>
+      <c r="L282" s="8"/>
+      <c r="M282" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="N282" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="O282" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="P282" s="20"/>
+      <c r="Q282" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="R282" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="S282" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="T282" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="U282" s="9"/>
+      <c r="V282" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="283" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B283" s="74"/>
+      <c r="C283" s="76"/>
+      <c r="D283" s="76"/>
+      <c r="E283" s="7"/>
+      <c r="F283" s="7"/>
+      <c r="G283" s="7"/>
+      <c r="H283" s="7"/>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="8"/>
+      <c r="L283" s="8"/>
+      <c r="M283" s="20"/>
+      <c r="N283" s="20"/>
+      <c r="O283" s="20"/>
+      <c r="P283" s="20"/>
+      <c r="Q283" s="9"/>
+      <c r="R283" s="9"/>
+      <c r="S283" s="9"/>
+      <c r="T283" s="9"/>
+      <c r="U283" s="9"/>
+      <c r="V283" s="13"/>
+    </row>
+    <row r="284" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B284" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C284" s="75">
+        <v>1</v>
+      </c>
+      <c r="D284" s="75">
+        <v>3</v>
+      </c>
+      <c r="E284" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="F284" s="7"/>
+      <c r="G284" s="7"/>
+      <c r="H284" s="7"/>
+      <c r="I284" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="J284" s="8"/>
+      <c r="K284" s="8"/>
+      <c r="L284" s="8"/>
+      <c r="M284" s="20"/>
+      <c r="N284" s="20"/>
+      <c r="O284" s="20"/>
+      <c r="P284" s="20"/>
+      <c r="Q284" s="9"/>
+      <c r="R284" s="9"/>
+      <c r="S284" s="9"/>
+      <c r="T284" s="9"/>
+      <c r="U284" s="9"/>
+      <c r="V284" s="13"/>
+    </row>
+    <row r="285" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B285" s="74"/>
+      <c r="C285" s="76"/>
+      <c r="D285" s="76"/>
+      <c r="E285" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="F285" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="G285" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="H285" s="7"/>
+      <c r="I285" s="8"/>
+      <c r="J285" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="K285" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="L285" s="8"/>
+      <c r="M285" s="20"/>
+      <c r="N285" s="20"/>
+      <c r="O285" s="20"/>
+      <c r="P285" s="20"/>
+      <c r="Q285" s="9"/>
+      <c r="R285" s="9"/>
+      <c r="S285" s="9"/>
+      <c r="T285" s="9"/>
+      <c r="U285" s="9"/>
+      <c r="V285" s="13"/>
+    </row>
+    <row r="286" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B286" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C286" s="75">
+        <v>1</v>
+      </c>
+      <c r="D286" s="75">
+        <v>0</v>
+      </c>
+      <c r="E286" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="F286" s="7"/>
+      <c r="G286" s="7"/>
+      <c r="H286" s="7"/>
+      <c r="I286" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="J286" s="8"/>
+      <c r="K286" s="8"/>
+      <c r="L286" s="8"/>
+      <c r="M286" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="N286" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="O286" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="P286" s="20"/>
+      <c r="Q286" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="R286" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="S286" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="T286" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="U286" s="9"/>
+      <c r="V286" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="287" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B287" s="74"/>
+      <c r="C287" s="76"/>
+      <c r="D287" s="76"/>
+      <c r="E287" s="7"/>
+      <c r="F287" s="7"/>
+      <c r="G287" s="7"/>
+      <c r="H287" s="7"/>
+      <c r="I287" s="8"/>
+      <c r="J287" s="8"/>
+      <c r="K287" s="8"/>
+      <c r="L287" s="8"/>
+      <c r="M287" s="20"/>
+      <c r="N287" s="20"/>
+      <c r="O287" s="20"/>
+      <c r="P287" s="20"/>
+      <c r="Q287" s="9"/>
+      <c r="R287" s="9"/>
+      <c r="S287" s="9"/>
+      <c r="T287" s="9"/>
+      <c r="U287" s="9"/>
+      <c r="V287" s="13"/>
+    </row>
+    <row r="288" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B288" s="73" t="s">
+        <v>439</v>
+      </c>
+      <c r="C288" s="75">
+        <v>0</v>
+      </c>
+      <c r="D288" s="75">
+        <v>1</v>
+      </c>
+      <c r="E288" s="7"/>
+      <c r="F288" s="7"/>
+      <c r="G288" s="7"/>
+      <c r="H288" s="7"/>
+      <c r="I288" s="8"/>
+      <c r="J288" s="8"/>
+      <c r="K288" s="8"/>
+      <c r="L288" s="8"/>
+      <c r="M288" s="20"/>
+      <c r="N288" s="20"/>
+      <c r="O288" s="20"/>
+      <c r="P288" s="20"/>
+      <c r="Q288" s="9"/>
+      <c r="R288" s="9"/>
+      <c r="S288" s="9"/>
+      <c r="T288" s="9"/>
+      <c r="U288" s="9"/>
+      <c r="V288" s="13"/>
+    </row>
+    <row r="289" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B289" s="74"/>
+      <c r="C289" s="76"/>
+      <c r="D289" s="76"/>
+      <c r="E289" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="F289" s="7"/>
+      <c r="G289" s="7"/>
+      <c r="H289" s="7"/>
+      <c r="I289" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J289" s="8"/>
+      <c r="K289" s="8"/>
+      <c r="L289" s="8"/>
+      <c r="M289" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="N289" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="O289" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="P289" s="20"/>
+      <c r="Q289" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="R289" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="S289" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="T289" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="U289" s="9"/>
+      <c r="V289" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="290" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B290" s="73" t="s">
+        <v>440</v>
+      </c>
+      <c r="C290" s="75">
+        <v>2</v>
+      </c>
+      <c r="D290" s="75">
+        <v>1</v>
+      </c>
+      <c r="E290" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="G290" s="7"/>
+      <c r="H290" s="7"/>
+      <c r="I290" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="J290" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="K290" s="8"/>
+      <c r="L290" s="8"/>
+      <c r="M290" s="20"/>
+      <c r="N290" s="20"/>
+      <c r="O290" s="20"/>
+      <c r="P290" s="20"/>
+      <c r="Q290" s="9"/>
+      <c r="R290" s="9"/>
+      <c r="S290" s="9"/>
+      <c r="T290" s="9"/>
+      <c r="U290" s="9"/>
+      <c r="V290" s="13"/>
+    </row>
+    <row r="291" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B291" s="74"/>
+      <c r="C291" s="76"/>
+      <c r="D291" s="76"/>
+      <c r="E291" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F291" s="7"/>
+      <c r="G291" s="7"/>
+      <c r="H291" s="7"/>
+      <c r="I291" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="J291" s="8"/>
+      <c r="K291" s="8"/>
+      <c r="L291" s="8"/>
+      <c r="M291" s="20"/>
+      <c r="N291" s="20"/>
+      <c r="O291" s="20"/>
+      <c r="P291" s="20"/>
+      <c r="Q291" s="9"/>
+      <c r="R291" s="9"/>
+      <c r="S291" s="9"/>
+      <c r="T291" s="9"/>
+      <c r="U291" s="9"/>
+      <c r="V291" s="13"/>
+    </row>
+    <row r="292" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B292" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
+      <c r="E292" s="2"/>
+      <c r="F292" s="2"/>
+      <c r="G292" s="2"/>
+      <c r="H292" s="2"/>
+      <c r="I292" s="2"/>
+      <c r="J292" s="2"/>
+      <c r="K292" s="2"/>
+      <c r="L292" s="2"/>
+      <c r="M292" s="2"/>
+      <c r="N292" s="2"/>
+      <c r="O292" s="2"/>
+      <c r="P292" s="2"/>
+      <c r="Q292" s="2"/>
+      <c r="R292" s="2"/>
+      <c r="S292" s="2"/>
+      <c r="T292" s="2"/>
+      <c r="U292" s="2"/>
+      <c r="V292" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="374">
+  <mergeCells count="396">
     <mergeCell ref="B262:B263"/>
     <mergeCell ref="C262:C263"/>
     <mergeCell ref="D262:D263"/>
@@ -25698,6 +26349,28 @@
     <mergeCell ref="B272:B273"/>
     <mergeCell ref="C272:C273"/>
     <mergeCell ref="D272:D273"/>
+    <mergeCell ref="E279:H279"/>
+    <mergeCell ref="I279:L279"/>
+    <mergeCell ref="M279:P279"/>
+    <mergeCell ref="Q279:V279"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="C280:C281"/>
+    <mergeCell ref="D280:D281"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="C282:C283"/>
+    <mergeCell ref="D282:D283"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="C290:C291"/>
+    <mergeCell ref="D290:D291"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="C284:C285"/>
+    <mergeCell ref="D284:D285"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="C286:C287"/>
+    <mergeCell ref="D286:D287"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="C288:C289"/>
+    <mergeCell ref="D288:D289"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -25739,19 +26412,19 @@
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
@@ -25869,35 +26542,35 @@
       </c>
       <c r="M4" s="21">
         <f t="shared" ref="M4:M16" si="2">VLOOKUP(L4,$B$4:$H$137,3,FALSE)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>351</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O18" si="3">VLOOKUP(N4,$B$4:$H$137,4,FALSE)</f>
-        <v>9</v>
+        <f t="shared" ref="O4:O12" si="3">VLOOKUP(N4,$B$4:$H$137,4,FALSE)</f>
+        <v>10</v>
       </c>
       <c r="P4" s="34" t="s">
         <v>221</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q18" si="4">VLOOKUP(P4,$B$4:$H$137,5,FALSE)</f>
-        <v>16</v>
+        <f t="shared" ref="Q4:Q16" si="4">VLOOKUP(P4,$B$4:$H$137,5,FALSE)</f>
+        <v>17</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>322</v>
       </c>
       <c r="S4" s="55">
-        <f t="shared" ref="S4:S16" si="5">VLOOKUP(R4,$B$4:$H$137,6,FALSE)</f>
+        <f t="shared" ref="S4:S17" si="5">VLOOKUP(R4,$B$4:$H$137,6,FALSE)</f>
         <v>23</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>228</v>
+        <v>42</v>
       </c>
       <c r="U4" s="56">
         <f t="shared" ref="U4:U13" si="6">VLOOKUP(T4,$B$4:$H$137,7,FALSE)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -25946,14 +26619,14 @@
       </c>
       <c r="M5" s="21">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>357</v>
+        <v>53</v>
       </c>
       <c r="O5" s="22">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P5" s="34" t="s">
         <v>304</v>
@@ -25967,14 +26640,14 @@
       </c>
       <c r="S5" s="55">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T5" s="36" t="s">
-        <v>42</v>
+        <v>228</v>
       </c>
       <c r="U5" s="56">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -26019,18 +26692,18 @@
         <v>3</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>221</v>
+        <v>398</v>
       </c>
       <c r="M6" s="21">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>221</v>
+        <v>357</v>
       </c>
       <c r="O6" s="22">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6" s="34" t="s">
         <v>64</v>
@@ -26044,7 +26717,7 @@
       </c>
       <c r="S6" s="55">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T6" s="36" t="s">
         <v>220</v>
@@ -26096,14 +26769,14 @@
         <v>4</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="M7" s="21">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>53</v>
+        <v>221</v>
       </c>
       <c r="O7" s="22">
         <f t="shared" si="3"/>
@@ -26173,11 +26846,11 @@
         <v>5</v>
       </c>
       <c r="L8" s="32" t="s">
-        <v>357</v>
+        <v>231</v>
       </c>
       <c r="M8" s="21">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>50</v>
@@ -26187,18 +26860,18 @@
         <v>5</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>376</v>
+        <v>53</v>
       </c>
       <c r="Q8" s="23">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R8" s="35" t="s">
-        <v>232</v>
+        <v>392</v>
       </c>
       <c r="S8" s="55">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T8" s="36" t="s">
         <v>397</v>
@@ -26219,7 +26892,7 @@
       </c>
       <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="D9" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B9)</f>
@@ -26235,7 +26908,7 @@
       </c>
       <c r="G9" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B9)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B9)</f>
@@ -26243,39 +26916,39 @@
       </c>
       <c r="I9" s="14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="2">
         <v>6</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M9" s="21">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="O9" s="22">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="Q9" s="23">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="R9" s="35" t="s">
-        <v>392</v>
+        <v>232</v>
       </c>
       <c r="S9" s="55">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T9" s="36" t="s">
         <v>298</v>
@@ -26327,32 +27000,32 @@
         <v>7</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="M10" s="21">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>403</v>
+        <v>223</v>
       </c>
       <c r="O10" s="22">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P10" s="34" t="s">
-        <v>53</v>
+        <v>382</v>
       </c>
       <c r="Q10" s="23">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R10" s="35" t="s">
-        <v>62</v>
+        <v>302</v>
       </c>
       <c r="S10" s="55">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T10" s="36" t="s">
         <v>299</v>
@@ -26373,11 +27046,11 @@
       </c>
       <c r="C11" s="2">
         <f t="shared" si="0"/>
-        <v>4.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D11" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B11)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B11)</f>
@@ -26397,7 +27070,7 @@
       </c>
       <c r="I11" s="14">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="2">
@@ -26411,25 +27084,25 @@
         <v>8</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>353</v>
+        <v>7</v>
       </c>
       <c r="O11" s="22">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" s="34" t="s">
         <v>7</v>
       </c>
       <c r="Q11" s="23">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R11" s="35" t="s">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="S11" s="55">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T11" s="36" t="s">
         <v>353</v>
@@ -26488,25 +27161,25 @@
         <v>7</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>313</v>
+        <v>403</v>
       </c>
       <c r="O12" s="22">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P12" s="34" t="s">
-        <v>383</v>
+        <v>299</v>
       </c>
       <c r="Q12" s="23">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R12" s="35" t="s">
-        <v>221</v>
+        <v>308</v>
       </c>
       <c r="S12" s="55">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" s="36" t="s">
         <v>361</v>
@@ -26564,22 +27237,17 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="N13" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="O13" s="22">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
+      <c r="N13" s="33"/>
+      <c r="O13" s="22"/>
       <c r="P13" s="34" t="s">
-        <v>316</v>
+        <v>403</v>
       </c>
       <c r="Q13" s="23">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R13" s="35" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="S13" s="55">
         <f t="shared" si="5"/>
@@ -26641,22 +27309,17 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N14" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="O14" s="22">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
+      <c r="N14" s="33"/>
+      <c r="O14" s="22"/>
       <c r="P14" s="34" t="s">
-        <v>313</v>
+        <v>383</v>
       </c>
       <c r="Q14" s="23">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R14" s="55" t="s">
-        <v>361</v>
+        <v>241</v>
       </c>
       <c r="S14" s="55">
         <f t="shared" si="5"/>
@@ -26713,22 +27376,17 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="O15" s="22">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
+      <c r="N15" s="33"/>
+      <c r="O15" s="22"/>
       <c r="P15" s="23" t="s">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="Q15" s="23">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="R15" s="55" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="S15" s="55">
         <f t="shared" si="5"/>
@@ -26748,19 +27406,19 @@
       </c>
       <c r="C16" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D16" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B16)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B16)</f>
@@ -26772,7 +27430,7 @@
       </c>
       <c r="I16" s="14">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="2">
@@ -26785,26 +27443,21 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="N16" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="O16" s="22">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
       <c r="P16" s="23" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="Q16" s="23">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" s="55" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="S16" s="55">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" s="56"/>
       <c r="U16" s="56"/>
@@ -26852,22 +27505,17 @@
       </c>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
-      <c r="N17" s="22" t="s">
-        <v>304</v>
-      </c>
-      <c r="O17" s="22">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="P17" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q17" s="23">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="R17" s="55"/>
-      <c r="S17" s="55"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="S17" s="55">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
       <c r="T17" s="56"/>
       <c r="U17" s="56"/>
     </row>
@@ -26914,20 +27562,10 @@
       </c>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
-      <c r="N18" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="O18" s="22">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="P18" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q18" s="23">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
       <c r="R18" s="55"/>
       <c r="S18" s="55"/>
       <c r="T18" s="56"/>
@@ -27217,7 +27855,7 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D26" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B26)</f>
@@ -27229,7 +27867,7 @@
       </c>
       <c r="F26" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B26)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B26)</f>
@@ -27241,7 +27879,7 @@
       </c>
       <c r="I26" s="14">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="15"/>
     </row>
@@ -27295,7 +27933,7 @@
       </c>
       <c r="C28" s="2">
         <f t="shared" si="0"/>
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="D28" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B28)</f>
@@ -27307,7 +27945,7 @@
       </c>
       <c r="F28" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B28)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B28)</f>
@@ -27319,7 +27957,7 @@
       </c>
       <c r="I28" s="14">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J28" s="15"/>
     </row>
@@ -27451,7 +28089,7 @@
       </c>
       <c r="C32" s="2">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D32" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B32)</f>
@@ -27459,11 +28097,11 @@
       </c>
       <c r="E32" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B32)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F32" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B32)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G32" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B32)</f>
@@ -27475,7 +28113,7 @@
       </c>
       <c r="I32" s="14">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J32" s="15"/>
     </row>
@@ -27685,15 +28323,15 @@
       </c>
       <c r="C38" s="2">
         <f t="shared" si="7"/>
-        <v>6.2</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="D38" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B38)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E38" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B38)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B38)</f>
@@ -27709,7 +28347,7 @@
       </c>
       <c r="I38" s="14">
         <f t="shared" si="8"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J38" s="15"/>
     </row>
@@ -27958,7 +28596,7 @@
       </c>
       <c r="C45" s="2">
         <f t="shared" si="7"/>
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D45" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B45)</f>
@@ -27974,7 +28612,7 @@
       </c>
       <c r="G45" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B45)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H45" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B45)</f>
@@ -27982,7 +28620,7 @@
       </c>
       <c r="I45" s="14">
         <f t="shared" si="8"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J45" s="15"/>
     </row>
@@ -28270,7 +28908,7 @@
       </c>
       <c r="C53" s="2">
         <f t="shared" si="7"/>
-        <v>2.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D53" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B53)</f>
@@ -28278,7 +28916,7 @@
       </c>
       <c r="E53" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B53)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B53)</f>
@@ -28294,7 +28932,7 @@
       </c>
       <c r="I53" s="14">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J53" s="15"/>
     </row>
@@ -28816,15 +29454,15 @@
       </c>
       <c r="C67" s="2">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="D67" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B67)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B67)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F67" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B67)</f>
@@ -28840,7 +29478,7 @@
       </c>
       <c r="I67" s="14">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J67" s="15"/>
     </row>
@@ -29050,7 +29688,7 @@
       </c>
       <c r="C73" s="2">
         <f t="shared" si="9"/>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D73" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B73)</f>
@@ -29062,7 +29700,7 @@
       </c>
       <c r="F73" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B73)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B73)</f>
@@ -29074,7 +29712,7 @@
       </c>
       <c r="I73" s="14">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J73" s="15"/>
     </row>
@@ -29284,15 +29922,15 @@
       </c>
       <c r="C79" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D79" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B79)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E79" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B79)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B79)</f>
@@ -29308,7 +29946,7 @@
       </c>
       <c r="I79" s="14">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J79" s="15"/>
     </row>
@@ -29401,7 +30039,7 @@
       </c>
       <c r="C82" s="2">
         <f t="shared" si="9"/>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D82" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B82)</f>
@@ -29409,7 +30047,7 @@
       </c>
       <c r="E82" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B82)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B82)</f>
@@ -29417,7 +30055,7 @@
       </c>
       <c r="G82" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B82)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H82" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B82)</f>
@@ -29425,7 +30063,7 @@
       </c>
       <c r="I82" s="14">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J82" s="15"/>
     </row>
@@ -29440,7 +30078,7 @@
       </c>
       <c r="C83" s="2">
         <f t="shared" si="9"/>
-        <v>2.5</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="D83" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B83)</f>
@@ -29448,11 +30086,11 @@
       </c>
       <c r="E83" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B83)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F83" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B83)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G83" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B83)</f>
@@ -29464,7 +30102,7 @@
       </c>
       <c r="I83" s="14">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J83" s="15"/>
     </row>
@@ -29518,7 +30156,7 @@
       </c>
       <c r="C85" s="2">
         <f t="shared" si="9"/>
-        <v>1.4000000000000001</v>
+        <v>2</v>
       </c>
       <c r="D85" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B85)</f>
@@ -29534,7 +30172,7 @@
       </c>
       <c r="G85" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B85)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H85" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B85)</f>
@@ -29542,7 +30180,7 @@
       </c>
       <c r="I85" s="14">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J85" s="15"/>
     </row>
@@ -29557,7 +30195,7 @@
       </c>
       <c r="C86" s="2">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D86" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B86)</f>
@@ -29573,7 +30211,7 @@
       </c>
       <c r="G86" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B86)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H86" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B86)</f>
@@ -29581,7 +30219,7 @@
       </c>
       <c r="I86" s="14">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J86" s="15"/>
     </row>
@@ -29674,7 +30312,7 @@
       </c>
       <c r="C89" s="2">
         <f t="shared" si="9"/>
-        <v>1.2000000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D89" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B89)</f>
@@ -29690,7 +30328,7 @@
       </c>
       <c r="G89" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B89)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H89" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B89)</f>
@@ -29698,7 +30336,7 @@
       </c>
       <c r="I89" s="14">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J89" s="15"/>
     </row>
@@ -30103,7 +30741,7 @@
       </c>
       <c r="C100" s="2">
         <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="D100" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B100)</f>
@@ -30115,7 +30753,7 @@
       </c>
       <c r="F100" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B100)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G100" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B100)</f>
@@ -30127,7 +30765,7 @@
       </c>
       <c r="I100" s="14">
         <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J100" s="15"/>
     </row>
@@ -30220,7 +30858,7 @@
       </c>
       <c r="C103" s="2">
         <f t="shared" si="11"/>
-        <v>4.8000000000000007</v>
+        <v>5.2</v>
       </c>
       <c r="D103" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
@@ -30236,7 +30874,7 @@
       </c>
       <c r="G103" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B103)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H103" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B103)</f>
@@ -30244,7 +30882,7 @@
       </c>
       <c r="I103" s="14">
         <f t="shared" si="12"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J103" s="15"/>
     </row>
@@ -30259,11 +30897,11 @@
       </c>
       <c r="C104" s="2">
         <f t="shared" si="11"/>
-        <v>2.4000000000000004</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="D104" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B104)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E104" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B104)</f>
@@ -30283,7 +30921,7 @@
       </c>
       <c r="I104" s="14">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J104" s="15"/>
     </row>
@@ -30298,7 +30936,7 @@
       </c>
       <c r="C105" s="2">
         <f t="shared" si="11"/>
-        <v>1.2000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D105" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B105)</f>
@@ -30310,7 +30948,7 @@
       </c>
       <c r="F105" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B105)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G105" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B105)</f>
@@ -30322,7 +30960,7 @@
       </c>
       <c r="I105" s="14">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -30526,7 +31164,7 @@
       </c>
       <c r="C111" s="2">
         <f t="shared" si="11"/>
-        <v>2.8000000000000003</v>
+        <v>3.2</v>
       </c>
       <c r="D111" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B111)</f>
@@ -30542,7 +31180,7 @@
       </c>
       <c r="G111" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B111)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H111" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B111)</f>
@@ -30550,7 +31188,7 @@
       </c>
       <c r="I111" s="14">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -30792,11 +31430,11 @@
       </c>
       <c r="C118" s="2">
         <f t="shared" si="11"/>
-        <v>3.0000000000000004</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="D118" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B118)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B118)</f>
@@ -30808,7 +31446,7 @@
       </c>
       <c r="G118" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B118)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H118" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B118)</f>
@@ -30816,7 +31454,7 @@
       </c>
       <c r="I118" s="14">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -30982,7 +31620,7 @@
       </c>
       <c r="C123" s="2">
         <f t="shared" si="11"/>
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D123" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B123)</f>
@@ -31002,11 +31640,11 @@
       </c>
       <c r="H123" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B123)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I123" s="14">
         <f t="shared" si="12"/>
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -32728,7 +33366,7 @@
       </c>
       <c r="G4" s="61">
         <f>VLOOKUP(F4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>7.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I4" s="96"/>
       <c r="J4" s="66">
@@ -32749,14 +33387,14 @@
       </c>
       <c r="Q4" s="62">
         <f>VLOOKUP(P4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>221</v>
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>33.4</v>
+        <v>34.700000000000003</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -32769,14 +33407,14 @@
       </c>
       <c r="E5" s="47">
         <f>VLOOKUP(D5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>221</v>
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>33.4</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="I5" s="96"/>
       <c r="J5" s="66">
@@ -32824,7 +33462,7 @@
       </c>
       <c r="G6" s="61">
         <f>VLOOKUP(F6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>17.2</v>
+        <v>18.2</v>
       </c>
       <c r="I6" s="96"/>
       <c r="J6" s="66">
@@ -32845,14 +33483,14 @@
       </c>
       <c r="Q6" s="69">
         <f>VLOOKUP(P6,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>230</v>
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -32865,7 +33503,7 @@
       </c>
       <c r="E7" s="47">
         <f>VLOOKUP(D7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="70" t="s">
         <v>304</v>
@@ -32913,7 +33551,7 @@
       </c>
       <c r="E8" s="47">
         <f>VLOOKUP(D8,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="62" t="s">
         <v>50</v>
@@ -32951,14 +33589,14 @@
       </c>
       <c r="E9" s="65">
         <f>VLOOKUP(D9,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="70" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="I9" s="99" t="s">
         <v>248</v>
@@ -32979,7 +33617,7 @@
       </c>
       <c r="Q9" s="69">
         <f>VLOOKUP(P9,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R9" s="65" t="s">
         <v>309</v>
@@ -33006,7 +33644,7 @@
       </c>
       <c r="G10" s="61">
         <f>VLOOKUP(F10,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="I10" s="95" t="s">
         <v>331</v>
@@ -33036,7 +33674,7 @@
       </c>
       <c r="S10" s="71">
         <f>VLOOKUP(R10,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
@@ -33049,14 +33687,14 @@
       </c>
       <c r="E11" s="65">
         <f>VLOOKUP(D11,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="70" t="s">
         <v>48</v>
       </c>
       <c r="G11" s="61">
         <f>VLOOKUP(F11,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I11" s="96"/>
       <c r="J11" s="66">
@@ -33097,14 +33735,14 @@
       </c>
       <c r="E12" s="65">
         <f>VLOOKUP(D12,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="70" t="s">
         <v>223</v>
       </c>
       <c r="G12" s="61">
         <f>VLOOKUP(F12,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>15.7</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="I12" s="96"/>
       <c r="J12" s="66">
@@ -33145,14 +33783,14 @@
       </c>
       <c r="E13" s="65">
         <f>VLOOKUP(D13,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="70" t="s">
         <v>241</v>
       </c>
       <c r="G13" s="61">
         <f>VLOOKUP(F13,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>16.2</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="66">
@@ -33181,14 +33819,14 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>228</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>25.8</v>
+        <v>26.8</v>
       </c>
       <c r="I14" s="97"/>
       <c r="J14" s="66">
@@ -33217,14 +33855,14 @@
       </c>
       <c r="E15" s="65">
         <f>VLOOKUP(D15,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" s="62" t="s">
         <v>299</v>
       </c>
       <c r="G15" s="63">
         <f>VLOOKUP(F15,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="N15"/>
       <c r="O15"/>
@@ -33243,14 +33881,14 @@
       </c>
       <c r="E16" s="65">
         <f>VLOOKUP(D16,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>230</v>
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="H16" s="37"/>
       <c r="I16" s="99" t="s">
@@ -34162,7 +34800,7 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -34280,7 +34918,7 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
@@ -34396,7 +35034,7 @@
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C9</f>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="I7" s="6">
         <f t="shared" si="3"/>
@@ -34618,7 +35256,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C15</f>
@@ -34732,11 +35370,11 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C16</f>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="3"/>
@@ -34846,7 +35484,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C17</f>
@@ -35515,11 +36153,11 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C26</f>
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="3"/>
@@ -35625,7 +36263,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C29</f>
@@ -35861,7 +36499,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C40</f>
@@ -36300,7 +36938,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C57</f>
@@ -36412,7 +37050,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C59</f>
@@ -36756,7 +37394,7 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C63</f>
@@ -37204,11 +37842,11 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C79</f>
-        <v>4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="6"/>
@@ -37320,11 +37958,11 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C83</f>
-        <v>3.5</v>
+        <v>4.3000000000000007</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="6"/>
@@ -37658,7 +38296,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C102</f>
@@ -37772,11 +38410,11 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C104</f>
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="6"/>
